--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="30240" windowHeight="12800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -7035,13 +7035,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7562,10 +7562,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
@@ -7580,22 +7580,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -27533,8 +27533,8 @@
       <c r="D82" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="10"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="9"/>
     </row>
     <row r="83" ht="17" spans="1:6">
       <c r="A83" s="3" t="s">
@@ -27549,8 +27549,8 @@
       <c r="D83" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="10"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="9"/>
     </row>
     <row r="84" ht="17" spans="1:6">
       <c r="A84" s="3" t="s">
@@ -27565,8 +27565,8 @@
       <c r="D84" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="10"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="9"/>
     </row>
     <row r="85" ht="17" spans="1:6">
       <c r="A85" s="3" t="s">
@@ -27581,8 +27581,8 @@
       <c r="D85" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="10"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="9"/>
     </row>
     <row r="86" ht="17" spans="1:6">
       <c r="A86" s="3" t="s">
@@ -27595,7 +27595,7 @@
         <v>912</v>
       </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="11"/>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" ht="17" spans="1:6">
       <c r="A87" s="3" t="s">
@@ -27608,7 +27608,7 @@
         <v>924</v>
       </c>
       <c r="D87" s="5"/>
-      <c r="E87" s="11"/>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" ht="17" spans="1:6">
       <c r="A88" s="3" t="s">
@@ -27621,7 +27621,7 @@
         <v>946</v>
       </c>
       <c r="D88" s="5"/>
-      <c r="E88" s="11"/>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" ht="17" spans="1:6">
       <c r="A89" s="3" t="s">
@@ -27634,7 +27634,7 @@
         <v>977</v>
       </c>
       <c r="D89" s="5"/>
-      <c r="E89" s="11"/>
+      <c r="E89" s="10"/>
     </row>
     <row r="90" ht="17" spans="1:6">
       <c r="A90" s="3" t="s">
@@ -27647,7 +27647,7 @@
         <v>993</v>
       </c>
       <c r="D90" s="5"/>
-      <c r="E90" s="11"/>
+      <c r="E90" s="10"/>
     </row>
     <row r="91" ht="17" spans="1:6">
       <c r="A91" s="3" t="s">
@@ -27660,7 +27660,7 @@
         <v>1005</v>
       </c>
       <c r="D91" s="5"/>
-      <c r="E91" s="11"/>
+      <c r="E91" s="10"/>
     </row>
     <row r="92" ht="17" spans="1:6">
       <c r="A92" s="3" t="s">
@@ -27673,7 +27673,7 @@
         <v>1013</v>
       </c>
       <c r="D92" s="5"/>
-      <c r="E92" s="9"/>
+      <c r="E92" s="6"/>
     </row>
     <row r="93" ht="17" spans="1:6">
       <c r="A93" s="3" t="s">
@@ -27686,7 +27686,7 @@
         <v>1021</v>
       </c>
       <c r="D93" s="5"/>
-      <c r="E93" s="9"/>
+      <c r="E93" s="6"/>
     </row>
     <row r="94" ht="17" spans="1:6">
       <c r="A94" s="3" t="s">
@@ -27699,7 +27699,7 @@
         <v>1115</v>
       </c>
       <c r="D94" s="5"/>
-      <c r="E94" s="11"/>
+      <c r="E94" s="10"/>
     </row>
     <row r="95" ht="17" spans="1:6">
       <c r="A95" s="3" t="s">
@@ -27712,7 +27712,7 @@
         <v>1132</v>
       </c>
       <c r="D95" s="5"/>
-      <c r="E95" s="11"/>
+      <c r="E95" s="10"/>
     </row>
     <row r="96" ht="17" spans="1:6">
       <c r="A96" s="3" t="s">
@@ -27725,7 +27725,7 @@
         <v>1142</v>
       </c>
       <c r="D96" s="5"/>
-      <c r="E96" s="11"/>
+      <c r="E96" s="10"/>
     </row>
     <row r="97" ht="17" spans="1:5">
       <c r="A97" s="3" t="s">
@@ -27738,7 +27738,7 @@
         <v>1168</v>
       </c>
       <c r="D97" s="5"/>
-      <c r="E97" s="9"/>
+      <c r="E97" s="11"/>
     </row>
     <row r="98" ht="17" spans="1:5">
       <c r="A98" s="3" t="s">
@@ -27753,7 +27753,7 @@
       <c r="D98" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E98" s="9"/>
+      <c r="E98" s="11"/>
     </row>
     <row r="99" ht="17" spans="1:5">
       <c r="A99" s="3" t="s">
@@ -27768,7 +27768,7 @@
       <c r="D99" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="10"/>
     </row>
     <row r="100" ht="17" spans="1:5">
       <c r="A100" s="3" t="s">
@@ -27783,7 +27783,7 @@
       <c r="D100" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E100" s="11"/>
+      <c r="E100" s="10"/>
     </row>
     <row r="101" ht="17" spans="1:5">
       <c r="A101" s="3" t="s">
@@ -27796,7 +27796,7 @@
         <v>1282</v>
       </c>
       <c r="D101" s="5"/>
-      <c r="E101" s="9"/>
+      <c r="E101" s="11"/>
     </row>
     <row r="102" ht="17" spans="1:5">
       <c r="A102" s="3" t="s">
@@ -27811,7 +27811,7 @@
       <c r="D102" s="5" t="s">
         <v>2235</v>
       </c>
-      <c r="E102" s="9"/>
+      <c r="E102" s="11"/>
     </row>
     <row r="103" ht="17" spans="1:5">
       <c r="A103" s="3" t="s">
@@ -27824,7 +27824,7 @@
         <v>1300</v>
       </c>
       <c r="D103" s="5"/>
-      <c r="E103" s="11"/>
+      <c r="E103" s="10"/>
     </row>
     <row r="104" ht="17" spans="1:5">
       <c r="A104" s="3" t="s">
@@ -27837,7 +27837,7 @@
         <v>1307</v>
       </c>
       <c r="D104" s="5"/>
-      <c r="E104" s="11"/>
+      <c r="E104" s="10"/>
     </row>
     <row r="105" ht="17" spans="1:5">
       <c r="A105" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="30240" windowHeight="12680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="2191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3094" uniqueCount="2185">
   <si>
     <t>应用名称</t>
   </si>
@@ -3766,16 +3766,7 @@
     <t>2、点击照片，进入照片tab页</t>
   </si>
   <si>
-    <t>3、点击年，切换到年视图；</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    点击月，切换到月视图，</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    点击日，切换到日视图； 重复执行步骤5次</t>
-  </si>
-  <si>
-    <t>4、双指捏合，从日视图切换到月视图；</t>
+    <t>3、双指捏合，从日视图切换到月视图；</t>
   </si>
   <si>
     <t xml:space="preserve">    双指捏合，从月视图切换到年视图；</t>
@@ -3787,22 +3778,22 @@
     <t xml:space="preserve">    双指捏开，从月视图切换到日视图，重复执行步骤5次</t>
   </si>
   <si>
-    <t>5、日视图向上抛滑5次，向下抛滑5次</t>
-  </si>
-  <si>
-    <t>6、日视图向上跟手滑5次，向下跟手滑5次</t>
-  </si>
-  <si>
-    <t>7、日视图向上滚动条滑5次，向下滚动条滑5次</t>
-  </si>
-  <si>
-    <t>8、点击查看第一张照片，进入大图</t>
-  </si>
-  <si>
-    <t>9、点击底部图片预览条，向右滑动3次</t>
-  </si>
-  <si>
-    <t>10、点击底部图片预览条，向左滑动3次</t>
+    <t>4、日视图向上抛滑5次，向下抛滑5次</t>
+  </si>
+  <si>
+    <t>5、日视图向上跟手滑5次，向下跟手滑5次</t>
+  </si>
+  <si>
+    <t>6、日视图向上滚动条滑5次，向下滚动条滑5次</t>
+  </si>
+  <si>
+    <t>7、点击查看第一张照片，进入大图</t>
+  </si>
+  <si>
+    <t>8、点击底部图片预览条，向右滑动3次</t>
+  </si>
+  <si>
+    <t>9、点击底部图片预览条，向左滑动3次</t>
   </si>
   <si>
     <t>11、点击左上角按钮退出到照片页</t>
@@ -6643,16 +6634,7 @@
     <t>6、返回作业帮主界面</t>
   </si>
   <si>
-    <t>负责人</t>
-  </si>
-  <si>
     <t>退出应用</t>
-  </si>
-  <si>
-    <t>王子健</t>
-  </si>
-  <si>
-    <t>方斌豪</t>
   </si>
   <si>
     <t>PerformanceDynamic_xianyu_0020</t>
@@ -6671,10 +6653,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -7206,16 +7193,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7224,46 +7208,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7272,10 +7259,10 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7284,10 +7271,10 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7296,10 +7283,10 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7308,10 +7295,10 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7320,10 +7307,10 @@
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7332,11 +7319,11 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7352,9 +7339,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -7363,6 +7347,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -7377,6 +7364,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7858,7 +7848,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2102"/>
+  <dimension ref="A1:E2099"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.2692307692308" customWidth="1"/>
@@ -15187,7 +15177,7 @@
       <c r="A860" s="11"/>
       <c r="B860" s="11"/>
       <c r="C860" s="11"/>
-      <c r="D860" s="11" t="s">
+      <c r="D860" s="14" t="s">
         <v>925</v>
       </c>
     </row>
@@ -16100,13 +16090,13 @@
       </c>
     </row>
     <row r="970" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A970" s="14" t="s">
+      <c r="A970" s="15" t="s">
         <v>1035</v>
       </c>
-      <c r="B970" s="14" t="s">
+      <c r="B970" s="15" t="s">
         <v>1036</v>
       </c>
-      <c r="C970" s="14" t="s">
+      <c r="C970" s="15" t="s">
         <v>1037</v>
       </c>
       <c r="D970" s="12" t="s">
@@ -16114,73 +16104,73 @@
       </c>
     </row>
     <row r="971" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A971" s="15"/>
-      <c r="B971" s="15"/>
-      <c r="C971" s="15"/>
+      <c r="A971" s="16"/>
+      <c r="B971" s="16"/>
+      <c r="C971" s="16"/>
       <c r="D971" s="12" t="s">
         <v>1039</v>
       </c>
     </row>
     <row r="972" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A972" s="15"/>
-      <c r="B972" s="15"/>
-      <c r="C972" s="15"/>
+      <c r="A972" s="16"/>
+      <c r="B972" s="16"/>
+      <c r="C972" s="16"/>
       <c r="D972" s="12" t="s">
         <v>1040</v>
       </c>
     </row>
     <row r="973" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A973" s="15"/>
-      <c r="B973" s="15"/>
-      <c r="C973" s="15"/>
+      <c r="A973" s="16"/>
+      <c r="B973" s="16"/>
+      <c r="C973" s="16"/>
       <c r="D973" s="12" t="s">
         <v>1041</v>
       </c>
     </row>
     <row r="974" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A974" s="15"/>
-      <c r="B974" s="15"/>
-      <c r="C974" s="15"/>
+      <c r="A974" s="16"/>
+      <c r="B974" s="16"/>
+      <c r="C974" s="16"/>
       <c r="D974" s="12" t="s">
         <v>1042</v>
       </c>
     </row>
     <row r="975" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A975" s="15"/>
-      <c r="B975" s="15"/>
-      <c r="C975" s="15"/>
+      <c r="A975" s="16"/>
+      <c r="B975" s="16"/>
+      <c r="C975" s="16"/>
       <c r="D975" s="12" t="s">
         <v>1043</v>
       </c>
     </row>
     <row r="976" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A976" s="15"/>
-      <c r="B976" s="15"/>
-      <c r="C976" s="15"/>
+      <c r="A976" s="16"/>
+      <c r="B976" s="16"/>
+      <c r="C976" s="16"/>
       <c r="D976" s="12" t="s">
         <v>1044</v>
       </c>
     </row>
     <row r="977" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A977" s="15"/>
-      <c r="B977" s="15"/>
-      <c r="C977" s="15"/>
+      <c r="A977" s="16"/>
+      <c r="B977" s="16"/>
+      <c r="C977" s="16"/>
       <c r="D977" s="12" t="s">
         <v>1045</v>
       </c>
     </row>
     <row r="978" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A978" s="15"/>
-      <c r="B978" s="15"/>
-      <c r="C978" s="15"/>
+      <c r="A978" s="16"/>
+      <c r="B978" s="16"/>
+      <c r="C978" s="16"/>
       <c r="D978" s="12" t="s">
         <v>1046</v>
       </c>
     </row>
     <row r="979" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A979" s="16"/>
-      <c r="B979" s="16"/>
-      <c r="C979" s="16"/>
+      <c r="A979" s="17"/>
+      <c r="B979" s="17"/>
+      <c r="C979" s="17"/>
       <c r="D979" s="12" t="s">
         <v>71</v>
       </c>
@@ -17686,15 +17676,21 @@
       <c r="B1158" s="11"/>
       <c r="C1158" s="11"/>
       <c r="D1158" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="1159" ht="17" customHeight="1" spans="1:4">
+      <c r="A1159" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1159" s="11" t="s">
         <v>1242</v>
       </c>
-    </row>
-    <row r="1159" ht="17" customHeight="1" spans="1:4">
-      <c r="A1159" s="11"/>
-      <c r="B1159" s="11"/>
-      <c r="C1159" s="11"/>
+      <c r="C1159" s="11" t="s">
+        <v>1243</v>
+      </c>
       <c r="D1159" s="11" t="s">
-        <v>1243</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="1160" ht="17" customHeight="1" spans="1:4">
@@ -17710,21 +17706,15 @@
       <c r="B1161" s="11"/>
       <c r="C1161" s="11"/>
       <c r="D1161" s="11" t="s">
-        <v>532</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="1162" ht="17" customHeight="1" spans="1:4">
-      <c r="A1162" s="11" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B1162" s="11" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C1162" s="11" t="s">
+      <c r="A1162" s="11"/>
+      <c r="B1162" s="11"/>
+      <c r="C1162" s="11"/>
+      <c r="D1162" s="11" t="s">
         <v>1246</v>
-      </c>
-      <c r="D1162" s="11" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="1163" ht="17" customHeight="1" spans="1:4">
@@ -17763,7 +17753,7 @@
       <c r="A1167" s="11"/>
       <c r="B1167" s="11"/>
       <c r="C1167" s="11"/>
-      <c r="D1167" s="11" t="s">
+      <c r="D1167" s="12" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -17820,7 +17810,7 @@
       <c r="B1174" s="11"/>
       <c r="C1174" s="11"/>
       <c r="D1174" s="11" t="s">
-        <v>1258</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="1175" ht="17" customHeight="1" spans="1:4">
@@ -17828,45 +17818,45 @@
       <c r="B1175" s="11"/>
       <c r="C1175" s="11"/>
       <c r="D1175" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="1176" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1176" s="12" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B1176" s="12" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C1176" s="12" t="s">
         <v>1259</v>
       </c>
-    </row>
-    <row r="1176" ht="17" customHeight="1" spans="1:4">
-      <c r="A1176" s="11"/>
-      <c r="B1176" s="11"/>
-      <c r="C1176" s="11"/>
-      <c r="D1176" s="11" t="s">
+      <c r="D1176" s="12" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="1177" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1177" s="12"/>
+      <c r="B1177" s="12"/>
+      <c r="C1177" s="12"/>
+      <c r="D1177" s="12" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="1178" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1178" s="12"/>
+      <c r="B1178" s="12"/>
+      <c r="C1178" s="12"/>
+      <c r="D1178" s="12" t="s">
         <v>1260</v>
       </c>
     </row>
-    <row r="1177" ht="17" customHeight="1" spans="1:4">
-      <c r="A1177" s="11"/>
-      <c r="B1177" s="11"/>
-      <c r="C1177" s="11"/>
-      <c r="D1177" s="11" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="1178" ht="17" customHeight="1" spans="1:4">
-      <c r="A1178" s="11"/>
-      <c r="B1178" s="11"/>
-      <c r="C1178" s="11"/>
-      <c r="D1178" s="11" t="s">
-        <v>532</v>
-      </c>
-    </row>
     <row r="1179" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1179" s="12" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B1179" s="12" t="s">
+      <c r="A1179" s="12"/>
+      <c r="B1179" s="12"/>
+      <c r="C1179" s="12"/>
+      <c r="D1179" s="12" t="s">
         <v>1261</v>
-      </c>
-      <c r="C1179" s="12" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D1179" s="12" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="1180" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -17874,7 +17864,7 @@
       <c r="B1180" s="12"/>
       <c r="C1180" s="12"/>
       <c r="D1180" s="12" t="s">
-        <v>1225</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="1181" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -17994,43 +17984,43 @@
       <c r="B1195" s="12"/>
       <c r="C1195" s="12"/>
       <c r="D1195" s="12" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="1196" ht="17" customHeight="1" spans="1:4">
+      <c r="A1196" s="11" t="s">
         <v>1277</v>
       </c>
-    </row>
-    <row r="1196" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1196" s="12"/>
-      <c r="B1196" s="12"/>
-      <c r="C1196" s="12"/>
-      <c r="D1196" s="12" t="s">
+      <c r="B1196" s="11" t="s">
         <v>1278</v>
       </c>
-    </row>
-    <row r="1197" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1197" s="12"/>
-      <c r="B1197" s="12"/>
-      <c r="C1197" s="12"/>
-      <c r="D1197" s="12" t="s">
+      <c r="C1196" s="11" t="s">
         <v>1279</v>
       </c>
-    </row>
-    <row r="1198" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1198" s="12"/>
-      <c r="B1198" s="12"/>
-      <c r="C1198" s="12"/>
-      <c r="D1198" s="12" t="s">
-        <v>478</v>
+      <c r="D1196" s="11" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="1197" ht="17" customHeight="1" spans="1:4">
+      <c r="A1197" s="11"/>
+      <c r="B1197" s="11"/>
+      <c r="C1197" s="11"/>
+      <c r="D1197" s="11" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="1198" ht="17" customHeight="1" spans="1:4">
+      <c r="A1198" s="11"/>
+      <c r="B1198" s="11"/>
+      <c r="C1198" s="11"/>
+      <c r="D1198" s="11" t="s">
+        <v>1282</v>
       </c>
     </row>
     <row r="1199" ht="17" customHeight="1" spans="1:4">
-      <c r="A1199" s="11" t="s">
-        <v>1280</v>
-      </c>
-      <c r="B1199" s="11" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C1199" s="11" t="s">
-        <v>1282</v>
-      </c>
+      <c r="A1199" s="11"/>
+      <c r="B1199" s="11"/>
+      <c r="C1199" s="11"/>
       <c r="D1199" s="11" t="s">
         <v>1283</v>
       </c>
@@ -18088,15 +18078,21 @@
       <c r="B1206" s="11"/>
       <c r="C1206" s="11"/>
       <c r="D1206" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1207" ht="17" customHeight="1" spans="1:4">
+      <c r="A1207" s="11" t="s">
         <v>1290</v>
       </c>
-    </row>
-    <row r="1207" ht="17" customHeight="1" spans="1:4">
-      <c r="A1207" s="11"/>
-      <c r="B1207" s="11"/>
-      <c r="C1207" s="11"/>
+      <c r="B1207" s="11" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C1207" s="11" t="s">
+        <v>1292</v>
+      </c>
       <c r="D1207" s="11" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="1208" ht="17" customHeight="1" spans="1:4">
@@ -18104,7 +18100,7 @@
       <c r="B1208" s="11"/>
       <c r="C1208" s="11"/>
       <c r="D1208" s="11" t="s">
-        <v>1292</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1209" ht="17" customHeight="1" spans="1:4">
@@ -18112,21 +18108,15 @@
       <c r="B1209" s="11"/>
       <c r="C1209" s="11"/>
       <c r="D1209" s="11" t="s">
-        <v>211</v>
+        <v>451</v>
       </c>
     </row>
     <row r="1210" ht="17" customHeight="1" spans="1:4">
-      <c r="A1210" s="11" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B1210" s="11" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C1210" s="11" t="s">
-        <v>1295</v>
-      </c>
+      <c r="A1210" s="11"/>
+      <c r="B1210" s="11"/>
+      <c r="C1210" s="11"/>
       <c r="D1210" s="11" t="s">
-        <v>1296</v>
+        <v>452</v>
       </c>
     </row>
     <row r="1211" ht="17" customHeight="1" spans="1:4">
@@ -18134,7 +18124,7 @@
       <c r="B1211" s="11"/>
       <c r="C1211" s="11"/>
       <c r="D1211" s="11" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="1212" ht="17" customHeight="1" spans="1:4">
@@ -18142,7 +18132,7 @@
       <c r="B1212" s="11"/>
       <c r="C1212" s="11"/>
       <c r="D1212" s="11" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="1213" ht="17" customHeight="1" spans="1:4">
@@ -18150,7 +18140,7 @@
       <c r="B1213" s="11"/>
       <c r="C1213" s="11"/>
       <c r="D1213" s="11" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="1214" ht="17" customHeight="1" spans="1:4">
@@ -18158,7 +18148,7 @@
       <c r="B1214" s="11"/>
       <c r="C1214" s="11"/>
       <c r="D1214" s="11" t="s">
-        <v>453</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="1215" ht="17" customHeight="1" spans="1:4">
@@ -18166,15 +18156,21 @@
       <c r="B1215" s="11"/>
       <c r="C1215" s="11"/>
       <c r="D1215" s="11" t="s">
-        <v>454</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1216" ht="17" customHeight="1" spans="1:4">
-      <c r="A1216" s="11"/>
-      <c r="B1216" s="11"/>
-      <c r="C1216" s="11"/>
+      <c r="A1216" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B1216" s="11" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C1216" s="11" t="s">
+        <v>1297</v>
+      </c>
       <c r="D1216" s="11" t="s">
-        <v>455</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1217" ht="17" customHeight="1" spans="1:4">
@@ -18182,27 +18178,21 @@
       <c r="B1217" s="11"/>
       <c r="C1217" s="11"/>
       <c r="D1217" s="11" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="1218" ht="17" customHeight="1" spans="1:4">
       <c r="A1218" s="11"/>
       <c r="B1218" s="11"/>
       <c r="C1218" s="11"/>
-      <c r="D1218" s="11" t="s">
-        <v>116</v>
+      <c r="D1218" s="12" t="s">
+        <v>1300</v>
       </c>
     </row>
     <row r="1219" ht="17" customHeight="1" spans="1:4">
-      <c r="A1219" s="11" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B1219" s="11" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C1219" s="11" t="s">
-        <v>1300</v>
-      </c>
+      <c r="A1219" s="11"/>
+      <c r="B1219" s="11"/>
+      <c r="C1219" s="11"/>
       <c r="D1219" s="11" t="s">
         <v>1301</v>
       </c>
@@ -18219,16 +18209,22 @@
       <c r="A1221" s="11"/>
       <c r="B1221" s="11"/>
       <c r="C1221" s="11"/>
-      <c r="D1221" s="12" t="s">
+      <c r="D1221" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1222" ht="17" customHeight="1" spans="1:4">
+      <c r="A1222" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B1222" s="11" t="s">
         <v>1303</v>
       </c>
-    </row>
-    <row r="1222" ht="17" customHeight="1" spans="1:4">
-      <c r="A1222" s="11"/>
-      <c r="B1222" s="11"/>
-      <c r="C1222" s="11"/>
+      <c r="C1222" s="11" t="s">
+        <v>1304</v>
+      </c>
       <c r="D1222" s="11" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1223" ht="17" customHeight="1" spans="1:4">
@@ -18236,7 +18232,7 @@
       <c r="B1223" s="11"/>
       <c r="C1223" s="11"/>
       <c r="D1223" s="11" t="s">
-        <v>1305</v>
+        <v>719</v>
       </c>
     </row>
     <row r="1224" ht="17" customHeight="1" spans="1:4">
@@ -18244,21 +18240,15 @@
       <c r="B1224" s="11"/>
       <c r="C1224" s="11"/>
       <c r="D1224" s="11" t="s">
-        <v>170</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="1225" ht="17" customHeight="1" spans="1:4">
-      <c r="A1225" s="11" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B1225" s="11" t="s">
+      <c r="A1225" s="11"/>
+      <c r="B1225" s="11"/>
+      <c r="C1225" s="11"/>
+      <c r="D1225" s="11" t="s">
         <v>1306</v>
-      </c>
-      <c r="C1225" s="11" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D1225" s="11" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="1226" ht="17" customHeight="1" spans="1:4">
@@ -18266,7 +18256,7 @@
       <c r="B1226" s="11"/>
       <c r="C1226" s="11"/>
       <c r="D1226" s="11" t="s">
-        <v>719</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="1227" ht="17" customHeight="1" spans="1:4">
@@ -18337,7 +18327,7 @@
       <c r="A1235" s="11"/>
       <c r="B1235" s="11"/>
       <c r="C1235" s="11"/>
-      <c r="D1235" s="11" t="s">
+      <c r="D1235" s="12" t="s">
         <v>1316</v>
       </c>
     </row>
@@ -18354,15 +18344,21 @@
       <c r="B1237" s="11"/>
       <c r="C1237" s="11"/>
       <c r="D1237" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1238" ht="17" customHeight="1" spans="1:4">
+      <c r="A1238" s="11" t="s">
         <v>1318</v>
       </c>
-    </row>
-    <row r="1238" ht="17" customHeight="1" spans="1:4">
-      <c r="A1238" s="11"/>
-      <c r="B1238" s="11"/>
-      <c r="C1238" s="11"/>
-      <c r="D1238" s="12" t="s">
+      <c r="B1238" s="11" t="s">
         <v>1319</v>
+      </c>
+      <c r="C1238" s="11" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D1238" s="11" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="1239" ht="17" customHeight="1" spans="1:4">
@@ -18370,7 +18366,7 @@
       <c r="B1239" s="11"/>
       <c r="C1239" s="11"/>
       <c r="D1239" s="11" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="1240" ht="17" customHeight="1" spans="1:4">
@@ -18378,19 +18374,13 @@
       <c r="B1240" s="11"/>
       <c r="C1240" s="11"/>
       <c r="D1240" s="11" t="s">
-        <v>180</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="1241" ht="17" customHeight="1" spans="1:4">
-      <c r="A1241" s="11" t="s">
-        <v>1321</v>
-      </c>
-      <c r="B1241" s="11" t="s">
-        <v>1322</v>
-      </c>
-      <c r="C1241" s="11" t="s">
-        <v>1323</v>
-      </c>
+      <c r="A1241" s="11"/>
+      <c r="B1241" s="11"/>
+      <c r="C1241" s="11"/>
       <c r="D1241" s="11" t="s">
         <v>1324</v>
       </c>
@@ -18468,11 +18458,17 @@
       </c>
     </row>
     <row r="1251" ht="17" customHeight="1" spans="1:4">
-      <c r="A1251" s="11"/>
-      <c r="B1251" s="11"/>
-      <c r="C1251" s="11"/>
+      <c r="A1251" s="11" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1251" s="11" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C1251" s="11" t="s">
+        <v>1336</v>
+      </c>
       <c r="D1251" s="11" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="1252" ht="17" customHeight="1" spans="1:4">
@@ -18480,7 +18476,7 @@
       <c r="B1252" s="11"/>
       <c r="C1252" s="11"/>
       <c r="D1252" s="11" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="1253" ht="17" customHeight="1" spans="1:4">
@@ -18488,19 +18484,13 @@
       <c r="B1253" s="11"/>
       <c r="C1253" s="11"/>
       <c r="D1253" s="11" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="1254" ht="17" customHeight="1" spans="1:4">
-      <c r="A1254" s="11" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B1254" s="11" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C1254" s="11" t="s">
-        <v>1339</v>
-      </c>
+      <c r="A1254" s="11"/>
+      <c r="B1254" s="11"/>
+      <c r="C1254" s="11"/>
       <c r="D1254" s="11" t="s">
         <v>1340</v>
       </c>
@@ -18534,22 +18524,28 @@
       <c r="B1258" s="11"/>
       <c r="C1258" s="11"/>
       <c r="D1258" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1259" ht="17" customHeight="1" spans="1:4">
+      <c r="A1259" s="11" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1259" s="11" t="s">
         <v>1344</v>
       </c>
-    </row>
-    <row r="1259" ht="17" customHeight="1" spans="1:4">
-      <c r="A1259" s="11"/>
-      <c r="B1259" s="11"/>
-      <c r="C1259" s="11"/>
+      <c r="C1259" s="11" t="s">
+        <v>1345</v>
+      </c>
       <c r="D1259" s="11" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="1260" ht="17" customHeight="1" spans="1:4">
       <c r="A1260" s="11"/>
       <c r="B1260" s="11"/>
       <c r="C1260" s="11"/>
-      <c r="D1260" s="11" t="s">
+      <c r="D1260" s="12" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -18558,28 +18554,22 @@
       <c r="B1261" s="11"/>
       <c r="C1261" s="11"/>
       <c r="D1261" s="11" t="s">
-        <v>127</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="1262" ht="17" customHeight="1" spans="1:4">
-      <c r="A1262" s="11" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B1262" s="11" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C1262" s="11" t="s">
+      <c r="A1262" s="11"/>
+      <c r="B1262" s="11"/>
+      <c r="C1262" s="11"/>
+      <c r="D1262" s="11" t="s">
         <v>1348</v>
-      </c>
-      <c r="D1262" s="11" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="1263" ht="17" customHeight="1" spans="1:4">
       <c r="A1263" s="11"/>
       <c r="B1263" s="11"/>
       <c r="C1263" s="11"/>
-      <c r="D1263" s="12" t="s">
+      <c r="D1263" s="11" t="s">
         <v>1349</v>
       </c>
     </row>
@@ -18587,7 +18577,7 @@
       <c r="A1264" s="11"/>
       <c r="B1264" s="11"/>
       <c r="C1264" s="11"/>
-      <c r="D1264" s="11" t="s">
+      <c r="D1264" s="12" t="s">
         <v>1350</v>
       </c>
     </row>
@@ -18611,7 +18601,7 @@
       <c r="A1267" s="11"/>
       <c r="B1267" s="11"/>
       <c r="C1267" s="11"/>
-      <c r="D1267" s="12" t="s">
+      <c r="D1267" s="11" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -18627,24 +18617,30 @@
       <c r="A1269" s="11"/>
       <c r="B1269" s="11"/>
       <c r="C1269" s="11"/>
-      <c r="D1269" s="11" t="s">
+      <c r="D1269" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1270" ht="17" customHeight="1" spans="1:4">
+      <c r="A1270" s="11" t="s">
         <v>1355</v>
       </c>
-    </row>
-    <row r="1270" ht="17" customHeight="1" spans="1:4">
-      <c r="A1270" s="11"/>
-      <c r="B1270" s="11"/>
-      <c r="C1270" s="11"/>
-      <c r="D1270" s="11" t="s">
+      <c r="B1270" s="11" t="s">
         <v>1356</v>
+      </c>
+      <c r="C1270" s="11" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D1270" s="13" t="s">
+        <v>1358</v>
       </c>
     </row>
     <row r="1271" ht="17" customHeight="1" spans="1:4">
       <c r="A1271" s="11"/>
       <c r="B1271" s="11"/>
       <c r="C1271" s="11"/>
-      <c r="D1271" s="11" t="s">
-        <v>1357</v>
+      <c r="D1271" s="13" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="1272" ht="17" customHeight="1" spans="1:4">
@@ -18652,21 +18648,15 @@
       <c r="B1272" s="11"/>
       <c r="C1272" s="11"/>
       <c r="D1272" s="13" t="s">
-        <v>211</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="1273" ht="17" customHeight="1" spans="1:4">
-      <c r="A1273" s="11" t="s">
-        <v>1358</v>
-      </c>
-      <c r="B1273" s="11" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C1273" s="11" t="s">
+      <c r="A1273" s="11"/>
+      <c r="B1273" s="11"/>
+      <c r="C1273" s="11"/>
+      <c r="D1273" s="13" t="s">
         <v>1360</v>
-      </c>
-      <c r="D1273" s="13" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="1274" ht="17" customHeight="1" spans="1:4">
@@ -18674,7 +18664,7 @@
       <c r="B1274" s="11"/>
       <c r="C1274" s="11"/>
       <c r="D1274" s="13" t="s">
-        <v>138</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="1275" ht="17" customHeight="1" spans="1:4">
@@ -18714,45 +18704,45 @@
       <c r="B1279" s="11"/>
       <c r="C1279" s="11"/>
       <c r="D1279" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1280" ht="17" customHeight="1" spans="1:4">
+      <c r="A1280" s="11" t="s">
         <v>1366</v>
       </c>
-    </row>
-    <row r="1280" ht="17" customHeight="1" spans="1:4">
-      <c r="A1280" s="11"/>
-      <c r="B1280" s="11"/>
-      <c r="C1280" s="11"/>
-      <c r="D1280" s="13" t="s">
+      <c r="B1280" s="11" t="s">
         <v>1367</v>
+      </c>
+      <c r="C1280" s="11" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D1280" s="11" t="s">
+        <v>1369</v>
       </c>
     </row>
     <row r="1281" ht="17" customHeight="1" spans="1:4">
       <c r="A1281" s="11"/>
       <c r="B1281" s="11"/>
       <c r="C1281" s="11"/>
-      <c r="D1281" s="13" t="s">
-        <v>1368</v>
+      <c r="D1281" s="11" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="1282" ht="17" customHeight="1" spans="1:4">
       <c r="A1282" s="11"/>
       <c r="B1282" s="11"/>
       <c r="C1282" s="11"/>
-      <c r="D1282" s="13" t="s">
-        <v>71</v>
+      <c r="D1282" s="11" t="s">
+        <v>1370</v>
       </c>
     </row>
     <row r="1283" ht="17" customHeight="1" spans="1:4">
-      <c r="A1283" s="11" t="s">
-        <v>1369</v>
-      </c>
-      <c r="B1283" s="11" t="s">
-        <v>1370</v>
-      </c>
-      <c r="C1283" s="11" t="s">
+      <c r="A1283" s="11"/>
+      <c r="B1283" s="11"/>
+      <c r="C1283" s="11"/>
+      <c r="D1283" s="11" t="s">
         <v>1371</v>
-      </c>
-      <c r="D1283" s="11" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="1284" ht="17" customHeight="1" spans="1:4">
@@ -18760,7 +18750,7 @@
       <c r="B1284" s="11"/>
       <c r="C1284" s="11"/>
       <c r="D1284" s="11" t="s">
-        <v>460</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="1285" ht="17" customHeight="1" spans="1:4">
@@ -18948,11 +18938,17 @@
       </c>
     </row>
     <row r="1308" ht="17" customHeight="1" spans="1:4">
-      <c r="A1308" s="11"/>
-      <c r="B1308" s="11"/>
-      <c r="C1308" s="11"/>
+      <c r="A1308" s="11" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B1308" s="11" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C1308" s="11" t="s">
+        <v>1397</v>
+      </c>
       <c r="D1308" s="11" t="s">
-        <v>1396</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="1309" ht="17" customHeight="1" spans="1:4">
@@ -18960,7 +18956,7 @@
       <c r="B1309" s="11"/>
       <c r="C1309" s="11"/>
       <c r="D1309" s="11" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="1310" ht="17" customHeight="1" spans="1:4">
@@ -18968,29 +18964,29 @@
       <c r="B1310" s="11"/>
       <c r="C1310" s="11"/>
       <c r="D1310" s="11" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="1311" ht="17" customHeight="1" spans="1:4">
-      <c r="A1311" s="11" t="s">
+      <c r="A1311" s="11"/>
+      <c r="B1311" s="11"/>
+      <c r="C1311" s="11"/>
+      <c r="D1311" s="11" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="1312" ht="17" customHeight="1" spans="1:4">
+      <c r="A1312" s="11" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B1312" s="11" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C1312" s="11" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D1312" s="11" t="s">
         <v>1369</v>
-      </c>
-      <c r="B1311" s="11" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C1311" s="11" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D1311" s="11" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="1312" ht="17" customHeight="1" spans="1:4">
-      <c r="A1312" s="11"/>
-      <c r="B1312" s="11"/>
-      <c r="C1312" s="11"/>
-      <c r="D1312" s="11" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="1313" ht="17" customHeight="1" spans="1:4">
@@ -18998,7 +18994,7 @@
       <c r="B1313" s="11"/>
       <c r="C1313" s="11"/>
       <c r="D1313" s="11" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="1314" ht="17" customHeight="1" spans="1:4">
@@ -19006,21 +19002,21 @@
       <c r="B1314" s="11"/>
       <c r="C1314" s="11"/>
       <c r="D1314" s="11" t="s">
-        <v>1403</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1315" ht="17" customHeight="1" spans="1:4">
       <c r="A1315" s="11" t="s">
-        <v>1369</v>
+        <v>1404</v>
       </c>
       <c r="B1315" s="11" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C1315" s="11" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D1315" s="11" t="s">
-        <v>1372</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="1316" ht="17" customHeight="1" spans="1:4">
@@ -19028,7 +19024,7 @@
       <c r="B1316" s="11"/>
       <c r="C1316" s="11"/>
       <c r="D1316" s="11" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="1317" ht="17" customHeight="1" spans="1:4">
@@ -19036,19 +19032,13 @@
       <c r="B1317" s="11"/>
       <c r="C1317" s="11"/>
       <c r="D1317" s="11" t="s">
-        <v>197</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="1318" ht="17" customHeight="1" spans="1:4">
-      <c r="A1318" s="11" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B1318" s="11" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C1318" s="11" t="s">
-        <v>1409</v>
-      </c>
+      <c r="A1318" s="11"/>
+      <c r="B1318" s="11"/>
+      <c r="C1318" s="11"/>
       <c r="D1318" s="11" t="s">
         <v>1410</v>
       </c>
@@ -19170,15 +19160,21 @@
       <c r="B1333" s="11"/>
       <c r="C1333" s="11"/>
       <c r="D1333" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1334" ht="17" customHeight="1" spans="1:4">
+      <c r="A1334" s="11" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B1334" s="11" t="s">
         <v>1425</v>
       </c>
-    </row>
-    <row r="1334" ht="17" customHeight="1" spans="1:4">
-      <c r="A1334" s="11"/>
-      <c r="B1334" s="11"/>
-      <c r="C1334" s="11"/>
+      <c r="C1334" s="11" t="s">
+        <v>1426</v>
+      </c>
       <c r="D1334" s="11" t="s">
-        <v>1426</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="1335" ht="17" customHeight="1" spans="1:4">
@@ -19194,21 +19190,15 @@
       <c r="B1336" s="11"/>
       <c r="C1336" s="11"/>
       <c r="D1336" s="11" t="s">
-        <v>25</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1337" ht="17" customHeight="1" spans="1:4">
-      <c r="A1337" s="11" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B1337" s="11" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C1337" s="11" t="s">
+      <c r="A1337" s="11"/>
+      <c r="B1337" s="11"/>
+      <c r="C1337" s="11"/>
+      <c r="D1337" s="11" t="s">
         <v>1429</v>
-      </c>
-      <c r="D1337" s="11" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="1338" ht="17" customHeight="1" spans="1:4">
@@ -19288,43 +19278,43 @@
       <c r="B1347" s="11"/>
       <c r="C1347" s="11"/>
       <c r="D1347" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1348" ht="17" customHeight="1" spans="1:4">
+      <c r="A1348" s="2" t="s">
         <v>1439</v>
       </c>
-    </row>
-    <row r="1348" ht="17" customHeight="1" spans="1:4">
-      <c r="A1348" s="11"/>
-      <c r="B1348" s="11"/>
-      <c r="C1348" s="11"/>
-      <c r="D1348" s="11" t="s">
+      <c r="B1348" s="2" t="s">
         <v>1440</v>
       </c>
+      <c r="C1348" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D1348" s="2" t="s">
+        <v>1442</v>
+      </c>
     </row>
     <row r="1349" ht="17" customHeight="1" spans="1:4">
-      <c r="A1349" s="11"/>
-      <c r="B1349" s="11"/>
-      <c r="C1349" s="11"/>
-      <c r="D1349" s="11" t="s">
-        <v>1441</v>
+      <c r="A1349" s="2"/>
+      <c r="B1349" s="2"/>
+      <c r="C1349" s="2"/>
+      <c r="D1349" s="2" t="s">
+        <v>1443</v>
       </c>
     </row>
     <row r="1350" ht="17" customHeight="1" spans="1:4">
-      <c r="A1350" s="11"/>
-      <c r="B1350" s="11"/>
-      <c r="C1350" s="11"/>
-      <c r="D1350" s="11" t="s">
-        <v>178</v>
+      <c r="A1350" s="2"/>
+      <c r="B1350" s="2"/>
+      <c r="C1350" s="2"/>
+      <c r="D1350" s="2" t="s">
+        <v>1444</v>
       </c>
     </row>
     <row r="1351" ht="17" customHeight="1" spans="1:4">
-      <c r="A1351" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B1351" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="C1351" s="2" t="s">
-        <v>1444</v>
-      </c>
+      <c r="A1351" s="2"/>
+      <c r="B1351" s="2"/>
+      <c r="C1351" s="2"/>
       <c r="D1351" s="2" t="s">
         <v>1445</v>
       </c>
@@ -19462,7 +19452,7 @@
       <c r="B1368" s="2"/>
       <c r="C1368" s="2"/>
       <c r="D1368" s="2" t="s">
-        <v>1462</v>
+        <v>772</v>
       </c>
     </row>
     <row r="1369" ht="17" customHeight="1" spans="1:4">
@@ -19470,7 +19460,7 @@
       <c r="B1369" s="2"/>
       <c r="C1369" s="2"/>
       <c r="D1369" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1370" ht="17" customHeight="1" spans="1:4">
@@ -19478,7 +19468,7 @@
       <c r="B1370" s="2"/>
       <c r="C1370" s="2"/>
       <c r="D1370" s="2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1371" ht="17" customHeight="1" spans="1:4">
@@ -19486,7 +19476,7 @@
       <c r="B1371" s="2"/>
       <c r="C1371" s="2"/>
       <c r="D1371" s="2" t="s">
-        <v>772</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1372" ht="17" customHeight="1" spans="1:4">
@@ -19510,7 +19500,7 @@
       <c r="B1374" s="2"/>
       <c r="C1374" s="2"/>
       <c r="D1374" s="2" t="s">
-        <v>1467</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1375" ht="17" customHeight="1" spans="1:4">
@@ -19518,7 +19508,7 @@
       <c r="B1375" s="2"/>
       <c r="C1375" s="2"/>
       <c r="D1375" s="2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1376" ht="17" customHeight="1" spans="1:4">
@@ -19526,7 +19516,7 @@
       <c r="B1376" s="2"/>
       <c r="C1376" s="2"/>
       <c r="D1376" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1377" ht="17" customHeight="1" spans="1:4">
@@ -19534,7 +19524,7 @@
       <c r="B1377" s="2"/>
       <c r="C1377" s="2"/>
       <c r="D1377" s="2" t="s">
-        <v>191</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1378" ht="17" customHeight="1" spans="1:4">
@@ -19586,39 +19576,39 @@
       </c>
     </row>
     <row r="1384" ht="17" customHeight="1" spans="1:4">
-      <c r="A1384" s="2"/>
-      <c r="B1384" s="2"/>
-      <c r="C1384" s="2"/>
-      <c r="D1384" s="2" t="s">
+      <c r="A1384" s="11" t="s">
         <v>1476</v>
       </c>
+      <c r="B1384" s="11" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C1384" s="11" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D1384" s="11" t="s">
+        <v>1479</v>
+      </c>
     </row>
     <row r="1385" ht="17" customHeight="1" spans="1:4">
-      <c r="A1385" s="2"/>
-      <c r="B1385" s="2"/>
-      <c r="C1385" s="2"/>
-      <c r="D1385" s="2" t="s">
-        <v>1477</v>
+      <c r="A1385" s="11"/>
+      <c r="B1385" s="11"/>
+      <c r="C1385" s="11"/>
+      <c r="D1385" s="11" t="s">
+        <v>1480</v>
       </c>
     </row>
     <row r="1386" ht="17" customHeight="1" spans="1:4">
-      <c r="A1386" s="2"/>
-      <c r="B1386" s="2"/>
-      <c r="C1386" s="2"/>
-      <c r="D1386" s="2" t="s">
-        <v>1478</v>
+      <c r="A1386" s="11"/>
+      <c r="B1386" s="11"/>
+      <c r="C1386" s="11"/>
+      <c r="D1386" s="11" t="s">
+        <v>1481</v>
       </c>
     </row>
     <row r="1387" ht="17" customHeight="1" spans="1:4">
-      <c r="A1387" s="11" t="s">
-        <v>1479</v>
-      </c>
-      <c r="B1387" s="11" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C1387" s="11" t="s">
-        <v>1481</v>
-      </c>
+      <c r="A1387" s="11"/>
+      <c r="B1387" s="11"/>
+      <c r="C1387" s="11"/>
       <c r="D1387" s="11" t="s">
         <v>1482</v>
       </c>
@@ -19628,7 +19618,7 @@
       <c r="B1388" s="11"/>
       <c r="C1388" s="11"/>
       <c r="D1388" s="11" t="s">
-        <v>1483</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1389" ht="17" customHeight="1" spans="1:4">
@@ -19636,7 +19626,7 @@
       <c r="B1389" s="11"/>
       <c r="C1389" s="11"/>
       <c r="D1389" s="11" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1390" ht="17" customHeight="1" spans="1:4">
@@ -19644,7 +19634,7 @@
       <c r="B1390" s="11"/>
       <c r="C1390" s="11"/>
       <c r="D1390" s="11" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1391" ht="17" customHeight="1" spans="1:4">
@@ -19652,7 +19642,7 @@
       <c r="B1391" s="11"/>
       <c r="C1391" s="11"/>
       <c r="D1391" s="11" t="s">
-        <v>315</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1392" ht="17" customHeight="1" spans="1:4">
@@ -19684,45 +19674,45 @@
       <c r="B1395" s="11"/>
       <c r="C1395" s="11"/>
       <c r="D1395" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1396" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1396" s="12" t="s">
         <v>1489</v>
       </c>
-    </row>
-    <row r="1396" ht="17" customHeight="1" spans="1:4">
-      <c r="A1396" s="11"/>
-      <c r="B1396" s="11"/>
-      <c r="C1396" s="11"/>
-      <c r="D1396" s="11" t="s">
+      <c r="B1396" s="12" t="s">
         <v>1490</v>
       </c>
-    </row>
-    <row r="1397" ht="17" customHeight="1" spans="1:4">
-      <c r="A1397" s="11"/>
-      <c r="B1397" s="11"/>
-      <c r="C1397" s="11"/>
-      <c r="D1397" s="11" t="s">
+      <c r="C1396" s="12" t="s">
         <v>1491</v>
       </c>
-    </row>
-    <row r="1398" ht="17" customHeight="1" spans="1:4">
-      <c r="A1398" s="11"/>
-      <c r="B1398" s="11"/>
-      <c r="C1398" s="11"/>
-      <c r="D1398" s="11" t="s">
-        <v>148</v>
+      <c r="D1396" s="12" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="1397" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1397" s="12"/>
+      <c r="B1397" s="12"/>
+      <c r="C1397" s="12"/>
+      <c r="D1397" s="12" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="1398" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1398" s="12"/>
+      <c r="B1398" s="12"/>
+      <c r="C1398" s="12"/>
+      <c r="D1398" s="12" t="s">
+        <v>1494</v>
       </c>
     </row>
     <row r="1399" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1399" s="12" t="s">
-        <v>1492</v>
-      </c>
-      <c r="B1399" s="12" t="s">
-        <v>1493</v>
-      </c>
-      <c r="C1399" s="12" t="s">
-        <v>1494</v>
-      </c>
+      <c r="A1399" s="12"/>
+      <c r="B1399" s="12"/>
+      <c r="C1399" s="12"/>
       <c r="D1399" s="12" t="s">
-        <v>1495</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1400" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -19730,7 +19720,7 @@
       <c r="B1400" s="12"/>
       <c r="C1400" s="12"/>
       <c r="D1400" s="12" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1401" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -19738,7 +19728,7 @@
       <c r="B1401" s="12"/>
       <c r="C1401" s="12"/>
       <c r="D1401" s="12" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1402" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -19746,7 +19736,7 @@
       <c r="B1402" s="12"/>
       <c r="C1402" s="12"/>
       <c r="D1402" s="12" t="s">
-        <v>1023</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1403" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -19802,43 +19792,43 @@
       <c r="B1409" s="12"/>
       <c r="C1409" s="12"/>
       <c r="D1409" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1410" ht="17" customHeight="1" spans="1:4">
+      <c r="A1410" s="11" t="s">
         <v>1504</v>
       </c>
-    </row>
-    <row r="1410" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1410" s="12"/>
-      <c r="B1410" s="12"/>
-      <c r="C1410" s="12"/>
-      <c r="D1410" s="12" t="s">
+      <c r="B1410" s="11" t="s">
         <v>1505</v>
       </c>
-    </row>
-    <row r="1411" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1411" s="12"/>
-      <c r="B1411" s="12"/>
-      <c r="C1411" s="12"/>
-      <c r="D1411" s="12" t="s">
+      <c r="C1410" s="11" t="s">
         <v>1506</v>
       </c>
-    </row>
-    <row r="1412" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1412" s="12"/>
-      <c r="B1412" s="12"/>
-      <c r="C1412" s="12"/>
-      <c r="D1412" s="12" t="s">
-        <v>178</v>
+      <c r="D1410" s="11" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1411" ht="17" customHeight="1" spans="1:4">
+      <c r="A1411" s="11"/>
+      <c r="B1411" s="11"/>
+      <c r="C1411" s="11"/>
+      <c r="D1411" s="11" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="1412" ht="17" customHeight="1" spans="1:4">
+      <c r="A1412" s="11"/>
+      <c r="B1412" s="11"/>
+      <c r="C1412" s="11"/>
+      <c r="D1412" s="11" t="s">
+        <v>1509</v>
       </c>
     </row>
     <row r="1413" ht="17" customHeight="1" spans="1:4">
-      <c r="A1413" s="11" t="s">
-        <v>1507</v>
-      </c>
-      <c r="B1413" s="11" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C1413" s="11" t="s">
-        <v>1509</v>
-      </c>
+      <c r="A1413" s="11"/>
+      <c r="B1413" s="11"/>
+      <c r="C1413" s="11"/>
       <c r="D1413" s="11" t="s">
         <v>1510</v>
       </c>
@@ -19944,15 +19934,21 @@
       <c r="B1426" s="11"/>
       <c r="C1426" s="11"/>
       <c r="D1426" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="1427" ht="17" customHeight="1" spans="1:4">
+      <c r="A1427" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B1427" s="11" t="s">
         <v>1523</v>
       </c>
-    </row>
-    <row r="1427" ht="17" customHeight="1" spans="1:4">
-      <c r="A1427" s="11"/>
-      <c r="B1427" s="11"/>
-      <c r="C1427" s="11"/>
+      <c r="C1427" s="11" t="s">
+        <v>1524</v>
+      </c>
       <c r="D1427" s="11" t="s">
-        <v>1524</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1428" ht="17" customHeight="1" spans="1:4">
@@ -19968,21 +19964,15 @@
       <c r="B1429" s="11"/>
       <c r="C1429" s="11"/>
       <c r="D1429" s="11" t="s">
-        <v>532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1430" ht="17" customHeight="1" spans="1:4">
-      <c r="A1430" s="11" t="s">
-        <v>1507</v>
-      </c>
-      <c r="B1430" s="11" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C1430" s="11" t="s">
+      <c r="A1430" s="11"/>
+      <c r="B1430" s="11"/>
+      <c r="C1430" s="11"/>
+      <c r="D1430" s="11" t="s">
         <v>1527</v>
-      </c>
-      <c r="D1430" s="11" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="1431" ht="17" customHeight="1" spans="1:4">
@@ -20070,15 +20060,21 @@
       <c r="B1441" s="11"/>
       <c r="C1441" s="11"/>
       <c r="D1441" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1442" ht="17" customHeight="1" spans="1:4">
+      <c r="A1442" s="11" t="s">
         <v>1538</v>
       </c>
-    </row>
-    <row r="1442" ht="17" customHeight="1" spans="1:4">
-      <c r="A1442" s="11"/>
-      <c r="B1442" s="11"/>
-      <c r="C1442" s="11"/>
+      <c r="B1442" s="11" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C1442" s="11" t="s">
+        <v>1540</v>
+      </c>
       <c r="D1442" s="11" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1443" ht="17" customHeight="1" spans="1:4">
@@ -20086,7 +20082,7 @@
       <c r="B1443" s="11"/>
       <c r="C1443" s="11"/>
       <c r="D1443" s="11" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1444" ht="17" customHeight="1" spans="1:4">
@@ -20094,19 +20090,13 @@
       <c r="B1444" s="11"/>
       <c r="C1444" s="11"/>
       <c r="D1444" s="11" t="s">
-        <v>87</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1445" ht="17" customHeight="1" spans="1:4">
-      <c r="A1445" s="11" t="s">
-        <v>1541</v>
-      </c>
-      <c r="B1445" s="11" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C1445" s="11" t="s">
-        <v>1543</v>
-      </c>
+      <c r="A1445" s="11"/>
+      <c r="B1445" s="11"/>
+      <c r="C1445" s="11"/>
       <c r="D1445" s="11" t="s">
         <v>1544</v>
       </c>
@@ -20192,11 +20182,17 @@
       </c>
     </row>
     <row r="1456" ht="17" customHeight="1" spans="1:4">
-      <c r="A1456" s="11"/>
-      <c r="B1456" s="11"/>
-      <c r="C1456" s="11"/>
+      <c r="A1456" s="11" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B1456" s="11" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C1456" s="11" t="s">
+        <v>1557</v>
+      </c>
       <c r="D1456" s="11" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1457" ht="17" customHeight="1" spans="1:4">
@@ -20204,7 +20200,7 @@
       <c r="B1457" s="11"/>
       <c r="C1457" s="11"/>
       <c r="D1457" s="11" t="s">
-        <v>1556</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1458" ht="17" customHeight="1" spans="1:4">
@@ -20212,21 +20208,15 @@
       <c r="B1458" s="11"/>
       <c r="C1458" s="11"/>
       <c r="D1458" s="11" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1459" ht="17" customHeight="1" spans="1:4">
-      <c r="A1459" s="11" t="s">
-        <v>1558</v>
-      </c>
-      <c r="B1459" s="11" t="s">
-        <v>1559</v>
-      </c>
-      <c r="C1459" s="11" t="s">
+      <c r="A1459" s="11"/>
+      <c r="B1459" s="11"/>
+      <c r="C1459" s="11"/>
+      <c r="D1459" s="11" t="s">
         <v>1560</v>
-      </c>
-      <c r="D1459" s="11" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="1460" ht="17" customHeight="1" spans="1:4">
@@ -20234,7 +20224,7 @@
       <c r="B1460" s="11"/>
       <c r="C1460" s="11"/>
       <c r="D1460" s="11" t="s">
-        <v>712</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1461" ht="17" customHeight="1" spans="1:4">
@@ -20242,15 +20232,21 @@
       <c r="B1461" s="11"/>
       <c r="C1461" s="11"/>
       <c r="D1461" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1462" ht="17" customHeight="1" spans="1:4">
+      <c r="A1462" s="11" t="s">
         <v>1562</v>
       </c>
-    </row>
-    <row r="1462" ht="17" customHeight="1" spans="1:4">
-      <c r="A1462" s="11"/>
-      <c r="B1462" s="11"/>
-      <c r="C1462" s="11"/>
+      <c r="B1462" s="11" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C1462" s="11" t="s">
+        <v>1564</v>
+      </c>
       <c r="D1462" s="11" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1463" ht="17" customHeight="1" spans="1:4">
@@ -20258,7 +20254,7 @@
       <c r="B1463" s="11"/>
       <c r="C1463" s="11"/>
       <c r="D1463" s="11" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1464" ht="17" customHeight="1" spans="1:4">
@@ -20266,19 +20262,13 @@
       <c r="B1464" s="11"/>
       <c r="C1464" s="11"/>
       <c r="D1464" s="11" t="s">
-        <v>170</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1465" ht="17" customHeight="1" spans="1:4">
-      <c r="A1465" s="11" t="s">
-        <v>1565</v>
-      </c>
-      <c r="B1465" s="11" t="s">
-        <v>1566</v>
-      </c>
-      <c r="C1465" s="11" t="s">
-        <v>1567</v>
-      </c>
+      <c r="A1465" s="11"/>
+      <c r="B1465" s="11"/>
+      <c r="C1465" s="11"/>
       <c r="D1465" s="11" t="s">
         <v>1568</v>
       </c>
@@ -20360,43 +20350,43 @@
       <c r="B1475" s="11"/>
       <c r="C1475" s="11"/>
       <c r="D1475" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1476" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1476" s="12" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="1476" ht="17" customHeight="1" spans="1:4">
-      <c r="A1476" s="11"/>
-      <c r="B1476" s="11"/>
-      <c r="C1476" s="11"/>
-      <c r="D1476" s="11" t="s">
+      <c r="B1476" s="12" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="1477" ht="17" customHeight="1" spans="1:4">
-      <c r="A1477" s="11"/>
-      <c r="B1477" s="11"/>
-      <c r="C1477" s="11"/>
-      <c r="D1477" s="11" t="s">
+      <c r="C1476" s="12" t="s">
         <v>1580</v>
       </c>
-    </row>
-    <row r="1478" ht="17" customHeight="1" spans="1:4">
-      <c r="A1478" s="11"/>
-      <c r="B1478" s="11"/>
-      <c r="C1478" s="11"/>
-      <c r="D1478" s="11" t="s">
-        <v>178</v>
+      <c r="D1476" s="12" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="1477" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1477" s="12"/>
+      <c r="B1477" s="12"/>
+      <c r="C1477" s="12"/>
+      <c r="D1477" s="12" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1478" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1478" s="12"/>
+      <c r="B1478" s="12"/>
+      <c r="C1478" s="12"/>
+      <c r="D1478" s="12" t="s">
+        <v>1583</v>
       </c>
     </row>
     <row r="1479" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1479" s="12" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B1479" s="12" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C1479" s="12" t="s">
-        <v>1583</v>
-      </c>
+      <c r="A1479" s="12"/>
+      <c r="B1479" s="12"/>
+      <c r="C1479" s="12"/>
       <c r="D1479" s="12" t="s">
         <v>1584</v>
       </c>
@@ -20478,43 +20468,43 @@
       <c r="B1489" s="12"/>
       <c r="C1489" s="12"/>
       <c r="D1489" s="12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1490" ht="17" customHeight="1" spans="1:4">
+      <c r="A1490" s="11" t="s">
         <v>1594</v>
       </c>
-    </row>
-    <row r="1490" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1490" s="12"/>
-      <c r="B1490" s="12"/>
-      <c r="C1490" s="12"/>
-      <c r="D1490" s="12" t="s">
+      <c r="B1490" s="11" t="s">
         <v>1595</v>
       </c>
-    </row>
-    <row r="1491" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1491" s="12"/>
-      <c r="B1491" s="12"/>
-      <c r="C1491" s="12"/>
-      <c r="D1491" s="12" t="s">
+      <c r="C1490" s="11" t="s">
         <v>1596</v>
       </c>
-    </row>
-    <row r="1492" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1492" s="12"/>
-      <c r="B1492" s="12"/>
-      <c r="C1492" s="12"/>
-      <c r="D1492" s="12" t="s">
-        <v>178</v>
+      <c r="D1490" s="11" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="1491" ht="17" customHeight="1" spans="1:4">
+      <c r="A1491" s="11"/>
+      <c r="B1491" s="11"/>
+      <c r="C1491" s="11"/>
+      <c r="D1491" s="11" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="1492" ht="17" customHeight="1" spans="1:4">
+      <c r="A1492" s="11"/>
+      <c r="B1492" s="11"/>
+      <c r="C1492" s="11"/>
+      <c r="D1492" s="11" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="1493" ht="17" customHeight="1" spans="1:4">
-      <c r="A1493" s="11" t="s">
-        <v>1597</v>
-      </c>
-      <c r="B1493" s="11" t="s">
-        <v>1598</v>
-      </c>
-      <c r="C1493" s="11" t="s">
-        <v>1599</v>
-      </c>
+      <c r="A1493" s="11"/>
+      <c r="B1493" s="11"/>
+      <c r="C1493" s="11"/>
       <c r="D1493" s="11" t="s">
         <v>1600</v>
       </c>
@@ -20532,15 +20522,21 @@
       <c r="B1495" s="11"/>
       <c r="C1495" s="11"/>
       <c r="D1495" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1496" ht="17" customHeight="1" spans="1:4">
+      <c r="A1496" s="11" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B1496" s="11" t="s">
         <v>1602</v>
       </c>
-    </row>
-    <row r="1496" ht="17" customHeight="1" spans="1:4">
-      <c r="A1496" s="11"/>
-      <c r="B1496" s="11"/>
-      <c r="C1496" s="11"/>
+      <c r="C1496" s="11" t="s">
+        <v>1603</v>
+      </c>
       <c r="D1496" s="11" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1497" ht="17" customHeight="1" spans="1:4">
@@ -20548,7 +20544,7 @@
       <c r="B1497" s="11"/>
       <c r="C1497" s="11"/>
       <c r="D1497" s="11" t="s">
-        <v>1604</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1498" ht="17" customHeight="1" spans="1:4">
@@ -20556,21 +20552,15 @@
       <c r="B1498" s="11"/>
       <c r="C1498" s="11"/>
       <c r="D1498" s="11" t="s">
-        <v>170</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1499" ht="17" customHeight="1" spans="1:4">
-      <c r="A1499" s="11" t="s">
-        <v>1597</v>
-      </c>
-      <c r="B1499" s="11" t="s">
+      <c r="A1499" s="11"/>
+      <c r="B1499" s="11"/>
+      <c r="C1499" s="11"/>
+      <c r="D1499" s="11" t="s">
         <v>1605</v>
-      </c>
-      <c r="C1499" s="11" t="s">
-        <v>1606</v>
-      </c>
-      <c r="D1499" s="11" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="1500" ht="17" customHeight="1" spans="1:4">
@@ -20578,7 +20568,7 @@
       <c r="B1500" s="11"/>
       <c r="C1500" s="11"/>
       <c r="D1500" s="11" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1501" ht="17" customHeight="1" spans="1:4">
@@ -20618,15 +20608,21 @@
       <c r="B1505" s="11"/>
       <c r="C1505" s="11"/>
       <c r="D1505" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1506" ht="17" customHeight="1" spans="1:4">
+      <c r="A1506" s="11" t="s">
         <v>1611</v>
       </c>
-    </row>
-    <row r="1506" ht="17" customHeight="1" spans="1:4">
-      <c r="A1506" s="11"/>
-      <c r="B1506" s="11"/>
-      <c r="C1506" s="11"/>
+      <c r="B1506" s="11" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C1506" s="11" t="s">
+        <v>1613</v>
+      </c>
       <c r="D1506" s="11" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1507" ht="17" customHeight="1" spans="1:4">
@@ -20634,7 +20630,7 @@
       <c r="B1507" s="11"/>
       <c r="C1507" s="11"/>
       <c r="D1507" s="11" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1508" ht="17" customHeight="1" spans="1:4">
@@ -20642,19 +20638,13 @@
       <c r="B1508" s="11"/>
       <c r="C1508" s="11"/>
       <c r="D1508" s="11" t="s">
-        <v>71</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1509" ht="17" customHeight="1" spans="1:4">
-      <c r="A1509" s="11" t="s">
-        <v>1614</v>
-      </c>
-      <c r="B1509" s="11" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C1509" s="11" t="s">
-        <v>1616</v>
-      </c>
+      <c r="A1509" s="11"/>
+      <c r="B1509" s="11"/>
+      <c r="C1509" s="11"/>
       <c r="D1509" s="11" t="s">
         <v>1617</v>
       </c>
@@ -20712,15 +20702,21 @@
       <c r="B1516" s="11"/>
       <c r="C1516" s="11"/>
       <c r="D1516" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1517" ht="17" customHeight="1" spans="1:4">
+      <c r="A1517" s="11" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1517" s="11" t="s">
         <v>1624</v>
       </c>
-    </row>
-    <row r="1517" ht="17" customHeight="1" spans="1:4">
-      <c r="A1517" s="11"/>
-      <c r="B1517" s="11"/>
-      <c r="C1517" s="11"/>
+      <c r="C1517" s="11" t="s">
+        <v>1625</v>
+      </c>
       <c r="D1517" s="11" t="s">
-        <v>1625</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1518" ht="17" customHeight="1" spans="1:4">
@@ -20736,21 +20732,15 @@
       <c r="B1519" s="11"/>
       <c r="C1519" s="11"/>
       <c r="D1519" s="11" t="s">
-        <v>211</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1520" ht="17" customHeight="1" spans="1:4">
-      <c r="A1520" s="11" t="s">
-        <v>1614</v>
-      </c>
-      <c r="B1520" s="11" t="s">
-        <v>1627</v>
-      </c>
-      <c r="C1520" s="11" t="s">
+      <c r="A1520" s="11"/>
+      <c r="B1520" s="11"/>
+      <c r="C1520" s="11"/>
+      <c r="D1520" s="11" t="s">
         <v>1628</v>
-      </c>
-      <c r="D1520" s="11" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="1521" ht="17" customHeight="1" spans="1:4">
@@ -20798,15 +20788,21 @@
       <c r="B1526" s="11"/>
       <c r="C1526" s="11"/>
       <c r="D1526" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1527" ht="17" customHeight="1" spans="1:4">
+      <c r="A1527" s="11" t="s">
         <v>1634</v>
       </c>
-    </row>
-    <row r="1527" ht="17" customHeight="1" spans="1:4">
-      <c r="A1527" s="11"/>
-      <c r="B1527" s="11"/>
-      <c r="C1527" s="11"/>
+      <c r="B1527" s="11" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C1527" s="11" t="s">
+        <v>1636</v>
+      </c>
       <c r="D1527" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1528" ht="17" customHeight="1" spans="1:4">
@@ -20814,7 +20810,7 @@
       <c r="B1528" s="11"/>
       <c r="C1528" s="11"/>
       <c r="D1528" s="11" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1529" ht="17" customHeight="1" spans="1:4">
@@ -20822,19 +20818,13 @@
       <c r="B1529" s="11"/>
       <c r="C1529" s="11"/>
       <c r="D1529" s="11" t="s">
-        <v>71</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1530" ht="17" customHeight="1" spans="1:4">
-      <c r="A1530" s="11" t="s">
-        <v>1637</v>
-      </c>
-      <c r="B1530" s="11" t="s">
-        <v>1638</v>
-      </c>
-      <c r="C1530" s="11" t="s">
-        <v>1639</v>
-      </c>
+      <c r="A1530" s="11"/>
+      <c r="B1530" s="11"/>
+      <c r="C1530" s="11"/>
       <c r="D1530" s="11" t="s">
         <v>1640</v>
       </c>
@@ -20900,15 +20890,21 @@
       <c r="B1538" s="11"/>
       <c r="C1538" s="11"/>
       <c r="D1538" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1539" ht="17" customHeight="1" spans="1:4">
+      <c r="A1539" s="11" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1539" s="11" t="s">
         <v>1648</v>
       </c>
-    </row>
-    <row r="1539" ht="17" customHeight="1" spans="1:4">
-      <c r="A1539" s="11"/>
-      <c r="B1539" s="11"/>
-      <c r="C1539" s="11"/>
+      <c r="C1539" s="11" t="s">
+        <v>1649</v>
+      </c>
       <c r="D1539" s="11" t="s">
-        <v>1649</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1540" ht="17" customHeight="1" spans="1:4">
@@ -20916,7 +20912,7 @@
       <c r="B1540" s="11"/>
       <c r="C1540" s="11"/>
       <c r="D1540" s="11" t="s">
-        <v>1650</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1541" ht="17" customHeight="1" spans="1:4">
@@ -20924,21 +20920,15 @@
       <c r="B1541" s="11"/>
       <c r="C1541" s="11"/>
       <c r="D1541" s="11" t="s">
-        <v>148</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1542" ht="17" customHeight="1" spans="1:4">
-      <c r="A1542" s="11" t="s">
-        <v>1637</v>
-      </c>
-      <c r="B1542" s="11" t="s">
+      <c r="A1542" s="11"/>
+      <c r="B1542" s="11"/>
+      <c r="C1542" s="11"/>
+      <c r="D1542" s="11" t="s">
         <v>1651</v>
-      </c>
-      <c r="C1542" s="11" t="s">
-        <v>1652</v>
-      </c>
-      <c r="D1542" s="11" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="1543" ht="17" customHeight="1" spans="1:4">
@@ -20946,7 +20936,7 @@
       <c r="B1543" s="11"/>
       <c r="C1543" s="11"/>
       <c r="D1543" s="11" t="s">
-        <v>138</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1544" ht="17" customHeight="1" spans="1:4">
@@ -20978,15 +20968,21 @@
       <c r="B1547" s="11"/>
       <c r="C1547" s="11"/>
       <c r="D1547" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1548" ht="17" customHeight="1" spans="1:4">
+      <c r="A1548" s="11" t="s">
         <v>1656</v>
       </c>
-    </row>
-    <row r="1548" ht="17" customHeight="1" spans="1:4">
-      <c r="A1548" s="11"/>
-      <c r="B1548" s="11"/>
-      <c r="C1548" s="11"/>
+      <c r="B1548" s="11" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C1548" s="11" t="s">
+        <v>1656</v>
+      </c>
       <c r="D1548" s="11" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1549" ht="17" customHeight="1" spans="1:4">
@@ -20994,29 +20990,29 @@
       <c r="B1549" s="11"/>
       <c r="C1549" s="11"/>
       <c r="D1549" s="11" t="s">
-        <v>1658</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1550" ht="17" customHeight="1" spans="1:4">
-      <c r="A1550" s="11"/>
-      <c r="B1550" s="11"/>
-      <c r="C1550" s="11"/>
+      <c r="A1550" s="11" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B1550" s="11" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C1550" s="11" t="s">
+        <v>1661</v>
+      </c>
       <c r="D1550" s="11" t="s">
-        <v>116</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1551" ht="17" customHeight="1" spans="1:4">
-      <c r="A1551" s="11" t="s">
-        <v>1659</v>
-      </c>
-      <c r="B1551" s="11" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C1551" s="11" t="s">
-        <v>1659</v>
-      </c>
+      <c r="A1551" s="11"/>
+      <c r="B1551" s="11"/>
+      <c r="C1551" s="11"/>
       <c r="D1551" s="11" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1552" ht="17" customHeight="1" spans="1:4">
@@ -21024,19 +21020,13 @@
       <c r="B1552" s="11"/>
       <c r="C1552" s="11"/>
       <c r="D1552" s="11" t="s">
-        <v>707</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1553" ht="17" customHeight="1" spans="1:4">
-      <c r="A1553" s="11" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B1553" s="11" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C1553" s="11" t="s">
-        <v>1664</v>
-      </c>
+      <c r="A1553" s="11"/>
+      <c r="B1553" s="11"/>
+      <c r="C1553" s="11"/>
       <c r="D1553" s="11" t="s">
         <v>1665</v>
       </c>
@@ -21086,15 +21076,21 @@
       <c r="B1559" s="11"/>
       <c r="C1559" s="11"/>
       <c r="D1559" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1560" ht="17" customHeight="1" spans="1:4">
+      <c r="A1560" s="11" t="s">
         <v>1671</v>
       </c>
-    </row>
-    <row r="1560" ht="17" customHeight="1" spans="1:4">
-      <c r="A1560" s="11"/>
-      <c r="B1560" s="11"/>
-      <c r="C1560" s="11"/>
+      <c r="B1560" s="11" t="s">
+        <v>1672</v>
+      </c>
+      <c r="C1560" s="11" t="s">
+        <v>1673</v>
+      </c>
       <c r="D1560" s="11" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1561" ht="17" customHeight="1" spans="1:4">
@@ -21102,7 +21098,7 @@
       <c r="B1561" s="11"/>
       <c r="C1561" s="11"/>
       <c r="D1561" s="11" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1562" ht="17" customHeight="1" spans="1:4">
@@ -21110,19 +21106,13 @@
       <c r="B1562" s="11"/>
       <c r="C1562" s="11"/>
       <c r="D1562" s="11" t="s">
-        <v>71</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1563" ht="17" customHeight="1" spans="1:4">
-      <c r="A1563" s="11" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B1563" s="11" t="s">
-        <v>1675</v>
-      </c>
-      <c r="C1563" s="11" t="s">
-        <v>1676</v>
-      </c>
+      <c r="A1563" s="11"/>
+      <c r="B1563" s="11"/>
+      <c r="C1563" s="11"/>
       <c r="D1563" s="11" t="s">
         <v>1677</v>
       </c>
@@ -21203,7 +21193,7 @@
       <c r="A1573" s="11"/>
       <c r="B1573" s="11"/>
       <c r="C1573" s="11"/>
-      <c r="D1573" s="11" t="s">
+      <c r="D1573" s="13" t="s">
         <v>1687</v>
       </c>
     </row>
@@ -21227,7 +21217,7 @@
       <c r="A1576" s="11"/>
       <c r="B1576" s="11"/>
       <c r="C1576" s="11"/>
-      <c r="D1576" s="13" t="s">
+      <c r="D1576" s="11" t="s">
         <v>1690</v>
       </c>
     </row>
@@ -21235,7 +21225,7 @@
       <c r="A1577" s="11"/>
       <c r="B1577" s="11"/>
       <c r="C1577" s="11"/>
-      <c r="D1577" s="11" t="s">
+      <c r="D1577" s="13" t="s">
         <v>1691</v>
       </c>
     </row>
@@ -21244,22 +21234,28 @@
       <c r="B1578" s="11"/>
       <c r="C1578" s="11"/>
       <c r="D1578" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1579" ht="17" customHeight="1" spans="1:4">
+      <c r="A1579" s="11" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B1579" s="11" t="s">
         <v>1692</v>
       </c>
-    </row>
-    <row r="1579" ht="17" customHeight="1" spans="1:4">
-      <c r="A1579" s="11"/>
-      <c r="B1579" s="11"/>
-      <c r="C1579" s="11"/>
+      <c r="C1579" s="11" t="s">
+        <v>1693</v>
+      </c>
       <c r="D1579" s="11" t="s">
-        <v>1693</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1580" ht="17" customHeight="1" spans="1:4">
       <c r="A1580" s="11"/>
       <c r="B1580" s="11"/>
       <c r="C1580" s="11"/>
-      <c r="D1580" s="13" t="s">
+      <c r="D1580" s="11" t="s">
         <v>1694</v>
       </c>
     </row>
@@ -21268,21 +21264,15 @@
       <c r="B1581" s="11"/>
       <c r="C1581" s="11"/>
       <c r="D1581" s="11" t="s">
-        <v>25</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1582" ht="17" customHeight="1" spans="1:4">
-      <c r="A1582" s="11" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B1582" s="11" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C1582" s="11" t="s">
+      <c r="A1582" s="11"/>
+      <c r="B1582" s="11"/>
+      <c r="C1582" s="11"/>
+      <c r="D1582" s="11" t="s">
         <v>1696</v>
-      </c>
-      <c r="D1582" s="11" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="1583" ht="17" customHeight="1" spans="1:4">
@@ -21370,15 +21360,21 @@
       <c r="B1593" s="11"/>
       <c r="C1593" s="11"/>
       <c r="D1593" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1594" ht="17" customHeight="1" spans="1:4">
+      <c r="A1594" s="11" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B1594" s="11" t="s">
         <v>1707</v>
       </c>
-    </row>
-    <row r="1594" ht="17" customHeight="1" spans="1:4">
-      <c r="A1594" s="11"/>
-      <c r="B1594" s="11"/>
-      <c r="C1594" s="11"/>
+      <c r="C1594" s="11" t="s">
+        <v>1708</v>
+      </c>
       <c r="D1594" s="11" t="s">
-        <v>1708</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1595" ht="17" customHeight="1" spans="1:4">
@@ -21386,7 +21382,7 @@
       <c r="B1595" s="11"/>
       <c r="C1595" s="11"/>
       <c r="D1595" s="11" t="s">
-        <v>1709</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1596" ht="17" customHeight="1" spans="1:4">
@@ -21394,21 +21390,15 @@
       <c r="B1596" s="11"/>
       <c r="C1596" s="11"/>
       <c r="D1596" s="11" t="s">
-        <v>87</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1597" ht="17" customHeight="1" spans="1:4">
-      <c r="A1597" s="11" t="s">
-        <v>1674</v>
-      </c>
-      <c r="B1597" s="11" t="s">
+      <c r="A1597" s="11"/>
+      <c r="B1597" s="11"/>
+      <c r="C1597" s="11"/>
+      <c r="D1597" s="11" t="s">
         <v>1710</v>
-      </c>
-      <c r="C1597" s="11" t="s">
-        <v>1711</v>
-      </c>
-      <c r="D1597" s="11" t="s">
-        <v>1677</v>
       </c>
     </row>
     <row r="1598" ht="17" customHeight="1" spans="1:4">
@@ -21416,7 +21406,7 @@
       <c r="B1598" s="11"/>
       <c r="C1598" s="11"/>
       <c r="D1598" s="11" t="s">
-        <v>1697</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1599" ht="17" customHeight="1" spans="1:4">
@@ -21520,15 +21510,21 @@
       <c r="B1611" s="11"/>
       <c r="C1611" s="11"/>
       <c r="D1611" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1612" ht="17" customHeight="1" spans="1:4">
+      <c r="A1612" s="11" t="s">
         <v>1724</v>
       </c>
-    </row>
-    <row r="1612" ht="17" customHeight="1" spans="1:4">
-      <c r="A1612" s="11"/>
-      <c r="B1612" s="11"/>
-      <c r="C1612" s="11"/>
+      <c r="B1612" s="11" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C1612" s="11" t="s">
+        <v>1726</v>
+      </c>
       <c r="D1612" s="11" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1613" ht="17" customHeight="1" spans="1:4">
@@ -21536,7 +21532,7 @@
       <c r="B1613" s="11"/>
       <c r="C1613" s="11"/>
       <c r="D1613" s="11" t="s">
-        <v>1726</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1614" ht="17" customHeight="1" spans="1:4">
@@ -21544,21 +21540,15 @@
       <c r="B1614" s="11"/>
       <c r="C1614" s="11"/>
       <c r="D1614" s="11" t="s">
-        <v>380</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1615" ht="17" customHeight="1" spans="1:4">
-      <c r="A1615" s="11" t="s">
-        <v>1727</v>
-      </c>
-      <c r="B1615" s="11" t="s">
-        <v>1728</v>
-      </c>
-      <c r="C1615" s="11" t="s">
+      <c r="A1615" s="11"/>
+      <c r="B1615" s="11"/>
+      <c r="C1615" s="11"/>
+      <c r="D1615" s="11" t="s">
         <v>1729</v>
-      </c>
-      <c r="D1615" s="11" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="1616" ht="17" customHeight="1" spans="1:4">
@@ -21566,7 +21556,7 @@
       <c r="B1616" s="11"/>
       <c r="C1616" s="11"/>
       <c r="D1616" s="11" t="s">
-        <v>1511</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1617" ht="17" customHeight="1" spans="1:4">
@@ -21598,7 +21588,7 @@
       <c r="B1620" s="11"/>
       <c r="C1620" s="11"/>
       <c r="D1620" s="11" t="s">
-        <v>1734</v>
+        <v>932</v>
       </c>
     </row>
     <row r="1621" ht="17" customHeight="1" spans="1:4">
@@ -21606,7 +21596,7 @@
       <c r="B1621" s="11"/>
       <c r="C1621" s="11"/>
       <c r="D1621" s="11" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1622" ht="17" customHeight="1" spans="1:4">
@@ -21614,7 +21604,7 @@
       <c r="B1622" s="11"/>
       <c r="C1622" s="11"/>
       <c r="D1622" s="11" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1623" ht="17" customHeight="1" spans="1:4">
@@ -21622,7 +21612,7 @@
       <c r="B1623" s="11"/>
       <c r="C1623" s="11"/>
       <c r="D1623" s="11" t="s">
-        <v>932</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1624" ht="17" customHeight="1" spans="1:4">
@@ -21646,15 +21636,21 @@
       <c r="B1626" s="11"/>
       <c r="C1626" s="11"/>
       <c r="D1626" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1627" ht="17" customHeight="1" spans="1:4">
+      <c r="A1627" s="11" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1627" s="11" t="s">
         <v>1739</v>
       </c>
-    </row>
-    <row r="1627" ht="17" customHeight="1" spans="1:4">
-      <c r="A1627" s="11"/>
-      <c r="B1627" s="11"/>
-      <c r="C1627" s="11"/>
+      <c r="C1627" s="11" t="s">
+        <v>1740</v>
+      </c>
       <c r="D1627" s="11" t="s">
-        <v>1740</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1628" ht="17" customHeight="1" spans="1:4">
@@ -21670,21 +21666,15 @@
       <c r="B1629" s="11"/>
       <c r="C1629" s="11"/>
       <c r="D1629" s="11" t="s">
-        <v>87</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1630" ht="17" customHeight="1" spans="1:4">
-      <c r="A1630" s="11" t="s">
-        <v>1727</v>
-      </c>
-      <c r="B1630" s="11" t="s">
-        <v>1742</v>
-      </c>
-      <c r="C1630" s="11" t="s">
+      <c r="A1630" s="11"/>
+      <c r="B1630" s="11"/>
+      <c r="C1630" s="11"/>
+      <c r="D1630" s="11" t="s">
         <v>1743</v>
-      </c>
-      <c r="D1630" s="11" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="1631" ht="17" customHeight="1" spans="1:4">
@@ -21716,15 +21706,21 @@
       <c r="B1634" s="11"/>
       <c r="C1634" s="11"/>
       <c r="D1634" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1635" ht="17" customHeight="1" spans="1:4">
+      <c r="A1635" s="11" t="s">
         <v>1747</v>
       </c>
-    </row>
-    <row r="1635" ht="17" customHeight="1" spans="1:4">
-      <c r="A1635" s="11"/>
-      <c r="B1635" s="11"/>
-      <c r="C1635" s="11"/>
+      <c r="B1635" s="11" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C1635" s="11" t="s">
+        <v>1749</v>
+      </c>
       <c r="D1635" s="11" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1636" ht="17" customHeight="1" spans="1:4">
@@ -21732,7 +21728,7 @@
       <c r="B1636" s="11"/>
       <c r="C1636" s="11"/>
       <c r="D1636" s="11" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1637" ht="17" customHeight="1" spans="1:4">
@@ -21740,19 +21736,13 @@
       <c r="B1637" s="11"/>
       <c r="C1637" s="11"/>
       <c r="D1637" s="11" t="s">
-        <v>127</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1638" ht="17" customHeight="1" spans="1:4">
-      <c r="A1638" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1638" s="11" t="s">
-        <v>1751</v>
-      </c>
-      <c r="C1638" s="11" t="s">
-        <v>1752</v>
-      </c>
+      <c r="A1638" s="11"/>
+      <c r="B1638" s="11"/>
+      <c r="C1638" s="11"/>
       <c r="D1638" s="11" t="s">
         <v>1753</v>
       </c>
@@ -21842,15 +21832,21 @@
       <c r="B1649" s="11"/>
       <c r="C1649" s="11"/>
       <c r="D1649" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1650" ht="17" customHeight="1" spans="1:4">
+      <c r="A1650" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1650" s="11" t="s">
         <v>1764</v>
       </c>
-    </row>
-    <row r="1650" ht="17" customHeight="1" spans="1:4">
-      <c r="A1650" s="11"/>
-      <c r="B1650" s="11"/>
-      <c r="C1650" s="11"/>
+      <c r="C1650" s="11" t="s">
+        <v>1765</v>
+      </c>
       <c r="D1650" s="11" t="s">
-        <v>1765</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1651" ht="17" customHeight="1" spans="1:4">
@@ -21866,21 +21862,15 @@
       <c r="B1652" s="11"/>
       <c r="C1652" s="11"/>
       <c r="D1652" s="11" t="s">
-        <v>87</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1653" ht="17" customHeight="1" spans="1:4">
-      <c r="A1653" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1653" s="11" t="s">
-        <v>1767</v>
-      </c>
-      <c r="C1653" s="11" t="s">
+      <c r="A1653" s="11"/>
+      <c r="B1653" s="11"/>
+      <c r="C1653" s="11"/>
+      <c r="D1653" s="11" t="s">
         <v>1768</v>
-      </c>
-      <c r="D1653" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1654" ht="17" customHeight="1" spans="1:4">
@@ -21960,15 +21950,21 @@
       <c r="B1663" s="11"/>
       <c r="C1663" s="11"/>
       <c r="D1663" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1664" ht="17" customHeight="1" spans="1:4">
+      <c r="A1664" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1664" s="11" t="s">
         <v>1778</v>
       </c>
-    </row>
-    <row r="1664" ht="17" customHeight="1" spans="1:4">
-      <c r="A1664" s="11"/>
-      <c r="B1664" s="11"/>
-      <c r="C1664" s="11"/>
+      <c r="C1664" s="11" t="s">
+        <v>1779</v>
+      </c>
       <c r="D1664" s="11" t="s">
-        <v>1779</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1665" ht="17" customHeight="1" spans="1:4">
@@ -21984,21 +21980,15 @@
       <c r="B1666" s="11"/>
       <c r="C1666" s="11"/>
       <c r="D1666" s="11" t="s">
-        <v>178</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1667" ht="17" customHeight="1" spans="1:4">
-      <c r="A1667" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1667" s="11" t="s">
-        <v>1781</v>
-      </c>
-      <c r="C1667" s="11" t="s">
+      <c r="A1667" s="11"/>
+      <c r="B1667" s="11"/>
+      <c r="C1667" s="11"/>
+      <c r="D1667" s="11" t="s">
         <v>1782</v>
-      </c>
-      <c r="D1667" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1668" ht="17" customHeight="1" spans="1:4">
@@ -22094,15 +22084,21 @@
       <c r="B1679" s="11"/>
       <c r="C1679" s="11"/>
       <c r="D1679" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1680" ht="17" customHeight="1" spans="1:4">
+      <c r="A1680" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1680" s="11" t="s">
         <v>1794</v>
       </c>
-    </row>
-    <row r="1680" ht="17" customHeight="1" spans="1:4">
-      <c r="A1680" s="11"/>
-      <c r="B1680" s="11"/>
-      <c r="C1680" s="11"/>
+      <c r="C1680" s="11" t="s">
+        <v>1795</v>
+      </c>
       <c r="D1680" s="11" t="s">
-        <v>1795</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1681" ht="17" customHeight="1" spans="1:4">
@@ -22118,21 +22114,15 @@
       <c r="B1682" s="11"/>
       <c r="C1682" s="11"/>
       <c r="D1682" s="11" t="s">
-        <v>180</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1683" ht="17" customHeight="1" spans="1:4">
-      <c r="A1683" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1683" s="11" t="s">
-        <v>1797</v>
-      </c>
-      <c r="C1683" s="11" t="s">
+      <c r="A1683" s="11"/>
+      <c r="B1683" s="11"/>
+      <c r="C1683" s="11"/>
+      <c r="D1683" s="11" t="s">
         <v>1798</v>
-      </c>
-      <c r="D1683" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1684" ht="17" customHeight="1" spans="1:4">
@@ -22236,15 +22226,21 @@
       <c r="B1696" s="11"/>
       <c r="C1696" s="11"/>
       <c r="D1696" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="1697" ht="17" customHeight="1" spans="1:4">
+      <c r="A1697" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1697" s="11" t="s">
         <v>1811</v>
       </c>
-    </row>
-    <row r="1697" ht="17" customHeight="1" spans="1:4">
-      <c r="A1697" s="11"/>
-      <c r="B1697" s="11"/>
-      <c r="C1697" s="11"/>
+      <c r="C1697" s="11" t="s">
+        <v>1812</v>
+      </c>
       <c r="D1697" s="11" t="s">
-        <v>1812</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1698" ht="17" customHeight="1" spans="1:4">
@@ -22252,7 +22248,7 @@
       <c r="B1698" s="11"/>
       <c r="C1698" s="11"/>
       <c r="D1698" s="11" t="s">
-        <v>1813</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1699" ht="17" customHeight="1" spans="1:4">
@@ -22260,21 +22256,15 @@
       <c r="B1699" s="11"/>
       <c r="C1699" s="11"/>
       <c r="D1699" s="11" t="s">
-        <v>532</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1700" ht="17" customHeight="1" spans="1:4">
-      <c r="A1700" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1700" s="11" t="s">
+      <c r="A1700" s="11"/>
+      <c r="B1700" s="11"/>
+      <c r="C1700" s="11"/>
+      <c r="D1700" s="11" t="s">
         <v>1814</v>
-      </c>
-      <c r="C1700" s="11" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D1700" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1701" ht="17" customHeight="1" spans="1:4">
@@ -22282,7 +22272,7 @@
       <c r="B1701" s="11"/>
       <c r="C1701" s="11"/>
       <c r="D1701" s="11" t="s">
-        <v>1783</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1702" ht="17" customHeight="1" spans="1:4">
@@ -22346,7 +22336,7 @@
       <c r="B1709" s="11"/>
       <c r="C1709" s="11"/>
       <c r="D1709" s="11" t="s">
-        <v>1823</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1710" ht="17" customHeight="1" spans="1:4">
@@ -22354,15 +22344,21 @@
       <c r="B1710" s="11"/>
       <c r="C1710" s="11"/>
       <c r="D1710" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1711" ht="17" customHeight="1" spans="1:4">
+      <c r="A1711" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1711" s="11" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C1711" s="11" t="s">
         <v>1824</v>
       </c>
-    </row>
-    <row r="1711" ht="17" customHeight="1" spans="1:4">
-      <c r="A1711" s="11"/>
-      <c r="B1711" s="11"/>
-      <c r="C1711" s="11"/>
       <c r="D1711" s="11" t="s">
-        <v>1825</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1712" ht="17" customHeight="1" spans="1:4">
@@ -22370,7 +22366,7 @@
       <c r="B1712" s="11"/>
       <c r="C1712" s="11"/>
       <c r="D1712" s="11" t="s">
-        <v>1780</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1713" ht="17" customHeight="1" spans="1:4">
@@ -22378,21 +22374,15 @@
       <c r="B1713" s="11"/>
       <c r="C1713" s="11"/>
       <c r="D1713" s="11" t="s">
-        <v>178</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1714" ht="17" customHeight="1" spans="1:4">
-      <c r="A1714" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1714" s="11" t="s">
-        <v>1826</v>
-      </c>
-      <c r="C1714" s="11" t="s">
+      <c r="A1714" s="11"/>
+      <c r="B1714" s="11"/>
+      <c r="C1714" s="11"/>
+      <c r="D1714" s="11" t="s">
         <v>1827</v>
-      </c>
-      <c r="D1714" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1715" ht="17" customHeight="1" spans="1:4">
@@ -22480,7 +22470,7 @@
       <c r="B1725" s="11"/>
       <c r="C1725" s="11"/>
       <c r="D1725" s="11" t="s">
-        <v>1838</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1726" ht="17" customHeight="1" spans="1:4">
@@ -22488,15 +22478,21 @@
       <c r="B1726" s="11"/>
       <c r="C1726" s="11"/>
       <c r="D1726" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1727" ht="17" customHeight="1" spans="1:4">
+      <c r="A1727" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1727" s="11" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1727" s="11" t="s">
         <v>1839</v>
       </c>
-    </row>
-    <row r="1727" ht="17" customHeight="1" spans="1:4">
-      <c r="A1727" s="11"/>
-      <c r="B1727" s="11"/>
-      <c r="C1727" s="11"/>
       <c r="D1727" s="11" t="s">
-        <v>1840</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1728" ht="17" customHeight="1" spans="1:4">
@@ -22504,7 +22500,7 @@
       <c r="B1728" s="11"/>
       <c r="C1728" s="11"/>
       <c r="D1728" s="11" t="s">
-        <v>1796</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1729" ht="17" customHeight="1" spans="1:4">
@@ -22512,21 +22508,15 @@
       <c r="B1729" s="11"/>
       <c r="C1729" s="11"/>
       <c r="D1729" s="11" t="s">
-        <v>180</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1730" ht="17" customHeight="1" spans="1:4">
-      <c r="A1730" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1730" s="11" t="s">
-        <v>1841</v>
-      </c>
-      <c r="C1730" s="11" t="s">
+      <c r="A1730" s="11"/>
+      <c r="B1730" s="11"/>
+      <c r="C1730" s="11"/>
+      <c r="D1730" s="11" t="s">
         <v>1842</v>
-      </c>
-      <c r="D1730" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1731" ht="17" customHeight="1" spans="1:4">
@@ -22542,7 +22532,7 @@
       <c r="B1732" s="11"/>
       <c r="C1732" s="11"/>
       <c r="D1732" s="11" t="s">
-        <v>1844</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1733" ht="17" customHeight="1" spans="1:4">
@@ -22550,7 +22540,7 @@
       <c r="B1733" s="11"/>
       <c r="C1733" s="11"/>
       <c r="D1733" s="11" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1734" ht="17" customHeight="1" spans="1:4">
@@ -22558,7 +22548,7 @@
       <c r="B1734" s="11"/>
       <c r="C1734" s="11"/>
       <c r="D1734" s="11" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1735" ht="17" customHeight="1" spans="1:4">
@@ -22566,15 +22556,21 @@
       <c r="B1735" s="11"/>
       <c r="C1735" s="11"/>
       <c r="D1735" s="11" t="s">
-        <v>1288</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1736" ht="17" customHeight="1" spans="1:4">
-      <c r="A1736" s="11"/>
-      <c r="B1736" s="11"/>
-      <c r="C1736" s="11"/>
+      <c r="A1736" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1736" s="11" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1736" s="11" t="s">
+        <v>1847</v>
+      </c>
       <c r="D1736" s="11" t="s">
-        <v>1847</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1737" ht="17" customHeight="1" spans="1:4">
@@ -22582,7 +22578,7 @@
       <c r="B1737" s="11"/>
       <c r="C1737" s="11"/>
       <c r="D1737" s="11" t="s">
-        <v>1848</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1738" ht="17" customHeight="1" spans="1:4">
@@ -22590,21 +22586,15 @@
       <c r="B1738" s="11"/>
       <c r="C1738" s="11"/>
       <c r="D1738" s="11" t="s">
-        <v>116</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1739" ht="17" customHeight="1" spans="1:4">
-      <c r="A1739" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1739" s="11" t="s">
+      <c r="A1739" s="11"/>
+      <c r="B1739" s="11"/>
+      <c r="C1739" s="11"/>
+      <c r="D1739" s="11" t="s">
         <v>1849</v>
-      </c>
-      <c r="C1739" s="11" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D1739" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1740" ht="17" customHeight="1" spans="1:4">
@@ -22612,7 +22602,7 @@
       <c r="B1740" s="11"/>
       <c r="C1740" s="11"/>
       <c r="D1740" s="11" t="s">
-        <v>1799</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1741" ht="17" customHeight="1" spans="1:4">
@@ -22676,7 +22666,7 @@
       <c r="B1748" s="11"/>
       <c r="C1748" s="11"/>
       <c r="D1748" s="11" t="s">
-        <v>1858</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1749" ht="17" customHeight="1" spans="1:4">
@@ -22684,15 +22674,21 @@
       <c r="B1749" s="11"/>
       <c r="C1749" s="11"/>
       <c r="D1749" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1750" ht="17" customHeight="1" spans="1:4">
+      <c r="A1750" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1750" s="11" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C1750" s="11" t="s">
         <v>1859</v>
       </c>
-    </row>
-    <row r="1750" ht="17" customHeight="1" spans="1:4">
-      <c r="A1750" s="11"/>
-      <c r="B1750" s="11"/>
-      <c r="C1750" s="11"/>
       <c r="D1750" s="11" t="s">
-        <v>1860</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1751" ht="17" customHeight="1" spans="1:4">
@@ -22700,7 +22696,7 @@
       <c r="B1751" s="11"/>
       <c r="C1751" s="11"/>
       <c r="D1751" s="11" t="s">
-        <v>1780</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1752" ht="17" customHeight="1" spans="1:4">
@@ -22708,19 +22704,13 @@
       <c r="B1752" s="11"/>
       <c r="C1752" s="11"/>
       <c r="D1752" s="11" t="s">
-        <v>178</v>
+        <v>947</v>
       </c>
     </row>
     <row r="1753" ht="17" customHeight="1" spans="1:4">
-      <c r="A1753" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1753" s="11" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C1753" s="11" t="s">
-        <v>1862</v>
-      </c>
+      <c r="A1753" s="11"/>
+      <c r="B1753" s="11"/>
+      <c r="C1753" s="11"/>
       <c r="D1753" s="11" t="s">
         <v>1753</v>
       </c>
@@ -22730,7 +22720,7 @@
       <c r="B1754" s="11"/>
       <c r="C1754" s="11"/>
       <c r="D1754" s="11" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1755" ht="17" customHeight="1" spans="1:4">
@@ -22738,7 +22728,7 @@
       <c r="B1755" s="11"/>
       <c r="C1755" s="11"/>
       <c r="D1755" s="11" t="s">
-        <v>947</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1756" ht="17" customHeight="1" spans="1:4">
@@ -22746,7 +22736,7 @@
       <c r="B1756" s="11"/>
       <c r="C1756" s="11"/>
       <c r="D1756" s="11" t="s">
-        <v>1756</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1757" ht="17" customHeight="1" spans="1:4">
@@ -22778,7 +22768,7 @@
       <c r="B1760" s="11"/>
       <c r="C1760" s="11"/>
       <c r="D1760" s="11" t="s">
-        <v>1867</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="1761" ht="17" customHeight="1" spans="1:4">
@@ -22786,15 +22776,21 @@
       <c r="B1761" s="11"/>
       <c r="C1761" s="11"/>
       <c r="D1761" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1762" ht="17" customHeight="1" spans="1:4">
+      <c r="A1762" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1762" s="11" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C1762" s="11" t="s">
         <v>1868</v>
       </c>
-    </row>
-    <row r="1762" ht="17" customHeight="1" spans="1:4">
-      <c r="A1762" s="11"/>
-      <c r="B1762" s="11"/>
-      <c r="C1762" s="11"/>
       <c r="D1762" s="11" t="s">
-        <v>1869</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1763" ht="17" customHeight="1" spans="1:4">
@@ -22802,7 +22798,7 @@
       <c r="B1763" s="11"/>
       <c r="C1763" s="11"/>
       <c r="D1763" s="11" t="s">
-        <v>1763</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1764" ht="17" customHeight="1" spans="1:4">
@@ -22810,21 +22806,15 @@
       <c r="B1764" s="11"/>
       <c r="C1764" s="11"/>
       <c r="D1764" s="11" t="s">
-        <v>148</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1765" ht="17" customHeight="1" spans="1:4">
-      <c r="A1765" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1765" s="11" t="s">
-        <v>1870</v>
-      </c>
-      <c r="C1765" s="11" t="s">
+      <c r="A1765" s="11"/>
+      <c r="B1765" s="11"/>
+      <c r="C1765" s="11"/>
+      <c r="D1765" s="11" t="s">
         <v>1871</v>
-      </c>
-      <c r="D1765" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1766" ht="17" customHeight="1" spans="1:4">
@@ -22896,7 +22886,7 @@
       <c r="B1774" s="11"/>
       <c r="C1774" s="11"/>
       <c r="D1774" s="11" t="s">
-        <v>1880</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1775" ht="17" customHeight="1" spans="1:4">
@@ -22904,15 +22894,21 @@
       <c r="B1775" s="11"/>
       <c r="C1775" s="11"/>
       <c r="D1775" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1776" ht="17" customHeight="1" spans="1:4">
+      <c r="A1776" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1776" s="11" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C1776" s="11" t="s">
         <v>1881</v>
       </c>
-    </row>
-    <row r="1776" ht="17" customHeight="1" spans="1:4">
-      <c r="A1776" s="11"/>
-      <c r="B1776" s="11"/>
-      <c r="C1776" s="11"/>
       <c r="D1776" s="11" t="s">
-        <v>1882</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1777" ht="17" customHeight="1" spans="1:4">
@@ -22920,7 +22916,7 @@
       <c r="B1777" s="11"/>
       <c r="C1777" s="11"/>
       <c r="D1777" s="11" t="s">
-        <v>1780</v>
+        <v>664</v>
       </c>
     </row>
     <row r="1778" ht="17" customHeight="1" spans="1:4">
@@ -22928,21 +22924,15 @@
       <c r="B1778" s="11"/>
       <c r="C1778" s="11"/>
       <c r="D1778" s="11" t="s">
-        <v>178</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1779" ht="17" customHeight="1" spans="1:4">
-      <c r="A1779" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1779" s="11" t="s">
+      <c r="A1779" s="11"/>
+      <c r="B1779" s="11"/>
+      <c r="C1779" s="11"/>
+      <c r="D1779" s="11" t="s">
         <v>1883</v>
-      </c>
-      <c r="C1779" s="11" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D1779" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1780" ht="17" customHeight="1" spans="1:4">
@@ -22950,7 +22940,7 @@
       <c r="B1780" s="11"/>
       <c r="C1780" s="11"/>
       <c r="D1780" s="11" t="s">
-        <v>664</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1781" ht="17" customHeight="1" spans="1:4">
@@ -23022,7 +23012,7 @@
       <c r="B1789" s="11"/>
       <c r="C1789" s="11"/>
       <c r="D1789" s="11" t="s">
-        <v>1893</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1790" ht="17" customHeight="1" spans="1:4">
@@ -23030,15 +23020,21 @@
       <c r="B1790" s="11"/>
       <c r="C1790" s="11"/>
       <c r="D1790" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1791" ht="17" customHeight="1" spans="1:4">
+      <c r="A1791" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1791" s="11" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C1791" s="11" t="s">
         <v>1894</v>
       </c>
-    </row>
-    <row r="1791" ht="17" customHeight="1" spans="1:4">
-      <c r="A1791" s="11"/>
-      <c r="B1791" s="11"/>
-      <c r="C1791" s="11"/>
       <c r="D1791" s="11" t="s">
-        <v>1895</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1792" ht="17" customHeight="1" spans="1:4">
@@ -23046,7 +23042,7 @@
       <c r="B1792" s="11"/>
       <c r="C1792" s="11"/>
       <c r="D1792" s="11" t="s">
-        <v>1766</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1793" ht="17" customHeight="1" spans="1:4">
@@ -23054,21 +23050,15 @@
       <c r="B1793" s="11"/>
       <c r="C1793" s="11"/>
       <c r="D1793" s="11" t="s">
-        <v>87</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1794" ht="17" customHeight="1" spans="1:4">
-      <c r="A1794" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1794" s="11" t="s">
+      <c r="A1794" s="11"/>
+      <c r="B1794" s="11"/>
+      <c r="C1794" s="11"/>
+      <c r="D1794" s="11" t="s">
         <v>1896</v>
-      </c>
-      <c r="C1794" s="11" t="s">
-        <v>1897</v>
-      </c>
-      <c r="D1794" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1795" ht="17" customHeight="1" spans="1:4">
@@ -23076,7 +23066,7 @@
       <c r="B1795" s="11"/>
       <c r="C1795" s="11"/>
       <c r="D1795" s="11" t="s">
-        <v>1799</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1796" ht="17" customHeight="1" spans="1:4">
@@ -23140,15 +23130,21 @@
       <c r="B1803" s="11"/>
       <c r="C1803" s="11"/>
       <c r="D1803" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1804" ht="17" customHeight="1" spans="1:4">
+      <c r="A1804" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1804" s="11" t="s">
         <v>1905</v>
       </c>
-    </row>
-    <row r="1804" ht="17" customHeight="1" spans="1:4">
-      <c r="A1804" s="11"/>
-      <c r="B1804" s="11"/>
-      <c r="C1804" s="11"/>
+      <c r="C1804" s="11" t="s">
+        <v>1906</v>
+      </c>
       <c r="D1804" s="11" t="s">
-        <v>1906</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1805" ht="17" customHeight="1" spans="1:4">
@@ -23156,7 +23152,7 @@
       <c r="B1805" s="11"/>
       <c r="C1805" s="11"/>
       <c r="D1805" s="11" t="s">
-        <v>1907</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1806" ht="17" customHeight="1" spans="1:4">
@@ -23164,21 +23160,15 @@
       <c r="B1806" s="11"/>
       <c r="C1806" s="11"/>
       <c r="D1806" s="11" t="s">
-        <v>675</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1807" ht="17" customHeight="1" spans="1:4">
-      <c r="A1807" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1807" s="11" t="s">
-        <v>1908</v>
-      </c>
-      <c r="C1807" s="11" t="s">
-        <v>1909</v>
-      </c>
+      <c r="A1807" s="11"/>
+      <c r="B1807" s="11"/>
+      <c r="C1807" s="11"/>
       <c r="D1807" s="11" t="s">
-        <v>1753</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1808" ht="17" customHeight="1" spans="1:4">
@@ -23186,7 +23176,7 @@
       <c r="B1808" s="11"/>
       <c r="C1808" s="11"/>
       <c r="D1808" s="11" t="s">
-        <v>1783</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1809" ht="17" customHeight="1" spans="1:4">
@@ -23194,7 +23184,7 @@
       <c r="B1809" s="11"/>
       <c r="C1809" s="11"/>
       <c r="D1809" s="11" t="s">
-        <v>1816</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1810" ht="17" customHeight="1" spans="1:4">
@@ -23298,15 +23288,21 @@
       <c r="B1822" s="11"/>
       <c r="C1822" s="11"/>
       <c r="D1822" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1823" ht="17" customHeight="1" spans="1:4">
+      <c r="A1823" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1823" s="11" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="1823" ht="17" customHeight="1" spans="1:4">
-      <c r="A1823" s="11"/>
-      <c r="B1823" s="11"/>
-      <c r="C1823" s="11"/>
+      <c r="C1823" s="11" t="s">
+        <v>1923</v>
+      </c>
       <c r="D1823" s="11" t="s">
-        <v>1923</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1824" ht="17" customHeight="1" spans="1:4">
@@ -23314,7 +23310,7 @@
       <c r="B1824" s="11"/>
       <c r="C1824" s="11"/>
       <c r="D1824" s="11" t="s">
-        <v>1924</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1825" ht="17" customHeight="1" spans="1:4">
@@ -23322,21 +23318,15 @@
       <c r="B1825" s="11"/>
       <c r="C1825" s="11"/>
       <c r="D1825" s="11" t="s">
-        <v>25</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1826" ht="17" customHeight="1" spans="1:4">
-      <c r="A1826" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1826" s="11" t="s">
+      <c r="A1826" s="11"/>
+      <c r="B1826" s="11"/>
+      <c r="C1826" s="11"/>
+      <c r="D1826" s="11" t="s">
         <v>1925</v>
-      </c>
-      <c r="C1826" s="11" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D1826" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1827" ht="17" customHeight="1" spans="1:4">
@@ -23344,7 +23334,7 @@
       <c r="B1827" s="11"/>
       <c r="C1827" s="11"/>
       <c r="D1827" s="11" t="s">
-        <v>1843</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1828" ht="17" customHeight="1" spans="1:4">
@@ -23360,15 +23350,21 @@
       <c r="B1829" s="11"/>
       <c r="C1829" s="11"/>
       <c r="D1829" s="11" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="1830" ht="17" customHeight="1" spans="1:4">
+      <c r="A1830" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1830" s="11" t="s">
         <v>1928</v>
       </c>
-    </row>
-    <row r="1830" ht="17" customHeight="1" spans="1:4">
-      <c r="A1830" s="11"/>
-      <c r="B1830" s="11"/>
-      <c r="C1830" s="11"/>
+      <c r="C1830" s="11" t="s">
+        <v>1929</v>
+      </c>
       <c r="D1830" s="11" t="s">
-        <v>1929</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1831" ht="17" customHeight="1" spans="1:4">
@@ -23376,7 +23372,7 @@
       <c r="B1831" s="11"/>
       <c r="C1831" s="11"/>
       <c r="D1831" s="11" t="s">
-        <v>1930</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1832" ht="17" customHeight="1" spans="1:4">
@@ -23384,21 +23380,15 @@
       <c r="B1832" s="11"/>
       <c r="C1832" s="11"/>
       <c r="D1832" s="11" t="s">
-        <v>419</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1833" ht="17" customHeight="1" spans="1:4">
-      <c r="A1833" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1833" s="11" t="s">
+      <c r="A1833" s="11"/>
+      <c r="B1833" s="11"/>
+      <c r="C1833" s="11"/>
+      <c r="D1833" s="11" t="s">
         <v>1931</v>
-      </c>
-      <c r="C1833" s="11" t="s">
-        <v>1932</v>
-      </c>
-      <c r="D1833" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1834" ht="17" customHeight="1" spans="1:4">
@@ -23406,7 +23396,7 @@
       <c r="B1834" s="11"/>
       <c r="C1834" s="11"/>
       <c r="D1834" s="11" t="s">
-        <v>1843</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1835" ht="17" customHeight="1" spans="1:4">
@@ -23414,15 +23404,21 @@
       <c r="B1835" s="11"/>
       <c r="C1835" s="11"/>
       <c r="D1835" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1836" ht="17" customHeight="1" spans="1:4">
+      <c r="A1836" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1836" s="11" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C1836" s="11" t="s">
         <v>1933</v>
       </c>
-    </row>
-    <row r="1836" ht="17" customHeight="1" spans="1:4">
-      <c r="A1836" s="11"/>
-      <c r="B1836" s="11"/>
-      <c r="C1836" s="11"/>
       <c r="D1836" s="11" t="s">
-        <v>1934</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1837" ht="17" customHeight="1" spans="1:4">
@@ -23430,7 +23426,7 @@
       <c r="B1837" s="11"/>
       <c r="C1837" s="11"/>
       <c r="D1837" s="11" t="s">
-        <v>1772</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1838" ht="17" customHeight="1" spans="1:4">
@@ -23438,21 +23434,15 @@
       <c r="B1838" s="11"/>
       <c r="C1838" s="11"/>
       <c r="D1838" s="11" t="s">
-        <v>170</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1839" ht="17" customHeight="1" spans="1:4">
-      <c r="A1839" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1839" s="11" t="s">
+      <c r="A1839" s="11"/>
+      <c r="B1839" s="11"/>
+      <c r="C1839" s="11"/>
+      <c r="D1839" s="11" t="s">
         <v>1935</v>
-      </c>
-      <c r="C1839" s="11" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D1839" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1840" ht="17" customHeight="1" spans="1:4">
@@ -23460,7 +23450,7 @@
       <c r="B1840" s="11"/>
       <c r="C1840" s="11"/>
       <c r="D1840" s="11" t="s">
-        <v>1843</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1841" ht="17" customHeight="1" spans="1:4">
@@ -23468,7 +23458,7 @@
       <c r="B1841" s="11"/>
       <c r="C1841" s="11"/>
       <c r="D1841" s="11" t="s">
-        <v>1937</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1842" ht="17" customHeight="1" spans="1:4">
@@ -23476,15 +23466,21 @@
       <c r="B1842" s="11"/>
       <c r="C1842" s="11"/>
       <c r="D1842" s="11" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="1843" ht="17" customHeight="1" spans="1:4">
+      <c r="A1843" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1843" s="11" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C1843" s="11" t="s">
         <v>1938</v>
       </c>
-    </row>
-    <row r="1843" ht="17" customHeight="1" spans="1:4">
-      <c r="A1843" s="11"/>
-      <c r="B1843" s="11"/>
-      <c r="C1843" s="11"/>
       <c r="D1843" s="11" t="s">
-        <v>1939</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1844" ht="17" customHeight="1" spans="1:4">
@@ -23492,7 +23488,7 @@
       <c r="B1844" s="11"/>
       <c r="C1844" s="11"/>
       <c r="D1844" s="11" t="s">
-        <v>1930</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1845" ht="17" customHeight="1" spans="1:4">
@@ -23500,21 +23496,15 @@
       <c r="B1845" s="11"/>
       <c r="C1845" s="11"/>
       <c r="D1845" s="11" t="s">
-        <v>419</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1846" ht="17" customHeight="1" spans="1:4">
-      <c r="A1846" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1846" s="11" t="s">
+      <c r="A1846" s="11"/>
+      <c r="B1846" s="11"/>
+      <c r="C1846" s="11"/>
+      <c r="D1846" s="11" t="s">
         <v>1940</v>
-      </c>
-      <c r="C1846" s="11" t="s">
-        <v>1941</v>
-      </c>
-      <c r="D1846" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1847" ht="17" customHeight="1" spans="1:4">
@@ -23522,7 +23512,7 @@
       <c r="B1847" s="11"/>
       <c r="C1847" s="11"/>
       <c r="D1847" s="11" t="s">
-        <v>1843</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1848" ht="17" customHeight="1" spans="1:4">
@@ -23530,15 +23520,21 @@
       <c r="B1848" s="11"/>
       <c r="C1848" s="11"/>
       <c r="D1848" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="1849" ht="17" customHeight="1" spans="1:4">
+      <c r="A1849" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1849" s="11" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C1849" s="11" t="s">
         <v>1942</v>
       </c>
-    </row>
-    <row r="1849" ht="17" customHeight="1" spans="1:4">
-      <c r="A1849" s="11"/>
-      <c r="B1849" s="11"/>
-      <c r="C1849" s="11"/>
       <c r="D1849" s="11" t="s">
-        <v>1943</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1850" ht="17" customHeight="1" spans="1:4">
@@ -23546,7 +23542,7 @@
       <c r="B1850" s="11"/>
       <c r="C1850" s="11"/>
       <c r="D1850" s="11" t="s">
-        <v>1772</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1851" ht="17" customHeight="1" spans="1:4">
@@ -23554,21 +23550,15 @@
       <c r="B1851" s="11"/>
       <c r="C1851" s="11"/>
       <c r="D1851" s="11" t="s">
-        <v>170</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1852" ht="17" customHeight="1" spans="1:4">
-      <c r="A1852" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1852" s="11" t="s">
+      <c r="A1852" s="11"/>
+      <c r="B1852" s="11"/>
+      <c r="C1852" s="11"/>
+      <c r="D1852" s="11" t="s">
         <v>1944</v>
-      </c>
-      <c r="C1852" s="11" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D1852" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1853" ht="17" customHeight="1" spans="1:4">
@@ -23576,7 +23566,7 @@
       <c r="B1853" s="11"/>
       <c r="C1853" s="11"/>
       <c r="D1853" s="11" t="s">
-        <v>1843</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1854" ht="17" customHeight="1" spans="1:4">
@@ -23616,15 +23606,21 @@
       <c r="B1858" s="11"/>
       <c r="C1858" s="11"/>
       <c r="D1858" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1859" ht="17" customHeight="1" spans="1:4">
+      <c r="A1859" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1859" s="11" t="s">
         <v>1950</v>
       </c>
-    </row>
-    <row r="1859" ht="17" customHeight="1" spans="1:4">
-      <c r="A1859" s="11"/>
-      <c r="B1859" s="11"/>
-      <c r="C1859" s="11"/>
+      <c r="C1859" s="11" t="s">
+        <v>1951</v>
+      </c>
       <c r="D1859" s="11" t="s">
-        <v>1951</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1860" ht="17" customHeight="1" spans="1:4">
@@ -23632,7 +23628,7 @@
       <c r="B1860" s="11"/>
       <c r="C1860" s="11"/>
       <c r="D1860" s="11" t="s">
-        <v>1952</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1861" ht="17" customHeight="1" spans="1:4">
@@ -23640,21 +23636,15 @@
       <c r="B1861" s="11"/>
       <c r="C1861" s="11"/>
       <c r="D1861" s="11" t="s">
-        <v>71</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1862" ht="17" customHeight="1" spans="1:4">
-      <c r="A1862" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1862" s="11" t="s">
-        <v>1953</v>
-      </c>
-      <c r="C1862" s="11" t="s">
-        <v>1954</v>
-      </c>
+      <c r="A1862" s="11"/>
+      <c r="B1862" s="11"/>
+      <c r="C1862" s="11"/>
       <c r="D1862" s="11" t="s">
-        <v>1753</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1863" ht="17" customHeight="1" spans="1:4">
@@ -23662,7 +23652,7 @@
       <c r="B1863" s="11"/>
       <c r="C1863" s="11"/>
       <c r="D1863" s="11" t="s">
-        <v>1799</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1864" ht="17" customHeight="1" spans="1:4">
@@ -23670,7 +23660,7 @@
       <c r="B1864" s="11"/>
       <c r="C1864" s="11"/>
       <c r="D1864" s="11" t="s">
-        <v>1851</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1865" ht="17" customHeight="1" spans="1:4">
@@ -23686,7 +23676,7 @@
       <c r="B1866" s="11"/>
       <c r="C1866" s="11"/>
       <c r="D1866" s="11" t="s">
-        <v>1956</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1867" ht="17" customHeight="1" spans="1:4">
@@ -23694,7 +23684,7 @@
       <c r="B1867" s="11"/>
       <c r="C1867" s="11"/>
       <c r="D1867" s="11" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1868" ht="17" customHeight="1" spans="1:4">
@@ -23702,7 +23692,7 @@
       <c r="B1868" s="11"/>
       <c r="C1868" s="11"/>
       <c r="D1868" s="11" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1869" ht="17" customHeight="1" spans="1:4">
@@ -23710,7 +23700,7 @@
       <c r="B1869" s="11"/>
       <c r="C1869" s="11"/>
       <c r="D1869" s="11" t="s">
-        <v>1805</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="1870" ht="17" customHeight="1" spans="1:4">
@@ -23718,15 +23708,21 @@
       <c r="B1870" s="11"/>
       <c r="C1870" s="11"/>
       <c r="D1870" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1871" ht="17" customHeight="1" spans="1:4">
+      <c r="A1871" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B1871" s="11" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C1871" s="11" t="s">
         <v>1959</v>
       </c>
-    </row>
-    <row r="1871" ht="17" customHeight="1" spans="1:4">
-      <c r="A1871" s="11"/>
-      <c r="B1871" s="11"/>
-      <c r="C1871" s="11"/>
       <c r="D1871" s="11" t="s">
-        <v>1960</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1872" ht="17" customHeight="1" spans="1:4">
@@ -23734,7 +23730,7 @@
       <c r="B1872" s="11"/>
       <c r="C1872" s="11"/>
       <c r="D1872" s="11" t="s">
-        <v>1763</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1873" ht="17" customHeight="1" spans="1:4">
@@ -23742,21 +23738,15 @@
       <c r="B1873" s="11"/>
       <c r="C1873" s="11"/>
       <c r="D1873" s="11" t="s">
-        <v>148</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1874" ht="17" customHeight="1" spans="1:4">
-      <c r="A1874" s="11" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B1874" s="11" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C1874" s="11" t="s">
+      <c r="A1874" s="11"/>
+      <c r="B1874" s="11"/>
+      <c r="C1874" s="11"/>
+      <c r="D1874" s="11" t="s">
         <v>1962</v>
-      </c>
-      <c r="D1874" s="11" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1875" ht="17" customHeight="1" spans="1:4">
@@ -23804,7 +23794,7 @@
       <c r="B1880" s="11"/>
       <c r="C1880" s="11"/>
       <c r="D1880" s="11" t="s">
-        <v>1968</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1881" ht="17" customHeight="1" spans="1:4">
@@ -23812,15 +23802,21 @@
       <c r="B1881" s="11"/>
       <c r="C1881" s="11"/>
       <c r="D1881" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1882" ht="17" customHeight="1" spans="1:4">
+      <c r="A1882" s="11" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1882" s="11" t="s">
         <v>1969</v>
       </c>
-    </row>
-    <row r="1882" ht="17" customHeight="1" spans="1:4">
-      <c r="A1882" s="11"/>
-      <c r="B1882" s="11"/>
-      <c r="C1882" s="11"/>
+      <c r="C1882" s="11" t="s">
+        <v>1970</v>
+      </c>
       <c r="D1882" s="11" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1883" ht="17" customHeight="1" spans="1:4">
@@ -23828,7 +23824,7 @@
       <c r="B1883" s="11"/>
       <c r="C1883" s="11"/>
       <c r="D1883" s="11" t="s">
-        <v>1791</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1884" ht="17" customHeight="1" spans="1:4">
@@ -23836,19 +23832,13 @@
       <c r="B1884" s="11"/>
       <c r="C1884" s="11"/>
       <c r="D1884" s="11" t="s">
-        <v>211</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1885" ht="17" customHeight="1" spans="1:4">
-      <c r="A1885" s="11" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B1885" s="11" t="s">
-        <v>1972</v>
-      </c>
-      <c r="C1885" s="11" t="s">
-        <v>1973</v>
-      </c>
+      <c r="A1885" s="11"/>
+      <c r="B1885" s="11"/>
+      <c r="C1885" s="11"/>
       <c r="D1885" s="11" t="s">
         <v>1974</v>
       </c>
@@ -23866,7 +23856,7 @@
       <c r="B1887" s="11"/>
       <c r="C1887" s="11"/>
       <c r="D1887" s="11" t="s">
-        <v>1976</v>
+        <v>668</v>
       </c>
     </row>
     <row r="1888" ht="17" customHeight="1" spans="1:4">
@@ -23874,7 +23864,7 @@
       <c r="B1888" s="11"/>
       <c r="C1888" s="11"/>
       <c r="D1888" s="11" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1889" ht="17" customHeight="1" spans="1:4">
@@ -23882,7 +23872,7 @@
       <c r="B1889" s="11"/>
       <c r="C1889" s="11"/>
       <c r="D1889" s="11" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1890" ht="17" customHeight="1" spans="1:4">
@@ -23890,7 +23880,7 @@
       <c r="B1890" s="11"/>
       <c r="C1890" s="11"/>
       <c r="D1890" s="11" t="s">
-        <v>668</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1891" ht="17" customHeight="1" spans="1:4">
@@ -23922,15 +23912,21 @@
       <c r="B1894" s="11"/>
       <c r="C1894" s="11"/>
       <c r="D1894" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1895" ht="17" customHeight="1" spans="1:4">
+      <c r="A1895" s="11" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1895" s="11" t="s">
         <v>1982</v>
       </c>
-    </row>
-    <row r="1895" ht="17" customHeight="1" spans="1:4">
-      <c r="A1895" s="11"/>
-      <c r="B1895" s="11"/>
-      <c r="C1895" s="11"/>
+      <c r="C1895" s="11" t="s">
+        <v>1983</v>
+      </c>
       <c r="D1895" s="11" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1896" ht="17" customHeight="1" spans="1:4">
@@ -23938,7 +23934,7 @@
       <c r="B1896" s="11"/>
       <c r="C1896" s="11"/>
       <c r="D1896" s="11" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1897" ht="17" customHeight="1" spans="1:4">
@@ -23946,19 +23942,13 @@
       <c r="B1897" s="11"/>
       <c r="C1897" s="11"/>
       <c r="D1897" s="11" t="s">
-        <v>675</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1898" ht="17" customHeight="1" spans="1:4">
-      <c r="A1898" s="11" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B1898" s="11" t="s">
-        <v>1985</v>
-      </c>
-      <c r="C1898" s="11" t="s">
-        <v>1986</v>
-      </c>
+      <c r="A1898" s="11"/>
+      <c r="B1898" s="11"/>
+      <c r="C1898" s="11"/>
       <c r="D1898" s="11" t="s">
         <v>1987</v>
       </c>
@@ -24056,15 +24046,21 @@
       <c r="B1910" s="11"/>
       <c r="C1910" s="11"/>
       <c r="D1910" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1911" ht="17" customHeight="1" spans="1:4">
+      <c r="A1911" s="11" t="s">
         <v>1999</v>
       </c>
-    </row>
-    <row r="1911" ht="17" customHeight="1" spans="1:4">
-      <c r="A1911" s="11"/>
-      <c r="B1911" s="11"/>
-      <c r="C1911" s="11"/>
+      <c r="B1911" s="11" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C1911" s="11" t="s">
+        <v>2001</v>
+      </c>
       <c r="D1911" s="11" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1912" ht="17" customHeight="1" spans="1:4">
@@ -24072,7 +24068,7 @@
       <c r="B1912" s="11"/>
       <c r="C1912" s="11"/>
       <c r="D1912" s="11" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="1913" ht="17" customHeight="1" spans="1:4">
@@ -24080,19 +24076,13 @@
       <c r="B1913" s="11"/>
       <c r="C1913" s="11"/>
       <c r="D1913" s="11" t="s">
-        <v>87</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1914" ht="17" customHeight="1" spans="1:4">
-      <c r="A1914" s="11" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B1914" s="11" t="s">
-        <v>2003</v>
-      </c>
-      <c r="C1914" s="11" t="s">
-        <v>2004</v>
-      </c>
+      <c r="A1914" s="11"/>
+      <c r="B1914" s="11"/>
+      <c r="C1914" s="11"/>
       <c r="D1914" s="11" t="s">
         <v>2005</v>
       </c>
@@ -24110,7 +24100,7 @@
       <c r="B1916" s="11"/>
       <c r="C1916" s="11"/>
       <c r="D1916" s="11" t="s">
-        <v>2007</v>
+        <v>668</v>
       </c>
     </row>
     <row r="1917" ht="17" customHeight="1" spans="1:4">
@@ -24118,7 +24108,7 @@
       <c r="B1917" s="11"/>
       <c r="C1917" s="11"/>
       <c r="D1917" s="11" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1918" ht="17" customHeight="1" spans="1:4">
@@ -24126,7 +24116,7 @@
       <c r="B1918" s="11"/>
       <c r="C1918" s="11"/>
       <c r="D1918" s="11" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1919" ht="17" customHeight="1" spans="1:4">
@@ -24134,7 +24124,7 @@
       <c r="B1919" s="11"/>
       <c r="C1919" s="11"/>
       <c r="D1919" s="11" t="s">
-        <v>668</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1920" ht="17" customHeight="1" spans="1:4">
@@ -24214,15 +24204,21 @@
       <c r="B1929" s="11"/>
       <c r="C1929" s="11"/>
       <c r="D1929" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1930" ht="17" customHeight="1" spans="1:4">
+      <c r="A1930" s="11" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1930" s="11" t="s">
         <v>2019</v>
       </c>
-    </row>
-    <row r="1930" ht="17" customHeight="1" spans="1:4">
-      <c r="A1930" s="11"/>
-      <c r="B1930" s="11"/>
-      <c r="C1930" s="11"/>
+      <c r="C1930" s="11" t="s">
+        <v>2020</v>
+      </c>
       <c r="D1930" s="11" t="s">
-        <v>2020</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1931" ht="17" customHeight="1" spans="1:4">
@@ -24238,21 +24234,15 @@
       <c r="B1932" s="11"/>
       <c r="C1932" s="11"/>
       <c r="D1932" s="11" t="s">
-        <v>25</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1933" ht="17" customHeight="1" spans="1:4">
-      <c r="A1933" s="11" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B1933" s="11" t="s">
-        <v>2022</v>
-      </c>
-      <c r="C1933" s="11" t="s">
+      <c r="A1933" s="11"/>
+      <c r="B1933" s="11"/>
+      <c r="C1933" s="11"/>
+      <c r="D1933" s="11" t="s">
         <v>2023</v>
-      </c>
-      <c r="D1933" s="11" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="1934" ht="17" customHeight="1" spans="1:4">
@@ -24308,15 +24298,21 @@
       <c r="B1940" s="11"/>
       <c r="C1940" s="11"/>
       <c r="D1940" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1941" ht="17" customHeight="1" spans="1:4">
+      <c r="A1941" s="11" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1941" s="11" t="s">
         <v>2030</v>
       </c>
-    </row>
-    <row r="1941" ht="17" customHeight="1" spans="1:4">
-      <c r="A1941" s="11"/>
-      <c r="B1941" s="11"/>
-      <c r="C1941" s="11"/>
+      <c r="C1941" s="11" t="s">
+        <v>2031</v>
+      </c>
       <c r="D1941" s="11" t="s">
-        <v>2031</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1942" ht="17" customHeight="1" spans="1:4">
@@ -24324,7 +24320,7 @@
       <c r="B1942" s="11"/>
       <c r="C1942" s="11"/>
       <c r="D1942" s="11" t="s">
-        <v>2032</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1943" ht="17" customHeight="1" spans="1:4">
@@ -24332,21 +24328,15 @@
       <c r="B1943" s="11"/>
       <c r="C1943" s="11"/>
       <c r="D1943" s="11" t="s">
-        <v>211</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1944" ht="17" customHeight="1" spans="1:4">
-      <c r="A1944" s="11" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B1944" s="11" t="s">
+      <c r="A1944" s="11"/>
+      <c r="B1944" s="11"/>
+      <c r="C1944" s="11"/>
+      <c r="D1944" s="11" t="s">
         <v>2033</v>
-      </c>
-      <c r="C1944" s="11" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D1944" s="11" t="s">
-        <v>2005</v>
       </c>
     </row>
     <row r="1945" ht="17" customHeight="1" spans="1:4">
@@ -24354,7 +24344,7 @@
       <c r="B1945" s="11"/>
       <c r="C1945" s="11"/>
       <c r="D1945" s="11" t="s">
-        <v>1483</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1946" ht="17" customHeight="1" spans="1:4">
@@ -24418,7 +24408,7 @@
       <c r="B1953" s="11"/>
       <c r="C1953" s="11"/>
       <c r="D1953" s="11" t="s">
-        <v>2042</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1954" ht="17" customHeight="1" spans="1:4">
@@ -24426,15 +24416,21 @@
       <c r="B1954" s="11"/>
       <c r="C1954" s="11"/>
       <c r="D1954" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1955" ht="17" customHeight="1" spans="1:4">
+      <c r="A1955" s="11" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1955" s="11" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C1955" s="11" t="s">
         <v>2043</v>
       </c>
-    </row>
-    <row r="1955" ht="17" customHeight="1" spans="1:4">
-      <c r="A1955" s="11"/>
-      <c r="B1955" s="11"/>
-      <c r="C1955" s="11"/>
       <c r="D1955" s="11" t="s">
-        <v>2044</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1956" ht="17" customHeight="1" spans="1:4">
@@ -24442,7 +24438,7 @@
       <c r="B1956" s="11"/>
       <c r="C1956" s="11"/>
       <c r="D1956" s="11" t="s">
-        <v>177</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1957" ht="17" customHeight="1" spans="1:4">
@@ -24450,21 +24446,15 @@
       <c r="B1957" s="11"/>
       <c r="C1957" s="11"/>
       <c r="D1957" s="11" t="s">
-        <v>178</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1958" ht="17" customHeight="1" spans="1:4">
-      <c r="A1958" s="11" t="s">
-        <v>2002</v>
-      </c>
-      <c r="B1958" s="11" t="s">
-        <v>2045</v>
-      </c>
-      <c r="C1958" s="11" t="s">
-        <v>2046</v>
-      </c>
+      <c r="A1958" s="11"/>
+      <c r="B1958" s="11"/>
+      <c r="C1958" s="11"/>
       <c r="D1958" s="11" t="s">
-        <v>2005</v>
+        <v>426</v>
       </c>
     </row>
     <row r="1959" ht="17" customHeight="1" spans="1:4">
@@ -24472,7 +24462,7 @@
       <c r="B1959" s="11"/>
       <c r="C1959" s="11"/>
       <c r="D1959" s="11" t="s">
-        <v>1483</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1960" ht="17" customHeight="1" spans="1:4">
@@ -24480,7 +24470,7 @@
       <c r="B1960" s="11"/>
       <c r="C1960" s="11"/>
       <c r="D1960" s="11" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1961" ht="17" customHeight="1" spans="1:4">
@@ -24488,7 +24478,7 @@
       <c r="B1961" s="11"/>
       <c r="C1961" s="11"/>
       <c r="D1961" s="11" t="s">
-        <v>426</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1962" ht="17" customHeight="1" spans="1:4">
@@ -24552,15 +24542,21 @@
       <c r="B1969" s="11"/>
       <c r="C1969" s="11"/>
       <c r="D1969" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1970" ht="17" customHeight="1" spans="1:4">
+      <c r="A1970" s="11" t="s">
         <v>2055</v>
       </c>
-    </row>
-    <row r="1970" ht="17" customHeight="1" spans="1:4">
-      <c r="A1970" s="11"/>
-      <c r="B1970" s="11"/>
-      <c r="C1970" s="11"/>
+      <c r="B1970" s="11" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C1970" s="11" t="s">
+        <v>2057</v>
+      </c>
       <c r="D1970" s="11" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1971" ht="17" customHeight="1" spans="1:4">
@@ -24568,7 +24564,7 @@
       <c r="B1971" s="11"/>
       <c r="C1971" s="11"/>
       <c r="D1971" s="11" t="s">
-        <v>2057</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1972" ht="17" customHeight="1" spans="1:4">
@@ -24576,21 +24572,15 @@
       <c r="B1972" s="11"/>
       <c r="C1972" s="11"/>
       <c r="D1972" s="11" t="s">
-        <v>164</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1973" ht="17" customHeight="1" spans="1:4">
-      <c r="A1973" s="11" t="s">
-        <v>2058</v>
-      </c>
-      <c r="B1973" s="11" t="s">
-        <v>2059</v>
-      </c>
-      <c r="C1973" s="11" t="s">
+      <c r="A1973" s="11"/>
+      <c r="B1973" s="11"/>
+      <c r="C1973" s="11"/>
+      <c r="D1973" s="11" t="s">
         <v>2060</v>
-      </c>
-      <c r="D1973" s="11" t="s">
-        <v>2061</v>
       </c>
     </row>
     <row r="1974" ht="17" customHeight="1" spans="1:4">
@@ -24598,7 +24588,7 @@
       <c r="B1974" s="11"/>
       <c r="C1974" s="11"/>
       <c r="D1974" s="11" t="s">
-        <v>712</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1975" ht="17" customHeight="1" spans="1:4">
@@ -24638,43 +24628,43 @@
       <c r="B1979" s="11"/>
       <c r="C1979" s="11"/>
       <c r="D1979" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1980" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1980" s="12" t="s">
         <v>2066</v>
       </c>
-    </row>
-    <row r="1980" ht="17" customHeight="1" spans="1:4">
-      <c r="A1980" s="11"/>
-      <c r="B1980" s="11"/>
-      <c r="C1980" s="11"/>
-      <c r="D1980" s="11" t="s">
+      <c r="B1980" s="12" t="s">
         <v>2067</v>
       </c>
-    </row>
-    <row r="1981" ht="17" customHeight="1" spans="1:4">
-      <c r="A1981" s="11"/>
-      <c r="B1981" s="11"/>
-      <c r="C1981" s="11"/>
-      <c r="D1981" s="11" t="s">
+      <c r="C1980" s="12" t="s">
         <v>2068</v>
       </c>
-    </row>
-    <row r="1982" ht="17" customHeight="1" spans="1:4">
-      <c r="A1982" s="11"/>
-      <c r="B1982" s="11"/>
-      <c r="C1982" s="11"/>
-      <c r="D1982" s="11" t="s">
-        <v>71</v>
+      <c r="D1980" s="12" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="1981" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1981" s="12"/>
+      <c r="B1981" s="12"/>
+      <c r="C1981" s="12"/>
+      <c r="D1981" s="12" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="1982" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1982" s="12"/>
+      <c r="B1982" s="12"/>
+      <c r="C1982" s="12"/>
+      <c r="D1982" s="12" t="s">
+        <v>2071</v>
       </c>
     </row>
     <row r="1983" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1983" s="12" t="s">
-        <v>2069</v>
-      </c>
-      <c r="B1983" s="12" t="s">
-        <v>2070</v>
-      </c>
-      <c r="C1983" s="12" t="s">
-        <v>2071</v>
-      </c>
+      <c r="A1983" s="12"/>
+      <c r="B1983" s="12"/>
+      <c r="C1983" s="12"/>
       <c r="D1983" s="12" t="s">
         <v>2072</v>
       </c>
@@ -24740,45 +24730,45 @@
       <c r="B1991" s="12"/>
       <c r="C1991" s="12"/>
       <c r="D1991" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1992" ht="17" customHeight="1" spans="1:4">
+      <c r="A1992" s="11" t="s">
         <v>2080</v>
       </c>
-    </row>
-    <row r="1992" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1992" s="12"/>
-      <c r="B1992" s="12"/>
-      <c r="C1992" s="12"/>
-      <c r="D1992" s="12" t="s">
+      <c r="B1992" s="11" t="s">
         <v>2081</v>
       </c>
-    </row>
-    <row r="1993" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1993" s="12"/>
-      <c r="B1993" s="12"/>
-      <c r="C1993" s="12"/>
-      <c r="D1993" s="12" t="s">
+      <c r="C1992" s="11" t="s">
         <v>2082</v>
       </c>
-    </row>
-    <row r="1994" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1994" s="12"/>
-      <c r="B1994" s="12"/>
-      <c r="C1994" s="12"/>
-      <c r="D1994" s="12" t="s">
-        <v>148</v>
+      <c r="D1992" s="11" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="1993" ht="17" customHeight="1" spans="1:4">
+      <c r="A1993" s="11"/>
+      <c r="B1993" s="11"/>
+      <c r="C1993" s="11"/>
+      <c r="D1993" s="11" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="1994" ht="17" customHeight="1" spans="1:4">
+      <c r="A1994" s="11"/>
+      <c r="B1994" s="11"/>
+      <c r="C1994" s="11"/>
+      <c r="D1994" s="11" t="s">
+        <v>1616</v>
       </c>
     </row>
     <row r="1995" ht="17" customHeight="1" spans="1:4">
-      <c r="A1995" s="11" t="s">
-        <v>2083</v>
-      </c>
-      <c r="B1995" s="11" t="s">
+      <c r="A1995" s="11"/>
+      <c r="B1995" s="11"/>
+      <c r="C1995" s="11"/>
+      <c r="D1995" s="11" t="s">
         <v>2084</v>
-      </c>
-      <c r="C1995" s="11" t="s">
-        <v>2085</v>
-      </c>
-      <c r="D1995" s="11" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="1996" ht="17" customHeight="1" spans="1:4">
@@ -24786,7 +24776,7 @@
       <c r="B1996" s="11"/>
       <c r="C1996" s="11"/>
       <c r="D1996" s="11" t="s">
-        <v>1618</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1997" ht="17" customHeight="1" spans="1:4">
@@ -24794,7 +24784,7 @@
       <c r="B1997" s="11"/>
       <c r="C1997" s="11"/>
       <c r="D1997" s="11" t="s">
-        <v>1619</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1998" ht="17" customHeight="1" spans="1:4">
@@ -24898,15 +24888,21 @@
       <c r="B2010" s="11"/>
       <c r="C2010" s="11"/>
       <c r="D2010" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2011" ht="17" customHeight="1" spans="1:4">
+      <c r="A2011" s="11" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B2011" s="11" t="s">
         <v>2099</v>
       </c>
-    </row>
-    <row r="2011" ht="17" customHeight="1" spans="1:4">
-      <c r="A2011" s="11"/>
-      <c r="B2011" s="11"/>
-      <c r="C2011" s="11"/>
+      <c r="C2011" s="11" t="s">
+        <v>2100</v>
+      </c>
       <c r="D2011" s="11" t="s">
-        <v>2100</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="2012" ht="17" customHeight="1" spans="1:4">
@@ -24922,21 +24918,15 @@
       <c r="B2013" s="11"/>
       <c r="C2013" s="11"/>
       <c r="D2013" s="11" t="s">
-        <v>25</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="2014" ht="17" customHeight="1" spans="1:4">
-      <c r="A2014" s="11" t="s">
-        <v>2083</v>
-      </c>
-      <c r="B2014" s="11" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C2014" s="11" t="s">
+      <c r="A2014" s="11"/>
+      <c r="B2014" s="11"/>
+      <c r="C2014" s="11"/>
+      <c r="D2014" s="11" t="s">
         <v>2103</v>
-      </c>
-      <c r="D2014" s="11" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="2015" ht="17" customHeight="1" spans="1:4">
@@ -25008,15 +24998,21 @@
       <c r="B2023" s="11"/>
       <c r="C2023" s="11"/>
       <c r="D2023" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2024" ht="17" customHeight="1" spans="1:4">
+      <c r="A2024" s="11" t="s">
         <v>2112</v>
       </c>
-    </row>
-    <row r="2024" ht="17" customHeight="1" spans="1:4">
-      <c r="A2024" s="11"/>
-      <c r="B2024" s="11"/>
-      <c r="C2024" s="11"/>
+      <c r="B2024" s="11" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C2024" s="11" t="s">
+        <v>2114</v>
+      </c>
       <c r="D2024" s="11" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="2025" ht="17" customHeight="1" spans="1:4">
@@ -25024,7 +25020,7 @@
       <c r="B2025" s="11"/>
       <c r="C2025" s="11"/>
       <c r="D2025" s="11" t="s">
-        <v>2114</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="2026" ht="17" customHeight="1" spans="1:4">
@@ -25032,21 +25028,15 @@
       <c r="B2026" s="11"/>
       <c r="C2026" s="11"/>
       <c r="D2026" s="11" t="s">
-        <v>675</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="2027" ht="17" customHeight="1" spans="1:4">
-      <c r="A2027" s="11" t="s">
-        <v>2115</v>
-      </c>
-      <c r="B2027" s="11" t="s">
-        <v>2116</v>
-      </c>
-      <c r="C2027" s="11" t="s">
-        <v>2117</v>
-      </c>
+      <c r="A2027" s="11"/>
+      <c r="B2027" s="11"/>
+      <c r="C2027" s="11"/>
       <c r="D2027" s="11" t="s">
-        <v>2118</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="2028" ht="17" customHeight="1" spans="1:4">
@@ -25062,7 +25052,7 @@
       <c r="B2029" s="11"/>
       <c r="C2029" s="11"/>
       <c r="D2029" s="11" t="s">
-        <v>2119</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="2030" ht="17" customHeight="1" spans="1:4">
@@ -25110,7 +25100,7 @@
       <c r="B2035" s="11"/>
       <c r="C2035" s="11"/>
       <c r="D2035" s="11" t="s">
-        <v>1332</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="2036" ht="17" customHeight="1" spans="1:4">
@@ -25122,11 +25112,17 @@
       </c>
     </row>
     <row r="2037" ht="17" customHeight="1" spans="1:4">
-      <c r="A2037" s="11"/>
-      <c r="B2037" s="11"/>
-      <c r="C2037" s="11"/>
+      <c r="A2037" s="11" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B2037" s="11" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C2037" s="11" t="s">
+        <v>2120</v>
+      </c>
       <c r="D2037" s="11" t="s">
-        <v>1334</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="2038" ht="17" customHeight="1" spans="1:4">
@@ -25134,7 +25130,7 @@
       <c r="B2038" s="11"/>
       <c r="C2038" s="11"/>
       <c r="D2038" s="11" t="s">
-        <v>2120</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2039" ht="17" customHeight="1" spans="1:4">
@@ -25142,21 +25138,15 @@
       <c r="B2039" s="11"/>
       <c r="C2039" s="11"/>
       <c r="D2039" s="11" t="s">
-        <v>1336</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2040" ht="17" customHeight="1" spans="1:4">
-      <c r="A2040" s="11" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B2040" s="11" t="s">
-        <v>2122</v>
-      </c>
-      <c r="C2040" s="11" t="s">
-        <v>2123</v>
-      </c>
+      <c r="A2040" s="11"/>
+      <c r="B2040" s="11"/>
+      <c r="C2040" s="11"/>
       <c r="D2040" s="11" t="s">
-        <v>2124</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2041" ht="17" customHeight="1" spans="1:4">
@@ -25164,7 +25154,7 @@
       <c r="B2041" s="11"/>
       <c r="C2041" s="11"/>
       <c r="D2041" s="11" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2042" ht="17" customHeight="1" spans="1:4">
@@ -25172,7 +25162,7 @@
       <c r="B2042" s="11"/>
       <c r="C2042" s="11"/>
       <c r="D2042" s="11" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2043" ht="17" customHeight="1" spans="1:4">
@@ -25180,7 +25170,7 @@
       <c r="B2043" s="11"/>
       <c r="C2043" s="11"/>
       <c r="D2043" s="11" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2044" ht="17" customHeight="1" spans="1:4">
@@ -25188,7 +25178,7 @@
       <c r="B2044" s="11"/>
       <c r="C2044" s="11"/>
       <c r="D2044" s="11" t="s">
-        <v>453</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="2045" ht="17" customHeight="1" spans="1:4">
@@ -25196,15 +25186,21 @@
       <c r="B2045" s="11"/>
       <c r="C2045" s="11"/>
       <c r="D2045" s="11" t="s">
-        <v>454</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2046" ht="17" customHeight="1" spans="1:4">
-      <c r="A2046" s="11"/>
-      <c r="B2046" s="11"/>
-      <c r="C2046" s="11"/>
+      <c r="A2046" s="11" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B2046" s="11" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C2046" s="11" t="s">
+        <v>2125</v>
+      </c>
       <c r="D2046" s="11" t="s">
-        <v>455</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="2047" ht="17" customHeight="1" spans="1:4">
@@ -25212,7 +25208,7 @@
       <c r="B2047" s="11"/>
       <c r="C2047" s="11"/>
       <c r="D2047" s="11" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="2048" ht="17" customHeight="1" spans="1:4">
@@ -25220,19 +25216,13 @@
       <c r="B2048" s="11"/>
       <c r="C2048" s="11"/>
       <c r="D2048" s="11" t="s">
-        <v>116</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="2049" ht="17" customHeight="1" spans="1:4">
-      <c r="A2049" s="11" t="s">
-        <v>2126</v>
-      </c>
-      <c r="B2049" s="11" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C2049" s="11" t="s">
-        <v>2128</v>
-      </c>
+      <c r="A2049" s="11"/>
+      <c r="B2049" s="11"/>
+      <c r="C2049" s="11"/>
       <c r="D2049" s="11" t="s">
         <v>2129</v>
       </c>
@@ -25362,43 +25352,43 @@
       <c r="B2065" s="11"/>
       <c r="C2065" s="11"/>
       <c r="D2065" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="2066" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2066" s="12" t="s">
         <v>2145</v>
       </c>
-    </row>
-    <row r="2066" ht="17" customHeight="1" spans="1:4">
-      <c r="A2066" s="11"/>
-      <c r="B2066" s="11"/>
-      <c r="C2066" s="11"/>
-      <c r="D2066" s="11" t="s">
+      <c r="B2066" s="12" t="s">
         <v>2146</v>
       </c>
-    </row>
-    <row r="2067" ht="17" customHeight="1" spans="1:4">
-      <c r="A2067" s="11"/>
-      <c r="B2067" s="11"/>
-      <c r="C2067" s="11"/>
-      <c r="D2067" s="11" t="s">
+      <c r="C2066" s="12" t="s">
         <v>2147</v>
       </c>
-    </row>
-    <row r="2068" ht="17" customHeight="1" spans="1:4">
-      <c r="A2068" s="11"/>
-      <c r="B2068" s="11"/>
-      <c r="C2068" s="11"/>
-      <c r="D2068" s="11" t="s">
-        <v>478</v>
+      <c r="D2066" s="12" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="2067" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2067" s="12"/>
+      <c r="B2067" s="12"/>
+      <c r="C2067" s="12"/>
+      <c r="D2067" s="12" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="2068" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2068" s="12"/>
+      <c r="B2068" s="12"/>
+      <c r="C2068" s="12"/>
+      <c r="D2068" s="12" t="s">
+        <v>2150</v>
       </c>
     </row>
     <row r="2069" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2069" s="12" t="s">
-        <v>2148</v>
-      </c>
-      <c r="B2069" s="12" t="s">
-        <v>2149</v>
-      </c>
-      <c r="C2069" s="12" t="s">
-        <v>2150</v>
-      </c>
+      <c r="A2069" s="12"/>
+      <c r="B2069" s="12"/>
+      <c r="C2069" s="12"/>
       <c r="D2069" s="12" t="s">
         <v>2151</v>
       </c>
@@ -25432,7 +25422,7 @@
       <c r="B2073" s="12"/>
       <c r="C2073" s="12"/>
       <c r="D2073" s="12" t="s">
-        <v>2155</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2074" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25440,7 +25430,7 @@
       <c r="B2074" s="12"/>
       <c r="C2074" s="12"/>
       <c r="D2074" s="12" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="2075" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25448,7 +25438,7 @@
       <c r="B2075" s="12"/>
       <c r="C2075" s="12"/>
       <c r="D2075" s="12" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="2076" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25456,43 +25446,43 @@
       <c r="B2076" s="12"/>
       <c r="C2076" s="12"/>
       <c r="D2076" s="12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="2077" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2077" s="12"/>
-      <c r="B2077" s="12"/>
-      <c r="C2077" s="12"/>
-      <c r="D2077" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2077" ht="17" customHeight="1" spans="1:4">
+      <c r="A2077" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B2077" s="2" t="s">
         <v>2158</v>
       </c>
-    </row>
-    <row r="2078" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2078" s="12"/>
-      <c r="B2078" s="12"/>
-      <c r="C2078" s="12"/>
-      <c r="D2078" s="12" t="s">
+      <c r="C2077" s="2" t="s">
         <v>2159</v>
       </c>
-    </row>
-    <row r="2079" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2079" s="12"/>
-      <c r="B2079" s="12"/>
-      <c r="C2079" s="12"/>
-      <c r="D2079" s="12" t="s">
-        <v>211</v>
+      <c r="D2077" s="2" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="2078" ht="17" customHeight="1" spans="1:4">
+      <c r="A2078" s="2"/>
+      <c r="B2078" s="2"/>
+      <c r="C2078" s="2"/>
+      <c r="D2078" s="2" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="2079" ht="17" customHeight="1" spans="1:4">
+      <c r="A2079" s="2"/>
+      <c r="B2079" s="2"/>
+      <c r="C2079" s="2"/>
+      <c r="D2079" s="2" t="s">
+        <v>2162</v>
       </c>
     </row>
     <row r="2080" ht="17" customHeight="1" spans="1:4">
-      <c r="A2080" s="2" t="s">
-        <v>2160</v>
-      </c>
-      <c r="B2080" s="2" t="s">
-        <v>2161</v>
-      </c>
-      <c r="C2080" s="2" t="s">
-        <v>2162</v>
-      </c>
+      <c r="A2080" s="2"/>
+      <c r="B2080" s="2"/>
+      <c r="C2080" s="2"/>
       <c r="D2080" s="2" t="s">
         <v>2163</v>
       </c>
@@ -25582,15 +25572,21 @@
       <c r="B2091" s="2"/>
       <c r="C2091" s="2"/>
       <c r="D2091" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2092" ht="17" customHeight="1" spans="1:4">
+      <c r="A2092" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B2092" s="2" t="s">
         <v>2174</v>
       </c>
-    </row>
-    <row r="2092" ht="17" customHeight="1" spans="1:4">
-      <c r="A2092" s="2"/>
-      <c r="B2092" s="2"/>
-      <c r="C2092" s="2"/>
+      <c r="C2092" s="2" t="s">
+        <v>2175</v>
+      </c>
       <c r="D2092" s="2" t="s">
-        <v>2175</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="2093" ht="17" customHeight="1" spans="1:4">
@@ -25606,21 +25602,15 @@
       <c r="B2094" s="2"/>
       <c r="C2094" s="2"/>
       <c r="D2094" s="2" t="s">
-        <v>87</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="2095" ht="17" customHeight="1" spans="1:4">
-      <c r="A2095" s="2" t="s">
-        <v>2160</v>
-      </c>
-      <c r="B2095" s="2" t="s">
-        <v>2177</v>
-      </c>
-      <c r="C2095" s="2" t="s">
+      <c r="A2095" s="2"/>
+      <c r="B2095" s="2"/>
+      <c r="C2095" s="2"/>
+      <c r="D2095" s="2" t="s">
         <v>2178</v>
-      </c>
-      <c r="D2095" s="2" t="s">
-        <v>2163</v>
       </c>
     </row>
     <row r="2096" ht="17" customHeight="1" spans="1:4">
@@ -25652,30 +25642,6 @@
       <c r="B2099" s="2"/>
       <c r="C2099" s="2"/>
       <c r="D2099" s="2" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="2100" ht="17" customHeight="1" spans="1:4">
-      <c r="A2100" s="2"/>
-      <c r="B2100" s="2"/>
-      <c r="C2100" s="2"/>
-      <c r="D2100" s="2" t="s">
-        <v>2183</v>
-      </c>
-    </row>
-    <row r="2101" ht="17" customHeight="1" spans="1:4">
-      <c r="A2101" s="2"/>
-      <c r="B2101" s="2"/>
-      <c r="C2101" s="2"/>
-      <c r="D2101" s="2" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="2102" ht="17" customHeight="1" spans="1:4">
-      <c r="A2102" s="2"/>
-      <c r="B2102" s="2"/>
-      <c r="C2102" s="2"/>
-      <c r="D2102" s="2" t="s">
         <v>419</v>
       </c>
     </row>
@@ -25771,80 +25737,80 @@
     <mergeCell ref="A1113:A1122"/>
     <mergeCell ref="A1123:A1128"/>
     <mergeCell ref="A1129:A1139"/>
-    <mergeCell ref="A1140:A1161"/>
-    <mergeCell ref="A1162:A1178"/>
-    <mergeCell ref="A1179:A1198"/>
-    <mergeCell ref="A1199:A1209"/>
-    <mergeCell ref="A1210:A1218"/>
-    <mergeCell ref="A1219:A1224"/>
-    <mergeCell ref="A1225:A1240"/>
-    <mergeCell ref="A1241:A1253"/>
-    <mergeCell ref="A1254:A1261"/>
-    <mergeCell ref="A1262:A1272"/>
-    <mergeCell ref="A1273:A1282"/>
-    <mergeCell ref="A1283:A1310"/>
-    <mergeCell ref="A1311:A1314"/>
-    <mergeCell ref="A1315:A1317"/>
-    <mergeCell ref="A1318:A1336"/>
-    <mergeCell ref="A1337:A1350"/>
-    <mergeCell ref="A1351:A1386"/>
-    <mergeCell ref="A1387:A1398"/>
-    <mergeCell ref="A1399:A1412"/>
-    <mergeCell ref="A1413:A1429"/>
-    <mergeCell ref="A1430:A1444"/>
-    <mergeCell ref="A1445:A1458"/>
-    <mergeCell ref="A1459:A1464"/>
-    <mergeCell ref="A1465:A1478"/>
-    <mergeCell ref="A1479:A1492"/>
-    <mergeCell ref="A1493:A1498"/>
-    <mergeCell ref="A1499:A1508"/>
-    <mergeCell ref="A1509:A1519"/>
-    <mergeCell ref="A1520:A1529"/>
-    <mergeCell ref="A1530:A1541"/>
-    <mergeCell ref="A1542:A1550"/>
-    <mergeCell ref="A1551:A1552"/>
-    <mergeCell ref="A1553:A1562"/>
-    <mergeCell ref="A1563:A1581"/>
-    <mergeCell ref="A1582:A1596"/>
-    <mergeCell ref="A1597:A1614"/>
-    <mergeCell ref="A1615:A1629"/>
-    <mergeCell ref="A1630:A1637"/>
-    <mergeCell ref="A1638:A1652"/>
-    <mergeCell ref="A1653:A1666"/>
-    <mergeCell ref="A1667:A1682"/>
-    <mergeCell ref="A1683:A1699"/>
-    <mergeCell ref="A1700:A1713"/>
-    <mergeCell ref="A1714:A1729"/>
-    <mergeCell ref="A1730:A1738"/>
-    <mergeCell ref="A1739:A1752"/>
-    <mergeCell ref="A1753:A1764"/>
-    <mergeCell ref="A1765:A1778"/>
-    <mergeCell ref="A1779:A1793"/>
-    <mergeCell ref="A1794:A1806"/>
-    <mergeCell ref="A1807:A1825"/>
-    <mergeCell ref="A1826:A1832"/>
-    <mergeCell ref="A1833:A1838"/>
-    <mergeCell ref="A1839:A1845"/>
-    <mergeCell ref="A1846:A1851"/>
-    <mergeCell ref="A1852:A1861"/>
-    <mergeCell ref="A1862:A1873"/>
-    <mergeCell ref="A1874:A1884"/>
-    <mergeCell ref="A1885:A1897"/>
-    <mergeCell ref="A1898:A1913"/>
-    <mergeCell ref="A1914:A1932"/>
-    <mergeCell ref="A1933:A1943"/>
-    <mergeCell ref="A1944:A1957"/>
-    <mergeCell ref="A1958:A1972"/>
-    <mergeCell ref="A1973:A1982"/>
-    <mergeCell ref="A1983:A1994"/>
-    <mergeCell ref="A1995:A2013"/>
-    <mergeCell ref="A2014:A2026"/>
-    <mergeCell ref="A2027:A2039"/>
-    <mergeCell ref="A2040:A2048"/>
-    <mergeCell ref="A2049:A2068"/>
-    <mergeCell ref="A2069:A2079"/>
-    <mergeCell ref="A2080:A2094"/>
-    <mergeCell ref="A2095:A2102"/>
+    <mergeCell ref="A1140:A1158"/>
+    <mergeCell ref="A1159:A1175"/>
+    <mergeCell ref="A1176:A1195"/>
+    <mergeCell ref="A1196:A1206"/>
+    <mergeCell ref="A1207:A1215"/>
+    <mergeCell ref="A1216:A1221"/>
+    <mergeCell ref="A1222:A1237"/>
+    <mergeCell ref="A1238:A1250"/>
+    <mergeCell ref="A1251:A1258"/>
+    <mergeCell ref="A1259:A1269"/>
+    <mergeCell ref="A1270:A1279"/>
+    <mergeCell ref="A1280:A1307"/>
+    <mergeCell ref="A1308:A1311"/>
+    <mergeCell ref="A1312:A1314"/>
+    <mergeCell ref="A1315:A1333"/>
+    <mergeCell ref="A1334:A1347"/>
+    <mergeCell ref="A1348:A1383"/>
+    <mergeCell ref="A1384:A1395"/>
+    <mergeCell ref="A1396:A1409"/>
+    <mergeCell ref="A1410:A1426"/>
+    <mergeCell ref="A1427:A1441"/>
+    <mergeCell ref="A1442:A1455"/>
+    <mergeCell ref="A1456:A1461"/>
+    <mergeCell ref="A1462:A1475"/>
+    <mergeCell ref="A1476:A1489"/>
+    <mergeCell ref="A1490:A1495"/>
+    <mergeCell ref="A1496:A1505"/>
+    <mergeCell ref="A1506:A1516"/>
+    <mergeCell ref="A1517:A1526"/>
+    <mergeCell ref="A1527:A1538"/>
+    <mergeCell ref="A1539:A1547"/>
+    <mergeCell ref="A1548:A1549"/>
+    <mergeCell ref="A1550:A1559"/>
+    <mergeCell ref="A1560:A1578"/>
+    <mergeCell ref="A1579:A1593"/>
+    <mergeCell ref="A1594:A1611"/>
+    <mergeCell ref="A1612:A1626"/>
+    <mergeCell ref="A1627:A1634"/>
+    <mergeCell ref="A1635:A1649"/>
+    <mergeCell ref="A1650:A1663"/>
+    <mergeCell ref="A1664:A1679"/>
+    <mergeCell ref="A1680:A1696"/>
+    <mergeCell ref="A1697:A1710"/>
+    <mergeCell ref="A1711:A1726"/>
+    <mergeCell ref="A1727:A1735"/>
+    <mergeCell ref="A1736:A1749"/>
+    <mergeCell ref="A1750:A1761"/>
+    <mergeCell ref="A1762:A1775"/>
+    <mergeCell ref="A1776:A1790"/>
+    <mergeCell ref="A1791:A1803"/>
+    <mergeCell ref="A1804:A1822"/>
+    <mergeCell ref="A1823:A1829"/>
+    <mergeCell ref="A1830:A1835"/>
+    <mergeCell ref="A1836:A1842"/>
+    <mergeCell ref="A1843:A1848"/>
+    <mergeCell ref="A1849:A1858"/>
+    <mergeCell ref="A1859:A1870"/>
+    <mergeCell ref="A1871:A1881"/>
+    <mergeCell ref="A1882:A1894"/>
+    <mergeCell ref="A1895:A1910"/>
+    <mergeCell ref="A1911:A1929"/>
+    <mergeCell ref="A1930:A1940"/>
+    <mergeCell ref="A1941:A1954"/>
+    <mergeCell ref="A1955:A1969"/>
+    <mergeCell ref="A1970:A1979"/>
+    <mergeCell ref="A1980:A1991"/>
+    <mergeCell ref="A1992:A2010"/>
+    <mergeCell ref="A2011:A2023"/>
+    <mergeCell ref="A2024:A2036"/>
+    <mergeCell ref="A2037:A2045"/>
+    <mergeCell ref="A2046:A2065"/>
+    <mergeCell ref="A2066:A2076"/>
+    <mergeCell ref="A2077:A2091"/>
+    <mergeCell ref="A2092:A2099"/>
     <mergeCell ref="B2:B20"/>
     <mergeCell ref="B21:B54"/>
     <mergeCell ref="B55:B64"/>
@@ -25935,80 +25901,80 @@
     <mergeCell ref="B1113:B1122"/>
     <mergeCell ref="B1123:B1128"/>
     <mergeCell ref="B1129:B1139"/>
-    <mergeCell ref="B1140:B1161"/>
-    <mergeCell ref="B1162:B1178"/>
-    <mergeCell ref="B1179:B1198"/>
-    <mergeCell ref="B1199:B1209"/>
-    <mergeCell ref="B1210:B1218"/>
-    <mergeCell ref="B1219:B1224"/>
-    <mergeCell ref="B1225:B1240"/>
-    <mergeCell ref="B1241:B1253"/>
-    <mergeCell ref="B1254:B1261"/>
-    <mergeCell ref="B1262:B1272"/>
-    <mergeCell ref="B1273:B1282"/>
-    <mergeCell ref="B1283:B1310"/>
-    <mergeCell ref="B1311:B1314"/>
-    <mergeCell ref="B1315:B1317"/>
-    <mergeCell ref="B1318:B1336"/>
-    <mergeCell ref="B1337:B1350"/>
-    <mergeCell ref="B1351:B1386"/>
-    <mergeCell ref="B1387:B1398"/>
-    <mergeCell ref="B1399:B1412"/>
-    <mergeCell ref="B1413:B1429"/>
-    <mergeCell ref="B1430:B1444"/>
-    <mergeCell ref="B1445:B1458"/>
-    <mergeCell ref="B1459:B1464"/>
-    <mergeCell ref="B1465:B1478"/>
-    <mergeCell ref="B1479:B1492"/>
-    <mergeCell ref="B1493:B1498"/>
-    <mergeCell ref="B1499:B1508"/>
-    <mergeCell ref="B1509:B1519"/>
-    <mergeCell ref="B1520:B1529"/>
-    <mergeCell ref="B1530:B1541"/>
-    <mergeCell ref="B1542:B1550"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B1553:B1562"/>
-    <mergeCell ref="B1563:B1581"/>
-    <mergeCell ref="B1582:B1596"/>
-    <mergeCell ref="B1597:B1614"/>
-    <mergeCell ref="B1615:B1629"/>
-    <mergeCell ref="B1630:B1637"/>
-    <mergeCell ref="B1638:B1652"/>
-    <mergeCell ref="B1653:B1666"/>
-    <mergeCell ref="B1667:B1682"/>
-    <mergeCell ref="B1683:B1699"/>
-    <mergeCell ref="B1700:B1713"/>
-    <mergeCell ref="B1714:B1729"/>
-    <mergeCell ref="B1730:B1738"/>
-    <mergeCell ref="B1739:B1752"/>
-    <mergeCell ref="B1753:B1764"/>
-    <mergeCell ref="B1765:B1778"/>
-    <mergeCell ref="B1779:B1793"/>
-    <mergeCell ref="B1794:B1806"/>
-    <mergeCell ref="B1807:B1825"/>
-    <mergeCell ref="B1826:B1832"/>
-    <mergeCell ref="B1833:B1838"/>
-    <mergeCell ref="B1839:B1845"/>
-    <mergeCell ref="B1846:B1851"/>
-    <mergeCell ref="B1852:B1861"/>
-    <mergeCell ref="B1862:B1873"/>
-    <mergeCell ref="B1874:B1884"/>
-    <mergeCell ref="B1885:B1897"/>
-    <mergeCell ref="B1898:B1913"/>
-    <mergeCell ref="B1914:B1932"/>
-    <mergeCell ref="B1933:B1943"/>
-    <mergeCell ref="B1944:B1957"/>
-    <mergeCell ref="B1958:B1972"/>
-    <mergeCell ref="B1973:B1982"/>
-    <mergeCell ref="B1983:B1994"/>
-    <mergeCell ref="B1995:B2013"/>
-    <mergeCell ref="B2014:B2026"/>
-    <mergeCell ref="B2027:B2039"/>
-    <mergeCell ref="B2040:B2048"/>
-    <mergeCell ref="B2049:B2068"/>
-    <mergeCell ref="B2069:B2079"/>
-    <mergeCell ref="B2080:B2094"/>
-    <mergeCell ref="B2095:B2102"/>
+    <mergeCell ref="B1140:B1158"/>
+    <mergeCell ref="B1159:B1175"/>
+    <mergeCell ref="B1176:B1195"/>
+    <mergeCell ref="B1196:B1206"/>
+    <mergeCell ref="B1207:B1215"/>
+    <mergeCell ref="B1216:B1221"/>
+    <mergeCell ref="B1222:B1237"/>
+    <mergeCell ref="B1238:B1250"/>
+    <mergeCell ref="B1251:B1258"/>
+    <mergeCell ref="B1259:B1269"/>
+    <mergeCell ref="B1270:B1279"/>
+    <mergeCell ref="B1280:B1307"/>
+    <mergeCell ref="B1308:B1311"/>
+    <mergeCell ref="B1312:B1314"/>
+    <mergeCell ref="B1315:B1333"/>
+    <mergeCell ref="B1334:B1347"/>
+    <mergeCell ref="B1348:B1383"/>
+    <mergeCell ref="B1384:B1395"/>
+    <mergeCell ref="B1396:B1409"/>
+    <mergeCell ref="B1410:B1426"/>
+    <mergeCell ref="B1427:B1441"/>
+    <mergeCell ref="B1442:B1455"/>
+    <mergeCell ref="B1456:B1461"/>
+    <mergeCell ref="B1462:B1475"/>
+    <mergeCell ref="B1476:B1489"/>
+    <mergeCell ref="B1490:B1495"/>
+    <mergeCell ref="B1496:B1505"/>
+    <mergeCell ref="B1506:B1516"/>
+    <mergeCell ref="B1517:B1526"/>
+    <mergeCell ref="B1527:B1538"/>
+    <mergeCell ref="B1539:B1547"/>
+    <mergeCell ref="B1548:B1549"/>
+    <mergeCell ref="B1550:B1559"/>
+    <mergeCell ref="B1560:B1578"/>
+    <mergeCell ref="B1579:B1593"/>
+    <mergeCell ref="B1594:B1611"/>
+    <mergeCell ref="B1612:B1626"/>
+    <mergeCell ref="B1627:B1634"/>
+    <mergeCell ref="B1635:B1649"/>
+    <mergeCell ref="B1650:B1663"/>
+    <mergeCell ref="B1664:B1679"/>
+    <mergeCell ref="B1680:B1696"/>
+    <mergeCell ref="B1697:B1710"/>
+    <mergeCell ref="B1711:B1726"/>
+    <mergeCell ref="B1727:B1735"/>
+    <mergeCell ref="B1736:B1749"/>
+    <mergeCell ref="B1750:B1761"/>
+    <mergeCell ref="B1762:B1775"/>
+    <mergeCell ref="B1776:B1790"/>
+    <mergeCell ref="B1791:B1803"/>
+    <mergeCell ref="B1804:B1822"/>
+    <mergeCell ref="B1823:B1829"/>
+    <mergeCell ref="B1830:B1835"/>
+    <mergeCell ref="B1836:B1842"/>
+    <mergeCell ref="B1843:B1848"/>
+    <mergeCell ref="B1849:B1858"/>
+    <mergeCell ref="B1859:B1870"/>
+    <mergeCell ref="B1871:B1881"/>
+    <mergeCell ref="B1882:B1894"/>
+    <mergeCell ref="B1895:B1910"/>
+    <mergeCell ref="B1911:B1929"/>
+    <mergeCell ref="B1930:B1940"/>
+    <mergeCell ref="B1941:B1954"/>
+    <mergeCell ref="B1955:B1969"/>
+    <mergeCell ref="B1970:B1979"/>
+    <mergeCell ref="B1980:B1991"/>
+    <mergeCell ref="B1992:B2010"/>
+    <mergeCell ref="B2011:B2023"/>
+    <mergeCell ref="B2024:B2036"/>
+    <mergeCell ref="B2037:B2045"/>
+    <mergeCell ref="B2046:B2065"/>
+    <mergeCell ref="B2066:B2076"/>
+    <mergeCell ref="B2077:B2091"/>
+    <mergeCell ref="B2092:B2099"/>
     <mergeCell ref="C2:C20"/>
     <mergeCell ref="C21:C54"/>
     <mergeCell ref="C55:C64"/>
@@ -26099,80 +26065,80 @@
     <mergeCell ref="C1113:C1122"/>
     <mergeCell ref="C1123:C1128"/>
     <mergeCell ref="C1129:C1139"/>
-    <mergeCell ref="C1140:C1161"/>
-    <mergeCell ref="C1162:C1178"/>
-    <mergeCell ref="C1179:C1198"/>
-    <mergeCell ref="C1199:C1209"/>
-    <mergeCell ref="C1210:C1218"/>
-    <mergeCell ref="C1219:C1224"/>
-    <mergeCell ref="C1225:C1240"/>
-    <mergeCell ref="C1241:C1253"/>
-    <mergeCell ref="C1254:C1261"/>
-    <mergeCell ref="C1262:C1272"/>
-    <mergeCell ref="C1273:C1282"/>
-    <mergeCell ref="C1283:C1310"/>
-    <mergeCell ref="C1311:C1314"/>
-    <mergeCell ref="C1315:C1317"/>
-    <mergeCell ref="C1318:C1336"/>
-    <mergeCell ref="C1337:C1350"/>
-    <mergeCell ref="C1351:C1386"/>
-    <mergeCell ref="C1387:C1398"/>
-    <mergeCell ref="C1399:C1412"/>
-    <mergeCell ref="C1413:C1429"/>
-    <mergeCell ref="C1430:C1444"/>
-    <mergeCell ref="C1445:C1458"/>
-    <mergeCell ref="C1459:C1464"/>
-    <mergeCell ref="C1465:C1478"/>
-    <mergeCell ref="C1479:C1492"/>
-    <mergeCell ref="C1493:C1498"/>
-    <mergeCell ref="C1499:C1508"/>
-    <mergeCell ref="C1509:C1519"/>
-    <mergeCell ref="C1520:C1529"/>
-    <mergeCell ref="C1530:C1541"/>
-    <mergeCell ref="C1542:C1550"/>
-    <mergeCell ref="C1551:C1552"/>
-    <mergeCell ref="C1553:C1562"/>
-    <mergeCell ref="C1563:C1581"/>
-    <mergeCell ref="C1582:C1596"/>
-    <mergeCell ref="C1597:C1614"/>
-    <mergeCell ref="C1615:C1629"/>
-    <mergeCell ref="C1630:C1637"/>
-    <mergeCell ref="C1638:C1652"/>
-    <mergeCell ref="C1653:C1666"/>
-    <mergeCell ref="C1667:C1682"/>
-    <mergeCell ref="C1683:C1699"/>
-    <mergeCell ref="C1700:C1713"/>
-    <mergeCell ref="C1714:C1729"/>
-    <mergeCell ref="C1730:C1738"/>
-    <mergeCell ref="C1739:C1752"/>
-    <mergeCell ref="C1753:C1764"/>
-    <mergeCell ref="C1765:C1778"/>
-    <mergeCell ref="C1779:C1793"/>
-    <mergeCell ref="C1794:C1806"/>
-    <mergeCell ref="C1807:C1825"/>
-    <mergeCell ref="C1826:C1832"/>
-    <mergeCell ref="C1833:C1838"/>
-    <mergeCell ref="C1839:C1845"/>
-    <mergeCell ref="C1846:C1851"/>
-    <mergeCell ref="C1852:C1861"/>
-    <mergeCell ref="C1862:C1873"/>
-    <mergeCell ref="C1874:C1884"/>
-    <mergeCell ref="C1885:C1897"/>
-    <mergeCell ref="C1898:C1913"/>
-    <mergeCell ref="C1914:C1932"/>
-    <mergeCell ref="C1933:C1943"/>
-    <mergeCell ref="C1944:C1957"/>
-    <mergeCell ref="C1958:C1972"/>
-    <mergeCell ref="C1973:C1982"/>
-    <mergeCell ref="C1983:C1994"/>
-    <mergeCell ref="C1995:C2013"/>
-    <mergeCell ref="C2014:C2026"/>
-    <mergeCell ref="C2027:C2039"/>
-    <mergeCell ref="C2040:C2048"/>
-    <mergeCell ref="C2049:C2068"/>
-    <mergeCell ref="C2069:C2079"/>
-    <mergeCell ref="C2080:C2094"/>
-    <mergeCell ref="C2095:C2102"/>
+    <mergeCell ref="C1140:C1158"/>
+    <mergeCell ref="C1159:C1175"/>
+    <mergeCell ref="C1176:C1195"/>
+    <mergeCell ref="C1196:C1206"/>
+    <mergeCell ref="C1207:C1215"/>
+    <mergeCell ref="C1216:C1221"/>
+    <mergeCell ref="C1222:C1237"/>
+    <mergeCell ref="C1238:C1250"/>
+    <mergeCell ref="C1251:C1258"/>
+    <mergeCell ref="C1259:C1269"/>
+    <mergeCell ref="C1270:C1279"/>
+    <mergeCell ref="C1280:C1307"/>
+    <mergeCell ref="C1308:C1311"/>
+    <mergeCell ref="C1312:C1314"/>
+    <mergeCell ref="C1315:C1333"/>
+    <mergeCell ref="C1334:C1347"/>
+    <mergeCell ref="C1348:C1383"/>
+    <mergeCell ref="C1384:C1395"/>
+    <mergeCell ref="C1396:C1409"/>
+    <mergeCell ref="C1410:C1426"/>
+    <mergeCell ref="C1427:C1441"/>
+    <mergeCell ref="C1442:C1455"/>
+    <mergeCell ref="C1456:C1461"/>
+    <mergeCell ref="C1462:C1475"/>
+    <mergeCell ref="C1476:C1489"/>
+    <mergeCell ref="C1490:C1495"/>
+    <mergeCell ref="C1496:C1505"/>
+    <mergeCell ref="C1506:C1516"/>
+    <mergeCell ref="C1517:C1526"/>
+    <mergeCell ref="C1527:C1538"/>
+    <mergeCell ref="C1539:C1547"/>
+    <mergeCell ref="C1548:C1549"/>
+    <mergeCell ref="C1550:C1559"/>
+    <mergeCell ref="C1560:C1578"/>
+    <mergeCell ref="C1579:C1593"/>
+    <mergeCell ref="C1594:C1611"/>
+    <mergeCell ref="C1612:C1626"/>
+    <mergeCell ref="C1627:C1634"/>
+    <mergeCell ref="C1635:C1649"/>
+    <mergeCell ref="C1650:C1663"/>
+    <mergeCell ref="C1664:C1679"/>
+    <mergeCell ref="C1680:C1696"/>
+    <mergeCell ref="C1697:C1710"/>
+    <mergeCell ref="C1711:C1726"/>
+    <mergeCell ref="C1727:C1735"/>
+    <mergeCell ref="C1736:C1749"/>
+    <mergeCell ref="C1750:C1761"/>
+    <mergeCell ref="C1762:C1775"/>
+    <mergeCell ref="C1776:C1790"/>
+    <mergeCell ref="C1791:C1803"/>
+    <mergeCell ref="C1804:C1822"/>
+    <mergeCell ref="C1823:C1829"/>
+    <mergeCell ref="C1830:C1835"/>
+    <mergeCell ref="C1836:C1842"/>
+    <mergeCell ref="C1843:C1848"/>
+    <mergeCell ref="C1849:C1858"/>
+    <mergeCell ref="C1859:C1870"/>
+    <mergeCell ref="C1871:C1881"/>
+    <mergeCell ref="C1882:C1894"/>
+    <mergeCell ref="C1895:C1910"/>
+    <mergeCell ref="C1911:C1929"/>
+    <mergeCell ref="C1930:C1940"/>
+    <mergeCell ref="C1941:C1954"/>
+    <mergeCell ref="C1955:C1969"/>
+    <mergeCell ref="C1970:C1979"/>
+    <mergeCell ref="C1980:C1991"/>
+    <mergeCell ref="C1992:C2010"/>
+    <mergeCell ref="C2011:C2023"/>
+    <mergeCell ref="C2024:C2036"/>
+    <mergeCell ref="C2037:C2045"/>
+    <mergeCell ref="C2046:C2065"/>
+    <mergeCell ref="C2066:C2076"/>
+    <mergeCell ref="C2077:C2091"/>
+    <mergeCell ref="C2092:C2099"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -26182,15 +26148,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:E166"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.7788461538462" style="1" customWidth="1"/>
     <col min="2" max="2" width="47.1057692307692" customWidth="1"/>
     <col min="3" max="3" width="52.7788461538462" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:6">
+    <row r="1" ht="17" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -26200,13 +26166,10 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2185</v>
-      </c>
+      <c r="D1" s="3"/>
       <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" ht="17" spans="1:6">
+    </row>
+    <row r="2" ht="17" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
@@ -26216,11 +26179,10 @@
       <c r="C2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" ht="17" spans="1:6">
+    </row>
+    <row r="3" ht="17" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>105</v>
       </c>
@@ -26230,11 +26192,10 @@
       <c r="C3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" ht="17" spans="1:6">
+    </row>
+    <row r="4" ht="17" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>221</v>
       </c>
@@ -26244,11 +26205,10 @@
       <c r="C4" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" ht="17" spans="1:6">
+    </row>
+    <row r="5" ht="17" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>221</v>
       </c>
@@ -26258,11 +26218,10 @@
       <c r="C5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" ht="17" spans="1:6">
+    </row>
+    <row r="6" ht="17" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>221</v>
       </c>
@@ -26272,11 +26231,10 @@
       <c r="C6" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" ht="17" spans="1:6">
+    </row>
+    <row r="7" ht="17" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>308</v>
       </c>
@@ -26286,11 +26244,10 @@
       <c r="C7" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" ht="17" spans="1:6">
+    </row>
+    <row r="8" ht="17" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>386</v>
       </c>
@@ -26300,39 +26257,36 @@
       <c r="C8" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="17" spans="1:6">
+    </row>
+    <row r="9" ht="17" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D9" s="5"/>
+        <v>1491</v>
+      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" ht="17" spans="1:6">
+    </row>
+    <row r="10" ht="17" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2150</v>
-      </c>
-      <c r="D10" s="5"/>
+        <v>2147</v>
+      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" ht="17" spans="1:6">
+    </row>
+    <row r="11" ht="17" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>807</v>
       </c>
@@ -26342,11 +26296,10 @@
       <c r="C11" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" ht="17" spans="1:6">
+    </row>
+    <row r="12" ht="17" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>807</v>
       </c>
@@ -26356,11 +26309,10 @@
       <c r="C12" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" ht="17" spans="1:6">
+    </row>
+    <row r="13" ht="17" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>829</v>
       </c>
@@ -26370,11 +26322,10 @@
       <c r="C13" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="D13" s="5"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" ht="17" spans="1:6">
+    </row>
+    <row r="14" ht="17" spans="1:5">
       <c r="A14" s="2" t="s">
         <v>838</v>
       </c>
@@ -26384,11 +26335,10 @@
       <c r="C14" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" ht="17" spans="1:6">
+    </row>
+    <row r="15" ht="17" spans="1:5">
       <c r="A15" s="2" t="s">
         <v>838</v>
       </c>
@@ -26398,11 +26348,10 @@
       <c r="C15" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="D15" s="5"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" ht="17" spans="1:6">
+    </row>
+    <row r="16" ht="17" spans="1:5">
       <c r="A16" s="2" t="s">
         <v>864</v>
       </c>
@@ -26412,11 +26361,10 @@
       <c r="C16" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="D16" s="5"/>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" ht="17" spans="1:6">
+    </row>
+    <row r="17" ht="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>1035</v>
       </c>
@@ -26424,13 +26372,12 @@
         <v>1036</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2186</v>
-      </c>
-      <c r="D17" s="5"/>
+        <v>2182</v>
+      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" ht="17" spans="1:6">
+    </row>
+    <row r="18" ht="17" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>1035</v>
       </c>
@@ -26440,11 +26387,10 @@
       <c r="C18" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" ht="17" spans="1:6">
+    </row>
+    <row r="19" ht="17" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>1035</v>
       </c>
@@ -26454,11 +26400,10 @@
       <c r="C19" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="D19" s="5"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" ht="17" spans="1:6">
+    </row>
+    <row r="20" ht="17" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>1035</v>
       </c>
@@ -26468,11 +26413,10 @@
       <c r="C20" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" ht="17" spans="1:6">
+    </row>
+    <row r="21" ht="17" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>1035</v>
       </c>
@@ -26482,53 +26426,49 @@
       <c r="C21" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" ht="17" spans="1:6">
+    </row>
+    <row r="22" ht="17" spans="1:5">
       <c r="A22" s="2" t="s">
         <v>1221</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D22" s="5"/>
+        <v>1259</v>
+      </c>
+      <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" ht="17" spans="1:6">
+    </row>
+    <row r="23" ht="17" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1583</v>
-      </c>
-      <c r="D23" s="5"/>
+        <v>1580</v>
+      </c>
+      <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" ht="17" spans="1:6">
+    </row>
+    <row r="24" ht="17" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2071</v>
-      </c>
-      <c r="D24" s="5"/>
+        <v>2068</v>
+      </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" ht="17" spans="1:6">
+    </row>
+    <row r="25" ht="17" spans="1:5">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
@@ -26540,9 +26480,8 @@
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" ht="17" spans="1:6">
+    </row>
+    <row r="26" ht="17" spans="1:5">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -26554,25 +26493,21 @@
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" ht="17" spans="1:6">
+    </row>
+    <row r="27" ht="17" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D27" s="5"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" ht="17" spans="1:6">
+    </row>
+    <row r="28" ht="17" spans="1:5">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
@@ -26584,9 +26519,8 @@
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" ht="17" spans="1:6">
+    </row>
+    <row r="29" ht="17" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>117</v>
       </c>
@@ -26598,9 +26532,8 @@
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" ht="17" spans="1:6">
+    </row>
+    <row r="30" ht="17" spans="1:5">
       <c r="A30" s="2" t="s">
         <v>117</v>
       </c>
@@ -26612,9 +26545,8 @@
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="6"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" ht="17" spans="1:6">
+    </row>
+    <row r="31" ht="17" spans="1:5">
       <c r="A31" s="2" t="s">
         <v>117</v>
       </c>
@@ -26626,9 +26558,8 @@
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" ht="17" spans="1:6">
+    </row>
+    <row r="32" ht="17" spans="1:5">
       <c r="A32" s="2" t="s">
         <v>117</v>
       </c>
@@ -26640,9 +26571,8 @@
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" ht="17" spans="1:6">
+    </row>
+    <row r="33" ht="17" spans="1:5">
       <c r="A33" s="2" t="s">
         <v>117</v>
       </c>
@@ -26654,41 +26584,34 @@
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" ht="17" spans="1:6">
+    </row>
+    <row r="34" ht="17" spans="1:5">
       <c r="A34" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>192</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D34" s="5"/>
       <c r="E34" s="6"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" ht="17" spans="1:6">
+    </row>
+    <row r="35" ht="17" spans="1:5">
       <c r="A35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D35" s="5"/>
       <c r="E35" s="6"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" ht="17" spans="1:6">
+    </row>
+    <row r="36" ht="17" spans="1:5">
       <c r="A36" s="2" t="s">
         <v>198</v>
       </c>
@@ -26700,9 +26623,8 @@
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="6"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" ht="17" spans="1:6">
+    </row>
+    <row r="37" ht="17" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>212</v>
       </c>
@@ -26714,41 +26636,34 @@
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="6"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" ht="17" spans="1:6">
+    </row>
+    <row r="38" ht="17" spans="1:5">
       <c r="A38" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>222</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D38" s="5"/>
       <c r="E38" s="6"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" ht="17" spans="1:6">
+    </row>
+    <row r="39" ht="17" spans="1:5">
       <c r="A39" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>233</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D39" s="5"/>
       <c r="E39" s="6"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" ht="17" spans="1:6">
+    </row>
+    <row r="40" ht="17" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>258</v>
       </c>
@@ -26759,10 +26674,9 @@
         <v>260</v>
       </c>
       <c r="D40" s="5"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" ht="17" spans="1:6">
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" ht="17" spans="1:5">
       <c r="A41" s="2" t="s">
         <v>258</v>
       </c>
@@ -26773,10 +26687,9 @@
         <v>273</v>
       </c>
       <c r="D41" s="5"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" ht="17" spans="1:6">
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" ht="17" spans="1:5">
       <c r="A42" s="2" t="s">
         <v>258</v>
       </c>
@@ -26787,10 +26700,9 @@
         <v>289</v>
       </c>
       <c r="D42" s="5"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="3"/>
-    </row>
-    <row r="43" ht="17" spans="1:6">
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" ht="17" spans="1:5">
       <c r="A43" s="2" t="s">
         <v>258</v>
       </c>
@@ -26801,90 +26713,74 @@
         <v>299</v>
       </c>
       <c r="D43" s="5"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="3"/>
-    </row>
-    <row r="44" ht="17" spans="1:6">
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" ht="17" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>321</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D44" s="5"/>
       <c r="E44" s="6"/>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" ht="17" spans="1:6">
+    </row>
+    <row r="45" ht="17" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>331</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D45" s="5"/>
       <c r="E45" s="6"/>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" ht="17" spans="1:6">
+    </row>
+    <row r="46" ht="17" spans="1:5">
       <c r="A46" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>338</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D46" s="5"/>
       <c r="E46" s="6"/>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" ht="17" spans="1:6">
+    </row>
+    <row r="47" ht="17" spans="1:5">
       <c r="A47" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>362</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D47" s="5"/>
       <c r="E47" s="6"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" ht="17" spans="1:6">
+    </row>
+    <row r="48" ht="17" spans="1:5">
       <c r="A48" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>381</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>2187</v>
-      </c>
+      <c r="D48" s="5"/>
       <c r="E48" s="6"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" ht="17" spans="1:6">
+    </row>
+    <row r="49" ht="17" spans="1:5">
       <c r="A49" s="2" t="s">
         <v>396</v>
       </c>
@@ -26895,10 +26791,9 @@
         <v>398</v>
       </c>
       <c r="D49" s="5"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="3"/>
-    </row>
-    <row r="50" ht="17" spans="1:6">
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" ht="17" spans="1:5">
       <c r="A50" s="2" t="s">
         <v>420</v>
       </c>
@@ -26909,10 +26804,9 @@
         <v>422</v>
       </c>
       <c r="D50" s="5"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" ht="17" spans="1:6">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" ht="17" spans="1:5">
       <c r="A51" s="2" t="s">
         <v>420</v>
       </c>
@@ -26923,138 +26817,113 @@
         <v>437</v>
       </c>
       <c r="D51" s="5"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="3"/>
-    </row>
-    <row r="52" ht="17" spans="1:6">
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" ht="17" spans="1:5">
       <c r="A52" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>411</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="3"/>
-    </row>
-    <row r="53" ht="17" spans="1:6">
+      <c r="D52" s="5"/>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" ht="17" spans="1:5">
       <c r="A53" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>447</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="3"/>
-    </row>
-    <row r="54" ht="17" spans="1:6">
+      <c r="D53" s="5"/>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" ht="17" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>694</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="3"/>
-    </row>
-    <row r="55" ht="17" spans="1:6">
+      <c r="D54" s="5"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" ht="17" spans="1:5">
       <c r="A55" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>705</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="56" ht="17" spans="1:6">
+      <c r="D55" s="5"/>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" ht="17" spans="1:5">
       <c r="A56" s="2" t="s">
         <v>1188</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>1189</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>1190</v>
       </c>
-      <c r="D56" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="3"/>
-    </row>
-    <row r="57" ht="17" spans="1:6">
+      <c r="D56" s="5"/>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" ht="17" spans="1:5">
       <c r="A57" s="2" t="s">
         <v>1208</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>1209</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>1210</v>
       </c>
-      <c r="D57" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="3"/>
-    </row>
-    <row r="58" ht="17" spans="1:6">
+      <c r="D57" s="5"/>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" ht="17" spans="1:5">
       <c r="A58" s="2" t="s">
-        <v>1541</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>1542</v>
+        <v>1538</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>1539</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>1543</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="3"/>
-    </row>
-    <row r="59" ht="17" spans="1:6">
+        <v>1540</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" ht="17" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>2122</v>
+        <v>2118</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>2119</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2123</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" ht="17" spans="1:6">
+        <v>2120</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" ht="17" spans="1:5">
       <c r="A60" s="2" t="s">
         <v>456</v>
       </c>
@@ -27065,10 +26934,9 @@
         <v>458</v>
       </c>
       <c r="D60" s="5"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="3"/>
-    </row>
-    <row r="61" ht="17" spans="1:6">
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" ht="17" spans="1:5">
       <c r="A61" s="2" t="s">
         <v>479</v>
       </c>
@@ -27079,10 +26947,9 @@
         <v>481</v>
       </c>
       <c r="D61" s="5"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="3"/>
-    </row>
-    <row r="62" ht="17" spans="1:6">
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" ht="17" spans="1:5">
       <c r="A62" s="2" t="s">
         <v>479</v>
       </c>
@@ -27093,10 +26960,9 @@
         <v>491</v>
       </c>
       <c r="D62" s="5"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="3"/>
-    </row>
-    <row r="63" ht="17" spans="1:6">
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" ht="17" spans="1:5">
       <c r="A63" s="2" t="s">
         <v>514</v>
       </c>
@@ -27107,42 +26973,35 @@
         <v>516</v>
       </c>
       <c r="D63" s="5"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="3"/>
-    </row>
-    <row r="64" ht="17" spans="1:6">
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" ht="17" spans="1:5">
       <c r="A64" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>534</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="3"/>
-    </row>
-    <row r="65" ht="17" spans="1:6">
+      <c r="D64" s="5"/>
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" ht="17" spans="1:5">
       <c r="A65" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>537</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" ht="17" spans="1:6">
+      <c r="D65" s="5"/>
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" ht="17" spans="1:5">
       <c r="A66" s="2" t="s">
         <v>553</v>
       </c>
@@ -27153,42 +27012,35 @@
         <v>555</v>
       </c>
       <c r="D66" s="5"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="3"/>
-    </row>
-    <row r="67" ht="17" spans="1:6">
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" ht="17" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>565</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="3"/>
-    </row>
-    <row r="68" ht="17" spans="1:6">
+      <c r="D67" s="5"/>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" ht="17" spans="1:5">
       <c r="A68" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>574</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="3"/>
-    </row>
-    <row r="69" ht="17" spans="1:6">
+      <c r="D68" s="5"/>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" ht="17" spans="1:5">
       <c r="A69" s="2" t="s">
         <v>553</v>
       </c>
@@ -27199,10 +27051,9 @@
         <v>598</v>
       </c>
       <c r="D69" s="5"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="3"/>
-    </row>
-    <row r="70" ht="17" spans="1:6">
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" ht="17" spans="1:5">
       <c r="A70" s="2" t="s">
         <v>553</v>
       </c>
@@ -27213,74 +27064,61 @@
         <v>617</v>
       </c>
       <c r="D70" s="5"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="3"/>
-    </row>
-    <row r="71" ht="17" spans="1:6">
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" ht="17" spans="1:5">
       <c r="A71" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>650</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="D71" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="3"/>
-    </row>
-    <row r="72" ht="17" spans="1:6">
+      <c r="D71" s="5"/>
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" ht="17" spans="1:5">
       <c r="A72" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>662</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D72" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="3"/>
-    </row>
-    <row r="73" ht="17" spans="1:6">
+      <c r="D72" s="5"/>
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" ht="17" spans="1:5">
       <c r="A73" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>676</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="D73" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E73" s="6"/>
-      <c r="F73" s="3"/>
-    </row>
-    <row r="74" ht="17" spans="1:6">
+      <c r="D73" s="5"/>
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" ht="17" spans="1:5">
       <c r="A74" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>687</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>2187</v>
-      </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="3"/>
-    </row>
-    <row r="75" ht="17" spans="1:6">
+      <c r="D74" s="5"/>
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" ht="17" spans="1:5">
       <c r="A75" s="2" t="s">
         <v>708</v>
       </c>
@@ -27291,10 +27129,9 @@
         <v>710</v>
       </c>
       <c r="D75" s="5"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" ht="17" spans="1:6">
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" ht="17" spans="1:5">
       <c r="A76" s="2" t="s">
         <v>708</v>
       </c>
@@ -27305,26 +27142,22 @@
         <v>718</v>
       </c>
       <c r="D76" s="5"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="3"/>
-    </row>
-    <row r="77" ht="17" spans="1:6">
+      <c r="E76" s="3"/>
+    </row>
+    <row r="77" ht="17" spans="1:5">
       <c r="A77" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>731</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" ht="17" spans="1:6">
+      <c r="D77" s="5"/>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" ht="17" spans="1:5">
       <c r="A78" s="2" t="s">
         <v>743</v>
       </c>
@@ -27335,10 +27168,9 @@
         <v>743</v>
       </c>
       <c r="D78" s="5"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="3"/>
-    </row>
-    <row r="79" ht="17" spans="1:6">
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" ht="17" spans="1:5">
       <c r="A79" s="2" t="s">
         <v>746</v>
       </c>
@@ -27349,106 +27181,87 @@
         <v>746</v>
       </c>
       <c r="D79" s="5"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="3"/>
-    </row>
-    <row r="80" ht="17" spans="1:6">
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" ht="17" spans="1:5">
       <c r="A80" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>750</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="3"/>
-    </row>
-    <row r="81" ht="17" spans="1:6">
+      <c r="D80" s="5"/>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" ht="17" spans="1:5">
       <c r="A81" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>773</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="D81" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="3"/>
-    </row>
-    <row r="82" ht="17" spans="1:6">
+      <c r="D81" s="5"/>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" ht="17" spans="1:5">
       <c r="A82" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>791</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="D82" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="5"/>
-    </row>
-    <row r="83" ht="17" spans="1:6">
+      <c r="D82" s="5"/>
+      <c r="E82" s="8"/>
+    </row>
+    <row r="83" ht="17" spans="1:5">
       <c r="A83" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>800</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="D83" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="5"/>
-    </row>
-    <row r="84" ht="17" spans="1:6">
+      <c r="D83" s="5"/>
+      <c r="E83" s="8"/>
+    </row>
+    <row r="84" ht="17" spans="1:5">
       <c r="A84" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>881</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="D84" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="5"/>
-    </row>
-    <row r="85" ht="17" spans="1:6">
+      <c r="D84" s="5"/>
+      <c r="E84" s="8"/>
+    </row>
+    <row r="85" ht="17" spans="1:5">
       <c r="A85" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>896</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="5"/>
-    </row>
-    <row r="86" ht="17" spans="1:6">
+      <c r="D85" s="5"/>
+      <c r="E85" s="8"/>
+    </row>
+    <row r="86" ht="17" spans="1:5">
       <c r="A86" s="2" t="s">
         <v>910</v>
       </c>
@@ -27459,10 +27272,9 @@
         <v>912</v>
       </c>
       <c r="D86" s="5"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="3"/>
-    </row>
-    <row r="87" ht="17" spans="1:6">
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" ht="17" spans="1:5">
       <c r="A87" s="2" t="s">
         <v>910</v>
       </c>
@@ -27473,10 +27285,9 @@
         <v>924</v>
       </c>
       <c r="D87" s="5"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="3"/>
-    </row>
-    <row r="88" ht="17" spans="1:6">
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" ht="17" spans="1:5">
       <c r="A88" s="2" t="s">
         <v>910</v>
       </c>
@@ -27487,10 +27298,9 @@
         <v>946</v>
       </c>
       <c r="D88" s="5"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="3"/>
-    </row>
-    <row r="89" ht="17" spans="1:6">
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" ht="17" spans="1:5">
       <c r="A89" s="2" t="s">
         <v>910</v>
       </c>
@@ -27501,10 +27311,9 @@
         <v>977</v>
       </c>
       <c r="D89" s="5"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="3"/>
-    </row>
-    <row r="90" ht="17" spans="1:6">
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" ht="17" spans="1:5">
       <c r="A90" s="2" t="s">
         <v>991</v>
       </c>
@@ -27515,10 +27324,9 @@
         <v>993</v>
       </c>
       <c r="D90" s="5"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="3"/>
-    </row>
-    <row r="91" ht="17" spans="1:6">
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" ht="17" spans="1:5">
       <c r="A91" s="2" t="s">
         <v>991</v>
       </c>
@@ -27529,10 +27337,9 @@
         <v>1005</v>
       </c>
       <c r="D91" s="5"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="3"/>
-    </row>
-    <row r="92" ht="17" spans="1:6">
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" ht="17" spans="1:5">
       <c r="A92" s="2" t="s">
         <v>1011</v>
       </c>
@@ -27543,10 +27350,9 @@
         <v>1013</v>
       </c>
       <c r="D92" s="5"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="3"/>
-    </row>
-    <row r="93" ht="17" spans="1:6">
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" ht="17" spans="1:5">
       <c r="A93" s="2" t="s">
         <v>1011</v>
       </c>
@@ -27557,10 +27363,9 @@
         <v>1021</v>
       </c>
       <c r="D93" s="5"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="3"/>
-    </row>
-    <row r="94" ht="17" spans="1:6">
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" ht="17" spans="1:5">
       <c r="A94" s="2" t="s">
         <v>1113</v>
       </c>
@@ -27570,11 +27375,10 @@
       <c r="C94" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="D94" s="5"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="3"/>
-    </row>
-    <row r="95" ht="17" spans="1:6">
+      <c r="D94" s="9"/>
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" ht="17" spans="1:5">
       <c r="A95" s="2" t="s">
         <v>1113</v>
       </c>
@@ -27584,11 +27388,10 @@
       <c r="C95" s="2" t="s">
         <v>1132</v>
       </c>
-      <c r="D95" s="5"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="3"/>
-    </row>
-    <row r="96" ht="17" spans="1:6">
+      <c r="D95" s="9"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" ht="17" spans="1:5">
       <c r="A96" s="2" t="s">
         <v>1113</v>
       </c>
@@ -27598,11 +27401,10 @@
       <c r="C96" s="2" t="s">
         <v>1142</v>
       </c>
-      <c r="D96" s="5"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="3"/>
-    </row>
-    <row r="97" ht="17" spans="1:6">
+      <c r="D96" s="9"/>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" ht="17" spans="1:5">
       <c r="A97" s="2" t="s">
         <v>1166</v>
       </c>
@@ -27613,1012 +27415,904 @@
         <v>1168</v>
       </c>
       <c r="D97" s="5"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="3"/>
-    </row>
-    <row r="98" ht="17" spans="1:6">
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" ht="17" spans="1:5">
       <c r="A98" s="2" t="s">
         <v>1200</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="7" t="s">
         <v>1201</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="3"/>
-    </row>
-    <row r="99" ht="17" spans="1:6">
+      <c r="D98" s="5"/>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" ht="17" spans="1:5">
       <c r="A99" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="7" t="s">
         <v>1222</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E99" s="9"/>
-      <c r="F99" s="3"/>
-    </row>
-    <row r="100" ht="17" spans="1:6">
+      <c r="D99" s="5"/>
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" ht="17" spans="1:5">
       <c r="A100" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="B100" s="8" t="s">
-        <v>1245</v>
+      <c r="B100" s="7" t="s">
+        <v>1242</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E100" s="9"/>
-      <c r="F100" s="3"/>
-    </row>
-    <row r="101" ht="17" spans="1:6">
+        <v>1243</v>
+      </c>
+      <c r="D100" s="5"/>
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" ht="17" spans="1:5">
       <c r="A101" s="2" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="D101" s="5"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="3"/>
-    </row>
-    <row r="102" ht="17" spans="1:6">
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" ht="17" spans="1:5">
       <c r="A102" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>1294</v>
+        <v>1290</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>1291</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D102" s="5"/>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" ht="17" spans="1:5">
+      <c r="A103" s="2" t="s">
         <v>1295</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="3"/>
-    </row>
-    <row r="103" ht="17" spans="1:6">
-      <c r="A103" s="2" t="s">
-        <v>1298</v>
-      </c>
       <c r="B103" s="2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="D103" s="5"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="3"/>
-    </row>
-    <row r="104" ht="17" spans="1:6">
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" ht="17" spans="1:5">
       <c r="A104" s="2" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="D104" s="5"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="3"/>
-    </row>
-    <row r="105" ht="17" spans="1:6">
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" ht="17" spans="1:5">
       <c r="A105" s="2" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="D105" s="5"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="3"/>
-    </row>
-    <row r="106" ht="17" spans="1:6">
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" ht="17" spans="1:5">
       <c r="A106" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-    </row>
-    <row r="107" ht="17" spans="1:6">
+    </row>
+    <row r="107" ht="17" spans="1:5">
       <c r="A107" s="2" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="D107" s="5"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-    </row>
-    <row r="108" ht="17" spans="1:6">
+      <c r="E107" s="6"/>
+    </row>
+    <row r="108" ht="17" spans="1:5">
       <c r="A108" s="2" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-    </row>
-    <row r="109" ht="17" spans="1:6">
+    </row>
+    <row r="109" ht="17" spans="1:5">
       <c r="A109" s="2" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-    </row>
-    <row r="110" ht="17" spans="1:6">
+    </row>
+    <row r="110" ht="17" spans="1:5">
       <c r="A110" s="2" t="s">
-        <v>1369</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>1399</v>
+        <v>1366</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>1396</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1397</v>
+      </c>
+      <c r="D110" s="5"/>
       <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-    </row>
-    <row r="111" ht="17" spans="1:6">
+    </row>
+    <row r="111" ht="17" spans="1:5">
       <c r="A111" s="2" t="s">
-        <v>1369</v>
-      </c>
-      <c r="B111" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D111" s="5"/>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" ht="17" spans="1:5">
+      <c r="A112" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>1405</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-    </row>
-    <row r="112" ht="17" spans="1:6">
-      <c r="A112" s="2" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>1408</v>
-      </c>
       <c r="C112" s="2" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-    </row>
-    <row r="113" ht="17" spans="1:6">
+    </row>
+    <row r="113" ht="17" spans="1:5">
       <c r="A113" s="2" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-    </row>
-    <row r="114" ht="17" spans="1:6">
+    </row>
+    <row r="114" ht="17" spans="1:5">
       <c r="A114" s="2" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>1443</v>
+        <v>1439</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>1440</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1441</v>
+      </c>
+      <c r="D114" s="5"/>
       <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-    </row>
-    <row r="115" ht="17" spans="1:6">
+    </row>
+    <row r="115" ht="17" spans="1:5">
       <c r="A115" s="2" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="D115" s="5"/>
+        <v>1478</v>
+      </c>
+      <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-    </row>
-    <row r="116" ht="17" spans="1:6">
+    </row>
+    <row r="116" ht="17" spans="1:5">
       <c r="A116" s="2" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D116" s="5"/>
+        <v>1506</v>
+      </c>
+      <c r="D116" s="3"/>
       <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-    </row>
-    <row r="117" ht="17" spans="1:6">
+    </row>
+    <row r="117" ht="17" spans="1:5">
       <c r="A117" s="2" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1527</v>
-      </c>
-      <c r="D117" s="5"/>
+        <v>1524</v>
+      </c>
+      <c r="D117" s="3"/>
       <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-    </row>
-    <row r="118" ht="17" spans="1:6">
+    </row>
+    <row r="118" ht="17" spans="1:5">
       <c r="A118" s="2" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D118" s="5"/>
+        <v>1557</v>
+      </c>
+      <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-    </row>
-    <row r="119" ht="17" spans="1:6">
+    </row>
+    <row r="119" ht="17" spans="1:5">
       <c r="A119" s="2" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1567</v>
-      </c>
-      <c r="D119" s="5"/>
+        <v>1564</v>
+      </c>
+      <c r="D119" s="3"/>
       <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-    </row>
-    <row r="120" ht="17" spans="1:6">
+    </row>
+    <row r="120" ht="17" spans="1:5">
       <c r="A120" s="2" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D120" s="5"/>
+        <v>1596</v>
+      </c>
+      <c r="D120" s="3"/>
       <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-    </row>
-    <row r="121" ht="17" spans="1:6">
+    </row>
+    <row r="121" ht="17" spans="1:5">
       <c r="A121" s="2" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1606</v>
-      </c>
-      <c r="D121" s="5"/>
+        <v>1603</v>
+      </c>
+      <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-    </row>
-    <row r="122" ht="17" spans="1:6">
+    </row>
+    <row r="122" ht="17" spans="1:5">
       <c r="A122" s="2" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="D122" s="5"/>
+        <v>1613</v>
+      </c>
+      <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-    </row>
-    <row r="123" ht="17" spans="1:6">
+    </row>
+    <row r="123" ht="17" spans="1:5">
       <c r="A123" s="2" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1628</v>
-      </c>
-      <c r="D123" s="5"/>
+        <v>1625</v>
+      </c>
+      <c r="D123" s="3"/>
       <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
-    </row>
-    <row r="124" ht="17" spans="1:6">
+    </row>
+    <row r="124" ht="17" spans="1:5">
       <c r="A124" s="2" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1639</v>
-      </c>
-      <c r="D124" s="5"/>
+        <v>1636</v>
+      </c>
+      <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-    </row>
-    <row r="125" ht="17" spans="1:6">
+    </row>
+    <row r="125" ht="17" spans="1:5">
       <c r="A125" s="2" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>1652</v>
-      </c>
-      <c r="D125" s="5"/>
+        <v>1649</v>
+      </c>
+      <c r="D125" s="3"/>
       <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
-    </row>
-    <row r="126" ht="17" spans="1:6">
+    </row>
+    <row r="126" ht="17" spans="1:5">
       <c r="A126" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D126" s="5"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" ht="17" spans="1:5">
+      <c r="A127" s="2" t="s">
         <v>1659</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B127" s="7" t="s">
         <v>1660</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>1659</v>
-      </c>
-      <c r="D126" s="5"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="3"/>
-    </row>
-    <row r="127" ht="17" spans="1:6">
-      <c r="A127" s="2" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>1663</v>
-      </c>
       <c r="C127" s="2" t="s">
-        <v>1664</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1661</v>
+      </c>
+      <c r="D127" s="3"/>
       <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-    </row>
-    <row r="128" ht="17" spans="1:6">
+    </row>
+    <row r="128" ht="17" spans="1:5">
       <c r="A128" s="2" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1676</v>
-      </c>
-      <c r="D128" s="5"/>
+        <v>1673</v>
+      </c>
+      <c r="D128" s="3"/>
       <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
-    </row>
-    <row r="129" ht="17" spans="1:6">
+    </row>
+    <row r="129" ht="17" spans="1:5">
       <c r="A129" s="2" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>1696</v>
-      </c>
-      <c r="D129" s="5"/>
+        <v>1693</v>
+      </c>
+      <c r="D129" s="3"/>
       <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-    </row>
-    <row r="130" ht="17" spans="1:6">
+    </row>
+    <row r="130" ht="17" spans="1:5">
       <c r="A130" s="2" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1711</v>
-      </c>
-      <c r="D130" s="5"/>
+        <v>1708</v>
+      </c>
+      <c r="D130" s="3"/>
       <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
-    </row>
-    <row r="131" ht="17" spans="1:6">
+    </row>
+    <row r="131" ht="17" spans="1:5">
       <c r="A131" s="2" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>1729</v>
-      </c>
-      <c r="D131" s="5"/>
+        <v>1726</v>
+      </c>
+      <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-    </row>
-    <row r="132" ht="17" spans="1:6">
+    </row>
+    <row r="132" ht="17" spans="1:5">
       <c r="A132" s="2" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1743</v>
-      </c>
-      <c r="D132" s="5"/>
+        <v>1740</v>
+      </c>
+      <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-    </row>
-    <row r="133" ht="17" spans="1:6">
+    </row>
+    <row r="133" ht="17" spans="1:5">
       <c r="A133" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1752</v>
-      </c>
-      <c r="D133" s="5"/>
+        <v>1749</v>
+      </c>
+      <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
-    </row>
-    <row r="134" ht="17" spans="1:6">
+    </row>
+    <row r="134" ht="17" spans="1:5">
       <c r="A134" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1768</v>
-      </c>
-      <c r="D134" s="5"/>
+        <v>1765</v>
+      </c>
+      <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
-    </row>
-    <row r="135" ht="17" spans="1:6">
+    </row>
+    <row r="135" ht="17" spans="1:5">
       <c r="A135" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1782</v>
-      </c>
-      <c r="D135" s="5"/>
+        <v>1779</v>
+      </c>
+      <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
-    </row>
-    <row r="136" ht="17" spans="1:6">
+    </row>
+    <row r="136" ht="17" spans="1:5">
       <c r="A136" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>1797</v>
+        <v>1747</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>1794</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1798</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1795</v>
+      </c>
+      <c r="D136" s="3"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
-    </row>
-    <row r="137" ht="17" spans="1:6">
+    </row>
+    <row r="137" ht="17" spans="1:5">
       <c r="A137" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>1814</v>
+        <v>1747</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>1811</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1812</v>
+      </c>
+      <c r="D137" s="3"/>
       <c r="E137" s="3"/>
-      <c r="F137" s="3"/>
-    </row>
-    <row r="138" ht="17" spans="1:6">
+    </row>
+    <row r="138" ht="17" spans="1:5">
       <c r="A138" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D138" s="5"/>
+        <v>1824</v>
+      </c>
+      <c r="D138" s="3"/>
       <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-    </row>
-    <row r="139" ht="17" spans="1:6">
+    </row>
+    <row r="139" ht="17" spans="1:5">
       <c r="A139" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="D139" s="5"/>
+        <v>1839</v>
+      </c>
+      <c r="D139" s="3"/>
       <c r="E139" s="3"/>
-      <c r="F139" s="3"/>
-    </row>
-    <row r="140" ht="17" spans="1:6">
+    </row>
+    <row r="140" ht="17" spans="1:5">
       <c r="A140" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="D140" s="5"/>
+        <v>1847</v>
+      </c>
+      <c r="D140" s="3"/>
       <c r="E140" s="3"/>
-      <c r="F140" s="3"/>
-    </row>
-    <row r="141" ht="17" spans="1:6">
+    </row>
+    <row r="141" ht="17" spans="1:5">
       <c r="A141" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1862</v>
-      </c>
-      <c r="D141" s="5"/>
+        <v>1859</v>
+      </c>
+      <c r="D141" s="3"/>
       <c r="E141" s="3"/>
-      <c r="F141" s="3"/>
-    </row>
-    <row r="142" ht="17" spans="1:6">
+    </row>
+    <row r="142" ht="17" spans="1:5">
       <c r="A142" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D142" s="5"/>
+        <v>1868</v>
+      </c>
+      <c r="D142" s="3"/>
       <c r="E142" s="3"/>
-      <c r="F142" s="3"/>
-    </row>
-    <row r="143" ht="17" spans="1:6">
+    </row>
+    <row r="143" ht="17" spans="1:5">
       <c r="A143" s="2" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D143" s="5"/>
+        <v>1881</v>
+      </c>
+      <c r="D143" s="3"/>
       <c r="E143" s="3"/>
-      <c r="F143" s="3"/>
-    </row>
-    <row r="144" ht="17" spans="1:6">
+    </row>
+    <row r="144" ht="17" spans="1:5">
       <c r="A144" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B144" s="8" t="s">
-        <v>1896</v>
+        <v>1747</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>1893</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1897</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1894</v>
+      </c>
+      <c r="D144" s="3"/>
       <c r="E144" s="3"/>
-      <c r="F144" s="3"/>
-    </row>
-    <row r="145" ht="17" spans="1:6">
+    </row>
+    <row r="145" ht="17" spans="1:5">
       <c r="A145" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>1908</v>
+        <v>1747</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>1905</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1906</v>
+      </c>
+      <c r="D145" s="3"/>
       <c r="E145" s="3"/>
-      <c r="F145" s="3"/>
-    </row>
-    <row r="146" ht="17" spans="1:6">
+    </row>
+    <row r="146" ht="17" spans="1:5">
       <c r="A146" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>1925</v>
+        <v>1747</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>1922</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1923</v>
+      </c>
+      <c r="D146" s="3"/>
       <c r="E146" s="3"/>
-      <c r="F146" s="3"/>
-    </row>
-    <row r="147" ht="17" spans="1:6">
+    </row>
+    <row r="147" ht="17" spans="1:5">
       <c r="A147" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B147" s="8" t="s">
-        <v>1931</v>
+        <v>1747</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>1928</v>
       </c>
       <c r="C147" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" ht="17" spans="1:5">
+      <c r="A148" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B148" s="7" t="s">
         <v>1932</v>
       </c>
-      <c r="D147" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E147" s="3"/>
-      <c r="F147" s="3"/>
-    </row>
-    <row r="148" ht="17" spans="1:6">
-      <c r="A148" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B148" s="8" t="s">
-        <v>1935</v>
-      </c>
       <c r="C148" s="2" t="s">
-        <v>1936</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1933</v>
+      </c>
+      <c r="D148" s="3"/>
       <c r="E148" s="3"/>
-      <c r="F148" s="3"/>
-    </row>
-    <row r="149" ht="17" spans="1:6">
+    </row>
+    <row r="149" ht="17" spans="1:5">
       <c r="A149" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B149" s="8" t="s">
-        <v>1940</v>
+        <v>1747</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>1937</v>
       </c>
       <c r="C149" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D149" s="3"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" ht="17" spans="1:5">
+      <c r="A150" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B150" s="7" t="s">
         <v>1941</v>
       </c>
-      <c r="D149" s="5" t="s">
-        <v>2188</v>
-      </c>
-      <c r="E149" s="3"/>
-      <c r="F149" s="3"/>
-    </row>
-    <row r="150" ht="17" spans="1:6">
-      <c r="A150" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B150" s="8" t="s">
-        <v>1944</v>
-      </c>
       <c r="C150" s="2" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1942</v>
+      </c>
+      <c r="D150" s="3"/>
       <c r="E150" s="3"/>
-      <c r="F150" s="3"/>
-    </row>
-    <row r="151" ht="17" spans="1:6">
+    </row>
+    <row r="151" ht="17" spans="1:5">
       <c r="A151" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B151" s="8" t="s">
-        <v>1953</v>
+        <v>1747</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>1950</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1954</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1951</v>
+      </c>
+      <c r="D151" s="3"/>
       <c r="E151" s="3"/>
-      <c r="F151" s="3"/>
-    </row>
-    <row r="152" ht="17" spans="1:6">
+    </row>
+    <row r="152" ht="17" spans="1:5">
       <c r="A152" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B152" s="8" t="s">
-        <v>1961</v>
+        <v>1747</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>1958</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>2188</v>
-      </c>
+        <v>1959</v>
+      </c>
+      <c r="D152" s="3"/>
       <c r="E152" s="3"/>
-      <c r="F152" s="3"/>
-    </row>
-    <row r="153" ht="17" spans="1:6">
+    </row>
+    <row r="153" ht="17" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D153" s="5"/>
+        <v>1970</v>
+      </c>
+      <c r="D153" s="3"/>
       <c r="E153" s="3"/>
-      <c r="F153" s="3"/>
-    </row>
-    <row r="154" ht="17" spans="1:6">
+    </row>
+    <row r="154" ht="17" spans="1:5">
       <c r="A154" s="2" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D154" s="5"/>
+        <v>1983</v>
+      </c>
+      <c r="D154" s="3"/>
       <c r="E154" s="3"/>
-      <c r="F154" s="3"/>
-    </row>
-    <row r="155" ht="17" spans="1:6">
+    </row>
+    <row r="155" ht="17" spans="1:5">
       <c r="A155" s="2" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>2004</v>
-      </c>
-      <c r="D155" s="5"/>
+        <v>2001</v>
+      </c>
+      <c r="D155" s="3"/>
       <c r="E155" s="3"/>
-      <c r="F155" s="3"/>
-    </row>
-    <row r="156" ht="17" spans="1:6">
+    </row>
+    <row r="156" ht="17" spans="1:5">
       <c r="A156" s="2" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>2023</v>
-      </c>
-      <c r="D156" s="5"/>
+        <v>2020</v>
+      </c>
+      <c r="D156" s="3"/>
       <c r="E156" s="3"/>
-      <c r="F156" s="3"/>
-    </row>
-    <row r="157" ht="17" spans="1:6">
+    </row>
+    <row r="157" ht="17" spans="1:5">
       <c r="A157" s="2" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D157" s="5"/>
+        <v>2031</v>
+      </c>
+      <c r="D157" s="3"/>
       <c r="E157" s="3"/>
-      <c r="F157" s="3"/>
-    </row>
-    <row r="158" ht="17" spans="1:6">
+    </row>
+    <row r="158" ht="17" spans="1:5">
       <c r="A158" s="2" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>2046</v>
-      </c>
-      <c r="D158" s="5"/>
+        <v>2043</v>
+      </c>
+      <c r="D158" s="3"/>
       <c r="E158" s="3"/>
-      <c r="F158" s="3"/>
-    </row>
-    <row r="159" ht="17" spans="1:6">
+    </row>
+    <row r="159" ht="17" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>2060</v>
-      </c>
-      <c r="D159" s="5"/>
+        <v>2057</v>
+      </c>
+      <c r="D159" s="3"/>
       <c r="E159" s="3"/>
-      <c r="F159" s="3"/>
-    </row>
-    <row r="160" ht="17" spans="1:6">
+    </row>
+    <row r="160" ht="17" spans="1:5">
       <c r="A160" s="2" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2189</v>
+        <v>2183</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>2190</v>
-      </c>
-      <c r="D160" s="5"/>
+        <v>2184</v>
+      </c>
+      <c r="D160" s="3"/>
       <c r="E160" s="3"/>
-      <c r="F160" s="3"/>
-    </row>
-    <row r="161" ht="17" spans="1:6">
+    </row>
+    <row r="161" ht="17" spans="1:5">
       <c r="A161" s="2" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>2085</v>
-      </c>
-      <c r="D161" s="5"/>
+        <v>2082</v>
+      </c>
+      <c r="D161" s="3"/>
       <c r="E161" s="3"/>
-      <c r="F161" s="3"/>
-    </row>
-    <row r="162" ht="17" spans="1:6">
+    </row>
+    <row r="162" ht="17" spans="1:5">
       <c r="A162" s="2" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>2103</v>
-      </c>
-      <c r="D162" s="5"/>
+        <v>2100</v>
+      </c>
+      <c r="D162" s="3"/>
       <c r="E162" s="3"/>
-      <c r="F162" s="3"/>
-    </row>
-    <row r="163" ht="17" spans="1:6">
+    </row>
+    <row r="163" ht="17" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>2117</v>
-      </c>
-      <c r="D163" s="5"/>
+        <v>2114</v>
+      </c>
+      <c r="D163" s="3"/>
       <c r="E163" s="3"/>
-      <c r="F163" s="3"/>
-    </row>
-    <row r="164" ht="17" spans="1:6">
+    </row>
+    <row r="164" ht="17" spans="1:5">
       <c r="A164" s="2" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>2128</v>
-      </c>
-      <c r="D164" s="5"/>
+        <v>2125</v>
+      </c>
+      <c r="D164" s="3"/>
       <c r="E164" s="3"/>
-      <c r="F164" s="3"/>
-    </row>
-    <row r="165" ht="17" spans="1:6">
+    </row>
+    <row r="165" ht="17" spans="1:5">
       <c r="A165" s="2" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>2162</v>
-      </c>
-      <c r="D165" s="5"/>
+        <v>2159</v>
+      </c>
+      <c r="D165" s="3"/>
       <c r="E165" s="3"/>
-      <c r="F165" s="3"/>
-    </row>
-    <row r="166" ht="17" spans="1:6">
+    </row>
+    <row r="166" ht="17" spans="1:5">
       <c r="A166" s="2" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>2178</v>
-      </c>
-      <c r="D166" s="5"/>
+        <v>2175</v>
+      </c>
+      <c r="D166" s="3"/>
       <c r="E166" s="3"/>
-      <c r="F166" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -27648,7 +27648,7 @@
       <c r="C115" s="2" t="s">
         <v>1478</v>
       </c>
-      <c r="D115" s="3"/>
+      <c r="D115" s="5"/>
       <c r="E115" s="3"/>
     </row>
     <row r="116" ht="17" spans="1:5">
@@ -27661,7 +27661,7 @@
       <c r="C116" s="2" t="s">
         <v>1506</v>
       </c>
-      <c r="D116" s="3"/>
+      <c r="D116" s="5"/>
       <c r="E116" s="3"/>
     </row>
     <row r="117" ht="17" spans="1:5">
@@ -27674,7 +27674,7 @@
       <c r="C117" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="D117" s="3"/>
+      <c r="D117" s="5"/>
       <c r="E117" s="3"/>
     </row>
     <row r="118" ht="17" spans="1:5">
@@ -27687,7 +27687,7 @@
       <c r="C118" s="2" t="s">
         <v>1557</v>
       </c>
-      <c r="D118" s="3"/>
+      <c r="D118" s="5"/>
       <c r="E118" s="3"/>
     </row>
     <row r="119" ht="17" spans="1:5">
@@ -27713,7 +27713,7 @@
       <c r="C120" s="2" t="s">
         <v>1596</v>
       </c>
-      <c r="D120" s="3"/>
+      <c r="D120" s="5"/>
       <c r="E120" s="3"/>
     </row>
     <row r="121" ht="17" spans="1:5">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12680" activeTab="1"/>
+    <workbookView windowHeight="16300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3094" uniqueCount="2185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="2176">
   <si>
     <t>应用名称</t>
   </si>
@@ -5080,10 +5080,10 @@
     <t>2、主页浏览，上下各滑动5次</t>
   </si>
   <si>
-    <t>3、点击天气主页面右上方四个角</t>
-  </si>
-  <si>
-    <t>4、点击管理城市</t>
+    <t>3、点击天气主页面右下方三点三线</t>
+  </si>
+  <si>
+    <t>4、点击左上按钮，再返回（单击空白）</t>
   </si>
   <si>
     <t>5、点击城市管理界面的第一个城市</t>
@@ -5092,13 +5092,7 @@
     <t>6、滑动切换不同城市，左滑5次，右滑5次，重复操作5次</t>
   </si>
   <si>
-    <t>7、点击查看更多天气</t>
-  </si>
-  <si>
-    <t>8、左右各滑动1次查看近日天气</t>
-  </si>
-  <si>
-    <t>9、返回天气主界面</t>
+    <t>7、返回天气主界面</t>
   </si>
   <si>
     <t>微博</t>
@@ -5320,10 +5314,10 @@
     <t>4、向上抛滑3次，浏览运动页面</t>
   </si>
   <si>
-    <t>5、点击底部唯品奥莱，进入唯品奥莱页面</t>
-  </si>
-  <si>
-    <t>6、上滑2次，下滑2次，浏览唯品奥莱页面</t>
+    <t>5、点击底部天天低价，进入天天低价页面</t>
+  </si>
+  <si>
+    <t>6、上滑2次，下滑2次，浏览天天低价页面</t>
   </si>
   <si>
     <t>7、返回唯品会主界面</t>
@@ -5530,7 +5524,7 @@
     <t>3、点击公众号</t>
   </si>
   <si>
-    <t>4、点击华为手机的公众号名片，点击右上角人头像</t>
+    <t>4、点击华为手机（或者华为）的公众号名片，点击右上角人头像</t>
   </si>
   <si>
     <t>5、浏览公众号</t>
@@ -5812,46 +5806,34 @@
     <t>4、点击腾讯新闻的公众号名片</t>
   </si>
   <si>
-    <t>5、点击屏幕底部早报晚报后点击晚报</t>
-  </si>
-  <si>
-    <t>6、浏览晚报，上滑5次，下滑5次</t>
-  </si>
-  <si>
-    <t>7、返回测试公众号界面</t>
-  </si>
-  <si>
-    <t>8、点击央视新闻的公众号名片</t>
-  </si>
-  <si>
-    <t>9、点击屏幕底部文博日历查看详情</t>
-  </si>
-  <si>
-    <t>10、浏览文博日历，上滑2次，下滑2次</t>
-  </si>
-  <si>
-    <t>11、返回央视新闻对话界面</t>
-  </si>
-  <si>
-    <t>12、点击屏幕底部夜读查看详情</t>
-  </si>
-  <si>
-    <t>13、浏览夜读，上滑2次，下滑2次</t>
-  </si>
-  <si>
-    <t>14、返回微信首页</t>
-  </si>
-  <si>
-    <t>15、点击订阅号</t>
-  </si>
-  <si>
-    <t>16、点击腾讯新闻</t>
-  </si>
-  <si>
-    <t>17、腾讯新闻页面下滑3次</t>
-  </si>
-  <si>
-    <t>18、返回微信主界面</t>
+    <t>5、返回公众号界面</t>
+  </si>
+  <si>
+    <t>6、点击央视新闻的公众号名片</t>
+  </si>
+  <si>
+    <t>7、点击屏幕底部文博日历查看详情</t>
+  </si>
+  <si>
+    <t>8、浏览任意主题（如打卡笔记），上滑2次，下滑2次</t>
+  </si>
+  <si>
+    <t>9、返回央视新闻对话界面</t>
+  </si>
+  <si>
+    <t>10、点击屏幕底部夜读查看详情</t>
+  </si>
+  <si>
+    <t>11、返回微信首页</t>
+  </si>
+  <si>
+    <t>12、点击订阅号</t>
+  </si>
+  <si>
+    <t>13、点击腾讯新闻</t>
+  </si>
+  <si>
+    <t>14、腾讯新闻页面下滑3次</t>
   </si>
   <si>
     <t>PerformanceDynamic_weixin_0140</t>
@@ -6007,7 +5989,7 @@
     <t>2、首页左右滑动各5次</t>
   </si>
   <si>
-    <t>3、点击底部导航云文档icon后，点击首页icon,重复五次</t>
+    <t>3、点击底部导航云盘icon后，点击首页icon,重复五次</t>
   </si>
   <si>
     <t>4、点击我</t>
@@ -6025,7 +6007,7 @@
     <t>9、点击首页</t>
   </si>
   <si>
-    <t>10、点击欢迎使用WPS云文档</t>
+    <t>10、点击欢迎使用WPS云文档（最近里面）</t>
   </si>
   <si>
     <t>11、上下滑动5次浏览文档页</t>
@@ -6055,34 +6037,31 @@
     <t>5、文件列表滑动，上滑3次，下滑3次</t>
   </si>
   <si>
-    <t>5、点击右下角红色+</t>
-  </si>
-  <si>
-    <t>6、点击文字icon</t>
-  </si>
-  <si>
-    <t>7、输入动态性能测试</t>
-  </si>
-  <si>
-    <t>8、点左上角保存按钮</t>
-  </si>
-  <si>
-    <t>9、点击本地文件夹，进入保存页面</t>
-  </si>
-  <si>
-    <t>10、点击文档文件夹</t>
-  </si>
-  <si>
-    <t>11、点击右上角√进行保存</t>
-  </si>
-  <si>
-    <t>12、返回首页</t>
-  </si>
-  <si>
-    <t>13、点击一个文档进行浏览</t>
-  </si>
-  <si>
-    <t>14、返回首页</t>
+    <t>6、点击右下角红色+</t>
+  </si>
+  <si>
+    <t>7、点击文字icon</t>
+  </si>
+  <si>
+    <t>8、输入动态性能测试</t>
+  </si>
+  <si>
+    <t>9、点左上角保存按钮</t>
+  </si>
+  <si>
+    <t>10、点击本机，进入保存页面</t>
+  </si>
+  <si>
+    <t>11、点击文档文件夹</t>
+  </si>
+  <si>
+    <t>12、点击右上角√进行保存</t>
+  </si>
+  <si>
+    <t>14、点击一个文档进行浏览</t>
+  </si>
+  <si>
+    <t>15、返回首页</t>
   </si>
   <si>
     <t>小红书</t>
@@ -6109,7 +6088,7 @@
     <t>5、浏览图片内容，向左滑动3次</t>
   </si>
   <si>
-    <t>7、点击设置图标，进入设置界面</t>
+    <t>7、点击左上角三横、点击设置图标，进入设置界面</t>
   </si>
   <si>
     <t>8、返回小红书主界面</t>
@@ -6130,7 +6109,7 @@
     <t>13、点击首页，进入首页</t>
   </si>
   <si>
-    <t>14、点击加号按钮，进入照片界面</t>
+    <t>14、点击加号按钮，进入从相册选择界面</t>
   </si>
   <si>
     <t>15、上滑3次，下滑3次，浏览照片界面</t>
@@ -6238,7 +6217,7 @@
     <t>9、返回小红书主界面</t>
   </si>
   <si>
-    <t>10、点击视频tab页</t>
+    <t>10、点击视频tab页（RED）</t>
   </si>
   <si>
     <t>11、随便点击一个视频，浏览10秒</t>
@@ -6340,7 +6319,7 @@
     <t>1、启动携程旅行</t>
   </si>
   <si>
-    <t>4、点击民宿客栈,切换到民宿客栈页面</t>
+    <t>4、点击民宿/客栈,切换到民宿客栈页面</t>
   </si>
   <si>
     <t>5、向上抛滑2次，浏览民宿客栈页面</t>
@@ -6349,7 +6328,7 @@
     <t>6、向下抛滑3次，浏览民宿客栈页面</t>
   </si>
   <si>
-    <t>7、点击开始搜索按钮，切换到搜索页面</t>
+    <t>7、点击查询按钮，切换到查询页面</t>
   </si>
   <si>
     <t>8、输入臻选民宿，点击搜索</t>
@@ -6391,10 +6370,10 @@
     <t>携程旅行预订机票和火车票</t>
   </si>
   <si>
-    <t>2、点击机票</t>
-  </si>
-  <si>
-    <t>3、点击搜索</t>
+    <t>2、点击机票（如果有弹窗，点掉弹窗）</t>
+  </si>
+  <si>
+    <t>3、点击查询</t>
   </si>
   <si>
     <t>4、上滑3次下滑4次浏览搜索结果</t>
@@ -6439,6 +6418,9 @@
     <t>3、点击动漫tab页</t>
   </si>
   <si>
+    <t>4、动漫tab页浏览上滑3次，下滑3次</t>
+  </si>
+  <si>
     <t>12、返回优酷主界面</t>
   </si>
   <si>
@@ -6517,7 +6499,7 @@
     <t>17、返回知乎首页</t>
   </si>
   <si>
-    <t>18、点击底部tab栏发现</t>
+    <t>18、点击底部tab栏看山</t>
   </si>
   <si>
     <t>19、返回知乎主界面</t>
@@ -6580,7 +6562,7 @@
     <t>4、点击拍照</t>
   </si>
   <si>
-    <t>5、返回作业帮首页</t>
+    <t>5、左上角两次x，返回作业帮首页</t>
   </si>
   <si>
     <t>6、点击作业批改</t>
@@ -6589,7 +6571,7 @@
     <t>7、返回作业帮首页</t>
   </si>
   <si>
-    <t>8、点击练习tab</t>
+    <t>8、点击练习（同步学练）tab</t>
   </si>
   <si>
     <t>9、上滑2次，下滑2次，浏览练习页面</t>
@@ -6601,10 +6583,10 @@
     <t>11、上滑2次，下滑2次，浏览VIP页面</t>
   </si>
   <si>
-    <t>12、点击热搜TOP</t>
-  </si>
-  <si>
-    <t>13、上滑2次，下滑2次，浏览热搜TOP页面</t>
+    <t>12、点击学习好物</t>
+  </si>
+  <si>
+    <t>13、上滑2次，下滑2次，浏览学习好物页面</t>
   </si>
   <si>
     <t>14、返回作业帮主界面</t>
@@ -6616,7 +6598,7 @@
     <t>作业帮搜索成语故事浏览</t>
   </si>
   <si>
-    <t>2、点击搜索框，进入搜索界面</t>
+    <t>2、点击搜索框，进入下方搜索界面</t>
   </si>
   <si>
     <t>3、输入成语故事，点击搜索，进入搜索结果界面</t>
@@ -6628,19 +6610,10 @@
     <t>4、点击查看更多，上滑一次</t>
   </si>
   <si>
-    <t>5、点击值得鼓励</t>
-  </si>
-  <si>
-    <t>6、返回作业帮主界面</t>
+    <t>6、上划一次，返回作业帮主界面</t>
   </si>
   <si>
     <t>退出应用</t>
-  </si>
-  <si>
-    <t>PerformanceDynamic_xianyu_0020</t>
-  </si>
-  <si>
-    <t>闲鱼浏览新发和服饰</t>
   </si>
 </sst>
 </file>
@@ -7848,7 +7821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2099"/>
+  <dimension ref="A1:E2094"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.2692307692308" customWidth="1"/>
@@ -21060,15 +21033,21 @@
       <c r="B1557" s="11"/>
       <c r="C1557" s="11"/>
       <c r="D1557" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1558" ht="17" customHeight="1" spans="1:4">
+      <c r="A1558" s="11" t="s">
         <v>1669</v>
       </c>
-    </row>
-    <row r="1558" ht="17" customHeight="1" spans="1:4">
-      <c r="A1558" s="11"/>
-      <c r="B1558" s="11"/>
-      <c r="C1558" s="11"/>
+      <c r="B1558" s="11" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C1558" s="11" t="s">
+        <v>1671</v>
+      </c>
       <c r="D1558" s="11" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1559" ht="17" customHeight="1" spans="1:4">
@@ -21076,19 +21055,13 @@
       <c r="B1559" s="11"/>
       <c r="C1559" s="11"/>
       <c r="D1559" s="11" t="s">
-        <v>71</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1560" ht="17" customHeight="1" spans="1:4">
-      <c r="A1560" s="11" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B1560" s="11" t="s">
-        <v>1672</v>
-      </c>
-      <c r="C1560" s="11" t="s">
-        <v>1673</v>
-      </c>
+      <c r="A1560" s="11"/>
+      <c r="B1560" s="11"/>
+      <c r="C1560" s="11"/>
       <c r="D1560" s="11" t="s">
         <v>1674</v>
       </c>
@@ -21177,7 +21150,7 @@
       <c r="A1571" s="11"/>
       <c r="B1571" s="11"/>
       <c r="C1571" s="11"/>
-      <c r="D1571" s="11" t="s">
+      <c r="D1571" s="13" t="s">
         <v>1685</v>
       </c>
     </row>
@@ -21193,7 +21166,7 @@
       <c r="A1573" s="11"/>
       <c r="B1573" s="11"/>
       <c r="C1573" s="11"/>
-      <c r="D1573" s="13" t="s">
+      <c r="D1573" s="11" t="s">
         <v>1687</v>
       </c>
     </row>
@@ -21209,7 +21182,7 @@
       <c r="A1575" s="11"/>
       <c r="B1575" s="11"/>
       <c r="C1575" s="11"/>
-      <c r="D1575" s="11" t="s">
+      <c r="D1575" s="13" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -21218,15 +21191,21 @@
       <c r="B1576" s="11"/>
       <c r="C1576" s="11"/>
       <c r="D1576" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1577" ht="17" customHeight="1" spans="1:4">
+      <c r="A1577" s="11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B1577" s="11" t="s">
         <v>1690</v>
       </c>
-    </row>
-    <row r="1577" ht="17" customHeight="1" spans="1:4">
-      <c r="A1577" s="11"/>
-      <c r="B1577" s="11"/>
-      <c r="C1577" s="11"/>
-      <c r="D1577" s="13" t="s">
+      <c r="C1577" s="11" t="s">
         <v>1691</v>
+      </c>
+      <c r="D1577" s="11" t="s">
+        <v>1672</v>
       </c>
     </row>
     <row r="1578" ht="17" customHeight="1" spans="1:4">
@@ -21234,21 +21213,15 @@
       <c r="B1578" s="11"/>
       <c r="C1578" s="11"/>
       <c r="D1578" s="11" t="s">
-        <v>25</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1579" ht="17" customHeight="1" spans="1:4">
-      <c r="A1579" s="11" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B1579" s="11" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C1579" s="11" t="s">
+      <c r="A1579" s="11"/>
+      <c r="B1579" s="11"/>
+      <c r="C1579" s="11"/>
+      <c r="D1579" s="11" t="s">
         <v>1693</v>
-      </c>
-      <c r="D1579" s="11" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="1580" ht="17" customHeight="1" spans="1:4">
@@ -21344,15 +21317,21 @@
       <c r="B1591" s="11"/>
       <c r="C1591" s="11"/>
       <c r="D1591" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1592" ht="17" customHeight="1" spans="1:4">
+      <c r="A1592" s="11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B1592" s="11" t="s">
         <v>1705</v>
       </c>
-    </row>
-    <row r="1592" ht="17" customHeight="1" spans="1:4">
-      <c r="A1592" s="11"/>
-      <c r="B1592" s="11"/>
-      <c r="C1592" s="11"/>
+      <c r="C1592" s="11" t="s">
+        <v>1706</v>
+      </c>
       <c r="D1592" s="11" t="s">
-        <v>1706</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1593" ht="17" customHeight="1" spans="1:4">
@@ -21360,21 +21339,15 @@
       <c r="B1593" s="11"/>
       <c r="C1593" s="11"/>
       <c r="D1593" s="11" t="s">
-        <v>87</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1594" ht="17" customHeight="1" spans="1:4">
-      <c r="A1594" s="11" t="s">
-        <v>1671</v>
-      </c>
-      <c r="B1594" s="11" t="s">
+      <c r="A1594" s="11"/>
+      <c r="B1594" s="11"/>
+      <c r="C1594" s="11"/>
+      <c r="D1594" s="11" t="s">
         <v>1707</v>
-      </c>
-      <c r="C1594" s="11" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D1594" s="11" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="1595" ht="17" customHeight="1" spans="1:4">
@@ -21382,7 +21355,7 @@
       <c r="B1595" s="11"/>
       <c r="C1595" s="11"/>
       <c r="D1595" s="11" t="s">
-        <v>1694</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1596" ht="17" customHeight="1" spans="1:4">
@@ -21494,15 +21467,21 @@
       <c r="B1609" s="11"/>
       <c r="C1609" s="11"/>
       <c r="D1609" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="1610" ht="17" customHeight="1" spans="1:4">
+      <c r="A1610" s="11" t="s">
         <v>1722</v>
       </c>
-    </row>
-    <row r="1610" ht="17" customHeight="1" spans="1:4">
-      <c r="A1610" s="11"/>
-      <c r="B1610" s="11"/>
-      <c r="C1610" s="11"/>
+      <c r="B1610" s="11" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C1610" s="11" t="s">
+        <v>1724</v>
+      </c>
       <c r="D1610" s="11" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1611" ht="17" customHeight="1" spans="1:4">
@@ -21510,21 +21489,15 @@
       <c r="B1611" s="11"/>
       <c r="C1611" s="11"/>
       <c r="D1611" s="11" t="s">
-        <v>380</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1612" ht="17" customHeight="1" spans="1:4">
-      <c r="A1612" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="B1612" s="11" t="s">
-        <v>1725</v>
-      </c>
-      <c r="C1612" s="11" t="s">
+      <c r="A1612" s="11"/>
+      <c r="B1612" s="11"/>
+      <c r="C1612" s="11"/>
+      <c r="D1612" s="11" t="s">
         <v>1726</v>
-      </c>
-      <c r="D1612" s="11" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="1613" ht="17" customHeight="1" spans="1:4">
@@ -21532,7 +21505,7 @@
       <c r="B1613" s="11"/>
       <c r="C1613" s="11"/>
       <c r="D1613" s="11" t="s">
-        <v>1508</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1614" ht="17" customHeight="1" spans="1:4">
@@ -21572,7 +21545,7 @@
       <c r="B1618" s="11"/>
       <c r="C1618" s="11"/>
       <c r="D1618" s="11" t="s">
-        <v>1732</v>
+        <v>932</v>
       </c>
     </row>
     <row r="1619" ht="17" customHeight="1" spans="1:4">
@@ -21580,7 +21553,7 @@
       <c r="B1619" s="11"/>
       <c r="C1619" s="11"/>
       <c r="D1619" s="11" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1620" ht="17" customHeight="1" spans="1:4">
@@ -21588,7 +21561,7 @@
       <c r="B1620" s="11"/>
       <c r="C1620" s="11"/>
       <c r="D1620" s="11" t="s">
-        <v>932</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1621" ht="17" customHeight="1" spans="1:4">
@@ -21620,15 +21593,21 @@
       <c r="B1624" s="11"/>
       <c r="C1624" s="11"/>
       <c r="D1624" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1625" ht="17" customHeight="1" spans="1:4">
+      <c r="A1625" s="11" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B1625" s="11" t="s">
         <v>1737</v>
       </c>
-    </row>
-    <row r="1625" ht="17" customHeight="1" spans="1:4">
-      <c r="A1625" s="11"/>
-      <c r="B1625" s="11"/>
-      <c r="C1625" s="11"/>
+      <c r="C1625" s="11" t="s">
+        <v>1738</v>
+      </c>
       <c r="D1625" s="11" t="s">
-        <v>1738</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1626" ht="17" customHeight="1" spans="1:4">
@@ -21636,21 +21615,15 @@
       <c r="B1626" s="11"/>
       <c r="C1626" s="11"/>
       <c r="D1626" s="11" t="s">
-        <v>87</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1627" ht="17" customHeight="1" spans="1:4">
-      <c r="A1627" s="11" t="s">
-        <v>1724</v>
-      </c>
-      <c r="B1627" s="11" t="s">
-        <v>1739</v>
-      </c>
-      <c r="C1627" s="11" t="s">
+      <c r="A1627" s="11"/>
+      <c r="B1627" s="11"/>
+      <c r="C1627" s="11"/>
+      <c r="D1627" s="11" t="s">
         <v>1740</v>
-      </c>
-      <c r="D1627" s="11" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="1628" ht="17" customHeight="1" spans="1:4">
@@ -21690,35 +21663,35 @@
       <c r="B1632" s="11"/>
       <c r="C1632" s="11"/>
       <c r="D1632" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="1633" ht="17" customHeight="1" spans="1:4">
+      <c r="A1633" s="11" t="s">
         <v>1745</v>
       </c>
-    </row>
-    <row r="1633" ht="17" customHeight="1" spans="1:4">
-      <c r="A1633" s="11"/>
-      <c r="B1633" s="11"/>
-      <c r="C1633" s="11"/>
+      <c r="B1633" s="11" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C1633" s="11" t="s">
+        <v>1747</v>
+      </c>
       <c r="D1633" s="11" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1634" ht="17" customHeight="1" spans="1:4">
       <c r="A1634" s="11"/>
       <c r="B1634" s="11"/>
       <c r="C1634" s="11"/>
-      <c r="D1634" s="11" t="s">
-        <v>127</v>
+      <c r="D1634" s="12" t="s">
+        <v>1749</v>
       </c>
     </row>
     <row r="1635" ht="17" customHeight="1" spans="1:4">
-      <c r="A1635" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1635" s="11" t="s">
-        <v>1748</v>
-      </c>
-      <c r="C1635" s="11" t="s">
-        <v>1749</v>
-      </c>
+      <c r="A1635" s="11"/>
+      <c r="B1635" s="11"/>
+      <c r="C1635" s="11"/>
       <c r="D1635" s="11" t="s">
         <v>1750</v>
       </c>
@@ -21767,7 +21740,7 @@
       <c r="A1641" s="11"/>
       <c r="B1641" s="11"/>
       <c r="C1641" s="11"/>
-      <c r="D1641" s="11" t="s">
+      <c r="D1641" s="12" t="s">
         <v>1756</v>
       </c>
     </row>
@@ -21816,15 +21789,21 @@
       <c r="B1647" s="11"/>
       <c r="C1647" s="11"/>
       <c r="D1647" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1648" ht="17" customHeight="1" spans="1:4">
+      <c r="A1648" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1648" s="11" t="s">
         <v>1762</v>
       </c>
-    </row>
-    <row r="1648" ht="17" customHeight="1" spans="1:4">
-      <c r="A1648" s="11"/>
-      <c r="B1648" s="11"/>
-      <c r="C1648" s="11"/>
+      <c r="C1648" s="11" t="s">
+        <v>1763</v>
+      </c>
       <c r="D1648" s="11" t="s">
-        <v>1763</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1649" ht="17" customHeight="1" spans="1:4">
@@ -21832,21 +21811,15 @@
       <c r="B1649" s="11"/>
       <c r="C1649" s="11"/>
       <c r="D1649" s="11" t="s">
-        <v>87</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="1650" ht="17" customHeight="1" spans="1:4">
-      <c r="A1650" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1650" s="11" t="s">
-        <v>1764</v>
-      </c>
-      <c r="C1650" s="11" t="s">
+      <c r="A1650" s="11"/>
+      <c r="B1650" s="11"/>
+      <c r="C1650" s="11"/>
+      <c r="D1650" s="11" t="s">
         <v>1765</v>
-      </c>
-      <c r="D1650" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1651" ht="17" customHeight="1" spans="1:4">
@@ -21934,15 +21907,21 @@
       <c r="B1661" s="11"/>
       <c r="C1661" s="11"/>
       <c r="D1661" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1662" ht="17" customHeight="1" spans="1:4">
+      <c r="A1662" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1662" s="11" t="s">
         <v>1776</v>
       </c>
-    </row>
-    <row r="1662" ht="17" customHeight="1" spans="1:4">
-      <c r="A1662" s="11"/>
-      <c r="B1662" s="11"/>
-      <c r="C1662" s="11"/>
+      <c r="C1662" s="11" t="s">
+        <v>1777</v>
+      </c>
       <c r="D1662" s="11" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1663" ht="17" customHeight="1" spans="1:4">
@@ -21950,21 +21929,15 @@
       <c r="B1663" s="11"/>
       <c r="C1663" s="11"/>
       <c r="D1663" s="11" t="s">
-        <v>178</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1664" ht="17" customHeight="1" spans="1:4">
-      <c r="A1664" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1664" s="11" t="s">
-        <v>1778</v>
-      </c>
-      <c r="C1664" s="11" t="s">
+      <c r="A1664" s="11"/>
+      <c r="B1664" s="11"/>
+      <c r="C1664" s="11"/>
+      <c r="D1664" s="11" t="s">
         <v>1779</v>
-      </c>
-      <c r="D1664" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1665" ht="17" customHeight="1" spans="1:4">
@@ -22068,15 +22041,21 @@
       <c r="B1677" s="11"/>
       <c r="C1677" s="11"/>
       <c r="D1677" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1678" ht="17" customHeight="1" spans="1:4">
+      <c r="A1678" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1678" s="11" t="s">
         <v>1792</v>
       </c>
-    </row>
-    <row r="1678" ht="17" customHeight="1" spans="1:4">
-      <c r="A1678" s="11"/>
-      <c r="B1678" s="11"/>
-      <c r="C1678" s="11"/>
+      <c r="C1678" s="11" t="s">
+        <v>1793</v>
+      </c>
       <c r="D1678" s="11" t="s">
-        <v>1793</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1679" ht="17" customHeight="1" spans="1:4">
@@ -22084,21 +22063,15 @@
       <c r="B1679" s="11"/>
       <c r="C1679" s="11"/>
       <c r="D1679" s="11" t="s">
-        <v>180</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1680" ht="17" customHeight="1" spans="1:4">
-      <c r="A1680" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1680" s="11" t="s">
-        <v>1794</v>
-      </c>
-      <c r="C1680" s="11" t="s">
+      <c r="A1680" s="11"/>
+      <c r="B1680" s="11"/>
+      <c r="C1680" s="11"/>
+      <c r="D1680" s="11" t="s">
         <v>1795</v>
-      </c>
-      <c r="D1680" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1681" ht="17" customHeight="1" spans="1:4">
@@ -22210,15 +22183,21 @@
       <c r="B1694" s="11"/>
       <c r="C1694" s="11"/>
       <c r="D1694" s="11" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="1695" ht="17" customHeight="1" spans="1:4">
+      <c r="A1695" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1695" s="11" t="s">
         <v>1809</v>
       </c>
-    </row>
-    <row r="1695" ht="17" customHeight="1" spans="1:4">
-      <c r="A1695" s="11"/>
-      <c r="B1695" s="11"/>
-      <c r="C1695" s="11"/>
+      <c r="C1695" s="11" t="s">
+        <v>1810</v>
+      </c>
       <c r="D1695" s="11" t="s">
-        <v>1810</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1696" ht="17" customHeight="1" spans="1:4">
@@ -22226,29 +22205,23 @@
       <c r="B1696" s="11"/>
       <c r="C1696" s="11"/>
       <c r="D1696" s="11" t="s">
-        <v>532</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1697" ht="17" customHeight="1" spans="1:4">
-      <c r="A1697" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1697" s="11" t="s">
+      <c r="A1697" s="11"/>
+      <c r="B1697" s="11"/>
+      <c r="C1697" s="11"/>
+      <c r="D1697" s="11" t="s">
         <v>1811</v>
-      </c>
-      <c r="C1697" s="11" t="s">
-        <v>1812</v>
-      </c>
-      <c r="D1697" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1698" ht="17" customHeight="1" spans="1:4">
       <c r="A1698" s="11"/>
       <c r="B1698" s="11"/>
       <c r="C1698" s="11"/>
-      <c r="D1698" s="11" t="s">
-        <v>1780</v>
+      <c r="D1698" s="12" t="s">
+        <v>1812</v>
       </c>
     </row>
     <row r="1699" ht="17" customHeight="1" spans="1:4">
@@ -22287,7 +22260,7 @@
       <c r="A1703" s="11"/>
       <c r="B1703" s="11"/>
       <c r="C1703" s="11"/>
-      <c r="D1703" s="11" t="s">
+      <c r="D1703" s="12" t="s">
         <v>1817</v>
       </c>
     </row>
@@ -22320,7 +22293,7 @@
       <c r="B1707" s="11"/>
       <c r="C1707" s="11"/>
       <c r="D1707" s="11" t="s">
-        <v>1821</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1708" ht="17" customHeight="1" spans="1:4">
@@ -22328,15 +22301,21 @@
       <c r="B1708" s="11"/>
       <c r="C1708" s="11"/>
       <c r="D1708" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1709" ht="17" customHeight="1" spans="1:4">
+      <c r="A1709" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1709" s="11" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1709" s="11" t="s">
         <v>1822</v>
       </c>
-    </row>
-    <row r="1709" ht="17" customHeight="1" spans="1:4">
-      <c r="A1709" s="11"/>
-      <c r="B1709" s="11"/>
-      <c r="C1709" s="11"/>
       <c r="D1709" s="11" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1710" ht="17" customHeight="1" spans="1:4">
@@ -22344,21 +22323,15 @@
       <c r="B1710" s="11"/>
       <c r="C1710" s="11"/>
       <c r="D1710" s="11" t="s">
-        <v>178</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1711" ht="17" customHeight="1" spans="1:4">
-      <c r="A1711" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1711" s="11" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C1711" s="11" t="s">
+      <c r="A1711" s="11"/>
+      <c r="B1711" s="11"/>
+      <c r="C1711" s="11"/>
+      <c r="D1711" s="11" t="s">
         <v>1824</v>
-      </c>
-      <c r="D1711" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1712" ht="17" customHeight="1" spans="1:4">
@@ -22454,7 +22427,7 @@
       <c r="B1723" s="11"/>
       <c r="C1723" s="11"/>
       <c r="D1723" s="11" t="s">
-        <v>1836</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1724" ht="17" customHeight="1" spans="1:4">
@@ -22462,15 +22435,21 @@
       <c r="B1724" s="11"/>
       <c r="C1724" s="11"/>
       <c r="D1724" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1725" ht="17" customHeight="1" spans="1:4">
+      <c r="A1725" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1725" s="11" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1725" s="11" t="s">
         <v>1837</v>
       </c>
-    </row>
-    <row r="1725" ht="17" customHeight="1" spans="1:4">
-      <c r="A1725" s="11"/>
-      <c r="B1725" s="11"/>
-      <c r="C1725" s="11"/>
       <c r="D1725" s="11" t="s">
-        <v>1793</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1726" ht="17" customHeight="1" spans="1:4">
@@ -22478,21 +22457,15 @@
       <c r="B1726" s="11"/>
       <c r="C1726" s="11"/>
       <c r="D1726" s="11" t="s">
-        <v>180</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1727" ht="17" customHeight="1" spans="1:4">
-      <c r="A1727" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1727" s="11" t="s">
-        <v>1838</v>
-      </c>
-      <c r="C1727" s="11" t="s">
+      <c r="A1727" s="11"/>
+      <c r="B1727" s="11"/>
+      <c r="C1727" s="11"/>
+      <c r="D1727" s="12" t="s">
         <v>1839</v>
-      </c>
-      <c r="D1727" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1728" ht="17" customHeight="1" spans="1:4">
@@ -22516,7 +22489,7 @@
       <c r="B1730" s="11"/>
       <c r="C1730" s="11"/>
       <c r="D1730" s="11" t="s">
-        <v>1842</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1731" ht="17" customHeight="1" spans="1:4">
@@ -22524,7 +22497,7 @@
       <c r="B1731" s="11"/>
       <c r="C1731" s="11"/>
       <c r="D1731" s="11" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1732" ht="17" customHeight="1" spans="1:4">
@@ -22532,7 +22505,7 @@
       <c r="B1732" s="11"/>
       <c r="C1732" s="11"/>
       <c r="D1732" s="11" t="s">
-        <v>1285</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="1733" ht="17" customHeight="1" spans="1:4">
@@ -22540,15 +22513,21 @@
       <c r="B1733" s="11"/>
       <c r="C1733" s="11"/>
       <c r="D1733" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1734" ht="17" customHeight="1" spans="1:4">
+      <c r="A1734" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1734" s="11" t="s">
         <v>1844</v>
       </c>
-    </row>
-    <row r="1734" ht="17" customHeight="1" spans="1:4">
-      <c r="A1734" s="11"/>
-      <c r="B1734" s="11"/>
-      <c r="C1734" s="11"/>
+      <c r="C1734" s="11" t="s">
+        <v>1845</v>
+      </c>
       <c r="D1734" s="11" t="s">
-        <v>1845</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1735" ht="17" customHeight="1" spans="1:4">
@@ -22556,21 +22535,15 @@
       <c r="B1735" s="11"/>
       <c r="C1735" s="11"/>
       <c r="D1735" s="11" t="s">
-        <v>116</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1736" ht="17" customHeight="1" spans="1:4">
-      <c r="A1736" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1736" s="11" t="s">
+      <c r="A1736" s="11"/>
+      <c r="B1736" s="11"/>
+      <c r="C1736" s="11"/>
+      <c r="D1736" s="11" t="s">
         <v>1846</v>
-      </c>
-      <c r="C1736" s="11" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D1736" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1737" ht="17" customHeight="1" spans="1:4">
@@ -22578,7 +22551,7 @@
       <c r="B1737" s="11"/>
       <c r="C1737" s="11"/>
       <c r="D1737" s="11" t="s">
-        <v>1796</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1738" ht="17" customHeight="1" spans="1:4">
@@ -22650,7 +22623,7 @@
       <c r="B1746" s="11"/>
       <c r="C1746" s="11"/>
       <c r="D1746" s="11" t="s">
-        <v>1856</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1747" ht="17" customHeight="1" spans="1:4">
@@ -22658,15 +22631,21 @@
       <c r="B1747" s="11"/>
       <c r="C1747" s="11"/>
       <c r="D1747" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1748" ht="17" customHeight="1" spans="1:4">
+      <c r="A1748" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1748" s="11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C1748" s="11" t="s">
         <v>1857</v>
       </c>
-    </row>
-    <row r="1748" ht="17" customHeight="1" spans="1:4">
-      <c r="A1748" s="11"/>
-      <c r="B1748" s="11"/>
-      <c r="C1748" s="11"/>
       <c r="D1748" s="11" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1749" ht="17" customHeight="1" spans="1:4">
@@ -22674,21 +22653,15 @@
       <c r="B1749" s="11"/>
       <c r="C1749" s="11"/>
       <c r="D1749" s="11" t="s">
-        <v>178</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1750" ht="17" customHeight="1" spans="1:4">
-      <c r="A1750" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1750" s="11" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C1750" s="11" t="s">
-        <v>1859</v>
-      </c>
+      <c r="A1750" s="11"/>
+      <c r="B1750" s="11"/>
+      <c r="C1750" s="11"/>
       <c r="D1750" s="11" t="s">
-        <v>1750</v>
+        <v>947</v>
       </c>
     </row>
     <row r="1751" ht="17" customHeight="1" spans="1:4">
@@ -22696,7 +22669,7 @@
       <c r="B1751" s="11"/>
       <c r="C1751" s="11"/>
       <c r="D1751" s="11" t="s">
-        <v>1860</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1752" ht="17" customHeight="1" spans="1:4">
@@ -22704,7 +22677,7 @@
       <c r="B1752" s="11"/>
       <c r="C1752" s="11"/>
       <c r="D1752" s="11" t="s">
-        <v>947</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1753" ht="17" customHeight="1" spans="1:4">
@@ -22712,7 +22685,7 @@
       <c r="B1753" s="11"/>
       <c r="C1753" s="11"/>
       <c r="D1753" s="11" t="s">
-        <v>1753</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1754" ht="17" customHeight="1" spans="1:4">
@@ -22752,7 +22725,7 @@
       <c r="B1758" s="11"/>
       <c r="C1758" s="11"/>
       <c r="D1758" s="11" t="s">
-        <v>1865</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1759" ht="17" customHeight="1" spans="1:4">
@@ -22760,15 +22733,21 @@
       <c r="B1759" s="11"/>
       <c r="C1759" s="11"/>
       <c r="D1759" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1760" ht="17" customHeight="1" spans="1:4">
+      <c r="A1760" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1760" s="11" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1760" s="11" t="s">
         <v>1866</v>
       </c>
-    </row>
-    <row r="1760" ht="17" customHeight="1" spans="1:4">
-      <c r="A1760" s="11"/>
-      <c r="B1760" s="11"/>
-      <c r="C1760" s="11"/>
       <c r="D1760" s="11" t="s">
-        <v>1760</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1761" ht="17" customHeight="1" spans="1:4">
@@ -22776,21 +22755,15 @@
       <c r="B1761" s="11"/>
       <c r="C1761" s="11"/>
       <c r="D1761" s="11" t="s">
-        <v>148</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1762" ht="17" customHeight="1" spans="1:4">
-      <c r="A1762" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1762" s="11" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C1762" s="11" t="s">
+      <c r="A1762" s="11"/>
+      <c r="B1762" s="11"/>
+      <c r="C1762" s="11"/>
+      <c r="D1762" s="11" t="s">
         <v>1868</v>
-      </c>
-      <c r="D1762" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1763" ht="17" customHeight="1" spans="1:4">
@@ -22870,7 +22843,7 @@
       <c r="B1772" s="11"/>
       <c r="C1772" s="11"/>
       <c r="D1772" s="11" t="s">
-        <v>1878</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1773" ht="17" customHeight="1" spans="1:4">
@@ -22878,15 +22851,21 @@
       <c r="B1773" s="11"/>
       <c r="C1773" s="11"/>
       <c r="D1773" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="1774" ht="17" customHeight="1" spans="1:4">
+      <c r="A1774" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1774" s="11" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1774" s="11" t="s">
         <v>1879</v>
       </c>
-    </row>
-    <row r="1774" ht="17" customHeight="1" spans="1:4">
-      <c r="A1774" s="11"/>
-      <c r="B1774" s="11"/>
-      <c r="C1774" s="11"/>
       <c r="D1774" s="11" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1775" ht="17" customHeight="1" spans="1:4">
@@ -22894,21 +22873,15 @@
       <c r="B1775" s="11"/>
       <c r="C1775" s="11"/>
       <c r="D1775" s="11" t="s">
-        <v>178</v>
+        <v>664</v>
       </c>
     </row>
     <row r="1776" ht="17" customHeight="1" spans="1:4">
-      <c r="A1776" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1776" s="11" t="s">
+      <c r="A1776" s="11"/>
+      <c r="B1776" s="11"/>
+      <c r="C1776" s="11"/>
+      <c r="D1776" s="11" t="s">
         <v>1880</v>
-      </c>
-      <c r="C1776" s="11" t="s">
-        <v>1881</v>
-      </c>
-      <c r="D1776" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1777" ht="17" customHeight="1" spans="1:4">
@@ -22916,7 +22889,7 @@
       <c r="B1777" s="11"/>
       <c r="C1777" s="11"/>
       <c r="D1777" s="11" t="s">
-        <v>664</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1778" ht="17" customHeight="1" spans="1:4">
@@ -22996,7 +22969,7 @@
       <c r="B1787" s="11"/>
       <c r="C1787" s="11"/>
       <c r="D1787" s="11" t="s">
-        <v>1891</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1788" ht="17" customHeight="1" spans="1:4">
@@ -23004,15 +22977,21 @@
       <c r="B1788" s="11"/>
       <c r="C1788" s="11"/>
       <c r="D1788" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1789" ht="17" customHeight="1" spans="1:4">
+      <c r="A1789" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1789" s="11" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C1789" s="11" t="s">
         <v>1892</v>
       </c>
-    </row>
-    <row r="1789" ht="17" customHeight="1" spans="1:4">
-      <c r="A1789" s="11"/>
-      <c r="B1789" s="11"/>
-      <c r="C1789" s="11"/>
       <c r="D1789" s="11" t="s">
-        <v>1763</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1790" ht="17" customHeight="1" spans="1:4">
@@ -23020,21 +22999,15 @@
       <c r="B1790" s="11"/>
       <c r="C1790" s="11"/>
       <c r="D1790" s="11" t="s">
-        <v>87</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1791" ht="17" customHeight="1" spans="1:4">
-      <c r="A1791" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1791" s="11" t="s">
+      <c r="A1791" s="11"/>
+      <c r="B1791" s="11"/>
+      <c r="C1791" s="11"/>
+      <c r="D1791" s="11" t="s">
         <v>1893</v>
-      </c>
-      <c r="C1791" s="11" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D1791" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1792" ht="17" customHeight="1" spans="1:4">
@@ -23042,7 +23015,7 @@
       <c r="B1792" s="11"/>
       <c r="C1792" s="11"/>
       <c r="D1792" s="11" t="s">
-        <v>1796</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1793" ht="17" customHeight="1" spans="1:4">
@@ -23114,15 +23087,21 @@
       <c r="B1801" s="11"/>
       <c r="C1801" s="11"/>
       <c r="D1801" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1802" ht="17" customHeight="1" spans="1:4">
+      <c r="A1802" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1802" s="11" t="s">
         <v>1903</v>
       </c>
-    </row>
-    <row r="1802" ht="17" customHeight="1" spans="1:4">
-      <c r="A1802" s="11"/>
-      <c r="B1802" s="11"/>
-      <c r="C1802" s="11"/>
+      <c r="C1802" s="11" t="s">
+        <v>1904</v>
+      </c>
       <c r="D1802" s="11" t="s">
-        <v>1904</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1803" ht="17" customHeight="1" spans="1:4">
@@ -23130,29 +23109,23 @@
       <c r="B1803" s="11"/>
       <c r="C1803" s="11"/>
       <c r="D1803" s="11" t="s">
-        <v>675</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1804" ht="17" customHeight="1" spans="1:4">
-      <c r="A1804" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1804" s="11" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C1804" s="11" t="s">
-        <v>1906</v>
-      </c>
+      <c r="A1804" s="11"/>
+      <c r="B1804" s="11"/>
+      <c r="C1804" s="11"/>
       <c r="D1804" s="11" t="s">
-        <v>1750</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1805" ht="17" customHeight="1" spans="1:4">
       <c r="A1805" s="11"/>
       <c r="B1805" s="11"/>
       <c r="C1805" s="11"/>
-      <c r="D1805" s="11" t="s">
-        <v>1780</v>
+      <c r="D1805" s="12" t="s">
+        <v>1905</v>
       </c>
     </row>
     <row r="1806" ht="17" customHeight="1" spans="1:4">
@@ -23160,7 +23133,7 @@
       <c r="B1806" s="11"/>
       <c r="C1806" s="11"/>
       <c r="D1806" s="11" t="s">
-        <v>1813</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1807" ht="17" customHeight="1" spans="1:4">
@@ -23240,7 +23213,7 @@
       <c r="B1816" s="11"/>
       <c r="C1816" s="11"/>
       <c r="D1816" s="11" t="s">
-        <v>1916</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1817" ht="17" customHeight="1" spans="1:4">
@@ -23248,15 +23221,21 @@
       <c r="B1817" s="11"/>
       <c r="C1817" s="11"/>
       <c r="D1817" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1818" ht="17" customHeight="1" spans="1:4">
+      <c r="A1818" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1818" s="11" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C1818" s="11" t="s">
         <v>1917</v>
       </c>
-    </row>
-    <row r="1818" ht="17" customHeight="1" spans="1:4">
-      <c r="A1818" s="11"/>
-      <c r="B1818" s="11"/>
-      <c r="C1818" s="11"/>
       <c r="D1818" s="11" t="s">
-        <v>1918</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1819" ht="17" customHeight="1" spans="1:4">
@@ -23264,15 +23243,15 @@
       <c r="B1819" s="11"/>
       <c r="C1819" s="11"/>
       <c r="D1819" s="11" t="s">
-        <v>1919</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1820" ht="17" customHeight="1" spans="1:4">
       <c r="A1820" s="11"/>
       <c r="B1820" s="11"/>
       <c r="C1820" s="11"/>
-      <c r="D1820" s="11" t="s">
-        <v>1920</v>
+      <c r="D1820" s="12" t="s">
+        <v>1918</v>
       </c>
     </row>
     <row r="1821" ht="17" customHeight="1" spans="1:4">
@@ -23280,7 +23259,7 @@
       <c r="B1821" s="11"/>
       <c r="C1821" s="11"/>
       <c r="D1821" s="11" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1822" ht="17" customHeight="1" spans="1:4">
@@ -23288,21 +23267,15 @@
       <c r="B1822" s="11"/>
       <c r="C1822" s="11"/>
       <c r="D1822" s="11" t="s">
-        <v>25</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1823" ht="17" customHeight="1" spans="1:4">
-      <c r="A1823" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1823" s="11" t="s">
-        <v>1922</v>
-      </c>
-      <c r="C1823" s="11" t="s">
-        <v>1923</v>
-      </c>
+      <c r="A1823" s="11"/>
+      <c r="B1823" s="11"/>
+      <c r="C1823" s="11"/>
       <c r="D1823" s="11" t="s">
-        <v>1750</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1824" ht="17" customHeight="1" spans="1:4">
@@ -23310,15 +23283,21 @@
       <c r="B1824" s="11"/>
       <c r="C1824" s="11"/>
       <c r="D1824" s="11" t="s">
-        <v>1840</v>
+        <v>419</v>
       </c>
     </row>
     <row r="1825" ht="17" customHeight="1" spans="1:4">
-      <c r="A1825" s="11"/>
-      <c r="B1825" s="11"/>
-      <c r="C1825" s="11"/>
+      <c r="A1825" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1825" s="11" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C1825" s="11" t="s">
+        <v>1923</v>
+      </c>
       <c r="D1825" s="11" t="s">
-        <v>1924</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1826" ht="17" customHeight="1" spans="1:4">
@@ -23326,15 +23305,15 @@
       <c r="B1826" s="11"/>
       <c r="C1826" s="11"/>
       <c r="D1826" s="11" t="s">
-        <v>1925</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1827" ht="17" customHeight="1" spans="1:4">
       <c r="A1827" s="11"/>
       <c r="B1827" s="11"/>
       <c r="C1827" s="11"/>
-      <c r="D1827" s="11" t="s">
-        <v>1926</v>
+      <c r="D1827" s="12" t="s">
+        <v>1924</v>
       </c>
     </row>
     <row r="1828" ht="17" customHeight="1" spans="1:4">
@@ -23342,7 +23321,7 @@
       <c r="B1828" s="11"/>
       <c r="C1828" s="11"/>
       <c r="D1828" s="11" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1829" ht="17" customHeight="1" spans="1:4">
@@ -23350,29 +23329,29 @@
       <c r="B1829" s="11"/>
       <c r="C1829" s="11"/>
       <c r="D1829" s="11" t="s">
-        <v>419</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1830" ht="17" customHeight="1" spans="1:4">
-      <c r="A1830" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1830" s="11" t="s">
-        <v>1928</v>
-      </c>
-      <c r="C1830" s="11" t="s">
-        <v>1929</v>
-      </c>
+      <c r="A1830" s="11"/>
+      <c r="B1830" s="11"/>
+      <c r="C1830" s="11"/>
       <c r="D1830" s="11" t="s">
-        <v>1750</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1831" ht="17" customHeight="1" spans="1:4">
-      <c r="A1831" s="11"/>
-      <c r="B1831" s="11"/>
-      <c r="C1831" s="11"/>
+      <c r="A1831" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1831" s="11" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C1831" s="11" t="s">
+        <v>1927</v>
+      </c>
       <c r="D1831" s="11" t="s">
-        <v>1840</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1832" ht="17" customHeight="1" spans="1:4">
@@ -23380,15 +23359,15 @@
       <c r="B1832" s="11"/>
       <c r="C1832" s="11"/>
       <c r="D1832" s="11" t="s">
-        <v>1930</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1833" ht="17" customHeight="1" spans="1:4">
       <c r="A1833" s="11"/>
       <c r="B1833" s="11"/>
       <c r="C1833" s="11"/>
-      <c r="D1833" s="11" t="s">
-        <v>1931</v>
+      <c r="D1833" s="12" t="s">
+        <v>1928</v>
       </c>
     </row>
     <row r="1834" ht="17" customHeight="1" spans="1:4">
@@ -23396,7 +23375,7 @@
       <c r="B1834" s="11"/>
       <c r="C1834" s="11"/>
       <c r="D1834" s="11" t="s">
-        <v>1769</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1835" ht="17" customHeight="1" spans="1:4">
@@ -23404,21 +23383,15 @@
       <c r="B1835" s="11"/>
       <c r="C1835" s="11"/>
       <c r="D1835" s="11" t="s">
-        <v>170</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1836" ht="17" customHeight="1" spans="1:4">
-      <c r="A1836" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1836" s="11" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C1836" s="11" t="s">
-        <v>1933</v>
-      </c>
+      <c r="A1836" s="11"/>
+      <c r="B1836" s="11"/>
+      <c r="C1836" s="11"/>
       <c r="D1836" s="11" t="s">
-        <v>1750</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1837" ht="17" customHeight="1" spans="1:4">
@@ -23426,15 +23399,21 @@
       <c r="B1837" s="11"/>
       <c r="C1837" s="11"/>
       <c r="D1837" s="11" t="s">
-        <v>1840</v>
+        <v>419</v>
       </c>
     </row>
     <row r="1838" ht="17" customHeight="1" spans="1:4">
-      <c r="A1838" s="11"/>
-      <c r="B1838" s="11"/>
-      <c r="C1838" s="11"/>
+      <c r="A1838" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1838" s="11" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C1838" s="11" t="s">
+        <v>1932</v>
+      </c>
       <c r="D1838" s="11" t="s">
-        <v>1934</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1839" ht="17" customHeight="1" spans="1:4">
@@ -23442,15 +23421,15 @@
       <c r="B1839" s="11"/>
       <c r="C1839" s="11"/>
       <c r="D1839" s="11" t="s">
-        <v>1935</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1840" ht="17" customHeight="1" spans="1:4">
       <c r="A1840" s="11"/>
       <c r="B1840" s="11"/>
       <c r="C1840" s="11"/>
-      <c r="D1840" s="11" t="s">
-        <v>1936</v>
+      <c r="D1840" s="12" t="s">
+        <v>1933</v>
       </c>
     </row>
     <row r="1841" ht="17" customHeight="1" spans="1:4">
@@ -23458,7 +23437,7 @@
       <c r="B1841" s="11"/>
       <c r="C1841" s="11"/>
       <c r="D1841" s="11" t="s">
-        <v>1927</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1842" ht="17" customHeight="1" spans="1:4">
@@ -23466,29 +23445,29 @@
       <c r="B1842" s="11"/>
       <c r="C1842" s="11"/>
       <c r="D1842" s="11" t="s">
-        <v>419</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1843" ht="17" customHeight="1" spans="1:4">
-      <c r="A1843" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1843" s="11" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C1843" s="11" t="s">
-        <v>1938</v>
-      </c>
+      <c r="A1843" s="11"/>
+      <c r="B1843" s="11"/>
+      <c r="C1843" s="11"/>
       <c r="D1843" s="11" t="s">
-        <v>1750</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1844" ht="17" customHeight="1" spans="1:4">
-      <c r="A1844" s="11"/>
-      <c r="B1844" s="11"/>
-      <c r="C1844" s="11"/>
+      <c r="A1844" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1844" s="11" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C1844" s="11" t="s">
+        <v>1936</v>
+      </c>
       <c r="D1844" s="11" t="s">
-        <v>1840</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1845" ht="17" customHeight="1" spans="1:4">
@@ -23496,15 +23475,15 @@
       <c r="B1845" s="11"/>
       <c r="C1845" s="11"/>
       <c r="D1845" s="11" t="s">
-        <v>1939</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1846" ht="17" customHeight="1" spans="1:4">
       <c r="A1846" s="11"/>
       <c r="B1846" s="11"/>
       <c r="C1846" s="11"/>
-      <c r="D1846" s="11" t="s">
-        <v>1940</v>
+      <c r="D1846" s="12" t="s">
+        <v>1937</v>
       </c>
     </row>
     <row r="1847" ht="17" customHeight="1" spans="1:4">
@@ -23512,7 +23491,7 @@
       <c r="B1847" s="11"/>
       <c r="C1847" s="11"/>
       <c r="D1847" s="11" t="s">
-        <v>1769</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1848" ht="17" customHeight="1" spans="1:4">
@@ -23520,21 +23499,15 @@
       <c r="B1848" s="11"/>
       <c r="C1848" s="11"/>
       <c r="D1848" s="11" t="s">
-        <v>170</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1849" ht="17" customHeight="1" spans="1:4">
-      <c r="A1849" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1849" s="11" t="s">
-        <v>1941</v>
-      </c>
-      <c r="C1849" s="11" t="s">
-        <v>1942</v>
-      </c>
+      <c r="A1849" s="11"/>
+      <c r="B1849" s="11"/>
+      <c r="C1849" s="11"/>
       <c r="D1849" s="11" t="s">
-        <v>1750</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1850" ht="17" customHeight="1" spans="1:4">
@@ -23542,7 +23515,7 @@
       <c r="B1850" s="11"/>
       <c r="C1850" s="11"/>
       <c r="D1850" s="11" t="s">
-        <v>1840</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1851" ht="17" customHeight="1" spans="1:4">
@@ -23550,7 +23523,7 @@
       <c r="B1851" s="11"/>
       <c r="C1851" s="11"/>
       <c r="D1851" s="11" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1852" ht="17" customHeight="1" spans="1:4">
@@ -23558,7 +23531,7 @@
       <c r="B1852" s="11"/>
       <c r="C1852" s="11"/>
       <c r="D1852" s="11" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1853" ht="17" customHeight="1" spans="1:4">
@@ -23566,15 +23539,21 @@
       <c r="B1853" s="11"/>
       <c r="C1853" s="11"/>
       <c r="D1853" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1854" ht="17" customHeight="1" spans="1:4">
+      <c r="A1854" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1854" s="11" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C1854" s="11" t="s">
         <v>1945</v>
       </c>
-    </row>
-    <row r="1854" ht="17" customHeight="1" spans="1:4">
-      <c r="A1854" s="11"/>
-      <c r="B1854" s="11"/>
-      <c r="C1854" s="11"/>
       <c r="D1854" s="11" t="s">
-        <v>1946</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1855" ht="17" customHeight="1" spans="1:4">
@@ -23582,7 +23561,7 @@
       <c r="B1855" s="11"/>
       <c r="C1855" s="11"/>
       <c r="D1855" s="11" t="s">
-        <v>1947</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1856" ht="17" customHeight="1" spans="1:4">
@@ -23590,7 +23569,7 @@
       <c r="B1856" s="11"/>
       <c r="C1856" s="11"/>
       <c r="D1856" s="11" t="s">
-        <v>1948</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1857" ht="17" customHeight="1" spans="1:4">
@@ -23598,7 +23577,7 @@
       <c r="B1857" s="11"/>
       <c r="C1857" s="11"/>
       <c r="D1857" s="11" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1858" ht="17" customHeight="1" spans="1:4">
@@ -23606,21 +23585,15 @@
       <c r="B1858" s="11"/>
       <c r="C1858" s="11"/>
       <c r="D1858" s="11" t="s">
-        <v>71</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1859" ht="17" customHeight="1" spans="1:4">
-      <c r="A1859" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1859" s="11" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C1859" s="11" t="s">
-        <v>1951</v>
-      </c>
+      <c r="A1859" s="11"/>
+      <c r="B1859" s="11"/>
+      <c r="C1859" s="11"/>
       <c r="D1859" s="11" t="s">
-        <v>1750</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1860" ht="17" customHeight="1" spans="1:4">
@@ -23628,7 +23601,7 @@
       <c r="B1860" s="11"/>
       <c r="C1860" s="11"/>
       <c r="D1860" s="11" t="s">
-        <v>1796</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="1861" ht="17" customHeight="1" spans="1:4">
@@ -23636,7 +23609,7 @@
       <c r="B1861" s="11"/>
       <c r="C1861" s="11"/>
       <c r="D1861" s="11" t="s">
-        <v>1848</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1862" ht="17" customHeight="1" spans="1:4">
@@ -23644,7 +23617,7 @@
       <c r="B1862" s="11"/>
       <c r="C1862" s="11"/>
       <c r="D1862" s="11" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1863" ht="17" customHeight="1" spans="1:4">
@@ -23652,7 +23625,7 @@
       <c r="B1863" s="11"/>
       <c r="C1863" s="11"/>
       <c r="D1863" s="11" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="1864" ht="17" customHeight="1" spans="1:4">
@@ -23660,7 +23633,7 @@
       <c r="B1864" s="11"/>
       <c r="C1864" s="11"/>
       <c r="D1864" s="11" t="s">
-        <v>1954</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1865" ht="17" customHeight="1" spans="1:4">
@@ -23668,15 +23641,21 @@
       <c r="B1865" s="11"/>
       <c r="C1865" s="11"/>
       <c r="D1865" s="11" t="s">
-        <v>1955</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1866" ht="17" customHeight="1" spans="1:4">
-      <c r="A1866" s="11"/>
-      <c r="B1866" s="11"/>
-      <c r="C1866" s="11"/>
+      <c r="A1866" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1866" s="11" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C1866" s="11" t="s">
+        <v>1953</v>
+      </c>
       <c r="D1866" s="11" t="s">
-        <v>1802</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1867" ht="17" customHeight="1" spans="1:4">
@@ -23684,7 +23663,7 @@
       <c r="B1867" s="11"/>
       <c r="C1867" s="11"/>
       <c r="D1867" s="11" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1868" ht="17" customHeight="1" spans="1:4">
@@ -23692,7 +23671,7 @@
       <c r="B1868" s="11"/>
       <c r="C1868" s="11"/>
       <c r="D1868" s="11" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1869" ht="17" customHeight="1" spans="1:4">
@@ -23700,29 +23679,23 @@
       <c r="B1869" s="11"/>
       <c r="C1869" s="11"/>
       <c r="D1869" s="11" t="s">
-        <v>1760</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1870" ht="17" customHeight="1" spans="1:4">
       <c r="A1870" s="11"/>
       <c r="B1870" s="11"/>
       <c r="C1870" s="11"/>
-      <c r="D1870" s="11" t="s">
-        <v>148</v>
+      <c r="D1870" s="12" t="s">
+        <v>1957</v>
       </c>
     </row>
     <row r="1871" ht="17" customHeight="1" spans="1:4">
-      <c r="A1871" s="11" t="s">
-        <v>1747</v>
-      </c>
-      <c r="B1871" s="11" t="s">
+      <c r="A1871" s="11"/>
+      <c r="B1871" s="11"/>
+      <c r="C1871" s="11"/>
+      <c r="D1871" s="11" t="s">
         <v>1958</v>
-      </c>
-      <c r="C1871" s="11" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D1871" s="11" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1872" ht="17" customHeight="1" spans="1:4">
@@ -23730,7 +23703,7 @@
       <c r="B1872" s="11"/>
       <c r="C1872" s="11"/>
       <c r="D1872" s="11" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1873" ht="17" customHeight="1" spans="1:4">
@@ -23738,7 +23711,7 @@
       <c r="B1873" s="11"/>
       <c r="C1873" s="11"/>
       <c r="D1873" s="11" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1874" ht="17" customHeight="1" spans="1:4">
@@ -23746,7 +23719,7 @@
       <c r="B1874" s="11"/>
       <c r="C1874" s="11"/>
       <c r="D1874" s="11" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1875" ht="17" customHeight="1" spans="1:4">
@@ -23754,7 +23727,7 @@
       <c r="B1875" s="11"/>
       <c r="C1875" s="11"/>
       <c r="D1875" s="11" t="s">
-        <v>1963</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1876" ht="17" customHeight="1" spans="1:4">
@@ -23762,13 +23735,19 @@
       <c r="B1876" s="11"/>
       <c r="C1876" s="11"/>
       <c r="D1876" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="1877" ht="17" customHeight="1" spans="1:4">
+      <c r="A1877" s="11" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1877" s="11" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C1877" s="11" t="s">
         <v>1964</v>
       </c>
-    </row>
-    <row r="1877" ht="17" customHeight="1" spans="1:4">
-      <c r="A1877" s="11"/>
-      <c r="B1877" s="11"/>
-      <c r="C1877" s="11"/>
       <c r="D1877" s="11" t="s">
         <v>1965</v>
       </c>
@@ -23794,7 +23773,7 @@
       <c r="B1880" s="11"/>
       <c r="C1880" s="11"/>
       <c r="D1880" s="11" t="s">
-        <v>1788</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1881" ht="17" customHeight="1" spans="1:4">
@@ -23802,21 +23781,15 @@
       <c r="B1881" s="11"/>
       <c r="C1881" s="11"/>
       <c r="D1881" s="11" t="s">
-        <v>211</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1882" ht="17" customHeight="1" spans="1:4">
-      <c r="A1882" s="11" t="s">
-        <v>1968</v>
-      </c>
-      <c r="B1882" s="11" t="s">
-        <v>1969</v>
-      </c>
-      <c r="C1882" s="11" t="s">
-        <v>1970</v>
-      </c>
+      <c r="A1882" s="11"/>
+      <c r="B1882" s="11"/>
+      <c r="C1882" s="11"/>
       <c r="D1882" s="11" t="s">
-        <v>1971</v>
+        <v>668</v>
       </c>
     </row>
     <row r="1883" ht="17" customHeight="1" spans="1:4">
@@ -23824,7 +23797,7 @@
       <c r="B1883" s="11"/>
       <c r="C1883" s="11"/>
       <c r="D1883" s="11" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1884" ht="17" customHeight="1" spans="1:4">
@@ -23832,7 +23805,7 @@
       <c r="B1884" s="11"/>
       <c r="C1884" s="11"/>
       <c r="D1884" s="11" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1885" ht="17" customHeight="1" spans="1:4">
@@ -23840,15 +23813,15 @@
       <c r="B1885" s="11"/>
       <c r="C1885" s="11"/>
       <c r="D1885" s="11" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1886" ht="17" customHeight="1" spans="1:4">
       <c r="A1886" s="11"/>
       <c r="B1886" s="11"/>
       <c r="C1886" s="11"/>
-      <c r="D1886" s="11" t="s">
-        <v>1975</v>
+      <c r="D1886" s="14" t="s">
+        <v>1973</v>
       </c>
     </row>
     <row r="1887" ht="17" customHeight="1" spans="1:4">
@@ -23856,7 +23829,7 @@
       <c r="B1887" s="11"/>
       <c r="C1887" s="11"/>
       <c r="D1887" s="11" t="s">
-        <v>668</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1888" ht="17" customHeight="1" spans="1:4">
@@ -23864,7 +23837,7 @@
       <c r="B1888" s="11"/>
       <c r="C1888" s="11"/>
       <c r="D1888" s="11" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1889" ht="17" customHeight="1" spans="1:4">
@@ -23872,13 +23845,19 @@
       <c r="B1889" s="11"/>
       <c r="C1889" s="11"/>
       <c r="D1889" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="1890" ht="17" customHeight="1" spans="1:4">
+      <c r="A1890" s="11" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1890" s="11" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C1890" s="11" t="s">
         <v>1977</v>
       </c>
-    </row>
-    <row r="1890" ht="17" customHeight="1" spans="1:4">
-      <c r="A1890" s="11"/>
-      <c r="B1890" s="11"/>
-      <c r="C1890" s="11"/>
       <c r="D1890" s="11" t="s">
         <v>1978</v>
       </c>
@@ -23912,21 +23891,15 @@
       <c r="B1894" s="11"/>
       <c r="C1894" s="11"/>
       <c r="D1894" s="11" t="s">
-        <v>675</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1895" ht="17" customHeight="1" spans="1:4">
-      <c r="A1895" s="11" t="s">
-        <v>1968</v>
-      </c>
-      <c r="B1895" s="11" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C1895" s="11" t="s">
+      <c r="A1895" s="11"/>
+      <c r="B1895" s="11"/>
+      <c r="C1895" s="11"/>
+      <c r="D1895" s="11" t="s">
         <v>1983</v>
-      </c>
-      <c r="D1895" s="11" t="s">
-        <v>1984</v>
       </c>
     </row>
     <row r="1896" ht="17" customHeight="1" spans="1:4">
@@ -23934,7 +23907,7 @@
       <c r="B1896" s="11"/>
       <c r="C1896" s="11"/>
       <c r="D1896" s="11" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1897" ht="17" customHeight="1" spans="1:4">
@@ -23942,7 +23915,7 @@
       <c r="B1897" s="11"/>
       <c r="C1897" s="11"/>
       <c r="D1897" s="11" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1898" ht="17" customHeight="1" spans="1:4">
@@ -23950,7 +23923,7 @@
       <c r="B1898" s="11"/>
       <c r="C1898" s="11"/>
       <c r="D1898" s="11" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1899" ht="17" customHeight="1" spans="1:4">
@@ -23958,7 +23931,7 @@
       <c r="B1899" s="11"/>
       <c r="C1899" s="11"/>
       <c r="D1899" s="11" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1900" ht="17" customHeight="1" spans="1:4">
@@ -23966,7 +23939,7 @@
       <c r="B1900" s="11"/>
       <c r="C1900" s="11"/>
       <c r="D1900" s="11" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1901" ht="17" customHeight="1" spans="1:4">
@@ -23974,7 +23947,7 @@
       <c r="B1901" s="11"/>
       <c r="C1901" s="11"/>
       <c r="D1901" s="11" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1902" ht="17" customHeight="1" spans="1:4">
@@ -23982,7 +23955,7 @@
       <c r="B1902" s="11"/>
       <c r="C1902" s="11"/>
       <c r="D1902" s="11" t="s">
-        <v>1991</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1903" ht="17" customHeight="1" spans="1:4">
@@ -23990,7 +23963,7 @@
       <c r="B1903" s="11"/>
       <c r="C1903" s="11"/>
       <c r="D1903" s="11" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1904" ht="17" customHeight="1" spans="1:4">
@@ -23998,7 +23971,7 @@
       <c r="B1904" s="11"/>
       <c r="C1904" s="11"/>
       <c r="D1904" s="11" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1905" ht="17" customHeight="1" spans="1:4">
@@ -24006,13 +23979,19 @@
       <c r="B1905" s="11"/>
       <c r="C1905" s="11"/>
       <c r="D1905" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="1906" ht="17" customHeight="1" spans="1:4">
+      <c r="A1906" s="11" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1906" s="11" t="s">
+        <v>1993</v>
+      </c>
+      <c r="C1906" s="11" t="s">
         <v>1994</v>
       </c>
-    </row>
-    <row r="1906" ht="17" customHeight="1" spans="1:4">
-      <c r="A1906" s="11"/>
-      <c r="B1906" s="11"/>
-      <c r="C1906" s="11"/>
       <c r="D1906" s="11" t="s">
         <v>1995</v>
       </c>
@@ -24046,21 +24025,15 @@
       <c r="B1910" s="11"/>
       <c r="C1910" s="11"/>
       <c r="D1910" s="11" t="s">
-        <v>87</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1911" ht="17" customHeight="1" spans="1:4">
-      <c r="A1911" s="11" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B1911" s="11" t="s">
-        <v>2000</v>
-      </c>
-      <c r="C1911" s="11" t="s">
-        <v>2001</v>
-      </c>
+      <c r="A1911" s="11"/>
+      <c r="B1911" s="11"/>
+      <c r="C1911" s="11"/>
       <c r="D1911" s="11" t="s">
-        <v>2002</v>
+        <v>668</v>
       </c>
     </row>
     <row r="1912" ht="17" customHeight="1" spans="1:4">
@@ -24068,7 +24041,7 @@
       <c r="B1912" s="11"/>
       <c r="C1912" s="11"/>
       <c r="D1912" s="11" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1913" ht="17" customHeight="1" spans="1:4">
@@ -24076,7 +24049,7 @@
       <c r="B1913" s="11"/>
       <c r="C1913" s="11"/>
       <c r="D1913" s="11" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1914" ht="17" customHeight="1" spans="1:4">
@@ -24084,7 +24057,7 @@
       <c r="B1914" s="11"/>
       <c r="C1914" s="11"/>
       <c r="D1914" s="11" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1915" ht="17" customHeight="1" spans="1:4">
@@ -24092,7 +24065,7 @@
       <c r="B1915" s="11"/>
       <c r="C1915" s="11"/>
       <c r="D1915" s="11" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="1916" ht="17" customHeight="1" spans="1:4">
@@ -24100,7 +24073,7 @@
       <c r="B1916" s="11"/>
       <c r="C1916" s="11"/>
       <c r="D1916" s="11" t="s">
-        <v>668</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1917" ht="17" customHeight="1" spans="1:4">
@@ -24108,7 +24081,7 @@
       <c r="B1917" s="11"/>
       <c r="C1917" s="11"/>
       <c r="D1917" s="11" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1918" ht="17" customHeight="1" spans="1:4">
@@ -24116,7 +24089,7 @@
       <c r="B1918" s="11"/>
       <c r="C1918" s="11"/>
       <c r="D1918" s="11" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1919" ht="17" customHeight="1" spans="1:4">
@@ -24124,7 +24097,7 @@
       <c r="B1919" s="11"/>
       <c r="C1919" s="11"/>
       <c r="D1919" s="11" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1920" ht="17" customHeight="1" spans="1:4">
@@ -24132,7 +24105,7 @@
       <c r="B1920" s="11"/>
       <c r="C1920" s="11"/>
       <c r="D1920" s="11" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1921" ht="17" customHeight="1" spans="1:4">
@@ -24140,7 +24113,7 @@
       <c r="B1921" s="11"/>
       <c r="C1921" s="11"/>
       <c r="D1921" s="11" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1922" ht="17" customHeight="1" spans="1:4">
@@ -24148,7 +24121,7 @@
       <c r="B1922" s="11"/>
       <c r="C1922" s="11"/>
       <c r="D1922" s="11" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1923" ht="17" customHeight="1" spans="1:4">
@@ -24156,7 +24129,7 @@
       <c r="B1923" s="11"/>
       <c r="C1923" s="11"/>
       <c r="D1923" s="11" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1924" ht="17" customHeight="1" spans="1:4">
@@ -24164,15 +24137,21 @@
       <c r="B1924" s="11"/>
       <c r="C1924" s="11"/>
       <c r="D1924" s="11" t="s">
-        <v>2014</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1925" ht="17" customHeight="1" spans="1:4">
-      <c r="A1925" s="11"/>
-      <c r="B1925" s="11"/>
-      <c r="C1925" s="11"/>
+      <c r="A1925" s="11" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1925" s="11" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C1925" s="11" t="s">
+        <v>2013</v>
+      </c>
       <c r="D1925" s="11" t="s">
-        <v>2015</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1926" ht="17" customHeight="1" spans="1:4">
@@ -24180,7 +24159,7 @@
       <c r="B1926" s="11"/>
       <c r="C1926" s="11"/>
       <c r="D1926" s="11" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="1927" ht="17" customHeight="1" spans="1:4">
@@ -24188,7 +24167,7 @@
       <c r="B1927" s="11"/>
       <c r="C1927" s="11"/>
       <c r="D1927" s="11" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1928" ht="17" customHeight="1" spans="1:4">
@@ -24196,7 +24175,7 @@
       <c r="B1928" s="11"/>
       <c r="C1928" s="11"/>
       <c r="D1928" s="11" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1929" ht="17" customHeight="1" spans="1:4">
@@ -24204,21 +24183,15 @@
       <c r="B1929" s="11"/>
       <c r="C1929" s="11"/>
       <c r="D1929" s="11" t="s">
-        <v>25</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1930" ht="17" customHeight="1" spans="1:4">
-      <c r="A1930" s="11" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B1930" s="11" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C1930" s="11" t="s">
-        <v>2020</v>
-      </c>
+      <c r="A1930" s="11"/>
+      <c r="B1930" s="11"/>
+      <c r="C1930" s="11"/>
       <c r="D1930" s="11" t="s">
-        <v>2002</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1931" ht="17" customHeight="1" spans="1:4">
@@ -24226,7 +24199,7 @@
       <c r="B1931" s="11"/>
       <c r="C1931" s="11"/>
       <c r="D1931" s="11" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1932" ht="17" customHeight="1" spans="1:4">
@@ -24234,7 +24207,7 @@
       <c r="B1932" s="11"/>
       <c r="C1932" s="11"/>
       <c r="D1932" s="11" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1933" ht="17" customHeight="1" spans="1:4">
@@ -24242,7 +24215,7 @@
       <c r="B1933" s="11"/>
       <c r="C1933" s="11"/>
       <c r="D1933" s="11" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1934" ht="17" customHeight="1" spans="1:4">
@@ -24250,7 +24223,7 @@
       <c r="B1934" s="11"/>
       <c r="C1934" s="11"/>
       <c r="D1934" s="11" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1935" ht="17" customHeight="1" spans="1:4">
@@ -24258,15 +24231,21 @@
       <c r="B1935" s="11"/>
       <c r="C1935" s="11"/>
       <c r="D1935" s="11" t="s">
-        <v>2025</v>
+        <v>211</v>
       </c>
     </row>
     <row r="1936" ht="17" customHeight="1" spans="1:4">
-      <c r="A1936" s="11"/>
-      <c r="B1936" s="11"/>
-      <c r="C1936" s="11"/>
+      <c r="A1936" s="11" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1936" s="11" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C1936" s="11" t="s">
+        <v>2024</v>
+      </c>
       <c r="D1936" s="11" t="s">
-        <v>2026</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1937" ht="17" customHeight="1" spans="1:4">
@@ -24274,7 +24253,7 @@
       <c r="B1937" s="11"/>
       <c r="C1937" s="11"/>
       <c r="D1937" s="11" t="s">
-        <v>2027</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1938" ht="17" customHeight="1" spans="1:4">
@@ -24282,7 +24261,7 @@
       <c r="B1938" s="11"/>
       <c r="C1938" s="11"/>
       <c r="D1938" s="11" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="1939" ht="17" customHeight="1" spans="1:4">
@@ -24290,7 +24269,7 @@
       <c r="B1939" s="11"/>
       <c r="C1939" s="11"/>
       <c r="D1939" s="11" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1940" ht="17" customHeight="1" spans="1:4">
@@ -24298,21 +24277,15 @@
       <c r="B1940" s="11"/>
       <c r="C1940" s="11"/>
       <c r="D1940" s="11" t="s">
-        <v>211</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1941" ht="17" customHeight="1" spans="1:4">
-      <c r="A1941" s="11" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B1941" s="11" t="s">
-        <v>2030</v>
-      </c>
-      <c r="C1941" s="11" t="s">
-        <v>2031</v>
-      </c>
+      <c r="A1941" s="11"/>
+      <c r="B1941" s="11"/>
+      <c r="C1941" s="11"/>
       <c r="D1941" s="11" t="s">
-        <v>2002</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1942" ht="17" customHeight="1" spans="1:4">
@@ -24320,7 +24293,7 @@
       <c r="B1942" s="11"/>
       <c r="C1942" s="11"/>
       <c r="D1942" s="11" t="s">
-        <v>1480</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1943" ht="17" customHeight="1" spans="1:4">
@@ -24328,7 +24301,7 @@
       <c r="B1943" s="11"/>
       <c r="C1943" s="11"/>
       <c r="D1943" s="11" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1944" ht="17" customHeight="1" spans="1:4">
@@ -24336,7 +24309,7 @@
       <c r="B1944" s="11"/>
       <c r="C1944" s="11"/>
       <c r="D1944" s="11" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1945" ht="17" customHeight="1" spans="1:4">
@@ -24344,7 +24317,7 @@
       <c r="B1945" s="11"/>
       <c r="C1945" s="11"/>
       <c r="D1945" s="11" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1946" ht="17" customHeight="1" spans="1:4">
@@ -24352,7 +24325,7 @@
       <c r="B1946" s="11"/>
       <c r="C1946" s="11"/>
       <c r="D1946" s="11" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1947" ht="17" customHeight="1" spans="1:4">
@@ -24360,7 +24333,7 @@
       <c r="B1947" s="11"/>
       <c r="C1947" s="11"/>
       <c r="D1947" s="11" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1948" ht="17" customHeight="1" spans="1:4">
@@ -24368,7 +24341,7 @@
       <c r="B1948" s="11"/>
       <c r="C1948" s="11"/>
       <c r="D1948" s="11" t="s">
-        <v>2037</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1949" ht="17" customHeight="1" spans="1:4">
@@ -24376,15 +24349,21 @@
       <c r="B1949" s="11"/>
       <c r="C1949" s="11"/>
       <c r="D1949" s="11" t="s">
-        <v>2038</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1950" ht="17" customHeight="1" spans="1:4">
-      <c r="A1950" s="11"/>
-      <c r="B1950" s="11"/>
-      <c r="C1950" s="11"/>
+      <c r="A1950" s="11" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1950" s="11" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C1950" s="11" t="s">
+        <v>2036</v>
+      </c>
       <c r="D1950" s="11" t="s">
-        <v>2039</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1951" ht="17" customHeight="1" spans="1:4">
@@ -24392,7 +24371,7 @@
       <c r="B1951" s="11"/>
       <c r="C1951" s="11"/>
       <c r="D1951" s="11" t="s">
-        <v>2040</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1952" ht="17" customHeight="1" spans="1:4">
@@ -24400,7 +24379,7 @@
       <c r="B1952" s="11"/>
       <c r="C1952" s="11"/>
       <c r="D1952" s="11" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1953" ht="17" customHeight="1" spans="1:4">
@@ -24408,7 +24387,7 @@
       <c r="B1953" s="11"/>
       <c r="C1953" s="11"/>
       <c r="D1953" s="11" t="s">
-        <v>177</v>
+        <v>426</v>
       </c>
     </row>
     <row r="1954" ht="17" customHeight="1" spans="1:4">
@@ -24416,21 +24395,15 @@
       <c r="B1954" s="11"/>
       <c r="C1954" s="11"/>
       <c r="D1954" s="11" t="s">
-        <v>178</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1955" ht="17" customHeight="1" spans="1:4">
-      <c r="A1955" s="11" t="s">
-        <v>1999</v>
-      </c>
-      <c r="B1955" s="11" t="s">
-        <v>2042</v>
-      </c>
-      <c r="C1955" s="11" t="s">
-        <v>2043</v>
-      </c>
+      <c r="A1955" s="11"/>
+      <c r="B1955" s="11"/>
+      <c r="C1955" s="11"/>
       <c r="D1955" s="11" t="s">
-        <v>2002</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1956" ht="17" customHeight="1" spans="1:4">
@@ -24438,7 +24411,7 @@
       <c r="B1956" s="11"/>
       <c r="C1956" s="11"/>
       <c r="D1956" s="11" t="s">
-        <v>1480</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1957" ht="17" customHeight="1" spans="1:4">
@@ -24446,7 +24419,7 @@
       <c r="B1957" s="11"/>
       <c r="C1957" s="11"/>
       <c r="D1957" s="11" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1958" ht="17" customHeight="1" spans="1:4">
@@ -24454,7 +24427,7 @@
       <c r="B1958" s="11"/>
       <c r="C1958" s="11"/>
       <c r="D1958" s="11" t="s">
-        <v>426</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1959" ht="17" customHeight="1" spans="1:4">
@@ -24462,7 +24435,7 @@
       <c r="B1959" s="11"/>
       <c r="C1959" s="11"/>
       <c r="D1959" s="11" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1960" ht="17" customHeight="1" spans="1:4">
@@ -24470,7 +24443,7 @@
       <c r="B1960" s="11"/>
       <c r="C1960" s="11"/>
       <c r="D1960" s="11" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1961" ht="17" customHeight="1" spans="1:4">
@@ -24478,7 +24451,7 @@
       <c r="B1961" s="11"/>
       <c r="C1961" s="11"/>
       <c r="D1961" s="11" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1962" ht="17" customHeight="1" spans="1:4">
@@ -24486,7 +24459,7 @@
       <c r="B1962" s="11"/>
       <c r="C1962" s="11"/>
       <c r="D1962" s="11" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1963" ht="17" customHeight="1" spans="1:4">
@@ -24494,7 +24467,7 @@
       <c r="B1963" s="11"/>
       <c r="C1963" s="11"/>
       <c r="D1963" s="11" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1964" ht="17" customHeight="1" spans="1:4">
@@ -24502,13 +24475,19 @@
       <c r="B1964" s="11"/>
       <c r="C1964" s="11"/>
       <c r="D1964" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1965" ht="17" customHeight="1" spans="1:4">
+      <c r="A1965" s="11" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1965" s="11" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C1965" s="11" t="s">
         <v>2050</v>
       </c>
-    </row>
-    <row r="1965" ht="17" customHeight="1" spans="1:4">
-      <c r="A1965" s="11"/>
-      <c r="B1965" s="11"/>
-      <c r="C1965" s="11"/>
       <c r="D1965" s="11" t="s">
         <v>2051</v>
       </c>
@@ -24518,7 +24497,7 @@
       <c r="B1966" s="11"/>
       <c r="C1966" s="11"/>
       <c r="D1966" s="11" t="s">
-        <v>2052</v>
+        <v>712</v>
       </c>
     </row>
     <row r="1967" ht="17" customHeight="1" spans="1:4">
@@ -24526,7 +24505,7 @@
       <c r="B1967" s="11"/>
       <c r="C1967" s="11"/>
       <c r="D1967" s="11" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1968" ht="17" customHeight="1" spans="1:4">
@@ -24534,7 +24513,7 @@
       <c r="B1968" s="11"/>
       <c r="C1968" s="11"/>
       <c r="D1968" s="11" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1969" ht="17" customHeight="1" spans="1:4">
@@ -24542,21 +24521,15 @@
       <c r="B1969" s="11"/>
       <c r="C1969" s="11"/>
       <c r="D1969" s="11" t="s">
-        <v>164</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1970" ht="17" customHeight="1" spans="1:4">
-      <c r="A1970" s="11" t="s">
+      <c r="A1970" s="11"/>
+      <c r="B1970" s="11"/>
+      <c r="C1970" s="11"/>
+      <c r="D1970" s="11" t="s">
         <v>2055</v>
-      </c>
-      <c r="B1970" s="11" t="s">
-        <v>2056</v>
-      </c>
-      <c r="C1970" s="11" t="s">
-        <v>2057</v>
-      </c>
-      <c r="D1970" s="11" t="s">
-        <v>2058</v>
       </c>
     </row>
     <row r="1971" ht="17" customHeight="1" spans="1:4">
@@ -24564,7 +24537,7 @@
       <c r="B1971" s="11"/>
       <c r="C1971" s="11"/>
       <c r="D1971" s="11" t="s">
-        <v>712</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1972" ht="17" customHeight="1" spans="1:4">
@@ -24572,7 +24545,7 @@
       <c r="B1972" s="11"/>
       <c r="C1972" s="11"/>
       <c r="D1972" s="11" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1973" ht="17" customHeight="1" spans="1:4">
@@ -24580,7 +24553,7 @@
       <c r="B1973" s="11"/>
       <c r="C1973" s="11"/>
       <c r="D1973" s="11" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1974" ht="17" customHeight="1" spans="1:4">
@@ -24588,61 +24561,61 @@
       <c r="B1974" s="11"/>
       <c r="C1974" s="11"/>
       <c r="D1974" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1975" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1975" s="12" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1975" s="12" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C1975" s="12" t="s">
         <v>2061</v>
       </c>
-    </row>
-    <row r="1975" ht="17" customHeight="1" spans="1:4">
-      <c r="A1975" s="11"/>
-      <c r="B1975" s="11"/>
-      <c r="C1975" s="11"/>
-      <c r="D1975" s="11" t="s">
+      <c r="D1975" s="12" t="s">
         <v>2062</v>
       </c>
     </row>
-    <row r="1976" ht="17" customHeight="1" spans="1:4">
-      <c r="A1976" s="11"/>
-      <c r="B1976" s="11"/>
-      <c r="C1976" s="11"/>
-      <c r="D1976" s="11" t="s">
+    <row r="1976" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1976" s="12"/>
+      <c r="B1976" s="12"/>
+      <c r="C1976" s="12"/>
+      <c r="D1976" s="12" t="s">
         <v>2063</v>
       </c>
     </row>
-    <row r="1977" ht="17" customHeight="1" spans="1:4">
-      <c r="A1977" s="11"/>
-      <c r="B1977" s="11"/>
-      <c r="C1977" s="11"/>
-      <c r="D1977" s="11" t="s">
+    <row r="1977" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1977" s="12"/>
+      <c r="B1977" s="12"/>
+      <c r="C1977" s="12"/>
+      <c r="D1977" s="12" t="s">
         <v>2064</v>
       </c>
     </row>
-    <row r="1978" ht="17" customHeight="1" spans="1:4">
-      <c r="A1978" s="11"/>
-      <c r="B1978" s="11"/>
-      <c r="C1978" s="11"/>
-      <c r="D1978" s="11" t="s">
+    <row r="1978" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1978" s="12"/>
+      <c r="B1978" s="12"/>
+      <c r="C1978" s="12"/>
+      <c r="D1978" s="12" t="s">
         <v>2065</v>
       </c>
     </row>
-    <row r="1979" ht="17" customHeight="1" spans="1:4">
-      <c r="A1979" s="11"/>
-      <c r="B1979" s="11"/>
-      <c r="C1979" s="11"/>
-      <c r="D1979" s="11" t="s">
-        <v>71</v>
+    <row r="1979" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A1979" s="12"/>
+      <c r="B1979" s="12"/>
+      <c r="C1979" s="12"/>
+      <c r="D1979" s="12" t="s">
+        <v>2066</v>
       </c>
     </row>
     <row r="1980" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1980" s="12" t="s">
-        <v>2066</v>
-      </c>
-      <c r="B1980" s="12" t="s">
+      <c r="A1980" s="12"/>
+      <c r="B1980" s="12"/>
+      <c r="C1980" s="12"/>
+      <c r="D1980" s="12" t="s">
         <v>2067</v>
-      </c>
-      <c r="C1980" s="12" t="s">
-        <v>2068</v>
-      </c>
-      <c r="D1980" s="12" t="s">
-        <v>2069</v>
       </c>
     </row>
     <row r="1981" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24650,7 +24623,7 @@
       <c r="B1981" s="12"/>
       <c r="C1981" s="12"/>
       <c r="D1981" s="12" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1982" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24658,7 +24631,7 @@
       <c r="B1982" s="12"/>
       <c r="C1982" s="12"/>
       <c r="D1982" s="12" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1983" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24666,7 +24639,7 @@
       <c r="B1983" s="12"/>
       <c r="C1983" s="12"/>
       <c r="D1983" s="12" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1984" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24674,7 +24647,7 @@
       <c r="B1984" s="12"/>
       <c r="C1984" s="12"/>
       <c r="D1984" s="12" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1985" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24682,7 +24655,7 @@
       <c r="B1985" s="12"/>
       <c r="C1985" s="12"/>
       <c r="D1985" s="12" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1986" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24690,61 +24663,61 @@
       <c r="B1986" s="12"/>
       <c r="C1986" s="12"/>
       <c r="D1986" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1987" ht="17" customHeight="1" spans="1:4">
+      <c r="A1987" s="11" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B1987" s="11" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1987" s="11" t="s">
         <v>2075</v>
       </c>
-    </row>
-    <row r="1987" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1987" s="12"/>
-      <c r="B1987" s="12"/>
-      <c r="C1987" s="12"/>
-      <c r="D1987" s="12" t="s">
+      <c r="D1987" s="11" t="s">
         <v>2076</v>
       </c>
     </row>
-    <row r="1988" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1988" s="12"/>
-      <c r="B1988" s="12"/>
-      <c r="C1988" s="12"/>
-      <c r="D1988" s="12" t="s">
+    <row r="1988" ht="17" customHeight="1" spans="1:4">
+      <c r="A1988" s="11"/>
+      <c r="B1988" s="11"/>
+      <c r="C1988" s="11"/>
+      <c r="D1988" s="11" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="1989" ht="17" customHeight="1" spans="1:4">
+      <c r="A1989" s="11"/>
+      <c r="B1989" s="11"/>
+      <c r="C1989" s="11"/>
+      <c r="D1989" s="11" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1990" ht="17" customHeight="1" spans="1:4">
+      <c r="A1990" s="11"/>
+      <c r="B1990" s="11"/>
+      <c r="C1990" s="11"/>
+      <c r="D1990" s="11" t="s">
         <v>2077</v>
       </c>
     </row>
-    <row r="1989" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1989" s="12"/>
-      <c r="B1989" s="12"/>
-      <c r="C1989" s="12"/>
-      <c r="D1989" s="12" t="s">
+    <row r="1991" ht="17" customHeight="1" spans="1:4">
+      <c r="A1991" s="11"/>
+      <c r="B1991" s="11"/>
+      <c r="C1991" s="11"/>
+      <c r="D1991" s="11" t="s">
         <v>2078</v>
       </c>
     </row>
-    <row r="1990" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1990" s="12"/>
-      <c r="B1990" s="12"/>
-      <c r="C1990" s="12"/>
-      <c r="D1990" s="12" t="s">
+    <row r="1992" ht="17" customHeight="1" spans="1:4">
+      <c r="A1992" s="11"/>
+      <c r="B1992" s="11"/>
+      <c r="C1992" s="11"/>
+      <c r="D1992" s="11" t="s">
         <v>2079</v>
-      </c>
-    </row>
-    <row r="1991" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A1991" s="12"/>
-      <c r="B1991" s="12"/>
-      <c r="C1991" s="12"/>
-      <c r="D1991" s="12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="1992" ht="17" customHeight="1" spans="1:4">
-      <c r="A1992" s="11" t="s">
-        <v>2080</v>
-      </c>
-      <c r="B1992" s="11" t="s">
-        <v>2081</v>
-      </c>
-      <c r="C1992" s="11" t="s">
-        <v>2082</v>
-      </c>
-      <c r="D1992" s="11" t="s">
-        <v>2083</v>
       </c>
     </row>
     <row r="1993" ht="17" customHeight="1" spans="1:4">
@@ -24752,7 +24725,7 @@
       <c r="B1993" s="11"/>
       <c r="C1993" s="11"/>
       <c r="D1993" s="11" t="s">
-        <v>1615</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1994" ht="17" customHeight="1" spans="1:4">
@@ -24760,7 +24733,7 @@
       <c r="B1994" s="11"/>
       <c r="C1994" s="11"/>
       <c r="D1994" s="11" t="s">
-        <v>1616</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1995" ht="17" customHeight="1" spans="1:4">
@@ -24768,7 +24741,7 @@
       <c r="B1995" s="11"/>
       <c r="C1995" s="11"/>
       <c r="D1995" s="11" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1996" ht="17" customHeight="1" spans="1:4">
@@ -24776,7 +24749,7 @@
       <c r="B1996" s="11"/>
       <c r="C1996" s="11"/>
       <c r="D1996" s="11" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1997" ht="17" customHeight="1" spans="1:4">
@@ -24784,7 +24757,7 @@
       <c r="B1997" s="11"/>
       <c r="C1997" s="11"/>
       <c r="D1997" s="11" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1998" ht="17" customHeight="1" spans="1:4">
@@ -24792,7 +24765,7 @@
       <c r="B1998" s="11"/>
       <c r="C1998" s="11"/>
       <c r="D1998" s="11" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1999" ht="17" customHeight="1" spans="1:4">
@@ -24800,7 +24773,7 @@
       <c r="B1999" s="11"/>
       <c r="C1999" s="11"/>
       <c r="D1999" s="11" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="2000" ht="17" customHeight="1" spans="1:4">
@@ -24808,7 +24781,7 @@
       <c r="B2000" s="11"/>
       <c r="C2000" s="11"/>
       <c r="D2000" s="11" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="2001" ht="17" customHeight="1" spans="1:4">
@@ -24816,7 +24789,7 @@
       <c r="B2001" s="11"/>
       <c r="C2001" s="11"/>
       <c r="D2001" s="11" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="2002" ht="17" customHeight="1" spans="1:4">
@@ -24824,7 +24797,7 @@
       <c r="B2002" s="11"/>
       <c r="C2002" s="11"/>
       <c r="D2002" s="11" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="2003" ht="17" customHeight="1" spans="1:4">
@@ -24832,7 +24805,7 @@
       <c r="B2003" s="11"/>
       <c r="C2003" s="11"/>
       <c r="D2003" s="11" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="2004" ht="17" customHeight="1" spans="1:4">
@@ -24840,7 +24813,7 @@
       <c r="B2004" s="11"/>
       <c r="C2004" s="11"/>
       <c r="D2004" s="11" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="2005" ht="17" customHeight="1" spans="1:4">
@@ -24848,15 +24821,21 @@
       <c r="B2005" s="11"/>
       <c r="C2005" s="11"/>
       <c r="D2005" s="11" t="s">
-        <v>2094</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2006" ht="17" customHeight="1" spans="1:4">
-      <c r="A2006" s="11"/>
-      <c r="B2006" s="11"/>
-      <c r="C2006" s="11"/>
+      <c r="A2006" s="11" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B2006" s="11" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C2006" s="11" t="s">
+        <v>2093</v>
+      </c>
       <c r="D2006" s="11" t="s">
-        <v>2095</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="2007" ht="17" customHeight="1" spans="1:4">
@@ -24864,7 +24843,7 @@
       <c r="B2007" s="11"/>
       <c r="C2007" s="11"/>
       <c r="D2007" s="11" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="2008" ht="17" customHeight="1" spans="1:4">
@@ -24872,7 +24851,7 @@
       <c r="B2008" s="11"/>
       <c r="C2008" s="11"/>
       <c r="D2008" s="11" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="2009" ht="17" customHeight="1" spans="1:4">
@@ -24880,7 +24859,7 @@
       <c r="B2009" s="11"/>
       <c r="C2009" s="11"/>
       <c r="D2009" s="11" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="2010" ht="17" customHeight="1" spans="1:4">
@@ -24888,21 +24867,15 @@
       <c r="B2010" s="11"/>
       <c r="C2010" s="11"/>
       <c r="D2010" s="11" t="s">
-        <v>25</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="2011" ht="17" customHeight="1" spans="1:4">
-      <c r="A2011" s="11" t="s">
-        <v>2080</v>
-      </c>
-      <c r="B2011" s="11" t="s">
-        <v>2099</v>
-      </c>
-      <c r="C2011" s="11" t="s">
-        <v>2100</v>
-      </c>
+      <c r="A2011" s="11"/>
+      <c r="B2011" s="11"/>
+      <c r="C2011" s="11"/>
       <c r="D2011" s="11" t="s">
-        <v>2083</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="2012" ht="17" customHeight="1" spans="1:4">
@@ -24910,7 +24883,7 @@
       <c r="B2012" s="11"/>
       <c r="C2012" s="11"/>
       <c r="D2012" s="11" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="2013" ht="17" customHeight="1" spans="1:4">
@@ -24918,7 +24891,7 @@
       <c r="B2013" s="11"/>
       <c r="C2013" s="11"/>
       <c r="D2013" s="11" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="2014" ht="17" customHeight="1" spans="1:4">
@@ -24926,7 +24899,7 @@
       <c r="B2014" s="11"/>
       <c r="C2014" s="11"/>
       <c r="D2014" s="11" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="2015" ht="17" customHeight="1" spans="1:4">
@@ -24934,7 +24907,7 @@
       <c r="B2015" s="11"/>
       <c r="C2015" s="11"/>
       <c r="D2015" s="11" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="2016" ht="17" customHeight="1" spans="1:4">
@@ -24942,7 +24915,7 @@
       <c r="B2016" s="11"/>
       <c r="C2016" s="11"/>
       <c r="D2016" s="11" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="2017" ht="17" customHeight="1" spans="1:4">
@@ -24950,7 +24923,7 @@
       <c r="B2017" s="11"/>
       <c r="C2017" s="11"/>
       <c r="D2017" s="11" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="2018" ht="17" customHeight="1" spans="1:4">
@@ -24958,13 +24931,19 @@
       <c r="B2018" s="11"/>
       <c r="C2018" s="11"/>
       <c r="D2018" s="11" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2019" ht="17" customHeight="1" spans="1:4">
+      <c r="A2019" s="11" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B2019" s="11" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C2019" s="11" t="s">
         <v>2107</v>
       </c>
-    </row>
-    <row r="2019" ht="17" customHeight="1" spans="1:4">
-      <c r="A2019" s="11"/>
-      <c r="B2019" s="11"/>
-      <c r="C2019" s="11"/>
       <c r="D2019" s="11" t="s">
         <v>2108</v>
       </c>
@@ -24974,7 +24953,7 @@
       <c r="B2020" s="11"/>
       <c r="C2020" s="11"/>
       <c r="D2020" s="11" t="s">
-        <v>2109</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="2021" ht="17" customHeight="1" spans="1:4">
@@ -24982,7 +24961,7 @@
       <c r="B2021" s="11"/>
       <c r="C2021" s="11"/>
       <c r="D2021" s="11" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="2022" ht="17" customHeight="1" spans="1:4">
@@ -24990,7 +24969,7 @@
       <c r="B2022" s="11"/>
       <c r="C2022" s="11"/>
       <c r="D2022" s="11" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="2023" ht="17" customHeight="1" spans="1:4">
@@ -24998,21 +24977,15 @@
       <c r="B2023" s="11"/>
       <c r="C2023" s="11"/>
       <c r="D2023" s="11" t="s">
-        <v>675</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="2024" ht="17" customHeight="1" spans="1:4">
-      <c r="A2024" s="11" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B2024" s="11" t="s">
-        <v>2113</v>
-      </c>
-      <c r="C2024" s="11" t="s">
-        <v>2114</v>
-      </c>
+      <c r="A2024" s="11"/>
+      <c r="B2024" s="11"/>
+      <c r="C2024" s="11"/>
       <c r="D2024" s="11" t="s">
-        <v>2115</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="2025" ht="17" customHeight="1" spans="1:4">
@@ -25020,7 +24993,7 @@
       <c r="B2025" s="11"/>
       <c r="C2025" s="11"/>
       <c r="D2025" s="11" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="2026" ht="17" customHeight="1" spans="1:4">
@@ -25028,7 +25001,7 @@
       <c r="B2026" s="11"/>
       <c r="C2026" s="11"/>
       <c r="D2026" s="11" t="s">
-        <v>2116</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="2027" ht="17" customHeight="1" spans="1:4">
@@ -25036,7 +25009,7 @@
       <c r="B2027" s="11"/>
       <c r="C2027" s="11"/>
       <c r="D2027" s="11" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="2028" ht="17" customHeight="1" spans="1:4">
@@ -25044,7 +25017,7 @@
       <c r="B2028" s="11"/>
       <c r="C2028" s="11"/>
       <c r="D2028" s="11" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="2029" ht="17" customHeight="1" spans="1:4">
@@ -25052,7 +25025,7 @@
       <c r="B2029" s="11"/>
       <c r="C2029" s="11"/>
       <c r="D2029" s="11" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="2030" ht="17" customHeight="1" spans="1:4">
@@ -25060,7 +25033,7 @@
       <c r="B2030" s="11"/>
       <c r="C2030" s="11"/>
       <c r="D2030" s="11" t="s">
-        <v>1327</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="2031" ht="17" customHeight="1" spans="1:4">
@@ -25068,15 +25041,21 @@
       <c r="B2031" s="11"/>
       <c r="C2031" s="11"/>
       <c r="D2031" s="11" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="2032" ht="17" customHeight="1" spans="1:4">
-      <c r="A2032" s="11"/>
-      <c r="B2032" s="11"/>
-      <c r="C2032" s="11"/>
+      <c r="A2032" s="11" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B2032" s="11" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C2032" s="11" t="s">
+        <v>2114</v>
+      </c>
       <c r="D2032" s="11" t="s">
-        <v>1329</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="2033" ht="17" customHeight="1" spans="1:4">
@@ -25084,7 +25063,7 @@
       <c r="B2033" s="11"/>
       <c r="C2033" s="11"/>
       <c r="D2033" s="11" t="s">
-        <v>1330</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2034" ht="17" customHeight="1" spans="1:4">
@@ -25092,7 +25071,7 @@
       <c r="B2034" s="11"/>
       <c r="C2034" s="11"/>
       <c r="D2034" s="11" t="s">
-        <v>1331</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2035" ht="17" customHeight="1" spans="1:4">
@@ -25100,7 +25079,7 @@
       <c r="B2035" s="11"/>
       <c r="C2035" s="11"/>
       <c r="D2035" s="11" t="s">
-        <v>2117</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2036" ht="17" customHeight="1" spans="1:4">
@@ -25108,21 +25087,15 @@
       <c r="B2036" s="11"/>
       <c r="C2036" s="11"/>
       <c r="D2036" s="11" t="s">
-        <v>1333</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2037" ht="17" customHeight="1" spans="1:4">
-      <c r="A2037" s="11" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B2037" s="11" t="s">
-        <v>2119</v>
-      </c>
-      <c r="C2037" s="11" t="s">
-        <v>2120</v>
-      </c>
+      <c r="A2037" s="11"/>
+      <c r="B2037" s="11"/>
+      <c r="C2037" s="11"/>
       <c r="D2037" s="11" t="s">
-        <v>2121</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2038" ht="17" customHeight="1" spans="1:4">
@@ -25130,7 +25103,7 @@
       <c r="B2038" s="11"/>
       <c r="C2038" s="11"/>
       <c r="D2038" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2039" ht="17" customHeight="1" spans="1:4">
@@ -25138,7 +25111,7 @@
       <c r="B2039" s="11"/>
       <c r="C2039" s="11"/>
       <c r="D2039" s="11" t="s">
-        <v>451</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="2040" ht="17" customHeight="1" spans="1:4">
@@ -25146,15 +25119,21 @@
       <c r="B2040" s="11"/>
       <c r="C2040" s="11"/>
       <c r="D2040" s="11" t="s">
-        <v>452</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2041" ht="17" customHeight="1" spans="1:4">
-      <c r="A2041" s="11"/>
-      <c r="B2041" s="11"/>
-      <c r="C2041" s="11"/>
+      <c r="A2041" s="11" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B2041" s="11" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C2041" s="11" t="s">
+        <v>2119</v>
+      </c>
       <c r="D2041" s="11" t="s">
-        <v>453</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="2042" ht="17" customHeight="1" spans="1:4">
@@ -25162,7 +25141,7 @@
       <c r="B2042" s="11"/>
       <c r="C2042" s="11"/>
       <c r="D2042" s="11" t="s">
-        <v>454</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="2043" ht="17" customHeight="1" spans="1:4">
@@ -25170,7 +25149,7 @@
       <c r="B2043" s="11"/>
       <c r="C2043" s="11"/>
       <c r="D2043" s="11" t="s">
-        <v>455</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="2044" ht="17" customHeight="1" spans="1:4">
@@ -25178,7 +25157,7 @@
       <c r="B2044" s="11"/>
       <c r="C2044" s="11"/>
       <c r="D2044" s="11" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2045" ht="17" customHeight="1" spans="1:4">
@@ -25186,21 +25165,15 @@
       <c r="B2045" s="11"/>
       <c r="C2045" s="11"/>
       <c r="D2045" s="11" t="s">
-        <v>116</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="2046" ht="17" customHeight="1" spans="1:4">
-      <c r="A2046" s="11" t="s">
-        <v>2123</v>
-      </c>
-      <c r="B2046" s="11" t="s">
-        <v>2124</v>
-      </c>
-      <c r="C2046" s="11" t="s">
+      <c r="A2046" s="11"/>
+      <c r="B2046" s="11"/>
+      <c r="C2046" s="11"/>
+      <c r="D2046" s="11" t="s">
         <v>2125</v>
-      </c>
-      <c r="D2046" s="11" t="s">
-        <v>2126</v>
       </c>
     </row>
     <row r="2047" ht="17" customHeight="1" spans="1:4">
@@ -25208,7 +25181,7 @@
       <c r="B2047" s="11"/>
       <c r="C2047" s="11"/>
       <c r="D2047" s="11" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="2048" ht="17" customHeight="1" spans="1:4">
@@ -25216,7 +25189,7 @@
       <c r="B2048" s="11"/>
       <c r="C2048" s="11"/>
       <c r="D2048" s="11" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="2049" ht="17" customHeight="1" spans="1:4">
@@ -25224,7 +25197,7 @@
       <c r="B2049" s="11"/>
       <c r="C2049" s="11"/>
       <c r="D2049" s="11" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="2050" ht="17" customHeight="1" spans="1:4">
@@ -25232,7 +25205,7 @@
       <c r="B2050" s="11"/>
       <c r="C2050" s="11"/>
       <c r="D2050" s="11" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="2051" ht="17" customHeight="1" spans="1:4">
@@ -25240,7 +25213,7 @@
       <c r="B2051" s="11"/>
       <c r="C2051" s="11"/>
       <c r="D2051" s="11" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="2052" ht="17" customHeight="1" spans="1:4">
@@ -25248,7 +25221,7 @@
       <c r="B2052" s="11"/>
       <c r="C2052" s="11"/>
       <c r="D2052" s="11" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="2053" ht="17" customHeight="1" spans="1:4">
@@ -25256,7 +25229,7 @@
       <c r="B2053" s="11"/>
       <c r="C2053" s="11"/>
       <c r="D2053" s="11" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="2054" ht="17" customHeight="1" spans="1:4">
@@ -25264,7 +25237,7 @@
       <c r="B2054" s="11"/>
       <c r="C2054" s="11"/>
       <c r="D2054" s="11" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="2055" ht="17" customHeight="1" spans="1:4">
@@ -25272,7 +25245,7 @@
       <c r="B2055" s="11"/>
       <c r="C2055" s="11"/>
       <c r="D2055" s="11" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="2056" ht="17" customHeight="1" spans="1:4">
@@ -25280,7 +25253,7 @@
       <c r="B2056" s="11"/>
       <c r="C2056" s="11"/>
       <c r="D2056" s="11" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="2057" ht="17" customHeight="1" spans="1:4">
@@ -25288,7 +25261,7 @@
       <c r="B2057" s="11"/>
       <c r="C2057" s="11"/>
       <c r="D2057" s="11" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="2058" ht="17" customHeight="1" spans="1:4">
@@ -25296,7 +25269,7 @@
       <c r="B2058" s="11"/>
       <c r="C2058" s="11"/>
       <c r="D2058" s="11" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="2059" ht="17" customHeight="1" spans="1:4">
@@ -25304,7 +25277,7 @@
       <c r="B2059" s="11"/>
       <c r="C2059" s="11"/>
       <c r="D2059" s="11" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="2060" ht="17" customHeight="1" spans="1:4">
@@ -25312,61 +25285,61 @@
       <c r="B2060" s="11"/>
       <c r="C2060" s="11"/>
       <c r="D2060" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="2061" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2061" s="12" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B2061" s="12" t="s">
         <v>2140</v>
       </c>
-    </row>
-    <row r="2061" ht="17" customHeight="1" spans="1:4">
-      <c r="A2061" s="11"/>
-      <c r="B2061" s="11"/>
-      <c r="C2061" s="11"/>
-      <c r="D2061" s="11" t="s">
+      <c r="C2061" s="12" t="s">
         <v>2141</v>
       </c>
-    </row>
-    <row r="2062" ht="17" customHeight="1" spans="1:4">
-      <c r="A2062" s="11"/>
-      <c r="B2062" s="11"/>
-      <c r="C2062" s="11"/>
-      <c r="D2062" s="11" t="s">
+      <c r="D2061" s="12" t="s">
         <v>2142</v>
       </c>
     </row>
-    <row r="2063" ht="17" customHeight="1" spans="1:4">
-      <c r="A2063" s="11"/>
-      <c r="B2063" s="11"/>
-      <c r="C2063" s="11"/>
-      <c r="D2063" s="11" t="s">
+    <row r="2062" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2062" s="12"/>
+      <c r="B2062" s="12"/>
+      <c r="C2062" s="12"/>
+      <c r="D2062" s="12" t="s">
         <v>2143</v>
       </c>
     </row>
-    <row r="2064" ht="17" customHeight="1" spans="1:4">
-      <c r="A2064" s="11"/>
-      <c r="B2064" s="11"/>
-      <c r="C2064" s="11"/>
-      <c r="D2064" s="11" t="s">
+    <row r="2063" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2063" s="12"/>
+      <c r="B2063" s="12"/>
+      <c r="C2063" s="12"/>
+      <c r="D2063" s="12" t="s">
         <v>2144</v>
       </c>
     </row>
-    <row r="2065" ht="17" customHeight="1" spans="1:4">
-      <c r="A2065" s="11"/>
-      <c r="B2065" s="11"/>
-      <c r="C2065" s="11"/>
-      <c r="D2065" s="11" t="s">
-        <v>478</v>
+    <row r="2064" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2064" s="12"/>
+      <c r="B2064" s="12"/>
+      <c r="C2064" s="12"/>
+      <c r="D2064" s="12" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="2065" ht="17" hidden="1" customHeight="1" spans="1:4">
+      <c r="A2065" s="12"/>
+      <c r="B2065" s="12"/>
+      <c r="C2065" s="12"/>
+      <c r="D2065" s="12" t="s">
+        <v>2146</v>
       </c>
     </row>
     <row r="2066" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2066" s="12" t="s">
-        <v>2145</v>
-      </c>
-      <c r="B2066" s="12" t="s">
-        <v>2146</v>
-      </c>
-      <c r="C2066" s="12" t="s">
+      <c r="A2066" s="12"/>
+      <c r="B2066" s="12"/>
+      <c r="C2066" s="12"/>
+      <c r="D2066" s="12" t="s">
         <v>2147</v>
-      </c>
-      <c r="D2066" s="12" t="s">
-        <v>2148</v>
       </c>
     </row>
     <row r="2067" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25374,7 +25347,7 @@
       <c r="B2067" s="12"/>
       <c r="C2067" s="12"/>
       <c r="D2067" s="12" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="2068" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25382,7 +25355,7 @@
       <c r="B2068" s="12"/>
       <c r="C2068" s="12"/>
       <c r="D2068" s="12" t="s">
-        <v>2150</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2069" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25390,7 +25363,7 @@
       <c r="B2069" s="12"/>
       <c r="C2069" s="12"/>
       <c r="D2069" s="12" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="2070" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25398,7 +25371,7 @@
       <c r="B2070" s="12"/>
       <c r="C2070" s="12"/>
       <c r="D2070" s="12" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="2071" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25406,61 +25379,61 @@
       <c r="B2071" s="12"/>
       <c r="C2071" s="12"/>
       <c r="D2071" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2072" ht="17" customHeight="1" spans="1:4">
+      <c r="A2072" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B2072" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C2072" s="2" t="s">
         <v>2153</v>
       </c>
-    </row>
-    <row r="2072" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2072" s="12"/>
-      <c r="B2072" s="12"/>
-      <c r="C2072" s="12"/>
-      <c r="D2072" s="12" t="s">
+      <c r="D2072" s="2" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="2073" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2073" s="12"/>
-      <c r="B2073" s="12"/>
-      <c r="C2073" s="12"/>
-      <c r="D2073" s="12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="2074" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2074" s="12"/>
-      <c r="B2074" s="12"/>
-      <c r="C2074" s="12"/>
-      <c r="D2074" s="12" t="s">
+    <row r="2073" ht="17" customHeight="1" spans="1:4">
+      <c r="A2073" s="2"/>
+      <c r="B2073" s="2"/>
+      <c r="C2073" s="2"/>
+      <c r="D2073" s="2" t="s">
         <v>2155</v>
       </c>
     </row>
-    <row r="2075" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2075" s="12"/>
-      <c r="B2075" s="12"/>
-      <c r="C2075" s="12"/>
-      <c r="D2075" s="12" t="s">
+    <row r="2074" ht="17" customHeight="1" spans="1:4">
+      <c r="A2074" s="2"/>
+      <c r="B2074" s="2"/>
+      <c r="C2074" s="2"/>
+      <c r="D2074" s="2" t="s">
         <v>2156</v>
       </c>
     </row>
-    <row r="2076" ht="17" hidden="1" customHeight="1" spans="1:4">
-      <c r="A2076" s="12"/>
-      <c r="B2076" s="12"/>
-      <c r="C2076" s="12"/>
-      <c r="D2076" s="12" t="s">
-        <v>211</v>
+    <row r="2075" ht="17" customHeight="1" spans="1:4">
+      <c r="A2075" s="2"/>
+      <c r="B2075" s="2"/>
+      <c r="C2075" s="2"/>
+      <c r="D2075" s="2" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="2076" ht="17" customHeight="1" spans="1:4">
+      <c r="A2076" s="2"/>
+      <c r="B2076" s="2"/>
+      <c r="C2076" s="2"/>
+      <c r="D2076" s="2" t="s">
+        <v>2158</v>
       </c>
     </row>
     <row r="2077" ht="17" customHeight="1" spans="1:4">
-      <c r="A2077" s="2" t="s">
-        <v>2157</v>
-      </c>
-      <c r="B2077" s="2" t="s">
-        <v>2158</v>
-      </c>
-      <c r="C2077" s="2" t="s">
+      <c r="A2077" s="2"/>
+      <c r="B2077" s="2"/>
+      <c r="C2077" s="2"/>
+      <c r="D2077" s="2" t="s">
         <v>2159</v>
-      </c>
-      <c r="D2077" s="2" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="2078" ht="17" customHeight="1" spans="1:4">
@@ -25468,7 +25441,7 @@
       <c r="B2078" s="2"/>
       <c r="C2078" s="2"/>
       <c r="D2078" s="2" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="2079" ht="17" customHeight="1" spans="1:4">
@@ -25476,7 +25449,7 @@
       <c r="B2079" s="2"/>
       <c r="C2079" s="2"/>
       <c r="D2079" s="2" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="2080" ht="17" customHeight="1" spans="1:4">
@@ -25484,7 +25457,7 @@
       <c r="B2080" s="2"/>
       <c r="C2080" s="2"/>
       <c r="D2080" s="2" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="2081" ht="17" customHeight="1" spans="1:4">
@@ -25492,7 +25465,7 @@
       <c r="B2081" s="2"/>
       <c r="C2081" s="2"/>
       <c r="D2081" s="2" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="2082" ht="17" customHeight="1" spans="1:4">
@@ -25500,7 +25473,7 @@
       <c r="B2082" s="2"/>
       <c r="C2082" s="2"/>
       <c r="D2082" s="2" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="2083" ht="17" customHeight="1" spans="1:4">
@@ -25508,7 +25481,7 @@
       <c r="B2083" s="2"/>
       <c r="C2083" s="2"/>
       <c r="D2083" s="2" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="2084" ht="17" customHeight="1" spans="1:4">
@@ -25516,7 +25489,7 @@
       <c r="B2084" s="2"/>
       <c r="C2084" s="2"/>
       <c r="D2084" s="2" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="2085" ht="17" customHeight="1" spans="1:4">
@@ -25524,7 +25497,7 @@
       <c r="B2085" s="2"/>
       <c r="C2085" s="2"/>
       <c r="D2085" s="2" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="2086" ht="17" customHeight="1" spans="1:4">
@@ -25532,15 +25505,21 @@
       <c r="B2086" s="2"/>
       <c r="C2086" s="2"/>
       <c r="D2086" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2087" ht="17" customHeight="1" spans="1:4">
+      <c r="A2087" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B2087" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C2087" s="2" t="s">
         <v>2169</v>
       </c>
-    </row>
-    <row r="2087" ht="17" customHeight="1" spans="1:4">
-      <c r="A2087" s="2"/>
-      <c r="B2087" s="2"/>
-      <c r="C2087" s="2"/>
       <c r="D2087" s="2" t="s">
-        <v>2170</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="2088" ht="17" customHeight="1" spans="1:4">
@@ -25548,7 +25527,7 @@
       <c r="B2088" s="2"/>
       <c r="C2088" s="2"/>
       <c r="D2088" s="2" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="2089" ht="17" customHeight="1" spans="1:4">
@@ -25556,7 +25535,7 @@
       <c r="B2089" s="2"/>
       <c r="C2089" s="2"/>
       <c r="D2089" s="2" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="2090" ht="17" customHeight="1" spans="1:4">
@@ -25564,7 +25543,7 @@
       <c r="B2090" s="2"/>
       <c r="C2090" s="2"/>
       <c r="D2090" s="2" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="2091" ht="17" customHeight="1" spans="1:4">
@@ -25572,21 +25551,15 @@
       <c r="B2091" s="2"/>
       <c r="C2091" s="2"/>
       <c r="D2091" s="2" t="s">
-        <v>87</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="2092" ht="17" customHeight="1" spans="1:4">
-      <c r="A2092" s="2" t="s">
-        <v>2157</v>
-      </c>
-      <c r="B2092" s="2" t="s">
-        <v>2174</v>
-      </c>
-      <c r="C2092" s="2" t="s">
-        <v>2175</v>
-      </c>
+      <c r="A2092" s="2"/>
+      <c r="B2092" s="2"/>
+      <c r="C2092" s="2"/>
       <c r="D2092" s="2" t="s">
-        <v>2160</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="2093" ht="17" customHeight="1" spans="1:4">
@@ -25594,7 +25567,7 @@
       <c r="B2093" s="2"/>
       <c r="C2093" s="2"/>
       <c r="D2093" s="2" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="2094" ht="17" customHeight="1" spans="1:4">
@@ -25602,46 +25575,6 @@
       <c r="B2094" s="2"/>
       <c r="C2094" s="2"/>
       <c r="D2094" s="2" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="2095" ht="17" customHeight="1" spans="1:4">
-      <c r="A2095" s="2"/>
-      <c r="B2095" s="2"/>
-      <c r="C2095" s="2"/>
-      <c r="D2095" s="2" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="2096" ht="17" customHeight="1" spans="1:4">
-      <c r="A2096" s="2"/>
-      <c r="B2096" s="2"/>
-      <c r="C2096" s="2"/>
-      <c r="D2096" s="2" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="2097" ht="17" customHeight="1" spans="1:4">
-      <c r="A2097" s="2"/>
-      <c r="B2097" s="2"/>
-      <c r="C2097" s="2"/>
-      <c r="D2097" s="2" t="s">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="2098" ht="17" customHeight="1" spans="1:4">
-      <c r="A2098" s="2"/>
-      <c r="B2098" s="2"/>
-      <c r="C2098" s="2"/>
-      <c r="D2098" s="2" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="2099" ht="17" customHeight="1" spans="1:4">
-      <c r="A2099" s="2"/>
-      <c r="B2099" s="2"/>
-      <c r="C2099" s="2"/>
-      <c r="D2099" s="2" t="s">
         <v>419</v>
       </c>
     </row>
@@ -25769,48 +25702,48 @@
     <mergeCell ref="A1527:A1538"/>
     <mergeCell ref="A1539:A1547"/>
     <mergeCell ref="A1548:A1549"/>
-    <mergeCell ref="A1550:A1559"/>
-    <mergeCell ref="A1560:A1578"/>
-    <mergeCell ref="A1579:A1593"/>
-    <mergeCell ref="A1594:A1611"/>
-    <mergeCell ref="A1612:A1626"/>
-    <mergeCell ref="A1627:A1634"/>
-    <mergeCell ref="A1635:A1649"/>
-    <mergeCell ref="A1650:A1663"/>
-    <mergeCell ref="A1664:A1679"/>
-    <mergeCell ref="A1680:A1696"/>
-    <mergeCell ref="A1697:A1710"/>
-    <mergeCell ref="A1711:A1726"/>
-    <mergeCell ref="A1727:A1735"/>
-    <mergeCell ref="A1736:A1749"/>
-    <mergeCell ref="A1750:A1761"/>
-    <mergeCell ref="A1762:A1775"/>
-    <mergeCell ref="A1776:A1790"/>
-    <mergeCell ref="A1791:A1803"/>
-    <mergeCell ref="A1804:A1822"/>
-    <mergeCell ref="A1823:A1829"/>
-    <mergeCell ref="A1830:A1835"/>
-    <mergeCell ref="A1836:A1842"/>
-    <mergeCell ref="A1843:A1848"/>
-    <mergeCell ref="A1849:A1858"/>
-    <mergeCell ref="A1859:A1870"/>
-    <mergeCell ref="A1871:A1881"/>
-    <mergeCell ref="A1882:A1894"/>
-    <mergeCell ref="A1895:A1910"/>
-    <mergeCell ref="A1911:A1929"/>
-    <mergeCell ref="A1930:A1940"/>
-    <mergeCell ref="A1941:A1954"/>
-    <mergeCell ref="A1955:A1969"/>
-    <mergeCell ref="A1970:A1979"/>
-    <mergeCell ref="A1980:A1991"/>
-    <mergeCell ref="A1992:A2010"/>
-    <mergeCell ref="A2011:A2023"/>
-    <mergeCell ref="A2024:A2036"/>
-    <mergeCell ref="A2037:A2045"/>
-    <mergeCell ref="A2046:A2065"/>
-    <mergeCell ref="A2066:A2076"/>
-    <mergeCell ref="A2077:A2091"/>
-    <mergeCell ref="A2092:A2099"/>
+    <mergeCell ref="A1550:A1557"/>
+    <mergeCell ref="A1558:A1576"/>
+    <mergeCell ref="A1577:A1591"/>
+    <mergeCell ref="A1592:A1609"/>
+    <mergeCell ref="A1610:A1624"/>
+    <mergeCell ref="A1625:A1632"/>
+    <mergeCell ref="A1633:A1647"/>
+    <mergeCell ref="A1648:A1661"/>
+    <mergeCell ref="A1662:A1677"/>
+    <mergeCell ref="A1678:A1694"/>
+    <mergeCell ref="A1695:A1708"/>
+    <mergeCell ref="A1709:A1724"/>
+    <mergeCell ref="A1725:A1733"/>
+    <mergeCell ref="A1734:A1747"/>
+    <mergeCell ref="A1748:A1759"/>
+    <mergeCell ref="A1760:A1773"/>
+    <mergeCell ref="A1774:A1788"/>
+    <mergeCell ref="A1789:A1801"/>
+    <mergeCell ref="A1802:A1817"/>
+    <mergeCell ref="A1818:A1824"/>
+    <mergeCell ref="A1825:A1830"/>
+    <mergeCell ref="A1831:A1837"/>
+    <mergeCell ref="A1838:A1843"/>
+    <mergeCell ref="A1844:A1853"/>
+    <mergeCell ref="A1854:A1865"/>
+    <mergeCell ref="A1866:A1876"/>
+    <mergeCell ref="A1877:A1889"/>
+    <mergeCell ref="A1890:A1905"/>
+    <mergeCell ref="A1906:A1924"/>
+    <mergeCell ref="A1925:A1935"/>
+    <mergeCell ref="A1936:A1949"/>
+    <mergeCell ref="A1950:A1964"/>
+    <mergeCell ref="A1965:A1974"/>
+    <mergeCell ref="A1975:A1986"/>
+    <mergeCell ref="A1987:A2005"/>
+    <mergeCell ref="A2006:A2018"/>
+    <mergeCell ref="A2019:A2031"/>
+    <mergeCell ref="A2032:A2040"/>
+    <mergeCell ref="A2041:A2060"/>
+    <mergeCell ref="A2061:A2071"/>
+    <mergeCell ref="A2072:A2086"/>
+    <mergeCell ref="A2087:A2094"/>
     <mergeCell ref="B2:B20"/>
     <mergeCell ref="B21:B54"/>
     <mergeCell ref="B55:B64"/>
@@ -25933,48 +25866,48 @@
     <mergeCell ref="B1527:B1538"/>
     <mergeCell ref="B1539:B1547"/>
     <mergeCell ref="B1548:B1549"/>
-    <mergeCell ref="B1550:B1559"/>
-    <mergeCell ref="B1560:B1578"/>
-    <mergeCell ref="B1579:B1593"/>
-    <mergeCell ref="B1594:B1611"/>
-    <mergeCell ref="B1612:B1626"/>
-    <mergeCell ref="B1627:B1634"/>
-    <mergeCell ref="B1635:B1649"/>
-    <mergeCell ref="B1650:B1663"/>
-    <mergeCell ref="B1664:B1679"/>
-    <mergeCell ref="B1680:B1696"/>
-    <mergeCell ref="B1697:B1710"/>
-    <mergeCell ref="B1711:B1726"/>
-    <mergeCell ref="B1727:B1735"/>
-    <mergeCell ref="B1736:B1749"/>
-    <mergeCell ref="B1750:B1761"/>
-    <mergeCell ref="B1762:B1775"/>
-    <mergeCell ref="B1776:B1790"/>
-    <mergeCell ref="B1791:B1803"/>
-    <mergeCell ref="B1804:B1822"/>
-    <mergeCell ref="B1823:B1829"/>
-    <mergeCell ref="B1830:B1835"/>
-    <mergeCell ref="B1836:B1842"/>
-    <mergeCell ref="B1843:B1848"/>
-    <mergeCell ref="B1849:B1858"/>
-    <mergeCell ref="B1859:B1870"/>
-    <mergeCell ref="B1871:B1881"/>
-    <mergeCell ref="B1882:B1894"/>
-    <mergeCell ref="B1895:B1910"/>
-    <mergeCell ref="B1911:B1929"/>
-    <mergeCell ref="B1930:B1940"/>
-    <mergeCell ref="B1941:B1954"/>
-    <mergeCell ref="B1955:B1969"/>
-    <mergeCell ref="B1970:B1979"/>
-    <mergeCell ref="B1980:B1991"/>
-    <mergeCell ref="B1992:B2010"/>
-    <mergeCell ref="B2011:B2023"/>
-    <mergeCell ref="B2024:B2036"/>
-    <mergeCell ref="B2037:B2045"/>
-    <mergeCell ref="B2046:B2065"/>
-    <mergeCell ref="B2066:B2076"/>
-    <mergeCell ref="B2077:B2091"/>
-    <mergeCell ref="B2092:B2099"/>
+    <mergeCell ref="B1550:B1557"/>
+    <mergeCell ref="B1558:B1576"/>
+    <mergeCell ref="B1577:B1591"/>
+    <mergeCell ref="B1592:B1609"/>
+    <mergeCell ref="B1610:B1624"/>
+    <mergeCell ref="B1625:B1632"/>
+    <mergeCell ref="B1633:B1647"/>
+    <mergeCell ref="B1648:B1661"/>
+    <mergeCell ref="B1662:B1677"/>
+    <mergeCell ref="B1678:B1694"/>
+    <mergeCell ref="B1695:B1708"/>
+    <mergeCell ref="B1709:B1724"/>
+    <mergeCell ref="B1725:B1733"/>
+    <mergeCell ref="B1734:B1747"/>
+    <mergeCell ref="B1748:B1759"/>
+    <mergeCell ref="B1760:B1773"/>
+    <mergeCell ref="B1774:B1788"/>
+    <mergeCell ref="B1789:B1801"/>
+    <mergeCell ref="B1802:B1817"/>
+    <mergeCell ref="B1818:B1824"/>
+    <mergeCell ref="B1825:B1830"/>
+    <mergeCell ref="B1831:B1837"/>
+    <mergeCell ref="B1838:B1843"/>
+    <mergeCell ref="B1844:B1853"/>
+    <mergeCell ref="B1854:B1865"/>
+    <mergeCell ref="B1866:B1876"/>
+    <mergeCell ref="B1877:B1889"/>
+    <mergeCell ref="B1890:B1905"/>
+    <mergeCell ref="B1906:B1924"/>
+    <mergeCell ref="B1925:B1935"/>
+    <mergeCell ref="B1936:B1949"/>
+    <mergeCell ref="B1950:B1964"/>
+    <mergeCell ref="B1965:B1974"/>
+    <mergeCell ref="B1975:B1986"/>
+    <mergeCell ref="B1987:B2005"/>
+    <mergeCell ref="B2006:B2018"/>
+    <mergeCell ref="B2019:B2031"/>
+    <mergeCell ref="B2032:B2040"/>
+    <mergeCell ref="B2041:B2060"/>
+    <mergeCell ref="B2061:B2071"/>
+    <mergeCell ref="B2072:B2086"/>
+    <mergeCell ref="B2087:B2094"/>
     <mergeCell ref="C2:C20"/>
     <mergeCell ref="C21:C54"/>
     <mergeCell ref="C55:C64"/>
@@ -26097,48 +26030,48 @@
     <mergeCell ref="C1527:C1538"/>
     <mergeCell ref="C1539:C1547"/>
     <mergeCell ref="C1548:C1549"/>
-    <mergeCell ref="C1550:C1559"/>
-    <mergeCell ref="C1560:C1578"/>
-    <mergeCell ref="C1579:C1593"/>
-    <mergeCell ref="C1594:C1611"/>
-    <mergeCell ref="C1612:C1626"/>
-    <mergeCell ref="C1627:C1634"/>
-    <mergeCell ref="C1635:C1649"/>
-    <mergeCell ref="C1650:C1663"/>
-    <mergeCell ref="C1664:C1679"/>
-    <mergeCell ref="C1680:C1696"/>
-    <mergeCell ref="C1697:C1710"/>
-    <mergeCell ref="C1711:C1726"/>
-    <mergeCell ref="C1727:C1735"/>
-    <mergeCell ref="C1736:C1749"/>
-    <mergeCell ref="C1750:C1761"/>
-    <mergeCell ref="C1762:C1775"/>
-    <mergeCell ref="C1776:C1790"/>
-    <mergeCell ref="C1791:C1803"/>
-    <mergeCell ref="C1804:C1822"/>
-    <mergeCell ref="C1823:C1829"/>
-    <mergeCell ref="C1830:C1835"/>
-    <mergeCell ref="C1836:C1842"/>
-    <mergeCell ref="C1843:C1848"/>
-    <mergeCell ref="C1849:C1858"/>
-    <mergeCell ref="C1859:C1870"/>
-    <mergeCell ref="C1871:C1881"/>
-    <mergeCell ref="C1882:C1894"/>
-    <mergeCell ref="C1895:C1910"/>
-    <mergeCell ref="C1911:C1929"/>
-    <mergeCell ref="C1930:C1940"/>
-    <mergeCell ref="C1941:C1954"/>
-    <mergeCell ref="C1955:C1969"/>
-    <mergeCell ref="C1970:C1979"/>
-    <mergeCell ref="C1980:C1991"/>
-    <mergeCell ref="C1992:C2010"/>
-    <mergeCell ref="C2011:C2023"/>
-    <mergeCell ref="C2024:C2036"/>
-    <mergeCell ref="C2037:C2045"/>
-    <mergeCell ref="C2046:C2065"/>
-    <mergeCell ref="C2066:C2076"/>
-    <mergeCell ref="C2077:C2091"/>
-    <mergeCell ref="C2092:C2099"/>
+    <mergeCell ref="C1550:C1557"/>
+    <mergeCell ref="C1558:C1576"/>
+    <mergeCell ref="C1577:C1591"/>
+    <mergeCell ref="C1592:C1609"/>
+    <mergeCell ref="C1610:C1624"/>
+    <mergeCell ref="C1625:C1632"/>
+    <mergeCell ref="C1633:C1647"/>
+    <mergeCell ref="C1648:C1661"/>
+    <mergeCell ref="C1662:C1677"/>
+    <mergeCell ref="C1678:C1694"/>
+    <mergeCell ref="C1695:C1708"/>
+    <mergeCell ref="C1709:C1724"/>
+    <mergeCell ref="C1725:C1733"/>
+    <mergeCell ref="C1734:C1747"/>
+    <mergeCell ref="C1748:C1759"/>
+    <mergeCell ref="C1760:C1773"/>
+    <mergeCell ref="C1774:C1788"/>
+    <mergeCell ref="C1789:C1801"/>
+    <mergeCell ref="C1802:C1817"/>
+    <mergeCell ref="C1818:C1824"/>
+    <mergeCell ref="C1825:C1830"/>
+    <mergeCell ref="C1831:C1837"/>
+    <mergeCell ref="C1838:C1843"/>
+    <mergeCell ref="C1844:C1853"/>
+    <mergeCell ref="C1854:C1865"/>
+    <mergeCell ref="C1866:C1876"/>
+    <mergeCell ref="C1877:C1889"/>
+    <mergeCell ref="C1890:C1905"/>
+    <mergeCell ref="C1906:C1924"/>
+    <mergeCell ref="C1925:C1935"/>
+    <mergeCell ref="C1936:C1949"/>
+    <mergeCell ref="C1950:C1964"/>
+    <mergeCell ref="C1965:C1974"/>
+    <mergeCell ref="C1975:C1986"/>
+    <mergeCell ref="C1987:C2005"/>
+    <mergeCell ref="C2006:C2018"/>
+    <mergeCell ref="C2019:C2031"/>
+    <mergeCell ref="C2032:C2040"/>
+    <mergeCell ref="C2041:C2060"/>
+    <mergeCell ref="C2061:C2071"/>
+    <mergeCell ref="C2072:C2086"/>
+    <mergeCell ref="C2087:C2094"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -26148,8 +26081,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E166"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:F165"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.7788461538462" style="1" customWidth="1"/>
     <col min="2" max="2" width="47.1057692307692" customWidth="1"/>
@@ -26275,13 +26208,13 @@
     </row>
     <row r="10" ht="17" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>2145</v>
+        <v>2139</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>2146</v>
+        <v>2140</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2147</v>
+        <v>2141</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -26372,7 +26305,7 @@
         <v>1036</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2182</v>
+        <v>2175</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -26457,13 +26390,13 @@
     </row>
     <row r="24" ht="17" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>2066</v>
+        <v>2059</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>2067</v>
+        <v>2060</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2068</v>
+        <v>2061</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -26912,13 +26845,13 @@
     </row>
     <row r="59" ht="17" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>2118</v>
+        <v>2112</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>2119</v>
+        <v>2113</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2120</v>
+        <v>2114</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="3"/>
@@ -27404,7 +27337,7 @@
       <c r="D96" s="9"/>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" ht="17" spans="1:5">
+    <row r="97" ht="17" spans="1:6">
       <c r="A97" s="2" t="s">
         <v>1166</v>
       </c>
@@ -27417,7 +27350,7 @@
       <c r="D97" s="5"/>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" ht="17" spans="1:5">
+    <row r="98" ht="17" spans="1:6">
       <c r="A98" s="2" t="s">
         <v>1200</v>
       </c>
@@ -27429,8 +27362,9 @@
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="3"/>
-    </row>
-    <row r="99" ht="17" spans="1:5">
+      <c r="F98" s="1"/>
+    </row>
+    <row r="99" ht="17" spans="1:6">
       <c r="A99" s="2" t="s">
         <v>1221</v>
       </c>
@@ -27442,8 +27376,9 @@
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3"/>
-    </row>
-    <row r="100" ht="17" spans="1:5">
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" ht="17" spans="1:6">
       <c r="A100" s="2" t="s">
         <v>1221</v>
       </c>
@@ -27455,8 +27390,9 @@
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="3"/>
-    </row>
-    <row r="101" ht="17" spans="1:5">
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" ht="17" spans="1:6">
       <c r="A101" s="2" t="s">
         <v>1277</v>
       </c>
@@ -27468,8 +27404,9 @@
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="3"/>
-    </row>
-    <row r="102" ht="17" spans="1:5">
+      <c r="F101" s="1"/>
+    </row>
+    <row r="102" ht="17" spans="1:6">
       <c r="A102" s="2" t="s">
         <v>1290</v>
       </c>
@@ -27481,8 +27418,9 @@
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="3"/>
-    </row>
-    <row r="103" ht="17" spans="1:5">
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" ht="17" spans="1:6">
       <c r="A103" s="2" t="s">
         <v>1295</v>
       </c>
@@ -27494,8 +27432,9 @@
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="3"/>
-    </row>
-    <row r="104" ht="17" spans="1:5">
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" ht="17" spans="1:6">
       <c r="A104" s="2" t="s">
         <v>1295</v>
       </c>
@@ -27507,8 +27446,9 @@
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3"/>
-    </row>
-    <row r="105" ht="17" spans="1:5">
+      <c r="F104" s="1"/>
+    </row>
+    <row r="105" ht="17" spans="1:6">
       <c r="A105" s="2" t="s">
         <v>1318</v>
       </c>
@@ -27520,8 +27460,9 @@
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="3"/>
-    </row>
-    <row r="106" ht="17" spans="1:5">
+      <c r="F105" s="1"/>
+    </row>
+    <row r="106" ht="17" spans="1:6">
       <c r="A106" s="2" t="s">
         <v>1334</v>
       </c>
@@ -27533,8 +27474,9 @@
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="3"/>
-    </row>
-    <row r="107" ht="17" spans="1:5">
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" ht="17" spans="1:6">
       <c r="A107" s="2" t="s">
         <v>1334</v>
       </c>
@@ -27546,8 +27488,9 @@
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="6"/>
-    </row>
-    <row r="108" ht="17" spans="1:5">
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" ht="17" spans="1:6">
       <c r="A108" s="2" t="s">
         <v>1355</v>
       </c>
@@ -27559,8 +27502,9 @@
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="3"/>
-    </row>
-    <row r="109" ht="17" spans="1:5">
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" ht="17" spans="1:6">
       <c r="A109" s="2" t="s">
         <v>1366</v>
       </c>
@@ -27572,8 +27516,9 @@
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="3"/>
-    </row>
-    <row r="110" ht="17" spans="1:5">
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" ht="17" spans="1:6">
       <c r="A110" s="2" t="s">
         <v>1366</v>
       </c>
@@ -27585,8 +27530,9 @@
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="3"/>
-    </row>
-    <row r="111" ht="17" spans="1:5">
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" ht="17" spans="1:6">
       <c r="A111" s="2" t="s">
         <v>1366</v>
       </c>
@@ -27598,8 +27544,9 @@
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="3"/>
-    </row>
-    <row r="112" ht="17" spans="1:5">
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" ht="17" spans="1:6">
       <c r="A112" s="2" t="s">
         <v>1404</v>
       </c>
@@ -27611,8 +27558,9 @@
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="3"/>
-    </row>
-    <row r="113" ht="17" spans="1:5">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" ht="17" spans="1:6">
       <c r="A113" s="2" t="s">
         <v>1404</v>
       </c>
@@ -27624,8 +27572,9 @@
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="3"/>
-    </row>
-    <row r="114" ht="17" spans="1:5">
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" ht="17" spans="1:6">
       <c r="A114" s="2" t="s">
         <v>1439</v>
       </c>
@@ -27637,8 +27586,9 @@
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="3"/>
-    </row>
-    <row r="115" ht="17" spans="1:5">
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" ht="17" spans="1:6">
       <c r="A115" s="2" t="s">
         <v>1476</v>
       </c>
@@ -27650,8 +27600,9 @@
       </c>
       <c r="D115" s="5"/>
       <c r="E115" s="3"/>
-    </row>
-    <row r="116" ht="17" spans="1:5">
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" ht="17" spans="1:6">
       <c r="A116" s="2" t="s">
         <v>1504</v>
       </c>
@@ -27663,8 +27614,9 @@
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="3"/>
-    </row>
-    <row r="117" ht="17" spans="1:5">
+      <c r="F116" s="1"/>
+    </row>
+    <row r="117" ht="17" spans="1:6">
       <c r="A117" s="2" t="s">
         <v>1504</v>
       </c>
@@ -27676,8 +27628,9 @@
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="3"/>
-    </row>
-    <row r="118" ht="17" spans="1:5">
+      <c r="F117" s="1"/>
+    </row>
+    <row r="118" ht="17" spans="1:6">
       <c r="A118" s="2" t="s">
         <v>1555</v>
       </c>
@@ -27689,8 +27642,9 @@
       </c>
       <c r="D118" s="5"/>
       <c r="E118" s="3"/>
-    </row>
-    <row r="119" ht="17" spans="1:5">
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119" ht="17" spans="1:6">
       <c r="A119" s="2" t="s">
         <v>1562</v>
       </c>
@@ -27700,10 +27654,11 @@
       <c r="C119" s="2" t="s">
         <v>1564</v>
       </c>
-      <c r="D119" s="3"/>
+      <c r="D119" s="5"/>
       <c r="E119" s="3"/>
-    </row>
-    <row r="120" ht="17" spans="1:5">
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" ht="17" spans="1:6">
       <c r="A120" s="2" t="s">
         <v>1594</v>
       </c>
@@ -27715,8 +27670,9 @@
       </c>
       <c r="D120" s="5"/>
       <c r="E120" s="3"/>
-    </row>
-    <row r="121" ht="17" spans="1:5">
+      <c r="F120" s="1"/>
+    </row>
+    <row r="121" ht="17" spans="1:6">
       <c r="A121" s="2" t="s">
         <v>1594</v>
       </c>
@@ -27726,10 +27682,11 @@
       <c r="C121" s="2" t="s">
         <v>1603</v>
       </c>
-      <c r="D121" s="3"/>
+      <c r="D121" s="5"/>
       <c r="E121" s="3"/>
-    </row>
-    <row r="122" ht="17" spans="1:5">
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" ht="17" spans="1:6">
       <c r="A122" s="2" t="s">
         <v>1611</v>
       </c>
@@ -27739,10 +27696,11 @@
       <c r="C122" s="2" t="s">
         <v>1613</v>
       </c>
-      <c r="D122" s="3"/>
+      <c r="D122" s="5"/>
       <c r="E122" s="3"/>
-    </row>
-    <row r="123" ht="17" spans="1:5">
+      <c r="F122" s="1"/>
+    </row>
+    <row r="123" ht="17" spans="1:6">
       <c r="A123" s="2" t="s">
         <v>1611</v>
       </c>
@@ -27752,10 +27710,11 @@
       <c r="C123" s="2" t="s">
         <v>1625</v>
       </c>
-      <c r="D123" s="3"/>
+      <c r="D123" s="5"/>
       <c r="E123" s="3"/>
-    </row>
-    <row r="124" ht="17" spans="1:5">
+      <c r="F123" s="1"/>
+    </row>
+    <row r="124" ht="17" spans="1:6">
       <c r="A124" s="2" t="s">
         <v>1634</v>
       </c>
@@ -27765,10 +27724,11 @@
       <c r="C124" s="2" t="s">
         <v>1636</v>
       </c>
-      <c r="D124" s="3"/>
+      <c r="D124" s="5"/>
       <c r="E124" s="3"/>
-    </row>
-    <row r="125" ht="17" spans="1:5">
+      <c r="F124" s="1"/>
+    </row>
+    <row r="125" ht="17" spans="1:6">
       <c r="A125" s="2" t="s">
         <v>1634</v>
       </c>
@@ -27778,10 +27738,11 @@
       <c r="C125" s="2" t="s">
         <v>1649</v>
       </c>
-      <c r="D125" s="3"/>
+      <c r="D125" s="5"/>
       <c r="E125" s="3"/>
-    </row>
-    <row r="126" ht="17" spans="1:5">
+      <c r="F125" s="1"/>
+    </row>
+    <row r="126" ht="17" spans="1:6">
       <c r="A126" s="2" t="s">
         <v>1656</v>
       </c>
@@ -27793,8 +27754,9 @@
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="3"/>
-    </row>
-    <row r="127" ht="17" spans="1:5">
+      <c r="F126" s="1"/>
+    </row>
+    <row r="127" ht="17" spans="1:6">
       <c r="A127" s="2" t="s">
         <v>1659</v>
       </c>
@@ -27804,515 +27766,519 @@
       <c r="C127" s="2" t="s">
         <v>1661</v>
       </c>
-      <c r="D127" s="3"/>
+      <c r="D127" s="5"/>
       <c r="E127" s="3"/>
-    </row>
-    <row r="128" ht="17" spans="1:5">
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" ht="17" spans="1:6">
       <c r="A128" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>1671</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>1672</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D128" s="3"/>
+      <c r="D128" s="5"/>
       <c r="E128" s="3"/>
-    </row>
-    <row r="129" ht="17" spans="1:5">
+      <c r="F128" s="1"/>
+    </row>
+    <row r="129" ht="17" spans="1:6">
       <c r="A129" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>1693</v>
-      </c>
-      <c r="D129" s="3"/>
+        <v>1691</v>
+      </c>
+      <c r="D129" s="5"/>
       <c r="E129" s="3"/>
-    </row>
-    <row r="130" ht="17" spans="1:5">
+      <c r="F129" s="1"/>
+    </row>
+    <row r="130" ht="17" spans="1:6">
       <c r="A130" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1708</v>
-      </c>
-      <c r="D130" s="3"/>
+        <v>1706</v>
+      </c>
+      <c r="D130" s="5"/>
       <c r="E130" s="3"/>
-    </row>
-    <row r="131" ht="17" spans="1:5">
+      <c r="F130" s="1"/>
+    </row>
+    <row r="131" ht="17" spans="1:6">
       <c r="A131" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>1724</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>1725</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>1726</v>
-      </c>
-      <c r="D131" s="3"/>
+      <c r="D131" s="5"/>
       <c r="E131" s="3"/>
-    </row>
-    <row r="132" ht="17" spans="1:5">
+      <c r="F131" s="1"/>
+    </row>
+    <row r="132" ht="17" spans="1:6">
       <c r="A132" s="2" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1740</v>
-      </c>
-      <c r="D132" s="3"/>
+        <v>1738</v>
+      </c>
+      <c r="D132" s="5"/>
       <c r="E132" s="3"/>
-    </row>
-    <row r="133" ht="17" spans="1:5">
+      <c r="F132" s="1"/>
+    </row>
+    <row r="133" ht="17" spans="1:6">
       <c r="A133" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>1747</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="D133" s="3"/>
+      <c r="D133" s="5"/>
       <c r="E133" s="3"/>
-    </row>
-    <row r="134" ht="17" spans="1:5">
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" ht="17" spans="1:6">
       <c r="A134" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D134" s="3"/>
+        <v>1763</v>
+      </c>
+      <c r="D134" s="5"/>
       <c r="E134" s="3"/>
-    </row>
-    <row r="135" ht="17" spans="1:5">
+      <c r="F134" s="1"/>
+    </row>
+    <row r="135" ht="17" spans="1:6">
       <c r="A135" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="D135" s="3"/>
+        <v>1777</v>
+      </c>
+      <c r="D135" s="5"/>
       <c r="E135" s="3"/>
-    </row>
-    <row r="136" ht="17" spans="1:5">
+      <c r="F135" s="1"/>
+    </row>
+    <row r="136" ht="17" spans="1:6">
       <c r="A136" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1795</v>
-      </c>
-      <c r="D136" s="3"/>
+        <v>1793</v>
+      </c>
+      <c r="D136" s="5"/>
       <c r="E136" s="3"/>
-    </row>
-    <row r="137" ht="17" spans="1:5">
+      <c r="F136" s="1"/>
+    </row>
+    <row r="137" ht="17" spans="1:6">
       <c r="A137" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1812</v>
-      </c>
-      <c r="D137" s="3"/>
+        <v>1810</v>
+      </c>
+      <c r="D137" s="5"/>
       <c r="E137" s="3"/>
-    </row>
-    <row r="138" ht="17" spans="1:5">
+      <c r="F137" s="1"/>
+    </row>
+    <row r="138" ht="17" spans="1:6">
       <c r="A138" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="D138" s="3"/>
+        <v>1822</v>
+      </c>
+      <c r="D138" s="5"/>
       <c r="E138" s="3"/>
-    </row>
-    <row r="139" ht="17" spans="1:5">
+      <c r="F138" s="1"/>
+    </row>
+    <row r="139" ht="17" spans="1:6">
       <c r="A139" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D139" s="3"/>
+        <v>1837</v>
+      </c>
+      <c r="D139" s="5"/>
       <c r="E139" s="3"/>
-    </row>
-    <row r="140" ht="17" spans="1:5">
+      <c r="F139" s="1"/>
+    </row>
+    <row r="140" ht="17" spans="1:6">
       <c r="A140" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1847</v>
-      </c>
-      <c r="D140" s="3"/>
+        <v>1845</v>
+      </c>
+      <c r="D140" s="5"/>
       <c r="E140" s="3"/>
-    </row>
-    <row r="141" ht="17" spans="1:5">
+      <c r="F140" s="1"/>
+    </row>
+    <row r="141" ht="17" spans="1:6">
       <c r="A141" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="D141" s="3"/>
+        <v>1857</v>
+      </c>
+      <c r="D141" s="5"/>
       <c r="E141" s="3"/>
-    </row>
-    <row r="142" ht="17" spans="1:5">
+      <c r="F141" s="1"/>
+    </row>
+    <row r="142" ht="17" spans="1:6">
       <c r="A142" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="D142" s="3"/>
+        <v>1866</v>
+      </c>
+      <c r="D142" s="5"/>
       <c r="E142" s="3"/>
-    </row>
-    <row r="143" ht="17" spans="1:5">
+      <c r="F142" s="1"/>
+    </row>
+    <row r="143" ht="17" spans="1:6">
       <c r="A143" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1881</v>
-      </c>
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
-    </row>
-    <row r="144" ht="17" spans="1:5">
+        <v>1879</v>
+      </c>
+      <c r="D143" s="5"/>
+      <c r="E143" s="6"/>
+      <c r="F143" s="1"/>
+    </row>
+    <row r="144" ht="17" spans="1:6">
       <c r="A144" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D144" s="3"/>
+        <v>1892</v>
+      </c>
+      <c r="D144" s="5"/>
       <c r="E144" s="3"/>
     </row>
     <row r="145" ht="17" spans="1:5">
       <c r="A145" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1906</v>
-      </c>
-      <c r="D145" s="3"/>
+        <v>1904</v>
+      </c>
+      <c r="D145" s="5"/>
       <c r="E145" s="3"/>
     </row>
     <row r="146" ht="17" spans="1:5">
       <c r="A146" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>1922</v>
+        <v>1916</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D146" s="3"/>
+        <v>1917</v>
+      </c>
+      <c r="D146" s="5"/>
       <c r="E146" s="3"/>
     </row>
     <row r="147" ht="17" spans="1:5">
       <c r="A147" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>1928</v>
+        <v>1922</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D147" s="3"/>
+        <v>1923</v>
+      </c>
+      <c r="D147" s="5"/>
       <c r="E147" s="3"/>
     </row>
     <row r="148" ht="17" spans="1:5">
       <c r="A148" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>1932</v>
+        <v>1926</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D148" s="3"/>
+        <v>1927</v>
+      </c>
+      <c r="D148" s="5"/>
       <c r="E148" s="3"/>
     </row>
     <row r="149" ht="17" spans="1:5">
       <c r="A149" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D149" s="3"/>
+        <v>1932</v>
+      </c>
+      <c r="D149" s="5"/>
       <c r="E149" s="3"/>
     </row>
     <row r="150" ht="17" spans="1:5">
       <c r="A150" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1942</v>
-      </c>
-      <c r="D150" s="3"/>
+        <v>1936</v>
+      </c>
+      <c r="D150" s="5"/>
       <c r="E150" s="3"/>
     </row>
     <row r="151" ht="17" spans="1:5">
       <c r="A151" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>1950</v>
+        <v>1944</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D151" s="3"/>
+        <v>1945</v>
+      </c>
+      <c r="D151" s="5"/>
       <c r="E151" s="3"/>
     </row>
     <row r="152" ht="17" spans="1:5">
       <c r="A152" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>1958</v>
+        <v>1952</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D152" s="3"/>
+        <v>1953</v>
+      </c>
+      <c r="D152" s="5"/>
       <c r="E152" s="3"/>
     </row>
     <row r="153" ht="17" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1969</v>
+        <v>1963</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1970</v>
-      </c>
-      <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
+        <v>1964</v>
+      </c>
+      <c r="D153" s="5"/>
+      <c r="E153" s="6"/>
     </row>
     <row r="154" ht="17" spans="1:5">
       <c r="A154" s="2" t="s">
-        <v>1968</v>
+        <v>1962</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1982</v>
+        <v>1976</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1983</v>
-      </c>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
+        <v>1977</v>
+      </c>
+      <c r="D154" s="5"/>
+      <c r="E154" s="6"/>
     </row>
     <row r="155" ht="17" spans="1:5">
       <c r="A155" s="2" t="s">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2000</v>
+        <v>1993</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>2001</v>
-      </c>
-      <c r="D155" s="3"/>
+        <v>1994</v>
+      </c>
+      <c r="D155" s="5"/>
       <c r="E155" s="3"/>
     </row>
     <row r="156" ht="17" spans="1:5">
       <c r="A156" s="2" t="s">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>2020</v>
-      </c>
-      <c r="D156" s="3"/>
+        <v>2013</v>
+      </c>
+      <c r="D156" s="5"/>
       <c r="E156" s="3"/>
     </row>
     <row r="157" ht="17" spans="1:5">
       <c r="A157" s="2" t="s">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2030</v>
+        <v>2023</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>2031</v>
-      </c>
-      <c r="D157" s="3"/>
+        <v>2024</v>
+      </c>
+      <c r="D157" s="5"/>
       <c r="E157" s="3"/>
     </row>
     <row r="158" ht="17" spans="1:5">
       <c r="A158" s="2" t="s">
-        <v>1999</v>
+        <v>1992</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2042</v>
+        <v>2035</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>2043</v>
-      </c>
-      <c r="D158" s="3"/>
+        <v>2036</v>
+      </c>
+      <c r="D158" s="5"/>
       <c r="E158" s="3"/>
     </row>
     <row r="159" ht="17" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2056</v>
+        <v>2049</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>2057</v>
-      </c>
-      <c r="D159" s="3"/>
+        <v>2050</v>
+      </c>
+      <c r="D159" s="5"/>
       <c r="E159" s="3"/>
     </row>
     <row r="160" ht="17" spans="1:5">
       <c r="A160" s="2" t="s">
-        <v>2055</v>
+        <v>2073</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2183</v>
+        <v>2074</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>2184</v>
-      </c>
-      <c r="D160" s="3"/>
+        <v>2075</v>
+      </c>
+      <c r="D160" s="5"/>
       <c r="E160" s="3"/>
     </row>
     <row r="161" ht="17" spans="1:5">
       <c r="A161" s="2" t="s">
-        <v>2080</v>
+        <v>2073</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2081</v>
+        <v>2092</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>2082</v>
-      </c>
-      <c r="D161" s="3"/>
+        <v>2093</v>
+      </c>
+      <c r="D161" s="5"/>
       <c r="E161" s="3"/>
     </row>
     <row r="162" ht="17" spans="1:5">
       <c r="A162" s="2" t="s">
-        <v>2080</v>
+        <v>2105</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2099</v>
+        <v>2106</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>2100</v>
-      </c>
-      <c r="D162" s="3"/>
+        <v>2107</v>
+      </c>
+      <c r="D162" s="5"/>
       <c r="E162" s="3"/>
     </row>
     <row r="163" ht="17" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>2112</v>
+        <v>2117</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2113</v>
+        <v>2118</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>2114</v>
-      </c>
-      <c r="D163" s="3"/>
+        <v>2119</v>
+      </c>
+      <c r="D163" s="5"/>
       <c r="E163" s="3"/>
     </row>
     <row r="164" ht="17" spans="1:5">
       <c r="A164" s="2" t="s">
-        <v>2123</v>
+        <v>2151</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2124</v>
+        <v>2152</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>2125</v>
-      </c>
-      <c r="D164" s="3"/>
+        <v>2153</v>
+      </c>
+      <c r="D164" s="5"/>
       <c r="E164" s="3"/>
     </row>
     <row r="165" ht="17" spans="1:5">
       <c r="A165" s="2" t="s">
-        <v>2157</v>
+        <v>2151</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2158</v>
+        <v>2168</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>2159</v>
-      </c>
-      <c r="D165" s="3"/>
+        <v>2169</v>
+      </c>
+      <c r="D165" s="5"/>
       <c r="E165" s="3"/>
-    </row>
-    <row r="166" ht="17" spans="1:5">
-      <c r="A166" s="2" t="s">
-        <v>2157</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>2174</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>2175</v>
-      </c>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16300"/>
+    <workbookView windowHeight="16300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="2176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="2177">
   <si>
     <t>应用名称</t>
   </si>
@@ -5470,160 +5470,163 @@
     <t>微信发送通话</t>
   </si>
   <si>
+    <t>2、点击“测试”，进入好友聊天页面</t>
+  </si>
+  <si>
+    <t>3、点击输入框，进入消息编辑界面</t>
+  </si>
+  <si>
+    <t>4、输入哈哈哈，点击发送</t>
+  </si>
+  <si>
+    <t>5、点击语音按钮，发送语音给好友</t>
+  </si>
+  <si>
+    <t>6、点击表情包按钮，进入表情框界面</t>
+  </si>
+  <si>
+    <t>7、点击选择前三个表情，点击发送</t>
+  </si>
+  <si>
+    <t>8、点击加号按钮，进入更多功能页面</t>
+  </si>
+  <si>
+    <t>9、点击视频通话，进入选择通话界面</t>
+  </si>
+  <si>
+    <t>10、点击视频通话，进入视频通话界面</t>
+  </si>
+  <si>
+    <t>11、点击挂断按钮，好友聊天页面</t>
+  </si>
+  <si>
+    <t>12、点击加号按钮，进入更多功能页面</t>
+  </si>
+  <si>
+    <t>13、点击视频通话，进入选择通话界面</t>
+  </si>
+  <si>
+    <t>14、点击语音通话，进入语音通话界面</t>
+  </si>
+  <si>
+    <t>15、点击挂断按钮，好友聊天页面</t>
+  </si>
+  <si>
+    <t>16、返回微信主界面</t>
+  </si>
+  <si>
+    <t>PerformanceDynamic_weixin_0050</t>
+  </si>
+  <si>
+    <t>微信科技类公众号浏览</t>
+  </si>
+  <si>
+    <t>3、点击公众号</t>
+  </si>
+  <si>
+    <t>4、点击华为手机（或者华为）的公众号名片，点击右上角人头像</t>
+  </si>
+  <si>
+    <t>5、浏览公众号</t>
+  </si>
+  <si>
+    <t>6、点击第一个文章</t>
+  </si>
+  <si>
+    <t>7、浏览搜索结果</t>
+  </si>
+  <si>
+    <t>8、返回测试公众号界面</t>
+  </si>
+  <si>
+    <t>9、点击HarmonyOS的公众号名片</t>
+  </si>
+  <si>
+    <t>10、点击屏幕底部HMOS后点击官网直达</t>
+  </si>
+  <si>
+    <t>11、上滑2次，下滑2次浏览文章</t>
+  </si>
+  <si>
+    <t>12、返回测试公众号界面</t>
+  </si>
+  <si>
+    <t>PerformanceDynamic_weixin_0060</t>
+  </si>
+  <si>
+    <t>微信发布朋友圈</t>
+  </si>
+  <si>
+    <t>2、进入朋友圈</t>
+  </si>
+  <si>
+    <t>3、点击右上角的相机图标</t>
+  </si>
+  <si>
+    <t>4、点击拍摄</t>
+  </si>
+  <si>
+    <t>5、返回朋友圈</t>
+  </si>
+  <si>
+    <t>6、点击右上角的相机图标</t>
+  </si>
+  <si>
+    <t>7、从相册选择，选择图片3张</t>
+  </si>
+  <si>
+    <t>8、点击预览</t>
+  </si>
+  <si>
+    <t>9、左滑2次浏览图片</t>
+  </si>
+  <si>
+    <t>10、点击右上角完成</t>
+  </si>
+  <si>
+    <t>11、点击所在位置</t>
+  </si>
+  <si>
+    <t>12、选择具体位置，点击完成</t>
+  </si>
+  <si>
+    <t>13、左滑返回一次</t>
+  </si>
+  <si>
+    <t>14、点击不保留</t>
+  </si>
+  <si>
+    <t>PerformanceDynamic_weixin_0070</t>
+  </si>
+  <si>
+    <t>瑞幸微信小程序浏览</t>
+  </si>
+  <si>
+    <t>2、下滑调出最近小程序页面</t>
+  </si>
+  <si>
+    <t>3、点击瑞幸小程序，切换到瑞幸咖啡页面</t>
+  </si>
+  <si>
+    <t>4、点击菜单，切换到菜单页</t>
+  </si>
+  <si>
+    <t>5、点击人气top</t>
+  </si>
+  <si>
+    <t>7、点击加入购物车</t>
+  </si>
+  <si>
+    <t>8、返回微信主界面</t>
+  </si>
+  <si>
+    <t>PerformanceDynamic_weixin_0080</t>
+  </si>
+  <si>
+    <t>微信拍摄和录像</t>
+  </si>
+  <si>
     <t>2、点击测试账号，进入好友聊天页面</t>
-  </si>
-  <si>
-    <t>3、点击输入框，进入消息编辑界面</t>
-  </si>
-  <si>
-    <t>4、输入哈哈哈，点击发送</t>
-  </si>
-  <si>
-    <t>5、点击语音按钮，发送语音给好友</t>
-  </si>
-  <si>
-    <t>6、点击表情包按钮，进入表情框界面</t>
-  </si>
-  <si>
-    <t>7、点击选择前三个表情，点击发送</t>
-  </si>
-  <si>
-    <t>8、点击加号按钮，进入更多功能页面</t>
-  </si>
-  <si>
-    <t>9、点击视频通话，进入选择通话界面</t>
-  </si>
-  <si>
-    <t>10、点击视频通话，进入视频通话界面</t>
-  </si>
-  <si>
-    <t>11、点击挂断按钮，好友聊天页面</t>
-  </si>
-  <si>
-    <t>12、点击加号按钮，进入更多功能页面</t>
-  </si>
-  <si>
-    <t>13、点击视频通话，进入选择通话界面</t>
-  </si>
-  <si>
-    <t>14、点击语音通话，进入语音通话界面</t>
-  </si>
-  <si>
-    <t>15、点击挂断按钮，好友聊天页面</t>
-  </si>
-  <si>
-    <t>16、返回微信主界面</t>
-  </si>
-  <si>
-    <t>PerformanceDynamic_weixin_0050</t>
-  </si>
-  <si>
-    <t>微信科技类公众号浏览</t>
-  </si>
-  <si>
-    <t>3、点击公众号</t>
-  </si>
-  <si>
-    <t>4、点击华为手机（或者华为）的公众号名片，点击右上角人头像</t>
-  </si>
-  <si>
-    <t>5、浏览公众号</t>
-  </si>
-  <si>
-    <t>6、点击第一个文章</t>
-  </si>
-  <si>
-    <t>7、浏览搜索结果</t>
-  </si>
-  <si>
-    <t>8、返回测试公众号界面</t>
-  </si>
-  <si>
-    <t>9、点击HarmonyOS的公众号名片</t>
-  </si>
-  <si>
-    <t>10、点击屏幕底部HMOS后点击官网直达</t>
-  </si>
-  <si>
-    <t>11、上滑2次，下滑2次浏览文章</t>
-  </si>
-  <si>
-    <t>12、返回测试公众号界面</t>
-  </si>
-  <si>
-    <t>PerformanceDynamic_weixin_0060</t>
-  </si>
-  <si>
-    <t>微信发布朋友圈</t>
-  </si>
-  <si>
-    <t>2、进入朋友圈</t>
-  </si>
-  <si>
-    <t>3、点击右上角的相机图标</t>
-  </si>
-  <si>
-    <t>4、点击拍摄</t>
-  </si>
-  <si>
-    <t>5、返回朋友圈</t>
-  </si>
-  <si>
-    <t>6、点击右上角的相机图标</t>
-  </si>
-  <si>
-    <t>7、从相册选择，选择图片3张</t>
-  </si>
-  <si>
-    <t>8、点击预览</t>
-  </si>
-  <si>
-    <t>9、左滑2次浏览图片</t>
-  </si>
-  <si>
-    <t>10、点击右上角完成</t>
-  </si>
-  <si>
-    <t>11、点击所在位置</t>
-  </si>
-  <si>
-    <t>12、选择具体位置，点击完成</t>
-  </si>
-  <si>
-    <t>13、左滑返回一次</t>
-  </si>
-  <si>
-    <t>14、点击不保留</t>
-  </si>
-  <si>
-    <t>PerformanceDynamic_weixin_0070</t>
-  </si>
-  <si>
-    <t>瑞幸微信小程序浏览</t>
-  </si>
-  <si>
-    <t>2、下滑调出最近小程序页面</t>
-  </si>
-  <si>
-    <t>3、点击瑞幸小程序，切换到瑞幸咖啡页面</t>
-  </si>
-  <si>
-    <t>4、点击菜单，切换到菜单页</t>
-  </si>
-  <si>
-    <t>5、点击人气top</t>
-  </si>
-  <si>
-    <t>7、点击加入购物车</t>
-  </si>
-  <si>
-    <t>8、返回微信主界面</t>
-  </si>
-  <si>
-    <t>PerformanceDynamic_weixin_0080</t>
-  </si>
-  <si>
-    <t>微信拍摄和录像</t>
   </si>
   <si>
     <t>3、点击加号按钮，进入更多功能页面</t>
@@ -22535,7 +22538,7 @@
       <c r="B1735" s="10"/>
       <c r="C1735" s="10"/>
       <c r="D1735" s="10" t="s">
-        <v>1794</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1736" ht="17" customHeight="1" spans="1:4">
@@ -22543,7 +22546,7 @@
       <c r="B1736" s="10"/>
       <c r="C1736" s="10"/>
       <c r="D1736" s="10" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1737" ht="17" customHeight="1" spans="1:4">
@@ -22551,7 +22554,7 @@
       <c r="B1737" s="10"/>
       <c r="C1737" s="10"/>
       <c r="D1737" s="10" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1738" ht="17" customHeight="1" spans="1:4">
@@ -22559,7 +22562,7 @@
       <c r="B1738" s="10"/>
       <c r="C1738" s="10"/>
       <c r="D1738" s="10" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1739" ht="17" customHeight="1" spans="1:4">
@@ -22567,7 +22570,7 @@
       <c r="B1739" s="10"/>
       <c r="C1739" s="10"/>
       <c r="D1739" s="10" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1740" ht="17" customHeight="1" spans="1:4">
@@ -22575,7 +22578,7 @@
       <c r="B1740" s="10"/>
       <c r="C1740" s="10"/>
       <c r="D1740" s="10" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1741" ht="17" customHeight="1" spans="1:4">
@@ -22583,7 +22586,7 @@
       <c r="B1741" s="10"/>
       <c r="C1741" s="10"/>
       <c r="D1741" s="10" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1742" ht="17" customHeight="1" spans="1:4">
@@ -22591,7 +22594,7 @@
       <c r="B1742" s="10"/>
       <c r="C1742" s="10"/>
       <c r="D1742" s="10" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1743" ht="17" customHeight="1" spans="1:4">
@@ -22599,7 +22602,7 @@
       <c r="B1743" s="10"/>
       <c r="C1743" s="10"/>
       <c r="D1743" s="10" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1744" ht="17" customHeight="1" spans="1:4">
@@ -22607,7 +22610,7 @@
       <c r="B1744" s="10"/>
       <c r="C1744" s="10"/>
       <c r="D1744" s="10" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1745" ht="17" customHeight="1" spans="1:4">
@@ -22615,7 +22618,7 @@
       <c r="B1745" s="10"/>
       <c r="C1745" s="10"/>
       <c r="D1745" s="10" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1746" ht="17" customHeight="1" spans="1:4">
@@ -22639,10 +22642,10 @@
         <v>1745</v>
       </c>
       <c r="B1748" s="10" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C1748" s="10" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="D1748" s="10" t="s">
         <v>1748</v>
@@ -22653,7 +22656,7 @@
       <c r="B1749" s="10"/>
       <c r="C1749" s="10"/>
       <c r="D1749" s="10" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1750" ht="17" customHeight="1" spans="1:4">
@@ -22677,7 +22680,7 @@
       <c r="B1752" s="10"/>
       <c r="C1752" s="10"/>
       <c r="D1752" s="10" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1753" ht="17" customHeight="1" spans="1:4">
@@ -22685,7 +22688,7 @@
       <c r="B1753" s="10"/>
       <c r="C1753" s="10"/>
       <c r="D1753" s="10" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1754" ht="17" customHeight="1" spans="1:4">
@@ -22693,7 +22696,7 @@
       <c r="B1754" s="10"/>
       <c r="C1754" s="10"/>
       <c r="D1754" s="10" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1755" ht="17" customHeight="1" spans="1:4">
@@ -22701,7 +22704,7 @@
       <c r="B1755" s="10"/>
       <c r="C1755" s="10"/>
       <c r="D1755" s="10" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1756" ht="17" customHeight="1" spans="1:4">
@@ -22709,7 +22712,7 @@
       <c r="B1756" s="10"/>
       <c r="C1756" s="10"/>
       <c r="D1756" s="10" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1757" ht="17" customHeight="1" spans="1:4">
@@ -22717,7 +22720,7 @@
       <c r="B1757" s="10"/>
       <c r="C1757" s="10"/>
       <c r="D1757" s="10" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1758" ht="17" customHeight="1" spans="1:4">
@@ -22741,10 +22744,10 @@
         <v>1745</v>
       </c>
       <c r="B1760" s="10" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C1760" s="10" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="D1760" s="10" t="s">
         <v>1748</v>
@@ -22755,7 +22758,7 @@
       <c r="B1761" s="10"/>
       <c r="C1761" s="10"/>
       <c r="D1761" s="10" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1762" ht="17" customHeight="1" spans="1:4">
@@ -22763,7 +22766,7 @@
       <c r="B1762" s="10"/>
       <c r="C1762" s="10"/>
       <c r="D1762" s="10" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1763" ht="17" customHeight="1" spans="1:4">
@@ -22771,7 +22774,7 @@
       <c r="B1763" s="10"/>
       <c r="C1763" s="10"/>
       <c r="D1763" s="10" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1764" ht="17" customHeight="1" spans="1:4">
@@ -22779,7 +22782,7 @@
       <c r="B1764" s="10"/>
       <c r="C1764" s="10"/>
       <c r="D1764" s="10" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1765" ht="17" customHeight="1" spans="1:4">
@@ -22787,7 +22790,7 @@
       <c r="B1765" s="10"/>
       <c r="C1765" s="10"/>
       <c r="D1765" s="10" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1766" ht="17" customHeight="1" spans="1:4">
@@ -22795,7 +22798,7 @@
       <c r="B1766" s="10"/>
       <c r="C1766" s="10"/>
       <c r="D1766" s="10" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1767" ht="17" customHeight="1" spans="1:4">
@@ -22803,7 +22806,7 @@
       <c r="B1767" s="10"/>
       <c r="C1767" s="10"/>
       <c r="D1767" s="10" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1768" ht="17" customHeight="1" spans="1:4">
@@ -22811,7 +22814,7 @@
       <c r="B1768" s="10"/>
       <c r="C1768" s="10"/>
       <c r="D1768" s="10" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1769" ht="17" customHeight="1" spans="1:4">
@@ -22819,7 +22822,7 @@
       <c r="B1769" s="10"/>
       <c r="C1769" s="10"/>
       <c r="D1769" s="10" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1770" ht="17" customHeight="1" spans="1:4">
@@ -22827,7 +22830,7 @@
       <c r="B1770" s="10"/>
       <c r="C1770" s="10"/>
       <c r="D1770" s="10" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1771" ht="17" customHeight="1" spans="1:4">
@@ -22835,7 +22838,7 @@
       <c r="B1771" s="10"/>
       <c r="C1771" s="10"/>
       <c r="D1771" s="10" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1772" ht="17" customHeight="1" spans="1:4">
@@ -22859,10 +22862,10 @@
         <v>1745</v>
       </c>
       <c r="B1774" s="10" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="C1774" s="10" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="D1774" s="10" t="s">
         <v>1748</v>
@@ -22881,7 +22884,7 @@
       <c r="B1776" s="10"/>
       <c r="C1776" s="10"/>
       <c r="D1776" s="10" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1777" ht="17" customHeight="1" spans="1:4">
@@ -22889,7 +22892,7 @@
       <c r="B1777" s="10"/>
       <c r="C1777" s="10"/>
       <c r="D1777" s="10" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1778" ht="17" customHeight="1" spans="1:4">
@@ -22897,7 +22900,7 @@
       <c r="B1778" s="10"/>
       <c r="C1778" s="10"/>
       <c r="D1778" s="10" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1779" ht="17" customHeight="1" spans="1:4">
@@ -22905,7 +22908,7 @@
       <c r="B1779" s="10"/>
       <c r="C1779" s="10"/>
       <c r="D1779" s="10" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1780" ht="17" customHeight="1" spans="1:4">
@@ -22913,7 +22916,7 @@
       <c r="B1780" s="10"/>
       <c r="C1780" s="10"/>
       <c r="D1780" s="10" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="1781" ht="17" customHeight="1" spans="1:4">
@@ -22921,7 +22924,7 @@
       <c r="B1781" s="10"/>
       <c r="C1781" s="10"/>
       <c r="D1781" s="10" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1782" ht="17" customHeight="1" spans="1:4">
@@ -22929,7 +22932,7 @@
       <c r="B1782" s="10"/>
       <c r="C1782" s="10"/>
       <c r="D1782" s="10" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1783" ht="17" customHeight="1" spans="1:4">
@@ -22937,7 +22940,7 @@
       <c r="B1783" s="10"/>
       <c r="C1783" s="10"/>
       <c r="D1783" s="10" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="1784" ht="17" customHeight="1" spans="1:4">
@@ -22945,7 +22948,7 @@
       <c r="B1784" s="10"/>
       <c r="C1784" s="10"/>
       <c r="D1784" s="10" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1785" ht="17" customHeight="1" spans="1:4">
@@ -22953,7 +22956,7 @@
       <c r="B1785" s="10"/>
       <c r="C1785" s="10"/>
       <c r="D1785" s="10" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="1786" ht="17" customHeight="1" spans="1:4">
@@ -22961,7 +22964,7 @@
       <c r="B1786" s="10"/>
       <c r="C1786" s="10"/>
       <c r="D1786" s="10" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1787" ht="17" customHeight="1" spans="1:4">
@@ -22985,10 +22988,10 @@
         <v>1745</v>
       </c>
       <c r="B1789" s="10" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C1789" s="10" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="D1789" s="10" t="s">
         <v>1748</v>
@@ -22999,7 +23002,7 @@
       <c r="B1790" s="10"/>
       <c r="C1790" s="10"/>
       <c r="D1790" s="10" t="s">
-        <v>1794</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1791" ht="17" customHeight="1" spans="1:4">
@@ -23007,7 +23010,7 @@
       <c r="B1791" s="10"/>
       <c r="C1791" s="10"/>
       <c r="D1791" s="10" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1792" ht="17" customHeight="1" spans="1:4">
@@ -23015,7 +23018,7 @@
       <c r="B1792" s="10"/>
       <c r="C1792" s="10"/>
       <c r="D1792" s="10" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1793" ht="17" customHeight="1" spans="1:4">
@@ -23023,7 +23026,7 @@
       <c r="B1793" s="10"/>
       <c r="C1793" s="10"/>
       <c r="D1793" s="10" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1794" ht="17" customHeight="1" spans="1:4">
@@ -23031,7 +23034,7 @@
       <c r="B1794" s="10"/>
       <c r="C1794" s="10"/>
       <c r="D1794" s="10" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1795" ht="17" customHeight="1" spans="1:4">
@@ -23039,7 +23042,7 @@
       <c r="B1795" s="10"/>
       <c r="C1795" s="10"/>
       <c r="D1795" s="10" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1796" ht="17" customHeight="1" spans="1:4">
@@ -23047,7 +23050,7 @@
       <c r="B1796" s="10"/>
       <c r="C1796" s="10"/>
       <c r="D1796" s="10" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1797" ht="17" customHeight="1" spans="1:4">
@@ -23055,7 +23058,7 @@
       <c r="B1797" s="10"/>
       <c r="C1797" s="10"/>
       <c r="D1797" s="10" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1798" ht="17" customHeight="1" spans="1:4">
@@ -23063,7 +23066,7 @@
       <c r="B1798" s="10"/>
       <c r="C1798" s="10"/>
       <c r="D1798" s="10" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1799" ht="17" customHeight="1" spans="1:4">
@@ -23071,7 +23074,7 @@
       <c r="B1799" s="10"/>
       <c r="C1799" s="10"/>
       <c r="D1799" s="10" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1800" ht="17" customHeight="1" spans="1:4">
@@ -23079,7 +23082,7 @@
       <c r="B1800" s="10"/>
       <c r="C1800" s="10"/>
       <c r="D1800" s="10" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1801" ht="17" customHeight="1" spans="1:4">
@@ -23095,10 +23098,10 @@
         <v>1745</v>
       </c>
       <c r="B1802" s="10" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C1802" s="10" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="D1802" s="10" t="s">
         <v>1748</v>
@@ -23125,7 +23128,7 @@
       <c r="B1805" s="10"/>
       <c r="C1805" s="10"/>
       <c r="D1805" s="11" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1806" ht="17" customHeight="1" spans="1:4">
@@ -23133,7 +23136,7 @@
       <c r="B1806" s="10"/>
       <c r="C1806" s="10"/>
       <c r="D1806" s="10" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1807" ht="17" customHeight="1" spans="1:4">
@@ -23141,7 +23144,7 @@
       <c r="B1807" s="10"/>
       <c r="C1807" s="10"/>
       <c r="D1807" s="10" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1808" ht="17" customHeight="1" spans="1:4">
@@ -23149,7 +23152,7 @@
       <c r="B1808" s="10"/>
       <c r="C1808" s="10"/>
       <c r="D1808" s="10" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1809" ht="17" customHeight="1" spans="1:4">
@@ -23157,7 +23160,7 @@
       <c r="B1809" s="10"/>
       <c r="C1809" s="10"/>
       <c r="D1809" s="10" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1810" ht="17" customHeight="1" spans="1:4">
@@ -23165,7 +23168,7 @@
       <c r="B1810" s="10"/>
       <c r="C1810" s="10"/>
       <c r="D1810" s="10" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1811" ht="17" customHeight="1" spans="1:4">
@@ -23173,7 +23176,7 @@
       <c r="B1811" s="10"/>
       <c r="C1811" s="10"/>
       <c r="D1811" s="10" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1812" ht="17" customHeight="1" spans="1:4">
@@ -23181,7 +23184,7 @@
       <c r="B1812" s="10"/>
       <c r="C1812" s="10"/>
       <c r="D1812" s="10" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1813" ht="17" customHeight="1" spans="1:4">
@@ -23189,7 +23192,7 @@
       <c r="B1813" s="10"/>
       <c r="C1813" s="10"/>
       <c r="D1813" s="10" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1814" ht="17" customHeight="1" spans="1:4">
@@ -23197,7 +23200,7 @@
       <c r="B1814" s="10"/>
       <c r="C1814" s="10"/>
       <c r="D1814" s="10" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1815" ht="17" customHeight="1" spans="1:4">
@@ -23205,7 +23208,7 @@
       <c r="B1815" s="10"/>
       <c r="C1815" s="10"/>
       <c r="D1815" s="10" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1816" ht="17" customHeight="1" spans="1:4">
@@ -23229,10 +23232,10 @@
         <v>1745</v>
       </c>
       <c r="B1818" s="10" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="C1818" s="10" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D1818" s="10" t="s">
         <v>1748</v>
@@ -23251,7 +23254,7 @@
       <c r="B1820" s="10"/>
       <c r="C1820" s="10"/>
       <c r="D1820" s="11" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1821" ht="17" customHeight="1" spans="1:4">
@@ -23259,7 +23262,7 @@
       <c r="B1821" s="10"/>
       <c r="C1821" s="10"/>
       <c r="D1821" s="10" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1822" ht="17" customHeight="1" spans="1:4">
@@ -23267,7 +23270,7 @@
       <c r="B1822" s="10"/>
       <c r="C1822" s="10"/>
       <c r="D1822" s="10" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1823" ht="17" customHeight="1" spans="1:4">
@@ -23275,7 +23278,7 @@
       <c r="B1823" s="10"/>
       <c r="C1823" s="10"/>
       <c r="D1823" s="10" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1824" ht="17" customHeight="1" spans="1:4">
@@ -23291,10 +23294,10 @@
         <v>1745</v>
       </c>
       <c r="B1825" s="10" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="C1825" s="10" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="D1825" s="10" t="s">
         <v>1748</v>
@@ -23313,7 +23316,7 @@
       <c r="B1827" s="10"/>
       <c r="C1827" s="10"/>
       <c r="D1827" s="11" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1828" ht="17" customHeight="1" spans="1:4">
@@ -23321,7 +23324,7 @@
       <c r="B1828" s="10"/>
       <c r="C1828" s="10"/>
       <c r="D1828" s="10" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1829" ht="17" customHeight="1" spans="1:4">
@@ -23345,10 +23348,10 @@
         <v>1745</v>
       </c>
       <c r="B1831" s="10" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C1831" s="10" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="D1831" s="10" t="s">
         <v>1748</v>
@@ -23367,7 +23370,7 @@
       <c r="B1833" s="10"/>
       <c r="C1833" s="10"/>
       <c r="D1833" s="11" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1834" ht="17" customHeight="1" spans="1:4">
@@ -23375,7 +23378,7 @@
       <c r="B1834" s="10"/>
       <c r="C1834" s="10"/>
       <c r="D1834" s="10" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1835" ht="17" customHeight="1" spans="1:4">
@@ -23383,7 +23386,7 @@
       <c r="B1835" s="10"/>
       <c r="C1835" s="10"/>
       <c r="D1835" s="10" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1836" ht="17" customHeight="1" spans="1:4">
@@ -23391,7 +23394,7 @@
       <c r="B1836" s="10"/>
       <c r="C1836" s="10"/>
       <c r="D1836" s="10" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1837" ht="17" customHeight="1" spans="1:4">
@@ -23407,10 +23410,10 @@
         <v>1745</v>
       </c>
       <c r="B1838" s="10" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C1838" s="10" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="D1838" s="10" t="s">
         <v>1748</v>
@@ -23429,7 +23432,7 @@
       <c r="B1840" s="10"/>
       <c r="C1840" s="10"/>
       <c r="D1840" s="11" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1841" ht="17" customHeight="1" spans="1:4">
@@ -23437,7 +23440,7 @@
       <c r="B1841" s="10"/>
       <c r="C1841" s="10"/>
       <c r="D1841" s="10" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1842" ht="17" customHeight="1" spans="1:4">
@@ -23461,10 +23464,10 @@
         <v>1745</v>
       </c>
       <c r="B1844" s="10" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C1844" s="10" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="D1844" s="10" t="s">
         <v>1748</v>
@@ -23483,7 +23486,7 @@
       <c r="B1846" s="10"/>
       <c r="C1846" s="10"/>
       <c r="D1846" s="11" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1847" ht="17" customHeight="1" spans="1:4">
@@ -23491,7 +23494,7 @@
       <c r="B1847" s="10"/>
       <c r="C1847" s="10"/>
       <c r="D1847" s="10" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1848" ht="17" customHeight="1" spans="1:4">
@@ -23499,7 +23502,7 @@
       <c r="B1848" s="10"/>
       <c r="C1848" s="10"/>
       <c r="D1848" s="10" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1849" ht="17" customHeight="1" spans="1:4">
@@ -23507,7 +23510,7 @@
       <c r="B1849" s="10"/>
       <c r="C1849" s="10"/>
       <c r="D1849" s="10" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1850" ht="17" customHeight="1" spans="1:4">
@@ -23515,7 +23518,7 @@
       <c r="B1850" s="10"/>
       <c r="C1850" s="10"/>
       <c r="D1850" s="10" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1851" ht="17" customHeight="1" spans="1:4">
@@ -23523,7 +23526,7 @@
       <c r="B1851" s="10"/>
       <c r="C1851" s="10"/>
       <c r="D1851" s="10" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1852" ht="17" customHeight="1" spans="1:4">
@@ -23531,7 +23534,7 @@
       <c r="B1852" s="10"/>
       <c r="C1852" s="10"/>
       <c r="D1852" s="10" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1853" ht="17" customHeight="1" spans="1:4">
@@ -23547,10 +23550,10 @@
         <v>1745</v>
       </c>
       <c r="B1854" s="10" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C1854" s="10" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D1854" s="10" t="s">
         <v>1748</v>
@@ -23561,7 +23564,7 @@
       <c r="B1855" s="10"/>
       <c r="C1855" s="10"/>
       <c r="D1855" s="10" t="s">
-        <v>1794</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1856" ht="17" customHeight="1" spans="1:4">
@@ -23569,7 +23572,7 @@
       <c r="B1856" s="10"/>
       <c r="C1856" s="10"/>
       <c r="D1856" s="10" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1857" ht="17" customHeight="1" spans="1:4">
@@ -23577,7 +23580,7 @@
       <c r="B1857" s="10"/>
       <c r="C1857" s="10"/>
       <c r="D1857" s="10" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1858" ht="17" customHeight="1" spans="1:4">
@@ -23585,7 +23588,7 @@
       <c r="B1858" s="10"/>
       <c r="C1858" s="10"/>
       <c r="D1858" s="10" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1859" ht="17" customHeight="1" spans="1:4">
@@ -23593,7 +23596,7 @@
       <c r="B1859" s="10"/>
       <c r="C1859" s="10"/>
       <c r="D1859" s="10" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="1860" ht="17" customHeight="1" spans="1:4">
@@ -23601,7 +23604,7 @@
       <c r="B1860" s="10"/>
       <c r="C1860" s="10"/>
       <c r="D1860" s="10" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1861" ht="17" customHeight="1" spans="1:4">
@@ -23617,7 +23620,7 @@
       <c r="B1862" s="10"/>
       <c r="C1862" s="10"/>
       <c r="D1862" s="10" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="1863" ht="17" customHeight="1" spans="1:4">
@@ -23625,7 +23628,7 @@
       <c r="B1863" s="10"/>
       <c r="C1863" s="10"/>
       <c r="D1863" s="10" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="1864" ht="17" customHeight="1" spans="1:4">
@@ -23649,10 +23652,10 @@
         <v>1745</v>
       </c>
       <c r="B1866" s="10" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C1866" s="10" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="D1866" s="10" t="s">
         <v>1748</v>
@@ -23663,7 +23666,7 @@
       <c r="B1867" s="10"/>
       <c r="C1867" s="10"/>
       <c r="D1867" s="10" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1868" ht="17" customHeight="1" spans="1:4">
@@ -23671,7 +23674,7 @@
       <c r="B1868" s="10"/>
       <c r="C1868" s="10"/>
       <c r="D1868" s="10" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1869" ht="17" customHeight="1" spans="1:4">
@@ -23679,7 +23682,7 @@
       <c r="B1869" s="10"/>
       <c r="C1869" s="10"/>
       <c r="D1869" s="10" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1870" ht="17" customHeight="1" spans="1:4">
@@ -23687,7 +23690,7 @@
       <c r="B1870" s="10"/>
       <c r="C1870" s="10"/>
       <c r="D1870" s="11" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1871" ht="17" customHeight="1" spans="1:4">
@@ -23695,7 +23698,7 @@
       <c r="B1871" s="10"/>
       <c r="C1871" s="10"/>
       <c r="D1871" s="10" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1872" ht="17" customHeight="1" spans="1:4">
@@ -23703,7 +23706,7 @@
       <c r="B1872" s="10"/>
       <c r="C1872" s="10"/>
       <c r="D1872" s="10" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1873" ht="17" customHeight="1" spans="1:4">
@@ -23711,7 +23714,7 @@
       <c r="B1873" s="10"/>
       <c r="C1873" s="10"/>
       <c r="D1873" s="10" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1874" ht="17" customHeight="1" spans="1:4">
@@ -23719,7 +23722,7 @@
       <c r="B1874" s="10"/>
       <c r="C1874" s="10"/>
       <c r="D1874" s="10" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1875" ht="17" customHeight="1" spans="1:4">
@@ -23740,16 +23743,16 @@
     </row>
     <row r="1877" ht="17" customHeight="1" spans="1:4">
       <c r="A1877" s="10" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1877" s="10" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="C1877" s="10" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="D1877" s="10" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1878" ht="17" customHeight="1" spans="1:4">
@@ -23757,7 +23760,7 @@
       <c r="B1878" s="10"/>
       <c r="C1878" s="10"/>
       <c r="D1878" s="10" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1879" ht="17" customHeight="1" spans="1:4">
@@ -23765,7 +23768,7 @@
       <c r="B1879" s="10"/>
       <c r="C1879" s="10"/>
       <c r="D1879" s="10" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1880" ht="17" customHeight="1" spans="1:4">
@@ -23773,7 +23776,7 @@
       <c r="B1880" s="10"/>
       <c r="C1880" s="10"/>
       <c r="D1880" s="10" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1881" ht="17" customHeight="1" spans="1:4">
@@ -23781,7 +23784,7 @@
       <c r="B1881" s="10"/>
       <c r="C1881" s="10"/>
       <c r="D1881" s="10" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1882" ht="17" customHeight="1" spans="1:4">
@@ -23797,7 +23800,7 @@
       <c r="B1883" s="10"/>
       <c r="C1883" s="10"/>
       <c r="D1883" s="10" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1884" ht="17" customHeight="1" spans="1:4">
@@ -23805,7 +23808,7 @@
       <c r="B1884" s="10"/>
       <c r="C1884" s="10"/>
       <c r="D1884" s="10" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1885" ht="17" customHeight="1" spans="1:4">
@@ -23813,7 +23816,7 @@
       <c r="B1885" s="10"/>
       <c r="C1885" s="10"/>
       <c r="D1885" s="10" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1886" ht="17" customHeight="1" spans="1:4">
@@ -23821,7 +23824,7 @@
       <c r="B1886" s="10"/>
       <c r="C1886" s="10"/>
       <c r="D1886" s="14" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1887" ht="17" customHeight="1" spans="1:4">
@@ -23829,7 +23832,7 @@
       <c r="B1887" s="10"/>
       <c r="C1887" s="10"/>
       <c r="D1887" s="10" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1888" ht="17" customHeight="1" spans="1:4">
@@ -23837,7 +23840,7 @@
       <c r="B1888" s="10"/>
       <c r="C1888" s="10"/>
       <c r="D1888" s="10" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1889" ht="17" customHeight="1" spans="1:4">
@@ -23850,16 +23853,16 @@
     </row>
     <row r="1890" ht="17" customHeight="1" spans="1:4">
       <c r="A1890" s="10" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1890" s="10" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="C1890" s="10" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="D1890" s="10" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1891" ht="17" customHeight="1" spans="1:4">
@@ -23867,7 +23870,7 @@
       <c r="B1891" s="10"/>
       <c r="C1891" s="10"/>
       <c r="D1891" s="10" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1892" ht="17" customHeight="1" spans="1:4">
@@ -23875,7 +23878,7 @@
       <c r="B1892" s="10"/>
       <c r="C1892" s="10"/>
       <c r="D1892" s="10" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1893" ht="17" customHeight="1" spans="1:4">
@@ -23883,7 +23886,7 @@
       <c r="B1893" s="10"/>
       <c r="C1893" s="10"/>
       <c r="D1893" s="10" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1894" ht="17" customHeight="1" spans="1:4">
@@ -23891,7 +23894,7 @@
       <c r="B1894" s="10"/>
       <c r="C1894" s="10"/>
       <c r="D1894" s="10" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1895" ht="17" customHeight="1" spans="1:4">
@@ -23899,7 +23902,7 @@
       <c r="B1895" s="10"/>
       <c r="C1895" s="10"/>
       <c r="D1895" s="10" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1896" ht="17" customHeight="1" spans="1:4">
@@ -23907,7 +23910,7 @@
       <c r="B1896" s="10"/>
       <c r="C1896" s="10"/>
       <c r="D1896" s="10" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1897" ht="17" customHeight="1" spans="1:4">
@@ -23915,7 +23918,7 @@
       <c r="B1897" s="10"/>
       <c r="C1897" s="10"/>
       <c r="D1897" s="10" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1898" ht="17" customHeight="1" spans="1:4">
@@ -23923,7 +23926,7 @@
       <c r="B1898" s="10"/>
       <c r="C1898" s="10"/>
       <c r="D1898" s="10" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1899" ht="17" customHeight="1" spans="1:4">
@@ -23931,7 +23934,7 @@
       <c r="B1899" s="10"/>
       <c r="C1899" s="10"/>
       <c r="D1899" s="10" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1900" ht="17" customHeight="1" spans="1:4">
@@ -23939,7 +23942,7 @@
       <c r="B1900" s="10"/>
       <c r="C1900" s="10"/>
       <c r="D1900" s="10" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1901" ht="17" customHeight="1" spans="1:4">
@@ -23947,7 +23950,7 @@
       <c r="B1901" s="10"/>
       <c r="C1901" s="10"/>
       <c r="D1901" s="10" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1902" ht="17" customHeight="1" spans="1:4">
@@ -23963,7 +23966,7 @@
       <c r="B1903" s="10"/>
       <c r="C1903" s="10"/>
       <c r="D1903" s="10" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1904" ht="17" customHeight="1" spans="1:4">
@@ -23971,7 +23974,7 @@
       <c r="B1904" s="10"/>
       <c r="C1904" s="10"/>
       <c r="D1904" s="10" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1905" ht="17" customHeight="1" spans="1:4">
@@ -23984,16 +23987,16 @@
     </row>
     <row r="1906" ht="17" customHeight="1" spans="1:4">
       <c r="A1906" s="10" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1906" s="10" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C1906" s="10" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D1906" s="10" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1907" ht="17" customHeight="1" spans="1:4">
@@ -24001,7 +24004,7 @@
       <c r="B1907" s="10"/>
       <c r="C1907" s="10"/>
       <c r="D1907" s="10" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="1908" ht="17" customHeight="1" spans="1:4">
@@ -24009,7 +24012,7 @@
       <c r="B1908" s="10"/>
       <c r="C1908" s="10"/>
       <c r="D1908" s="10" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="1909" ht="17" customHeight="1" spans="1:4">
@@ -24017,7 +24020,7 @@
       <c r="B1909" s="10"/>
       <c r="C1909" s="10"/>
       <c r="D1909" s="10" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1910" ht="17" customHeight="1" spans="1:4">
@@ -24025,7 +24028,7 @@
       <c r="B1910" s="10"/>
       <c r="C1910" s="10"/>
       <c r="D1910" s="10" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1911" ht="17" customHeight="1" spans="1:4">
@@ -24041,7 +24044,7 @@
       <c r="B1912" s="10"/>
       <c r="C1912" s="10"/>
       <c r="D1912" s="10" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1913" ht="17" customHeight="1" spans="1:4">
@@ -24049,7 +24052,7 @@
       <c r="B1913" s="10"/>
       <c r="C1913" s="10"/>
       <c r="D1913" s="10" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1914" ht="17" customHeight="1" spans="1:4">
@@ -24057,7 +24060,7 @@
       <c r="B1914" s="10"/>
       <c r="C1914" s="10"/>
       <c r="D1914" s="10" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="1915" ht="17" customHeight="1" spans="1:4">
@@ -24065,7 +24068,7 @@
       <c r="B1915" s="10"/>
       <c r="C1915" s="10"/>
       <c r="D1915" s="10" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1916" ht="17" customHeight="1" spans="1:4">
@@ -24073,7 +24076,7 @@
       <c r="B1916" s="10"/>
       <c r="C1916" s="10"/>
       <c r="D1916" s="10" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1917" ht="17" customHeight="1" spans="1:4">
@@ -24081,7 +24084,7 @@
       <c r="B1917" s="10"/>
       <c r="C1917" s="10"/>
       <c r="D1917" s="10" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1918" ht="17" customHeight="1" spans="1:4">
@@ -24089,7 +24092,7 @@
       <c r="B1918" s="10"/>
       <c r="C1918" s="10"/>
       <c r="D1918" s="10" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="1919" ht="17" customHeight="1" spans="1:4">
@@ -24097,7 +24100,7 @@
       <c r="B1919" s="10"/>
       <c r="C1919" s="10"/>
       <c r="D1919" s="10" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="1920" ht="17" customHeight="1" spans="1:4">
@@ -24105,7 +24108,7 @@
       <c r="B1920" s="10"/>
       <c r="C1920" s="10"/>
       <c r="D1920" s="10" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="1921" ht="17" customHeight="1" spans="1:4">
@@ -24113,7 +24116,7 @@
       <c r="B1921" s="10"/>
       <c r="C1921" s="10"/>
       <c r="D1921" s="10" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1922" ht="17" customHeight="1" spans="1:4">
@@ -24121,7 +24124,7 @@
       <c r="B1922" s="10"/>
       <c r="C1922" s="10"/>
       <c r="D1922" s="10" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="1923" ht="17" customHeight="1" spans="1:4">
@@ -24129,7 +24132,7 @@
       <c r="B1923" s="10"/>
       <c r="C1923" s="10"/>
       <c r="D1923" s="10" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="1924" ht="17" customHeight="1" spans="1:4">
@@ -24142,16 +24145,16 @@
     </row>
     <row r="1925" ht="17" customHeight="1" spans="1:4">
       <c r="A1925" s="10" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1925" s="10" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C1925" s="10" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D1925" s="10" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1926" ht="17" customHeight="1" spans="1:4">
@@ -24159,7 +24162,7 @@
       <c r="B1926" s="10"/>
       <c r="C1926" s="10"/>
       <c r="D1926" s="10" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="1927" ht="17" customHeight="1" spans="1:4">
@@ -24167,7 +24170,7 @@
       <c r="B1927" s="10"/>
       <c r="C1927" s="10"/>
       <c r="D1927" s="10" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="1928" ht="17" customHeight="1" spans="1:4">
@@ -24175,7 +24178,7 @@
       <c r="B1928" s="10"/>
       <c r="C1928" s="10"/>
       <c r="D1928" s="10" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="1929" ht="17" customHeight="1" spans="1:4">
@@ -24183,7 +24186,7 @@
       <c r="B1929" s="10"/>
       <c r="C1929" s="10"/>
       <c r="D1929" s="10" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="1930" ht="17" customHeight="1" spans="1:4">
@@ -24191,7 +24194,7 @@
       <c r="B1930" s="10"/>
       <c r="C1930" s="10"/>
       <c r="D1930" s="10" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="1931" ht="17" customHeight="1" spans="1:4">
@@ -24199,7 +24202,7 @@
       <c r="B1931" s="10"/>
       <c r="C1931" s="10"/>
       <c r="D1931" s="10" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="1932" ht="17" customHeight="1" spans="1:4">
@@ -24207,7 +24210,7 @@
       <c r="B1932" s="10"/>
       <c r="C1932" s="10"/>
       <c r="D1932" s="10" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="1933" ht="17" customHeight="1" spans="1:4">
@@ -24215,7 +24218,7 @@
       <c r="B1933" s="10"/>
       <c r="C1933" s="10"/>
       <c r="D1933" s="10" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="1934" ht="17" customHeight="1" spans="1:4">
@@ -24223,7 +24226,7 @@
       <c r="B1934" s="10"/>
       <c r="C1934" s="10"/>
       <c r="D1934" s="10" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="1935" ht="17" customHeight="1" spans="1:4">
@@ -24236,16 +24239,16 @@
     </row>
     <row r="1936" ht="17" customHeight="1" spans="1:4">
       <c r="A1936" s="10" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1936" s="10" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C1936" s="10" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D1936" s="10" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1937" ht="17" customHeight="1" spans="1:4">
@@ -24261,7 +24264,7 @@
       <c r="B1938" s="10"/>
       <c r="C1938" s="10"/>
       <c r="D1938" s="10" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="1939" ht="17" customHeight="1" spans="1:4">
@@ -24269,7 +24272,7 @@
       <c r="B1939" s="10"/>
       <c r="C1939" s="10"/>
       <c r="D1939" s="10" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="1940" ht="17" customHeight="1" spans="1:4">
@@ -24277,7 +24280,7 @@
       <c r="B1940" s="10"/>
       <c r="C1940" s="10"/>
       <c r="D1940" s="10" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="1941" ht="17" customHeight="1" spans="1:4">
@@ -24285,7 +24288,7 @@
       <c r="B1941" s="10"/>
       <c r="C1941" s="10"/>
       <c r="D1941" s="10" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1942" ht="17" customHeight="1" spans="1:4">
@@ -24293,7 +24296,7 @@
       <c r="B1942" s="10"/>
       <c r="C1942" s="10"/>
       <c r="D1942" s="10" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1943" ht="17" customHeight="1" spans="1:4">
@@ -24301,7 +24304,7 @@
       <c r="B1943" s="10"/>
       <c r="C1943" s="10"/>
       <c r="D1943" s="10" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1944" ht="17" customHeight="1" spans="1:4">
@@ -24309,7 +24312,7 @@
       <c r="B1944" s="10"/>
       <c r="C1944" s="10"/>
       <c r="D1944" s="10" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1945" ht="17" customHeight="1" spans="1:4">
@@ -24317,7 +24320,7 @@
       <c r="B1945" s="10"/>
       <c r="C1945" s="10"/>
       <c r="D1945" s="10" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1946" ht="17" customHeight="1" spans="1:4">
@@ -24325,7 +24328,7 @@
       <c r="B1946" s="10"/>
       <c r="C1946" s="10"/>
       <c r="D1946" s="10" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1947" ht="17" customHeight="1" spans="1:4">
@@ -24333,7 +24336,7 @@
       <c r="B1947" s="10"/>
       <c r="C1947" s="10"/>
       <c r="D1947" s="10" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1948" ht="17" customHeight="1" spans="1:4">
@@ -24354,16 +24357,16 @@
     </row>
     <row r="1950" ht="17" customHeight="1" spans="1:4">
       <c r="A1950" s="10" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1950" s="10" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="C1950" s="10" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="D1950" s="10" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1951" ht="17" customHeight="1" spans="1:4">
@@ -24379,7 +24382,7 @@
       <c r="B1952" s="10"/>
       <c r="C1952" s="10"/>
       <c r="D1952" s="10" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1953" ht="17" customHeight="1" spans="1:4">
@@ -24395,7 +24398,7 @@
       <c r="B1954" s="10"/>
       <c r="C1954" s="10"/>
       <c r="D1954" s="10" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1955" ht="17" customHeight="1" spans="1:4">
@@ -24403,7 +24406,7 @@
       <c r="B1955" s="10"/>
       <c r="C1955" s="10"/>
       <c r="D1955" s="10" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1956" ht="17" customHeight="1" spans="1:4">
@@ -24411,7 +24414,7 @@
       <c r="B1956" s="10"/>
       <c r="C1956" s="10"/>
       <c r="D1956" s="10" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1957" ht="17" customHeight="1" spans="1:4">
@@ -24419,7 +24422,7 @@
       <c r="B1957" s="10"/>
       <c r="C1957" s="10"/>
       <c r="D1957" s="10" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1958" ht="17" customHeight="1" spans="1:4">
@@ -24427,7 +24430,7 @@
       <c r="B1958" s="10"/>
       <c r="C1958" s="10"/>
       <c r="D1958" s="10" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1959" ht="17" customHeight="1" spans="1:4">
@@ -24435,7 +24438,7 @@
       <c r="B1959" s="10"/>
       <c r="C1959" s="10"/>
       <c r="D1959" s="10" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1960" ht="17" customHeight="1" spans="1:4">
@@ -24443,7 +24446,7 @@
       <c r="B1960" s="10"/>
       <c r="C1960" s="10"/>
       <c r="D1960" s="10" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1961" ht="17" customHeight="1" spans="1:4">
@@ -24451,7 +24454,7 @@
       <c r="B1961" s="10"/>
       <c r="C1961" s="10"/>
       <c r="D1961" s="10" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1962" ht="17" customHeight="1" spans="1:4">
@@ -24459,7 +24462,7 @@
       <c r="B1962" s="10"/>
       <c r="C1962" s="10"/>
       <c r="D1962" s="10" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1963" ht="17" customHeight="1" spans="1:4">
@@ -24467,7 +24470,7 @@
       <c r="B1963" s="10"/>
       <c r="C1963" s="10"/>
       <c r="D1963" s="10" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1964" ht="17" customHeight="1" spans="1:4">
@@ -24480,16 +24483,16 @@
     </row>
     <row r="1965" ht="17" customHeight="1" spans="1:4">
       <c r="A1965" s="10" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B1965" s="10" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C1965" s="10" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="D1965" s="10" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1966" ht="17" customHeight="1" spans="1:4">
@@ -24505,7 +24508,7 @@
       <c r="B1967" s="10"/>
       <c r="C1967" s="10"/>
       <c r="D1967" s="10" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1968" ht="17" customHeight="1" spans="1:4">
@@ -24513,7 +24516,7 @@
       <c r="B1968" s="10"/>
       <c r="C1968" s="10"/>
       <c r="D1968" s="10" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1969" ht="17" customHeight="1" spans="1:4">
@@ -24521,7 +24524,7 @@
       <c r="B1969" s="10"/>
       <c r="C1969" s="10"/>
       <c r="D1969" s="10" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="1970" ht="17" customHeight="1" spans="1:4">
@@ -24529,7 +24532,7 @@
       <c r="B1970" s="10"/>
       <c r="C1970" s="10"/>
       <c r="D1970" s="10" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1971" ht="17" customHeight="1" spans="1:4">
@@ -24537,7 +24540,7 @@
       <c r="B1971" s="10"/>
       <c r="C1971" s="10"/>
       <c r="D1971" s="10" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1972" ht="17" customHeight="1" spans="1:4">
@@ -24545,7 +24548,7 @@
       <c r="B1972" s="10"/>
       <c r="C1972" s="10"/>
       <c r="D1972" s="10" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1973" ht="17" customHeight="1" spans="1:4">
@@ -24553,7 +24556,7 @@
       <c r="B1973" s="10"/>
       <c r="C1973" s="10"/>
       <c r="D1973" s="10" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1974" ht="17" customHeight="1" spans="1:4">
@@ -24566,16 +24569,16 @@
     </row>
     <row r="1975" ht="17" hidden="1" customHeight="1" spans="1:4">
       <c r="A1975" s="11" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B1975" s="11" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="C1975" s="11" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="D1975" s="11" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1976" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24583,7 +24586,7 @@
       <c r="B1976" s="11"/>
       <c r="C1976" s="11"/>
       <c r="D1976" s="11" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1977" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24591,7 +24594,7 @@
       <c r="B1977" s="11"/>
       <c r="C1977" s="11"/>
       <c r="D1977" s="11" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1978" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24599,7 +24602,7 @@
       <c r="B1978" s="11"/>
       <c r="C1978" s="11"/>
       <c r="D1978" s="11" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1979" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24607,7 +24610,7 @@
       <c r="B1979" s="11"/>
       <c r="C1979" s="11"/>
       <c r="D1979" s="11" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1980" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24615,7 +24618,7 @@
       <c r="B1980" s="11"/>
       <c r="C1980" s="11"/>
       <c r="D1980" s="11" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1981" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24623,7 +24626,7 @@
       <c r="B1981" s="11"/>
       <c r="C1981" s="11"/>
       <c r="D1981" s="11" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1982" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24631,7 +24634,7 @@
       <c r="B1982" s="11"/>
       <c r="C1982" s="11"/>
       <c r="D1982" s="11" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1983" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24639,7 +24642,7 @@
       <c r="B1983" s="11"/>
       <c r="C1983" s="11"/>
       <c r="D1983" s="11" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1984" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24647,7 +24650,7 @@
       <c r="B1984" s="11"/>
       <c r="C1984" s="11"/>
       <c r="D1984" s="11" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1985" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24655,7 +24658,7 @@
       <c r="B1985" s="11"/>
       <c r="C1985" s="11"/>
       <c r="D1985" s="11" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1986" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -24668,16 +24671,16 @@
     </row>
     <row r="1987" ht="17" customHeight="1" spans="1:4">
       <c r="A1987" s="10" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B1987" s="10" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="C1987" s="10" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="D1987" s="10" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1988" ht="17" customHeight="1" spans="1:4">
@@ -24701,7 +24704,7 @@
       <c r="B1990" s="10"/>
       <c r="C1990" s="10"/>
       <c r="D1990" s="10" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1991" ht="17" customHeight="1" spans="1:4">
@@ -24709,7 +24712,7 @@
       <c r="B1991" s="10"/>
       <c r="C1991" s="10"/>
       <c r="D1991" s="10" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1992" ht="17" customHeight="1" spans="1:4">
@@ -24717,7 +24720,7 @@
       <c r="B1992" s="10"/>
       <c r="C1992" s="10"/>
       <c r="D1992" s="10" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1993" ht="17" customHeight="1" spans="1:4">
@@ -24725,7 +24728,7 @@
       <c r="B1993" s="10"/>
       <c r="C1993" s="10"/>
       <c r="D1993" s="10" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1994" ht="17" customHeight="1" spans="1:4">
@@ -24733,7 +24736,7 @@
       <c r="B1994" s="10"/>
       <c r="C1994" s="10"/>
       <c r="D1994" s="10" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1995" ht="17" customHeight="1" spans="1:4">
@@ -24741,7 +24744,7 @@
       <c r="B1995" s="10"/>
       <c r="C1995" s="10"/>
       <c r="D1995" s="10" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1996" ht="17" customHeight="1" spans="1:4">
@@ -24749,7 +24752,7 @@
       <c r="B1996" s="10"/>
       <c r="C1996" s="10"/>
       <c r="D1996" s="10" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1997" ht="17" customHeight="1" spans="1:4">
@@ -24757,7 +24760,7 @@
       <c r="B1997" s="10"/>
       <c r="C1997" s="10"/>
       <c r="D1997" s="10" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1998" ht="17" customHeight="1" spans="1:4">
@@ -24765,7 +24768,7 @@
       <c r="B1998" s="10"/>
       <c r="C1998" s="10"/>
       <c r="D1998" s="10" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1999" ht="17" customHeight="1" spans="1:4">
@@ -24773,7 +24776,7 @@
       <c r="B1999" s="10"/>
       <c r="C1999" s="10"/>
       <c r="D1999" s="10" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="2000" ht="17" customHeight="1" spans="1:4">
@@ -24781,7 +24784,7 @@
       <c r="B2000" s="10"/>
       <c r="C2000" s="10"/>
       <c r="D2000" s="10" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="2001" ht="17" customHeight="1" spans="1:4">
@@ -24789,7 +24792,7 @@
       <c r="B2001" s="10"/>
       <c r="C2001" s="10"/>
       <c r="D2001" s="10" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="2002" ht="17" customHeight="1" spans="1:4">
@@ -24797,7 +24800,7 @@
       <c r="B2002" s="10"/>
       <c r="C2002" s="10"/>
       <c r="D2002" s="10" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="2003" ht="17" customHeight="1" spans="1:4">
@@ -24805,7 +24808,7 @@
       <c r="B2003" s="10"/>
       <c r="C2003" s="10"/>
       <c r="D2003" s="10" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="2004" ht="17" customHeight="1" spans="1:4">
@@ -24813,7 +24816,7 @@
       <c r="B2004" s="10"/>
       <c r="C2004" s="10"/>
       <c r="D2004" s="10" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="2005" ht="17" customHeight="1" spans="1:4">
@@ -24826,16 +24829,16 @@
     </row>
     <row r="2006" ht="17" customHeight="1" spans="1:4">
       <c r="A2006" s="10" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B2006" s="10" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="C2006" s="10" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="D2006" s="10" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="2007" ht="17" customHeight="1" spans="1:4">
@@ -24843,7 +24846,7 @@
       <c r="B2007" s="10"/>
       <c r="C2007" s="10"/>
       <c r="D2007" s="10" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="2008" ht="17" customHeight="1" spans="1:4">
@@ -24851,7 +24854,7 @@
       <c r="B2008" s="10"/>
       <c r="C2008" s="10"/>
       <c r="D2008" s="10" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="2009" ht="17" customHeight="1" spans="1:4">
@@ -24859,7 +24862,7 @@
       <c r="B2009" s="10"/>
       <c r="C2009" s="10"/>
       <c r="D2009" s="10" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="2010" ht="17" customHeight="1" spans="1:4">
@@ -24867,7 +24870,7 @@
       <c r="B2010" s="10"/>
       <c r="C2010" s="10"/>
       <c r="D2010" s="10" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="2011" ht="17" customHeight="1" spans="1:4">
@@ -24875,7 +24878,7 @@
       <c r="B2011" s="10"/>
       <c r="C2011" s="10"/>
       <c r="D2011" s="10" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="2012" ht="17" customHeight="1" spans="1:4">
@@ -24883,7 +24886,7 @@
       <c r="B2012" s="10"/>
       <c r="C2012" s="10"/>
       <c r="D2012" s="10" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="2013" ht="17" customHeight="1" spans="1:4">
@@ -24891,7 +24894,7 @@
       <c r="B2013" s="10"/>
       <c r="C2013" s="10"/>
       <c r="D2013" s="10" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="2014" ht="17" customHeight="1" spans="1:4">
@@ -24899,7 +24902,7 @@
       <c r="B2014" s="10"/>
       <c r="C2014" s="10"/>
       <c r="D2014" s="10" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="2015" ht="17" customHeight="1" spans="1:4">
@@ -24907,7 +24910,7 @@
       <c r="B2015" s="10"/>
       <c r="C2015" s="10"/>
       <c r="D2015" s="10" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="2016" ht="17" customHeight="1" spans="1:4">
@@ -24915,7 +24918,7 @@
       <c r="B2016" s="10"/>
       <c r="C2016" s="10"/>
       <c r="D2016" s="10" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="2017" ht="17" customHeight="1" spans="1:4">
@@ -24923,7 +24926,7 @@
       <c r="B2017" s="10"/>
       <c r="C2017" s="10"/>
       <c r="D2017" s="10" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="2018" ht="17" customHeight="1" spans="1:4">
@@ -24936,16 +24939,16 @@
     </row>
     <row r="2019" ht="17" customHeight="1" spans="1:4">
       <c r="A2019" s="10" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B2019" s="10" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="C2019" s="10" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="D2019" s="10" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="2020" ht="17" customHeight="1" spans="1:4">
@@ -24961,7 +24964,7 @@
       <c r="B2021" s="10"/>
       <c r="C2021" s="10"/>
       <c r="D2021" s="10" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="2022" ht="17" customHeight="1" spans="1:4">
@@ -24969,7 +24972,7 @@
       <c r="B2022" s="10"/>
       <c r="C2022" s="10"/>
       <c r="D2022" s="10" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="2023" ht="17" customHeight="1" spans="1:4">
@@ -25033,7 +25036,7 @@
       <c r="B2030" s="10"/>
       <c r="C2030" s="10"/>
       <c r="D2030" s="10" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="2031" ht="17" customHeight="1" spans="1:4">
@@ -25046,16 +25049,16 @@
     </row>
     <row r="2032" ht="17" customHeight="1" spans="1:4">
       <c r="A2032" s="10" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B2032" s="10" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="C2032" s="10" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="D2032" s="10" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="2033" ht="17" customHeight="1" spans="1:4">
@@ -25111,7 +25114,7 @@
       <c r="B2039" s="10"/>
       <c r="C2039" s="10"/>
       <c r="D2039" s="10" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="2040" ht="17" customHeight="1" spans="1:4">
@@ -25124,16 +25127,16 @@
     </row>
     <row r="2041" ht="17" customHeight="1" spans="1:4">
       <c r="A2041" s="10" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="B2041" s="10" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="C2041" s="10" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="D2041" s="10" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="2042" ht="17" customHeight="1" spans="1:4">
@@ -25141,7 +25144,7 @@
       <c r="B2042" s="10"/>
       <c r="C2042" s="10"/>
       <c r="D2042" s="10" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="2043" ht="17" customHeight="1" spans="1:4">
@@ -25149,7 +25152,7 @@
       <c r="B2043" s="10"/>
       <c r="C2043" s="10"/>
       <c r="D2043" s="10" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="2044" ht="17" customHeight="1" spans="1:4">
@@ -25157,7 +25160,7 @@
       <c r="B2044" s="10"/>
       <c r="C2044" s="10"/>
       <c r="D2044" s="10" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="2045" ht="17" customHeight="1" spans="1:4">
@@ -25165,7 +25168,7 @@
       <c r="B2045" s="10"/>
       <c r="C2045" s="10"/>
       <c r="D2045" s="10" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="2046" ht="17" customHeight="1" spans="1:4">
@@ -25173,7 +25176,7 @@
       <c r="B2046" s="10"/>
       <c r="C2046" s="10"/>
       <c r="D2046" s="10" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="2047" ht="17" customHeight="1" spans="1:4">
@@ -25181,7 +25184,7 @@
       <c r="B2047" s="10"/>
       <c r="C2047" s="10"/>
       <c r="D2047" s="10" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="2048" ht="17" customHeight="1" spans="1:4">
@@ -25189,7 +25192,7 @@
       <c r="B2048" s="10"/>
       <c r="C2048" s="10"/>
       <c r="D2048" s="10" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="2049" ht="17" customHeight="1" spans="1:4">
@@ -25197,7 +25200,7 @@
       <c r="B2049" s="10"/>
       <c r="C2049" s="10"/>
       <c r="D2049" s="10" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="2050" ht="17" customHeight="1" spans="1:4">
@@ -25205,7 +25208,7 @@
       <c r="B2050" s="10"/>
       <c r="C2050" s="10"/>
       <c r="D2050" s="10" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="2051" ht="17" customHeight="1" spans="1:4">
@@ -25213,7 +25216,7 @@
       <c r="B2051" s="10"/>
       <c r="C2051" s="10"/>
       <c r="D2051" s="10" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="2052" ht="17" customHeight="1" spans="1:4">
@@ -25221,7 +25224,7 @@
       <c r="B2052" s="10"/>
       <c r="C2052" s="10"/>
       <c r="D2052" s="10" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="2053" ht="17" customHeight="1" spans="1:4">
@@ -25229,7 +25232,7 @@
       <c r="B2053" s="10"/>
       <c r="C2053" s="10"/>
       <c r="D2053" s="10" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="2054" ht="17" customHeight="1" spans="1:4">
@@ -25237,7 +25240,7 @@
       <c r="B2054" s="10"/>
       <c r="C2054" s="10"/>
       <c r="D2054" s="10" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="2055" ht="17" customHeight="1" spans="1:4">
@@ -25245,7 +25248,7 @@
       <c r="B2055" s="10"/>
       <c r="C2055" s="10"/>
       <c r="D2055" s="10" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="2056" ht="17" customHeight="1" spans="1:4">
@@ -25253,7 +25256,7 @@
       <c r="B2056" s="10"/>
       <c r="C2056" s="10"/>
       <c r="D2056" s="10" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="2057" ht="17" customHeight="1" spans="1:4">
@@ -25261,7 +25264,7 @@
       <c r="B2057" s="10"/>
       <c r="C2057" s="10"/>
       <c r="D2057" s="10" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="2058" ht="17" customHeight="1" spans="1:4">
@@ -25269,7 +25272,7 @@
       <c r="B2058" s="10"/>
       <c r="C2058" s="10"/>
       <c r="D2058" s="10" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="2059" ht="17" customHeight="1" spans="1:4">
@@ -25277,7 +25280,7 @@
       <c r="B2059" s="10"/>
       <c r="C2059" s="10"/>
       <c r="D2059" s="10" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="2060" ht="17" customHeight="1" spans="1:4">
@@ -25290,16 +25293,16 @@
     </row>
     <row r="2061" ht="17" hidden="1" customHeight="1" spans="1:4">
       <c r="A2061" s="11" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B2061" s="11" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="C2061" s="11" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="D2061" s="11" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="2062" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25307,7 +25310,7 @@
       <c r="B2062" s="11"/>
       <c r="C2062" s="11"/>
       <c r="D2062" s="11" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="2063" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25315,7 +25318,7 @@
       <c r="B2063" s="11"/>
       <c r="C2063" s="11"/>
       <c r="D2063" s="11" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="2064" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25323,7 +25326,7 @@
       <c r="B2064" s="11"/>
       <c r="C2064" s="11"/>
       <c r="D2064" s="11" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="2065" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25331,7 +25334,7 @@
       <c r="B2065" s="11"/>
       <c r="C2065" s="11"/>
       <c r="D2065" s="11" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="2066" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25339,7 +25342,7 @@
       <c r="B2066" s="11"/>
       <c r="C2066" s="11"/>
       <c r="D2066" s="11" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="2067" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25347,7 +25350,7 @@
       <c r="B2067" s="11"/>
       <c r="C2067" s="11"/>
       <c r="D2067" s="11" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="2068" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25363,7 +25366,7 @@
       <c r="B2069" s="11"/>
       <c r="C2069" s="11"/>
       <c r="D2069" s="11" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="2070" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25371,7 +25374,7 @@
       <c r="B2070" s="11"/>
       <c r="C2070" s="11"/>
       <c r="D2070" s="11" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="2071" ht="17" hidden="1" customHeight="1" spans="1:4">
@@ -25384,16 +25387,16 @@
     </row>
     <row r="2072" ht="17" customHeight="1" spans="1:4">
       <c r="A2072" s="2" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B2072" s="2" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="C2072" s="2" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="D2072" s="2" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="2073" ht="17" customHeight="1" spans="1:4">
@@ -25401,7 +25404,7 @@
       <c r="B2073" s="2"/>
       <c r="C2073" s="2"/>
       <c r="D2073" s="2" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="2074" ht="17" customHeight="1" spans="1:4">
@@ -25409,7 +25412,7 @@
       <c r="B2074" s="2"/>
       <c r="C2074" s="2"/>
       <c r="D2074" s="2" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="2075" ht="17" customHeight="1" spans="1:4">
@@ -25417,7 +25420,7 @@
       <c r="B2075" s="2"/>
       <c r="C2075" s="2"/>
       <c r="D2075" s="2" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="2076" ht="17" customHeight="1" spans="1:4">
@@ -25425,7 +25428,7 @@
       <c r="B2076" s="2"/>
       <c r="C2076" s="2"/>
       <c r="D2076" s="2" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="2077" ht="17" customHeight="1" spans="1:4">
@@ -25433,7 +25436,7 @@
       <c r="B2077" s="2"/>
       <c r="C2077" s="2"/>
       <c r="D2077" s="2" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="2078" ht="17" customHeight="1" spans="1:4">
@@ -25441,7 +25444,7 @@
       <c r="B2078" s="2"/>
       <c r="C2078" s="2"/>
       <c r="D2078" s="2" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="2079" ht="17" customHeight="1" spans="1:4">
@@ -25449,7 +25452,7 @@
       <c r="B2079" s="2"/>
       <c r="C2079" s="2"/>
       <c r="D2079" s="2" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="2080" ht="17" customHeight="1" spans="1:4">
@@ -25457,7 +25460,7 @@
       <c r="B2080" s="2"/>
       <c r="C2080" s="2"/>
       <c r="D2080" s="2" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="2081" ht="17" customHeight="1" spans="1:4">
@@ -25465,7 +25468,7 @@
       <c r="B2081" s="2"/>
       <c r="C2081" s="2"/>
       <c r="D2081" s="2" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="2082" ht="17" customHeight="1" spans="1:4">
@@ -25473,7 +25476,7 @@
       <c r="B2082" s="2"/>
       <c r="C2082" s="2"/>
       <c r="D2082" s="2" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="2083" ht="17" customHeight="1" spans="1:4">
@@ -25481,7 +25484,7 @@
       <c r="B2083" s="2"/>
       <c r="C2083" s="2"/>
       <c r="D2083" s="2" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="2084" ht="17" customHeight="1" spans="1:4">
@@ -25489,7 +25492,7 @@
       <c r="B2084" s="2"/>
       <c r="C2084" s="2"/>
       <c r="D2084" s="2" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="2085" ht="17" customHeight="1" spans="1:4">
@@ -25497,7 +25500,7 @@
       <c r="B2085" s="2"/>
       <c r="C2085" s="2"/>
       <c r="D2085" s="2" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="2086" ht="17" customHeight="1" spans="1:4">
@@ -25510,16 +25513,16 @@
     </row>
     <row r="2087" ht="17" customHeight="1" spans="1:4">
       <c r="A2087" s="2" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B2087" s="2" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="C2087" s="2" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="D2087" s="2" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="2088" ht="17" customHeight="1" spans="1:4">
@@ -25527,7 +25530,7 @@
       <c r="B2088" s="2"/>
       <c r="C2088" s="2"/>
       <c r="D2088" s="2" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="2089" ht="17" customHeight="1" spans="1:4">
@@ -25535,7 +25538,7 @@
       <c r="B2089" s="2"/>
       <c r="C2089" s="2"/>
       <c r="D2089" s="2" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="2090" ht="17" customHeight="1" spans="1:4">
@@ -25543,7 +25546,7 @@
       <c r="B2090" s="2"/>
       <c r="C2090" s="2"/>
       <c r="D2090" s="2" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="2091" ht="17" customHeight="1" spans="1:4">
@@ -25551,7 +25554,7 @@
       <c r="B2091" s="2"/>
       <c r="C2091" s="2"/>
       <c r="D2091" s="2" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="2092" ht="17" customHeight="1" spans="1:4">
@@ -25567,7 +25570,7 @@
       <c r="B2093" s="2"/>
       <c r="C2093" s="2"/>
       <c r="D2093" s="2" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="2094" ht="17" customHeight="1" spans="1:4">
@@ -26208,13 +26211,13 @@
     </row>
     <row r="10" ht="17" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -26305,7 +26308,7 @@
         <v>1036</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -26390,13 +26393,13 @@
     </row>
     <row r="24" ht="17" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -26633,7 +26636,7 @@
         <v>289</v>
       </c>
       <c r="D42" s="5"/>
-      <c r="E42" s="3"/>
+      <c r="E42" s="6"/>
     </row>
     <row r="43" ht="17" spans="1:5">
       <c r="A43" s="2" t="s">
@@ -26802,7 +26805,7 @@
         <v>704</v>
       </c>
       <c r="D55" s="5"/>
-      <c r="E55" s="3"/>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" ht="17" spans="1:5">
       <c r="A56" s="2" t="s">
@@ -26845,13 +26848,13 @@
     </row>
     <row r="59" ht="17" spans="1:5">
       <c r="A59" s="2" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="3"/>
@@ -27049,7 +27052,7 @@
         <v>688</v>
       </c>
       <c r="D74" s="5"/>
-      <c r="E74" s="3"/>
+      <c r="E74" s="6"/>
     </row>
     <row r="75" ht="17" spans="1:5">
       <c r="A75" s="2" t="s">
@@ -27088,7 +27091,7 @@
         <v>732</v>
       </c>
       <c r="D77" s="5"/>
-      <c r="E77" s="3"/>
+      <c r="E77" s="6"/>
     </row>
     <row r="78" ht="17" spans="1:5">
       <c r="A78" s="2" t="s">
@@ -27322,7 +27325,7 @@
         <v>1132</v>
       </c>
       <c r="D95" s="5"/>
-      <c r="E95" s="3"/>
+      <c r="E95" s="6"/>
     </row>
     <row r="96" ht="17" spans="1:5">
       <c r="A96" s="2" t="s">
@@ -27417,7 +27420,7 @@
         <v>1292</v>
       </c>
       <c r="D102" s="5"/>
-      <c r="E102" s="3"/>
+      <c r="E102" s="6"/>
       <c r="F102" s="1"/>
     </row>
     <row r="103" ht="17" spans="1:6">
@@ -27669,7 +27672,7 @@
         <v>1596</v>
       </c>
       <c r="D120" s="5"/>
-      <c r="E120" s="3"/>
+      <c r="E120" s="6"/>
       <c r="F120" s="1"/>
     </row>
     <row r="121" ht="17" spans="1:6">
@@ -27957,10 +27960,10 @@
         <v>1745</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="3"/>
@@ -27971,10 +27974,10 @@
         <v>1745</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="D142" s="5"/>
       <c r="E142" s="3"/>
@@ -27985,10 +27988,10 @@
         <v>1745</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="6"/>
@@ -27999,10 +28002,10 @@
         <v>1745</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="D144" s="5"/>
       <c r="E144" s="3"/>
@@ -28012,10 +28015,10 @@
         <v>1745</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="D145" s="5"/>
       <c r="E145" s="3"/>
@@ -28025,10 +28028,10 @@
         <v>1745</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="3"/>
@@ -28038,10 +28041,10 @@
         <v>1745</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="D147" s="5"/>
       <c r="E147" s="3"/>
@@ -28051,10 +28054,10 @@
         <v>1745</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="D148" s="5"/>
       <c r="E148" s="3"/>
@@ -28064,10 +28067,10 @@
         <v>1745</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="3"/>
@@ -28077,10 +28080,10 @@
         <v>1745</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="D150" s="5"/>
       <c r="E150" s="3"/>
@@ -28090,10 +28093,10 @@
         <v>1745</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D151" s="5"/>
       <c r="E151" s="3"/>
@@ -28103,179 +28106,179 @@
         <v>1745</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="D152" s="5"/>
       <c r="E152" s="3"/>
     </row>
     <row r="153" ht="17" spans="1:5">
       <c r="A153" s="2" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="D153" s="5"/>
       <c r="E153" s="6"/>
     </row>
     <row r="154" ht="17" spans="1:5">
       <c r="A154" s="2" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="D154" s="5"/>
       <c r="E154" s="6"/>
     </row>
     <row r="155" ht="17" spans="1:5">
       <c r="A155" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D155" s="5"/>
       <c r="E155" s="3"/>
     </row>
     <row r="156" ht="17" spans="1:5">
       <c r="A156" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D156" s="5"/>
       <c r="E156" s="3"/>
     </row>
     <row r="157" ht="17" spans="1:5">
       <c r="A157" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="3"/>
     </row>
     <row r="158" ht="17" spans="1:5">
       <c r="A158" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="3"/>
     </row>
     <row r="159" ht="17" spans="1:5">
       <c r="A159" s="2" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="D159" s="5"/>
       <c r="E159" s="3"/>
     </row>
     <row r="160" ht="17" spans="1:5">
       <c r="A160" s="2" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="3"/>
     </row>
     <row r="161" ht="17" spans="1:5">
       <c r="A161" s="2" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="D161" s="5"/>
       <c r="E161" s="3"/>
     </row>
     <row r="162" ht="17" spans="1:5">
       <c r="A162" s="2" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="3"/>
     </row>
     <row r="163" ht="17" spans="1:5">
       <c r="A163" s="2" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="D163" s="5"/>
       <c r="E163" s="3"/>
     </row>
     <row r="164" ht="17" spans="1:5">
       <c r="A164" s="2" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="3"/>
     </row>
     <row r="165" ht="17" spans="1:5">
       <c r="A165" s="2" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="D165" s="5"/>
       <c r="E165" s="3"/>
